--- a/artfynd/A 32341-2025 artfynd.xlsx
+++ b/artfynd/A 32341-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128413409</v>
+        <v>128407744</v>
       </c>
       <c r="B2" t="n">
-        <v>79621</v>
+        <v>79650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398477</v>
+        <v>398173</v>
       </c>
       <c r="R2" t="n">
-        <v>6951277</v>
+        <v>6950715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128407744</v>
+        <v>128412069</v>
       </c>
       <c r="B3" t="n">
-        <v>79650</v>
+        <v>57673</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398173</v>
+        <v>398298</v>
       </c>
       <c r="R3" t="n">
-        <v>6950715</v>
+        <v>6950883</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128412069</v>
+        <v>128413409</v>
       </c>
       <c r="B4" t="n">
-        <v>57673</v>
+        <v>79621</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +885,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398298</v>
+        <v>398477</v>
       </c>
       <c r="R4" t="n">
-        <v>6950883</v>
+        <v>6951277</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128411332</v>
+        <v>128412732</v>
       </c>
       <c r="B5" t="n">
-        <v>75156</v>
+        <v>79127</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>967</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>398187</v>
+        <v>398474</v>
       </c>
       <c r="R5" t="n">
-        <v>6950935</v>
+        <v>6951085</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1039,19 +1039,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1066,12 +1056,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1175,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128412732</v>
+        <v>128412850</v>
       </c>
       <c r="B7" t="n">
-        <v>79127</v>
+        <v>78438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>967</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128411857</v>
+        <v>128411332</v>
       </c>
       <c r="B8" t="n">
-        <v>57673</v>
+        <v>75156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,39 +1273,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>398298</v>
+        <v>398187</v>
       </c>
       <c r="R8" t="n">
-        <v>6950875</v>
+        <v>6950935</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,10 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128412850</v>
+        <v>128407432</v>
       </c>
       <c r="B9" t="n">
-        <v>78438</v>
+        <v>57673</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,34 +1380,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>398474</v>
+        <v>398269</v>
       </c>
       <c r="R9" t="n">
-        <v>6951085</v>
+        <v>6950563</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1452,9 +1442,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,22 +1469,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128407381</v>
+        <v>128415979</v>
       </c>
       <c r="B10" t="n">
-        <v>82873</v>
+        <v>57673</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,34 +1492,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>398271</v>
+        <v>398372</v>
       </c>
       <c r="R10" t="n">
-        <v>6950584</v>
+        <v>6950738</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1556,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1561,7 +1566,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1588,50 +1593,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128407432</v>
+        <v>128409340</v>
       </c>
       <c r="B11" t="n">
-        <v>57673</v>
+        <v>80164</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>398269</v>
+        <v>397997</v>
       </c>
       <c r="R11" t="n">
-        <v>6950563</v>
+        <v>6950677</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,19 +1661,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1688,44 +1678,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128409340</v>
+        <v>128407381</v>
       </c>
       <c r="B12" t="n">
-        <v>80164</v>
+        <v>82873</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>397997</v>
+        <v>398271</v>
       </c>
       <c r="R12" t="n">
-        <v>6950677</v>
+        <v>6950584</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,9 +1758,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1785,12 +1785,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128415979</v>
+        <v>128407947</v>
       </c>
       <c r="B14" t="n">
-        <v>57673</v>
+        <v>82873</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1905,39 +1905,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>398372</v>
+        <v>398154</v>
       </c>
       <c r="R14" t="n">
-        <v>6950738</v>
+        <v>6950756</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,7 +1964,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1979,7 +1974,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2006,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128410038</v>
+        <v>128411782</v>
       </c>
       <c r="B15" t="n">
         <v>75156</v>
@@ -2041,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>397967</v>
+        <v>398234</v>
       </c>
       <c r="R15" t="n">
-        <v>6950876</v>
+        <v>6950852</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2074,9 +2069,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2091,22 +2096,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128410559</v>
+        <v>128410038</v>
       </c>
       <c r="B16" t="n">
-        <v>57673</v>
+        <v>75156</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2114,39 +2119,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>398097</v>
+        <v>397967</v>
       </c>
       <c r="R16" t="n">
-        <v>6950870</v>
+        <v>6950876</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2176,19 +2176,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2203,22 +2193,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128406215</v>
+        <v>128410559</v>
       </c>
       <c r="B17" t="n">
-        <v>82873</v>
+        <v>57673</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,34 +2216,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>398336</v>
+        <v>398097</v>
       </c>
       <c r="R17" t="n">
-        <v>6950585</v>
+        <v>6950870</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2285,7 +2280,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2295,7 +2290,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2434,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128407947</v>
+        <v>128415613</v>
       </c>
       <c r="B19" t="n">
-        <v>82873</v>
+        <v>78699</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>398154</v>
+        <v>398437</v>
       </c>
       <c r="R19" t="n">
-        <v>6950756</v>
+        <v>6950808</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2502,19 +2497,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2529,22 +2514,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128411782</v>
+        <v>128415804</v>
       </c>
       <c r="B20" t="n">
-        <v>75156</v>
+        <v>78438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2552,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>398234</v>
+        <v>398394</v>
       </c>
       <c r="R20" t="n">
-        <v>6950852</v>
+        <v>6950811</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2745,7 +2730,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128405961</v>
+        <v>128408059</v>
       </c>
       <c r="B22" t="n">
         <v>57673</v>
@@ -2785,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>398364</v>
+        <v>398146</v>
       </c>
       <c r="R22" t="n">
-        <v>6950569</v>
+        <v>6950784</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2818,19 +2803,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2845,22 +2820,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128415613</v>
+        <v>128415681</v>
       </c>
       <c r="B23" t="n">
-        <v>78699</v>
+        <v>79621</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2868,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2892,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>398437</v>
+        <v>398394</v>
       </c>
       <c r="R23" t="n">
-        <v>6950808</v>
+        <v>6950811</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2925,9 +2900,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2942,22 +2927,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128415681</v>
+        <v>128410050</v>
       </c>
       <c r="B24" t="n">
-        <v>79621</v>
+        <v>82873</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,21 +2950,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2989,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>398394</v>
+        <v>397967</v>
       </c>
       <c r="R24" t="n">
-        <v>6950811</v>
+        <v>6950876</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3022,19 +3007,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3049,22 +3024,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128415804</v>
+        <v>128411229</v>
       </c>
       <c r="B25" t="n">
-        <v>78438</v>
+        <v>82873</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3072,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3096,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>398394</v>
+        <v>398118</v>
       </c>
       <c r="R25" t="n">
-        <v>6950811</v>
+        <v>6950921</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3129,19 +3104,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3156,22 +3121,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128408059</v>
+        <v>128416541</v>
       </c>
       <c r="B26" t="n">
-        <v>57673</v>
+        <v>82873</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3179,39 +3144,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>398146</v>
+        <v>398411</v>
       </c>
       <c r="R26" t="n">
-        <v>6950784</v>
+        <v>6950623</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3382,10 +3342,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128413330</v>
+        <v>128410205</v>
       </c>
       <c r="B28" t="n">
-        <v>78438</v>
+        <v>75156</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3393,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3417,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>398486</v>
+        <v>397980</v>
       </c>
       <c r="R28" t="n">
-        <v>6951242</v>
+        <v>6950909</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3479,7 +3439,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128410205</v>
+        <v>128411297</v>
       </c>
       <c r="B29" t="n">
         <v>75156</v>
@@ -3514,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>397980</v>
+        <v>398143</v>
       </c>
       <c r="R29" t="n">
-        <v>6950909</v>
+        <v>6950944</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3576,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128410050</v>
+        <v>128413330</v>
       </c>
       <c r="B30" t="n">
-        <v>82873</v>
+        <v>78438</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3587,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3611,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>397967</v>
+        <v>398486</v>
       </c>
       <c r="R30" t="n">
-        <v>6950876</v>
+        <v>6951242</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3673,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128411297</v>
+        <v>128411736</v>
       </c>
       <c r="B31" t="n">
-        <v>75156</v>
+        <v>91378</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3684,21 +3644,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3708,10 +3668,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>398143</v>
+        <v>398234</v>
       </c>
       <c r="R31" t="n">
-        <v>6950944</v>
+        <v>6950852</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3741,9 +3701,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3758,22 +3728,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128411229</v>
+        <v>128405964</v>
       </c>
       <c r="B32" t="n">
-        <v>82873</v>
+        <v>57673</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3781,34 +3751,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>398118</v>
+        <v>398364</v>
       </c>
       <c r="R32" t="n">
-        <v>6950921</v>
+        <v>6950589</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3867,10 +3842,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128416541</v>
+        <v>128412757</v>
       </c>
       <c r="B33" t="n">
-        <v>82873</v>
+        <v>57673</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3878,34 +3853,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>398411</v>
+        <v>398460</v>
       </c>
       <c r="R33" t="n">
-        <v>6950623</v>
+        <v>6951061</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3935,9 +3915,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3952,22 +3942,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128410403</v>
+        <v>128415952</v>
       </c>
       <c r="B34" t="n">
-        <v>75156</v>
+        <v>57673</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3975,34 +3965,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>398063</v>
+        <v>398385</v>
       </c>
       <c r="R34" t="n">
-        <v>6950893</v>
+        <v>6950755</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4173,10 +4168,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128411429</v>
+        <v>128408399</v>
       </c>
       <c r="B36" t="n">
-        <v>75156</v>
+        <v>82873</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4184,21 +4179,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4208,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398176</v>
+        <v>398076</v>
       </c>
       <c r="R36" t="n">
-        <v>6950885</v>
+        <v>6950793</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,10 +4265,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128405964</v>
+        <v>128410403</v>
       </c>
       <c r="B37" t="n">
-        <v>57673</v>
+        <v>75156</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4281,39 +4276,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>398364</v>
+        <v>398063</v>
       </c>
       <c r="R37" t="n">
-        <v>6950589</v>
+        <v>6950893</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4372,10 +4362,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128415952</v>
+        <v>128411429</v>
       </c>
       <c r="B38" t="n">
-        <v>57673</v>
+        <v>75156</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4383,39 +4373,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>398385</v>
+        <v>398176</v>
       </c>
       <c r="R38" t="n">
-        <v>6950755</v>
+        <v>6950885</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4474,32 +4459,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128408399</v>
+        <v>128405841</v>
       </c>
       <c r="B39" t="n">
-        <v>82873</v>
+        <v>92057</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4509,10 +4494,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>398076</v>
+        <v>398374</v>
       </c>
       <c r="R39" t="n">
-        <v>6950793</v>
+        <v>6950548</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4571,10 +4556,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128411736</v>
+        <v>128405669</v>
       </c>
       <c r="B40" t="n">
-        <v>91376</v>
+        <v>91378</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4606,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>398234</v>
+        <v>398398</v>
       </c>
       <c r="R40" t="n">
-        <v>6950852</v>
+        <v>6950569</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4639,19 +4624,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4666,62 +4641,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128412757</v>
+        <v>128412193</v>
       </c>
       <c r="B41" t="n">
-        <v>57673</v>
+        <v>80170</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>398460</v>
+        <v>398369</v>
       </c>
       <c r="R41" t="n">
-        <v>6951061</v>
+        <v>6950956</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4751,19 +4721,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4778,44 +4738,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128405841</v>
+        <v>128411735</v>
       </c>
       <c r="B42" t="n">
-        <v>92055</v>
+        <v>75156</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4825,10 +4785,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>398374</v>
+        <v>398227</v>
       </c>
       <c r="R42" t="n">
-        <v>6950548</v>
+        <v>6950881</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4887,10 +4847,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128405669</v>
+        <v>128412950</v>
       </c>
       <c r="B43" t="n">
-        <v>91376</v>
+        <v>57673</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4898,34 +4858,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>398398</v>
+        <v>398483</v>
       </c>
       <c r="R43" t="n">
-        <v>6950569</v>
+        <v>6951117</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4984,50 +4949,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128412950</v>
+        <v>128416366</v>
       </c>
       <c r="B44" t="n">
-        <v>57673</v>
+        <v>78395</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>398483</v>
+        <v>398419</v>
       </c>
       <c r="R44" t="n">
-        <v>6951117</v>
+        <v>6950678</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5086,45 +5046,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128412193</v>
+        <v>128414073</v>
       </c>
       <c r="B45" t="n">
-        <v>80170</v>
+        <v>57673</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>398369</v>
+        <v>398546</v>
       </c>
       <c r="R45" t="n">
-        <v>6950956</v>
+        <v>6951235</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5183,10 +5148,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128411735</v>
+        <v>128415930</v>
       </c>
       <c r="B46" t="n">
-        <v>75156</v>
+        <v>79621</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5194,21 +5159,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5218,10 +5183,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>398227</v>
+        <v>398387</v>
       </c>
       <c r="R46" t="n">
-        <v>6950881</v>
+        <v>6950766</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5280,10 +5245,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128415930</v>
+        <v>128407293</v>
       </c>
       <c r="B47" t="n">
-        <v>79621</v>
+        <v>79650</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5291,21 +5256,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5315,10 +5280,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>398387</v>
+        <v>398263</v>
       </c>
       <c r="R47" t="n">
-        <v>6950766</v>
+        <v>6950596</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5377,32 +5342,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128416366</v>
+        <v>128410408</v>
       </c>
       <c r="B48" t="n">
-        <v>78395</v>
+        <v>79032</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5412,10 +5377,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>398419</v>
+        <v>398063</v>
       </c>
       <c r="R48" t="n">
-        <v>6950678</v>
+        <v>6950893</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5474,7 +5439,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128414073</v>
+        <v>128412677</v>
       </c>
       <c r="B49" t="n">
         <v>57673</v>
@@ -5505,7 +5470,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5514,10 +5479,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>398546</v>
+        <v>398462</v>
       </c>
       <c r="R49" t="n">
-        <v>6951235</v>
+        <v>6951039</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5547,9 +5512,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5564,22 +5539,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128410408</v>
+        <v>128415972</v>
       </c>
       <c r="B50" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5587,34 +5562,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>398063</v>
+        <v>398396</v>
       </c>
       <c r="R50" t="n">
-        <v>6950893</v>
+        <v>6950719</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5676,7 +5656,7 @@
         <v>128406327</v>
       </c>
       <c r="B51" t="n">
-        <v>91376</v>
+        <v>91378</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5770,10 +5750,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128407293</v>
+        <v>128411964</v>
       </c>
       <c r="B52" t="n">
-        <v>79650</v>
+        <v>91378</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5781,21 +5761,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5805,10 +5785,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>398263</v>
+        <v>398278</v>
       </c>
       <c r="R52" t="n">
-        <v>6950596</v>
+        <v>6950881</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5867,10 +5847,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128415972</v>
+        <v>128415932</v>
       </c>
       <c r="B53" t="n">
-        <v>57673</v>
+        <v>79650</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5878,39 +5858,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>398396</v>
+        <v>398387</v>
       </c>
       <c r="R53" t="n">
-        <v>6950719</v>
+        <v>6950766</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5969,10 +5944,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128415932</v>
+        <v>128408097</v>
       </c>
       <c r="B54" t="n">
-        <v>79650</v>
+        <v>57833</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5980,37 +5955,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>398387</v>
+        <v>398159</v>
       </c>
       <c r="R54" t="n">
-        <v>6950766</v>
+        <v>6950801</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6037,9 +6017,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6054,65 +6044,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128408097</v>
+        <v>128412638</v>
       </c>
       <c r="B55" t="n">
-        <v>57833</v>
+        <v>57777</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>398159</v>
+        <v>398437</v>
       </c>
       <c r="R55" t="n">
-        <v>6950801</v>
+        <v>6951052</v>
       </c>
       <c r="S55" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6139,19 +6124,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6166,22 +6141,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128412638</v>
+        <v>128408773</v>
       </c>
       <c r="B56" t="n">
-        <v>57777</v>
+        <v>58043</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6189,16 +6164,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103031</v>
+        <v>103015</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6207,19 +6182,24 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>398437</v>
+        <v>398012</v>
       </c>
       <c r="R56" t="n">
-        <v>6951052</v>
+        <v>6950659</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6246,9 +6226,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6263,22 +6253,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128412677</v>
+        <v>128408521</v>
       </c>
       <c r="B57" t="n">
-        <v>57673</v>
+        <v>79650</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6286,39 +6276,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>398462</v>
+        <v>398019</v>
       </c>
       <c r="R57" t="n">
-        <v>6951039</v>
+        <v>6950740</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6348,19 +6333,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6375,22 +6350,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128411964</v>
+        <v>128405859</v>
       </c>
       <c r="B58" t="n">
-        <v>91376</v>
+        <v>57673</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6398,34 +6373,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>398278</v>
+        <v>398362</v>
       </c>
       <c r="R58" t="n">
-        <v>6950881</v>
+        <v>6950549</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6455,9 +6435,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6472,12 +6462,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6596,27 +6586,27 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128405859</v>
+        <v>128413955</v>
       </c>
       <c r="B60" t="n">
-        <v>57673</v>
+        <v>57514</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6627,7 +6617,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6636,13 +6626,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>398362</v>
+        <v>398517</v>
       </c>
       <c r="R60" t="n">
-        <v>6950549</v>
+        <v>6951283</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6669,19 +6659,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6696,65 +6676,60 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128413955</v>
+        <v>128409775</v>
       </c>
       <c r="B61" t="n">
-        <v>57514</v>
+        <v>79621</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102621</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>398517</v>
+        <v>398008</v>
       </c>
       <c r="R61" t="n">
-        <v>6951283</v>
+        <v>6950745</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6810,27 +6785,27 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128408773</v>
+        <v>128415706</v>
       </c>
       <c r="B62" t="n">
-        <v>58043</v>
+        <v>57673</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6841,7 +6816,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6850,13 +6825,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>398012</v>
+        <v>398411</v>
       </c>
       <c r="R62" t="n">
-        <v>6950659</v>
+        <v>6950796</v>
       </c>
       <c r="S62" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6883,19 +6858,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6910,22 +6875,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128408521</v>
+        <v>128416501</v>
       </c>
       <c r="B63" t="n">
-        <v>79650</v>
+        <v>57673</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6933,34 +6898,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>398019</v>
+        <v>398382</v>
       </c>
       <c r="R63" t="n">
-        <v>6950740</v>
+        <v>6950639</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6990,9 +6960,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7007,44 +6987,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128408249</v>
+        <v>128409691</v>
       </c>
       <c r="B64" t="n">
-        <v>78395</v>
+        <v>90393</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>498</v>
+        <v>1962</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7054,10 +7034,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>398138</v>
+        <v>398057</v>
       </c>
       <c r="R64" t="n">
-        <v>6950799</v>
+        <v>6950739</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7126,10 +7106,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128409775</v>
+        <v>128406318</v>
       </c>
       <c r="B65" t="n">
-        <v>79621</v>
+        <v>79032</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7137,21 +7117,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7161,10 +7141,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>398008</v>
+        <v>398333</v>
       </c>
       <c r="R65" t="n">
-        <v>6950745</v>
+        <v>6950603</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7223,10 +7203,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128406026</v>
+        <v>128415836</v>
       </c>
       <c r="B66" t="n">
-        <v>79650</v>
+        <v>78010</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7234,21 +7214,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7258,10 +7238,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>398364</v>
+        <v>398394</v>
       </c>
       <c r="R66" t="n">
-        <v>6950589</v>
+        <v>6950811</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7291,9 +7271,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7308,22 +7298,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128409691</v>
+        <v>128406026</v>
       </c>
       <c r="B67" t="n">
-        <v>90393</v>
+        <v>79650</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7331,21 +7321,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7355,10 +7345,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>398057</v>
+        <v>398364</v>
       </c>
       <c r="R67" t="n">
-        <v>6950739</v>
+        <v>6950589</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7388,19 +7378,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7415,22 +7395,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128406318</v>
+        <v>128407307</v>
       </c>
       <c r="B68" t="n">
-        <v>79032</v>
+        <v>78791</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7438,21 +7418,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7462,10 +7442,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>398333</v>
+        <v>398263</v>
       </c>
       <c r="R68" t="n">
-        <v>6950603</v>
+        <v>6950596</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7524,10 +7504,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128407307</v>
+        <v>128411931</v>
       </c>
       <c r="B69" t="n">
-        <v>78791</v>
+        <v>91378</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7535,21 +7515,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7559,10 +7539,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>398263</v>
+        <v>398276</v>
       </c>
       <c r="R69" t="n">
-        <v>6950596</v>
+        <v>6950842</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7621,7 +7601,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128416501</v>
+        <v>128411524</v>
       </c>
       <c r="B70" t="n">
         <v>57673</v>
@@ -7661,10 +7641,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>398382</v>
+        <v>398203</v>
       </c>
       <c r="R70" t="n">
-        <v>6950639</v>
+        <v>6950901</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7733,10 +7713,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128415836</v>
+        <v>128411612</v>
       </c>
       <c r="B71" t="n">
-        <v>78010</v>
+        <v>79111</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7744,21 +7724,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6487</v>
+        <v>864</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7768,10 +7748,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>398394</v>
+        <v>398200</v>
       </c>
       <c r="R71" t="n">
-        <v>6950811</v>
+        <v>6950918</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7801,19 +7781,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7828,22 +7798,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128415706</v>
+        <v>128411308</v>
       </c>
       <c r="B72" t="n">
-        <v>57673</v>
+        <v>75156</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7851,39 +7821,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>398411</v>
+        <v>398162</v>
       </c>
       <c r="R72" t="n">
-        <v>6950796</v>
+        <v>6950923</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8054,32 +8019,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128411612</v>
+        <v>128416207</v>
       </c>
       <c r="B74" t="n">
-        <v>79111</v>
+        <v>75154</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>864</v>
+        <v>6486</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8089,10 +8054,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>398200</v>
+        <v>398414</v>
       </c>
       <c r="R74" t="n">
-        <v>6950918</v>
+        <v>6950702</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8151,10 +8116,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128411931</v>
+        <v>128405468</v>
       </c>
       <c r="B75" t="n">
-        <v>91376</v>
+        <v>82873</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8162,34 +8127,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>398276</v>
+        <v>398405</v>
       </c>
       <c r="R75" t="n">
-        <v>6950842</v>
+        <v>6950503</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8248,7 +8213,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128411524</v>
+        <v>128412048</v>
       </c>
       <c r="B76" t="n">
         <v>57673</v>
@@ -8279,7 +8244,7 @@
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8288,10 +8253,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>398203</v>
+        <v>398329</v>
       </c>
       <c r="R76" t="n">
-        <v>6950901</v>
+        <v>6950952</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8360,10 +8325,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128411308</v>
+        <v>128406114</v>
       </c>
       <c r="B77" t="n">
-        <v>75156</v>
+        <v>57673</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8371,34 +8336,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>398162</v>
+        <v>398351</v>
       </c>
       <c r="R77" t="n">
-        <v>6950923</v>
+        <v>6950591</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8428,9 +8398,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8445,44 +8425,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128408651</v>
+        <v>128412622</v>
       </c>
       <c r="B78" t="n">
-        <v>91376</v>
+        <v>58043</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8492,13 +8472,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>397997</v>
+        <v>398437</v>
       </c>
       <c r="R78" t="n">
-        <v>6950686</v>
+        <v>6951052</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8525,19 +8505,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8552,22 +8522,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128406114</v>
+        <v>128412825</v>
       </c>
       <c r="B79" t="n">
-        <v>57673</v>
+        <v>79621</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8575,39 +8545,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>398351</v>
+        <v>398474</v>
       </c>
       <c r="R79" t="n">
-        <v>6950591</v>
+        <v>6951085</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8637,19 +8602,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8664,22 +8619,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128405468</v>
+        <v>128411329</v>
       </c>
       <c r="B80" t="n">
-        <v>82873</v>
+        <v>91378</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8687,34 +8642,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>398405</v>
+        <v>398173</v>
       </c>
       <c r="R80" t="n">
-        <v>6950503</v>
+        <v>6950901</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8773,45 +8728,50 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128416207</v>
+        <v>128405900</v>
       </c>
       <c r="B81" t="n">
-        <v>75154</v>
+        <v>57673</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>398414</v>
+        <v>398362</v>
       </c>
       <c r="R81" t="n">
-        <v>6950702</v>
+        <v>6950568</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8870,10 +8830,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128412048</v>
+        <v>128407528</v>
       </c>
       <c r="B82" t="n">
-        <v>57673</v>
+        <v>78699</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8881,39 +8841,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>398329</v>
+        <v>398225</v>
       </c>
       <c r="R82" t="n">
-        <v>6950952</v>
+        <v>6950599</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8943,19 +8898,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8970,44 +8915,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128412622</v>
+        <v>128411270</v>
       </c>
       <c r="B83" t="n">
-        <v>58043</v>
+        <v>78438</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103015</v>
+        <v>6437</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9017,13 +8962,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>398437</v>
+        <v>398139</v>
       </c>
       <c r="R83" t="n">
-        <v>6951052</v>
+        <v>6950929</v>
       </c>
       <c r="S83" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9079,10 +9024,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128412825</v>
+        <v>128416210</v>
       </c>
       <c r="B84" t="n">
-        <v>79621</v>
+        <v>91378</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9090,21 +9035,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9114,10 +9059,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>398474</v>
+        <v>398414</v>
       </c>
       <c r="R84" t="n">
-        <v>6951085</v>
+        <v>6950702</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9176,7 +9121,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128405900</v>
+        <v>128411972</v>
       </c>
       <c r="B85" t="n">
         <v>57673</v>
@@ -9216,10 +9161,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>398362</v>
+        <v>398278</v>
       </c>
       <c r="R85" t="n">
-        <v>6950568</v>
+        <v>6950881</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9278,10 +9223,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128411329</v>
+        <v>128407963</v>
       </c>
       <c r="B86" t="n">
-        <v>91376</v>
+        <v>57673</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9289,21 +9234,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9313,10 +9258,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>398173</v>
+        <v>398154</v>
       </c>
       <c r="R86" t="n">
-        <v>6950901</v>
+        <v>6950756</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9346,9 +9291,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9363,60 +9318,61 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128411270</v>
+        <v>128404962</v>
       </c>
       <c r="B87" t="n">
-        <v>78438</v>
+        <v>57838</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6437</v>
+        <v>266237</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>398139</v>
+        <v>398392</v>
       </c>
       <c r="R87" t="n">
-        <v>6950929</v>
+        <v>6950406</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9443,9 +9399,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9460,62 +9426,57 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128405590</v>
+        <v>128410048</v>
       </c>
       <c r="B88" t="n">
-        <v>57673</v>
+        <v>78395</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>398420</v>
+        <v>397967</v>
       </c>
       <c r="R88" t="n">
-        <v>6950543</v>
+        <v>6950876</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9545,19 +9506,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9572,22 +9523,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128416572</v>
+        <v>128415905</v>
       </c>
       <c r="B89" t="n">
-        <v>91376</v>
+        <v>78438</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9595,21 +9546,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9619,10 +9570,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>398382</v>
+        <v>398403</v>
       </c>
       <c r="R89" t="n">
-        <v>6950639</v>
+        <v>6950826</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9691,10 +9642,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128407528</v>
+        <v>128407736</v>
       </c>
       <c r="B90" t="n">
-        <v>78699</v>
+        <v>57673</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9702,34 +9653,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>398225</v>
+        <v>398169</v>
       </c>
       <c r="R90" t="n">
-        <v>6950599</v>
+        <v>6950711</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9759,9 +9715,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9776,22 +9742,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128416210</v>
+        <v>128405637</v>
       </c>
       <c r="B91" t="n">
-        <v>91376</v>
+        <v>91378</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9819,14 +9785,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>398414</v>
+        <v>398426</v>
       </c>
       <c r="R91" t="n">
-        <v>6950702</v>
+        <v>6950561</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9885,10 +9851,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128411972</v>
+        <v>128413415</v>
       </c>
       <c r="B92" t="n">
-        <v>57673</v>
+        <v>79650</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9896,39 +9862,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>398278</v>
+        <v>398477</v>
       </c>
       <c r="R92" t="n">
-        <v>6950881</v>
+        <v>6951277</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9987,49 +9948,53 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128404962</v>
+        <v>128410197</v>
       </c>
       <c r="B93" t="n">
-        <v>57838</v>
+        <v>57673</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>266237</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>398392</v>
+        <v>397996</v>
       </c>
       <c r="R93" t="n">
-        <v>6950406</v>
+        <v>6950884</v>
       </c>
       <c r="S93" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10058,7 +10023,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10068,7 +10033,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10095,7 +10060,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128414034</v>
+        <v>128411474</v>
       </c>
       <c r="B94" t="n">
         <v>57673</v>
@@ -10126,7 +10091,7 @@
       <c r="I94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -10135,10 +10100,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>398526</v>
+        <v>398202</v>
       </c>
       <c r="R94" t="n">
-        <v>6951240</v>
+        <v>6950905</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10168,19 +10133,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10195,22 +10150,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128407963</v>
+        <v>128413088</v>
       </c>
       <c r="B95" t="n">
-        <v>57673</v>
+        <v>82873</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10218,21 +10173,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10242,10 +10197,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>398154</v>
+        <v>398494</v>
       </c>
       <c r="R95" t="n">
-        <v>6950756</v>
+        <v>6951141</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10275,19 +10230,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10302,62 +10247,57 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128413146</v>
+        <v>128411728</v>
       </c>
       <c r="B96" t="n">
-        <v>57673</v>
+        <v>78395</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>398480</v>
+        <v>398227</v>
       </c>
       <c r="R96" t="n">
-        <v>6951148</v>
+        <v>6950881</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10387,19 +10327,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10414,22 +10344,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128407736</v>
+        <v>128410472</v>
       </c>
       <c r="B97" t="n">
-        <v>57673</v>
+        <v>75156</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10437,39 +10367,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>398169</v>
+        <v>398075</v>
       </c>
       <c r="R97" t="n">
-        <v>6950711</v>
+        <v>6950912</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10499,19 +10424,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10526,19 +10441,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128415905</v>
+        <v>128407311</v>
       </c>
       <c r="B98" t="n">
         <v>78438</v>
@@ -10573,10 +10488,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>398403</v>
+        <v>398263</v>
       </c>
       <c r="R98" t="n">
-        <v>6950826</v>
+        <v>6950596</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10606,19 +10521,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10633,57 +10538,62 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128410048</v>
+        <v>128415580</v>
       </c>
       <c r="B99" t="n">
-        <v>78395</v>
+        <v>57673</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>397967</v>
+        <v>398442</v>
       </c>
       <c r="R99" t="n">
-        <v>6950876</v>
+        <v>6950833</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10742,10 +10652,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128405637</v>
+        <v>128413083</v>
       </c>
       <c r="B100" t="n">
-        <v>91376</v>
+        <v>75156</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10753,34 +10663,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>398426</v>
+        <v>398494</v>
       </c>
       <c r="R100" t="n">
-        <v>6950561</v>
+        <v>6951141</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10839,10 +10749,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128413351</v>
+        <v>128413214</v>
       </c>
       <c r="B101" t="n">
-        <v>79621</v>
+        <v>57673</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10850,34 +10760,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>398484</v>
+        <v>398467</v>
       </c>
       <c r="R101" t="n">
-        <v>6951249</v>
+        <v>6951207</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10907,19 +10822,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10934,22 +10839,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128413415</v>
+        <v>128413296</v>
       </c>
       <c r="B102" t="n">
-        <v>79650</v>
+        <v>79621</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10957,21 +10862,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10981,10 +10886,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>398477</v>
+        <v>398463</v>
       </c>
       <c r="R102" t="n">
-        <v>6951277</v>
+        <v>6951234</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11043,10 +10948,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128411474</v>
+        <v>128407903</v>
       </c>
       <c r="B103" t="n">
-        <v>57673</v>
+        <v>81027</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11054,39 +10959,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>229436</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Halmgul örnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ochrolechia alboflavescens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wulfen) Zahlbr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>398202</v>
+        <v>398154</v>
       </c>
       <c r="R103" t="n">
-        <v>6950905</v>
+        <v>6950756</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11116,9 +11016,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11133,19 +11043,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128410197</v>
+        <v>128411857</v>
       </c>
       <c r="B104" t="n">
         <v>57673</v>
@@ -11174,21 +11084,24 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>397996</v>
+        <v>398298</v>
       </c>
       <c r="R104" t="n">
-        <v>6950884</v>
+        <v>6950875</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11231,6 +11144,11 @@
       <c r="AB104" t="inlineStr">
         <is>
           <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack samt miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11257,10 +11175,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128407311</v>
+        <v>128406215</v>
       </c>
       <c r="B105" t="n">
-        <v>78438</v>
+        <v>82873</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11268,21 +11186,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11292,10 +11210,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>398263</v>
+        <v>398336</v>
       </c>
       <c r="R105" t="n">
-        <v>6950596</v>
+        <v>6950585</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11325,9 +11243,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11342,22 +11270,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128410472</v>
+        <v>128405961</v>
       </c>
       <c r="B106" t="n">
-        <v>75156</v>
+        <v>57673</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11365,34 +11293,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>398075</v>
+        <v>398364</v>
       </c>
       <c r="R106" t="n">
-        <v>6950912</v>
+        <v>6950569</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11422,9 +11355,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11439,44 +11382,44 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128413088</v>
+        <v>128408249</v>
       </c>
       <c r="B107" t="n">
-        <v>82873</v>
+        <v>78395</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1312</v>
+        <v>498</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11486,10 +11429,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>398494</v>
+        <v>398138</v>
       </c>
       <c r="R107" t="n">
-        <v>6951141</v>
+        <v>6950799</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11519,9 +11462,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11536,44 +11489,44 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128411728</v>
+        <v>128408651</v>
       </c>
       <c r="B108" t="n">
-        <v>78395</v>
+        <v>91378</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11583,10 +11536,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>398227</v>
+        <v>397997</v>
       </c>
       <c r="R108" t="n">
-        <v>6950881</v>
+        <v>6950686</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11616,9 +11569,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11633,22 +11596,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128413296</v>
+        <v>128405590</v>
       </c>
       <c r="B109" t="n">
-        <v>79621</v>
+        <v>57673</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11656,34 +11619,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>398463</v>
+        <v>398420</v>
       </c>
       <c r="R109" t="n">
-        <v>6951234</v>
+        <v>6950543</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11713,9 +11681,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11730,22 +11708,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128413214</v>
+        <v>128416572</v>
       </c>
       <c r="B110" t="n">
-        <v>57673</v>
+        <v>91378</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11753,39 +11731,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>398467</v>
+        <v>398382</v>
       </c>
       <c r="R110" t="n">
-        <v>6951207</v>
+        <v>6950639</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11815,9 +11788,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11832,22 +11815,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128413083</v>
+        <v>128414034</v>
       </c>
       <c r="B111" t="n">
-        <v>75156</v>
+        <v>57673</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11855,34 +11838,39 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>398494</v>
+        <v>398526</v>
       </c>
       <c r="R111" t="n">
-        <v>6951141</v>
+        <v>6951240</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11912,9 +11900,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11929,19 +11927,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128415580</v>
+        <v>128413146</v>
       </c>
       <c r="B112" t="n">
         <v>57673</v>
@@ -11970,21 +11968,24 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>398442</v>
+        <v>398480</v>
       </c>
       <c r="R112" t="n">
-        <v>6950833</v>
+        <v>6951148</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12014,9 +12015,24 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Ringhack samt miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12031,22 +12047,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128407903</v>
+        <v>128413351</v>
       </c>
       <c r="B113" t="n">
-        <v>81027</v>
+        <v>79621</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12054,34 +12070,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229436</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Halmgul örnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ochrolechia alboflavescens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Wulfen) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>398154</v>
+        <v>398484</v>
       </c>
       <c r="R113" t="n">
-        <v>6950756</v>
+        <v>6951249</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12113,7 +12132,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12123,7 +12142,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Vedflamlav samt miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12132,6 +12156,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 32341-2025 artfynd.xlsx
+++ b/artfynd/A 32341-2025 artfynd.xlsx
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128411736</v>
+        <v>128408399</v>
       </c>
       <c r="B31" t="n">
-        <v>91378</v>
+        <v>82873</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3644,21 +3644,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>398234</v>
+        <v>398076</v>
       </c>
       <c r="R31" t="n">
-        <v>6950852</v>
+        <v>6950793</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3701,19 +3701,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3728,19 +3718,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128405964</v>
+        <v>128415952</v>
       </c>
       <c r="B32" t="n">
         <v>57673</v>
@@ -3780,10 +3770,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>398364</v>
+        <v>398385</v>
       </c>
       <c r="R32" t="n">
-        <v>6950589</v>
+        <v>6950755</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3842,10 +3832,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128412757</v>
+        <v>128411736</v>
       </c>
       <c r="B33" t="n">
-        <v>57673</v>
+        <v>91378</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,39 +3843,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>398460</v>
+        <v>398234</v>
       </c>
       <c r="R33" t="n">
-        <v>6951061</v>
+        <v>6950852</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3954,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128415952</v>
+        <v>128410403</v>
       </c>
       <c r="B34" t="n">
-        <v>57673</v>
+        <v>75156</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3965,39 +3950,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>398385</v>
+        <v>398063</v>
       </c>
       <c r="R34" t="n">
-        <v>6950755</v>
+        <v>6950893</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4056,53 +4036,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128413866</v>
+        <v>128411429</v>
       </c>
       <c r="B35" t="n">
-        <v>58043</v>
+        <v>75156</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398505</v>
+        <v>398176</v>
       </c>
       <c r="R35" t="n">
-        <v>6951279</v>
+        <v>6950885</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4129,19 +4104,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4156,22 +4121,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128408399</v>
+        <v>128405964</v>
       </c>
       <c r="B36" t="n">
-        <v>82873</v>
+        <v>57673</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4179,34 +4144,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398076</v>
+        <v>398364</v>
       </c>
       <c r="R36" t="n">
-        <v>6950793</v>
+        <v>6950589</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,10 +4235,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128410403</v>
+        <v>128412757</v>
       </c>
       <c r="B37" t="n">
-        <v>75156</v>
+        <v>57673</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4276,34 +4246,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>398063</v>
+        <v>398460</v>
       </c>
       <c r="R37" t="n">
-        <v>6950893</v>
+        <v>6951061</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4333,9 +4308,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4350,60 +4335,65 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128411429</v>
+        <v>128413866</v>
       </c>
       <c r="B38" t="n">
-        <v>75156</v>
+        <v>58043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>398176</v>
+        <v>398505</v>
       </c>
       <c r="R38" t="n">
-        <v>6950885</v>
+        <v>6951279</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4430,9 +4420,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4447,12 +4447,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5245,32 +5245,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128407293</v>
+        <v>128412638</v>
       </c>
       <c r="B47" t="n">
-        <v>79650</v>
+        <v>57777</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5280,13 +5280,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>398263</v>
+        <v>398437</v>
       </c>
       <c r="R47" t="n">
-        <v>6950596</v>
+        <v>6951052</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5342,10 +5342,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128410408</v>
+        <v>128407293</v>
       </c>
       <c r="B48" t="n">
-        <v>79032</v>
+        <v>79650</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5353,21 +5353,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>398063</v>
+        <v>398263</v>
       </c>
       <c r="R48" t="n">
-        <v>6950893</v>
+        <v>6950596</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5439,10 +5439,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128412677</v>
+        <v>128410408</v>
       </c>
       <c r="B49" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5450,39 +5450,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>398462</v>
+        <v>398063</v>
       </c>
       <c r="R49" t="n">
-        <v>6951039</v>
+        <v>6950893</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5512,19 +5507,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5539,19 +5524,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128415972</v>
+        <v>128412677</v>
       </c>
       <c r="B50" t="n">
         <v>57673</v>
@@ -5591,10 +5576,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>398396</v>
+        <v>398462</v>
       </c>
       <c r="R50" t="n">
-        <v>6950719</v>
+        <v>6951039</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5624,9 +5609,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5641,22 +5636,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128406327</v>
+        <v>128415972</v>
       </c>
       <c r="B51" t="n">
-        <v>91378</v>
+        <v>57673</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5664,34 +5659,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>398333</v>
+        <v>398396</v>
       </c>
       <c r="R51" t="n">
-        <v>6950603</v>
+        <v>6950719</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5750,7 +5750,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128411964</v>
+        <v>128406327</v>
       </c>
       <c r="B52" t="n">
         <v>91378</v>
@@ -5785,10 +5785,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>398278</v>
+        <v>398333</v>
       </c>
       <c r="R52" t="n">
-        <v>6950881</v>
+        <v>6950603</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5847,10 +5847,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128415932</v>
+        <v>128411964</v>
       </c>
       <c r="B53" t="n">
-        <v>79650</v>
+        <v>91378</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5858,21 +5858,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5882,10 +5882,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>398387</v>
+        <v>398278</v>
       </c>
       <c r="R53" t="n">
-        <v>6950766</v>
+        <v>6950881</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5944,10 +5944,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128408097</v>
+        <v>128415932</v>
       </c>
       <c r="B54" t="n">
-        <v>57833</v>
+        <v>79650</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5955,42 +5955,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>398159</v>
+        <v>398387</v>
       </c>
       <c r="R54" t="n">
-        <v>6950801</v>
+        <v>6950766</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6017,19 +6012,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6044,60 +6029,65 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128412638</v>
+        <v>128408097</v>
       </c>
       <c r="B55" t="n">
-        <v>57777</v>
+        <v>57833</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>398437</v>
+        <v>398159</v>
       </c>
       <c r="R55" t="n">
-        <v>6951052</v>
+        <v>6950801</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6124,9 +6114,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6141,65 +6141,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128408773</v>
+        <v>128408521</v>
       </c>
       <c r="B56" t="n">
-        <v>58043</v>
+        <v>79650</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>398012</v>
+        <v>398019</v>
       </c>
       <c r="R56" t="n">
-        <v>6950659</v>
+        <v>6950740</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6226,19 +6221,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6253,22 +6238,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128408521</v>
+        <v>128405859</v>
       </c>
       <c r="B57" t="n">
-        <v>79650</v>
+        <v>57673</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6276,34 +6261,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>398019</v>
+        <v>398362</v>
       </c>
       <c r="R57" t="n">
-        <v>6950740</v>
+        <v>6950549</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6333,9 +6323,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6350,19 +6350,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128405859</v>
+        <v>128413307</v>
       </c>
       <c r="B58" t="n">
         <v>57673</v>
@@ -6402,10 +6402,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>398362</v>
+        <v>398457</v>
       </c>
       <c r="R58" t="n">
-        <v>6950549</v>
+        <v>6951226</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6437,7 +6437,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6474,27 +6474,27 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128413307</v>
+        <v>128408773</v>
       </c>
       <c r="B59" t="n">
-        <v>57673</v>
+        <v>58043</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6505,7 +6505,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>398457</v>
+        <v>398012</v>
       </c>
       <c r="R59" t="n">
-        <v>6951226</v>
+        <v>6950659</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7504,10 +7504,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128411931</v>
+        <v>128411612</v>
       </c>
       <c r="B69" t="n">
-        <v>91378</v>
+        <v>79111</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7515,21 +7515,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7539,10 +7539,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>398276</v>
+        <v>398200</v>
       </c>
       <c r="R69" t="n">
-        <v>6950842</v>
+        <v>6950918</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7601,10 +7601,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128411524</v>
+        <v>128411308</v>
       </c>
       <c r="B70" t="n">
-        <v>57673</v>
+        <v>75156</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7612,39 +7612,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>398203</v>
+        <v>398162</v>
       </c>
       <c r="R70" t="n">
-        <v>6950901</v>
+        <v>6950923</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7674,19 +7669,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7701,22 +7686,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128411612</v>
+        <v>128411524</v>
       </c>
       <c r="B71" t="n">
-        <v>79111</v>
+        <v>57673</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7724,34 +7709,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>398200</v>
+        <v>398203</v>
       </c>
       <c r="R71" t="n">
-        <v>6950918</v>
+        <v>6950901</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7781,9 +7771,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7798,22 +7798,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128411308</v>
+        <v>128411931</v>
       </c>
       <c r="B72" t="n">
-        <v>75156</v>
+        <v>91378</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7821,21 +7821,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7845,10 +7845,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>398162</v>
+        <v>398276</v>
       </c>
       <c r="R72" t="n">
-        <v>6950923</v>
+        <v>6950842</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8019,45 +8019,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128416207</v>
+        <v>128405468</v>
       </c>
       <c r="B74" t="n">
-        <v>75154</v>
+        <v>82873</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6486</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>398414</v>
+        <v>398405</v>
       </c>
       <c r="R74" t="n">
-        <v>6950702</v>
+        <v>6950503</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8116,45 +8116,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128405468</v>
+        <v>128416207</v>
       </c>
       <c r="B75" t="n">
-        <v>82873</v>
+        <v>75154</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1312</v>
+        <v>6486</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>398405</v>
+        <v>398414</v>
       </c>
       <c r="R75" t="n">
-        <v>6950503</v>
+        <v>6950702</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9024,48 +9024,49 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128416210</v>
+        <v>128404962</v>
       </c>
       <c r="B84" t="n">
-        <v>91378</v>
+        <v>57838</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>266237</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>398414</v>
+        <v>398392</v>
       </c>
       <c r="R84" t="n">
-        <v>6950702</v>
+        <v>6950406</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9092,9 +9093,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9109,12 +9120,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9330,49 +9341,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128404962</v>
+        <v>128416210</v>
       </c>
       <c r="B87" t="n">
-        <v>57838</v>
+        <v>91378</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>266237</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>398392</v>
+        <v>398414</v>
       </c>
       <c r="R87" t="n">
-        <v>6950406</v>
+        <v>6950702</v>
       </c>
       <c r="S87" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9399,19 +9409,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9426,57 +9426,62 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128410048</v>
+        <v>128407736</v>
       </c>
       <c r="B88" t="n">
-        <v>78395</v>
+        <v>57673</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>397967</v>
+        <v>398169</v>
       </c>
       <c r="R88" t="n">
-        <v>6950876</v>
+        <v>6950711</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9506,9 +9511,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9523,44 +9538,44 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128415905</v>
+        <v>128410048</v>
       </c>
       <c r="B89" t="n">
-        <v>78438</v>
+        <v>78395</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6437</v>
+        <v>498</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9570,10 +9585,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>398403</v>
+        <v>397967</v>
       </c>
       <c r="R89" t="n">
-        <v>6950826</v>
+        <v>6950876</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9603,19 +9618,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9630,22 +9635,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128407736</v>
+        <v>128415905</v>
       </c>
       <c r="B90" t="n">
-        <v>57673</v>
+        <v>78438</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9653,39 +9658,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>398169</v>
+        <v>398403</v>
       </c>
       <c r="R90" t="n">
-        <v>6950711</v>
+        <v>6950826</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10550,10 +10550,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128415580</v>
+        <v>128413083</v>
       </c>
       <c r="B99" t="n">
-        <v>57673</v>
+        <v>75156</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10561,39 +10561,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>398442</v>
+        <v>398494</v>
       </c>
       <c r="R99" t="n">
-        <v>6950833</v>
+        <v>6951141</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10652,10 +10647,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128413083</v>
+        <v>128415580</v>
       </c>
       <c r="B100" t="n">
-        <v>75156</v>
+        <v>57673</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10663,34 +10658,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>398494</v>
+        <v>398442</v>
       </c>
       <c r="R100" t="n">
-        <v>6951141</v>
+        <v>6950833</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>

--- a/artfynd/A 32341-2025 artfynd.xlsx
+++ b/artfynd/A 32341-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128407744</v>
+        <v>128413409</v>
       </c>
       <c r="B2" t="n">
-        <v>79650</v>
+        <v>79673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398173</v>
+        <v>398477</v>
       </c>
       <c r="R2" t="n">
-        <v>6950715</v>
+        <v>6951277</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128412069</v>
+        <v>128407744</v>
       </c>
       <c r="B3" t="n">
-        <v>57673</v>
+        <v>79702</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398298</v>
+        <v>398173</v>
       </c>
       <c r="R3" t="n">
-        <v>6950883</v>
+        <v>6950715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128413409</v>
+        <v>128412069</v>
       </c>
       <c r="B4" t="n">
-        <v>79621</v>
+        <v>57685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398477</v>
+        <v>398298</v>
       </c>
       <c r="R4" t="n">
-        <v>6951277</v>
+        <v>6950883</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
         <v>128412732</v>
       </c>
       <c r="B5" t="n">
-        <v>79127</v>
+        <v>79178</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128415689</v>
       </c>
       <c r="B6" t="n">
-        <v>78438</v>
+        <v>78486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>128412850</v>
       </c>
       <c r="B7" t="n">
-        <v>78438</v>
+        <v>78486</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>128411332</v>
       </c>
       <c r="B8" t="n">
-        <v>75156</v>
+        <v>75171</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,50 +1369,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128407432</v>
+        <v>128409340</v>
       </c>
       <c r="B9" t="n">
-        <v>57673</v>
+        <v>80217</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>398269</v>
+        <v>397997</v>
       </c>
       <c r="R9" t="n">
-        <v>6950563</v>
+        <v>6950677</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1442,19 +1437,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,22 +1454,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128415979</v>
+        <v>128407381</v>
       </c>
       <c r="B10" t="n">
-        <v>57673</v>
+        <v>82942</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,39 +1477,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>398372</v>
+        <v>398271</v>
       </c>
       <c r="R10" t="n">
-        <v>6950738</v>
+        <v>6950584</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1536,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1566,7 +1546,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128409340</v>
+        <v>128412642</v>
       </c>
       <c r="B11" t="n">
-        <v>80164</v>
+        <v>57526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,21 +1584,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>102621</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1628,13 +1608,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>397997</v>
+        <v>398437</v>
       </c>
       <c r="R11" t="n">
-        <v>6950677</v>
+        <v>6951052</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1690,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128407381</v>
+        <v>128407432</v>
       </c>
       <c r="B12" t="n">
-        <v>82873</v>
+        <v>57685</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1701,34 +1681,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>398271</v>
+        <v>398269</v>
       </c>
       <c r="R12" t="n">
-        <v>6950584</v>
+        <v>6950563</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,27 +1782,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128412642</v>
+        <v>128415979</v>
       </c>
       <c r="B13" t="n">
-        <v>57514</v>
+        <v>57685</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1826,19 +1811,24 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>398437</v>
+        <v>398372</v>
       </c>
       <c r="R13" t="n">
-        <v>6951052</v>
+        <v>6950738</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1865,9 +1855,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1882,12 +1882,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1897,7 +1897,7 @@
         <v>128407947</v>
       </c>
       <c r="B14" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>128411782</v>
       </c>
       <c r="B15" t="n">
-        <v>75156</v>
+        <v>75171</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>128410038</v>
       </c>
       <c r="B16" t="n">
-        <v>75156</v>
+        <v>75171</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128410559</v>
+        <v>128415142</v>
       </c>
       <c r="B17" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>398097</v>
+        <v>398352</v>
       </c>
       <c r="R17" t="n">
-        <v>6950870</v>
+        <v>6950954</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128415142</v>
+        <v>128410559</v>
       </c>
       <c r="B18" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>398352</v>
+        <v>398097</v>
       </c>
       <c r="R18" t="n">
-        <v>6950954</v>
+        <v>6950870</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128415613</v>
+        <v>128415804</v>
       </c>
       <c r="B19" t="n">
-        <v>78699</v>
+        <v>78486</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2440,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>398437</v>
+        <v>398394</v>
       </c>
       <c r="R19" t="n">
-        <v>6950808</v>
+        <v>6950811</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2497,9 +2497,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2514,22 +2524,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128415804</v>
+        <v>128410565</v>
       </c>
       <c r="B20" t="n">
-        <v>78438</v>
+        <v>75171</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2537,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>398394</v>
+        <v>398088</v>
       </c>
       <c r="R20" t="n">
-        <v>6950811</v>
+        <v>6950909</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2594,19 +2604,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2621,22 +2621,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128410565</v>
+        <v>128408059</v>
       </c>
       <c r="B21" t="n">
-        <v>75156</v>
+        <v>57685</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,34 +2644,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>398088</v>
+        <v>398146</v>
       </c>
       <c r="R21" t="n">
-        <v>6950909</v>
+        <v>6950784</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128408059</v>
+        <v>128415613</v>
       </c>
       <c r="B22" t="n">
-        <v>57673</v>
+        <v>78749</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2741,39 +2746,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>398146</v>
+        <v>398437</v>
       </c>
       <c r="R22" t="n">
-        <v>6950784</v>
+        <v>6950808</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2835,7 +2835,7 @@
         <v>128415681</v>
       </c>
       <c r="B23" t="n">
-        <v>79621</v>
+        <v>79673</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128410050</v>
+        <v>128405816</v>
       </c>
       <c r="B24" t="n">
-        <v>82873</v>
+        <v>57685</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,34 +2950,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>397967</v>
+        <v>398390</v>
       </c>
       <c r="R24" t="n">
-        <v>6950876</v>
+        <v>6950541</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3007,9 +3012,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3024,22 +3039,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128411229</v>
+        <v>128410205</v>
       </c>
       <c r="B25" t="n">
-        <v>82873</v>
+        <v>75171</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3047,21 +3062,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>398118</v>
+        <v>397980</v>
       </c>
       <c r="R25" t="n">
-        <v>6950921</v>
+        <v>6950909</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128416541</v>
+        <v>128411297</v>
       </c>
       <c r="B26" t="n">
-        <v>82873</v>
+        <v>75171</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,21 +3159,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>398411</v>
+        <v>398143</v>
       </c>
       <c r="R26" t="n">
-        <v>6950623</v>
+        <v>6950944</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128405816</v>
+        <v>128413330</v>
       </c>
       <c r="B27" t="n">
-        <v>57673</v>
+        <v>78486</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,39 +3256,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>398390</v>
+        <v>398486</v>
       </c>
       <c r="R27" t="n">
-        <v>6950541</v>
+        <v>6951242</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3303,19 +3313,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3330,22 +3330,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128410205</v>
+        <v>128410050</v>
       </c>
       <c r="B28" t="n">
-        <v>75156</v>
+        <v>82942</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3353,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>397980</v>
+        <v>397967</v>
       </c>
       <c r="R28" t="n">
-        <v>6950909</v>
+        <v>6950876</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128411297</v>
+        <v>128411229</v>
       </c>
       <c r="B29" t="n">
-        <v>75156</v>
+        <v>82942</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3450,21 +3450,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>398143</v>
+        <v>398118</v>
       </c>
       <c r="R29" t="n">
-        <v>6950944</v>
+        <v>6950921</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128413330</v>
+        <v>128416541</v>
       </c>
       <c r="B30" t="n">
-        <v>78438</v>
+        <v>82942</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3547,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>398486</v>
+        <v>398411</v>
       </c>
       <c r="R30" t="n">
-        <v>6951242</v>
+        <v>6950623</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128408399</v>
+        <v>128411736</v>
       </c>
       <c r="B31" t="n">
-        <v>82873</v>
+        <v>91470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3644,21 +3644,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>398076</v>
+        <v>398234</v>
       </c>
       <c r="R31" t="n">
-        <v>6950793</v>
+        <v>6950852</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3701,9 +3701,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3718,22 +3728,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128415952</v>
+        <v>128410403</v>
       </c>
       <c r="B32" t="n">
-        <v>57673</v>
+        <v>75171</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3741,39 +3751,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>398385</v>
+        <v>398063</v>
       </c>
       <c r="R32" t="n">
-        <v>6950755</v>
+        <v>6950893</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3832,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128411736</v>
+        <v>128411429</v>
       </c>
       <c r="B33" t="n">
-        <v>91378</v>
+        <v>75171</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3843,21 +3848,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3867,10 +3872,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>398234</v>
+        <v>398176</v>
       </c>
       <c r="R33" t="n">
-        <v>6950852</v>
+        <v>6950885</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3900,19 +3905,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3927,22 +3922,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128410403</v>
+        <v>128408399</v>
       </c>
       <c r="B34" t="n">
-        <v>75156</v>
+        <v>82942</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3950,21 +3945,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3974,10 +3969,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>398063</v>
+        <v>398076</v>
       </c>
       <c r="R34" t="n">
-        <v>6950893</v>
+        <v>6950793</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4036,10 +4031,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128411429</v>
+        <v>128405964</v>
       </c>
       <c r="B35" t="n">
-        <v>75156</v>
+        <v>57685</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4047,34 +4042,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398176</v>
+        <v>398364</v>
       </c>
       <c r="R35" t="n">
-        <v>6950885</v>
+        <v>6950589</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128405964</v>
+        <v>128412757</v>
       </c>
       <c r="B36" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398364</v>
+        <v>398460</v>
       </c>
       <c r="R36" t="n">
-        <v>6950589</v>
+        <v>6951061</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4206,9 +4206,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4223,22 +4233,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128412757</v>
+        <v>128415952</v>
       </c>
       <c r="B37" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4266,7 +4276,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4275,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>398460</v>
+        <v>398385</v>
       </c>
       <c r="R37" t="n">
-        <v>6951061</v>
+        <v>6950755</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4308,19 +4318,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4335,12 +4335,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4350,7 +4350,7 @@
         <v>128413866</v>
       </c>
       <c r="B38" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4459,32 +4459,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128405841</v>
+        <v>128416366</v>
       </c>
       <c r="B39" t="n">
-        <v>92057</v>
+        <v>78443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3298</v>
+        <v>498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>398374</v>
+        <v>398419</v>
       </c>
       <c r="R39" t="n">
-        <v>6950548</v>
+        <v>6950678</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4556,32 +4556,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128405669</v>
+        <v>128405841</v>
       </c>
       <c r="B40" t="n">
-        <v>91378</v>
+        <v>92149</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>398398</v>
+        <v>398374</v>
       </c>
       <c r="R40" t="n">
-        <v>6950569</v>
+        <v>6950548</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,32 +4653,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128412193</v>
+        <v>128405669</v>
       </c>
       <c r="B41" t="n">
-        <v>80170</v>
+        <v>91470</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>398369</v>
+        <v>398398</v>
       </c>
       <c r="R41" t="n">
-        <v>6950956</v>
+        <v>6950569</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4750,32 +4750,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128411735</v>
+        <v>128412193</v>
       </c>
       <c r="B42" t="n">
-        <v>75156</v>
+        <v>80223</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4785,10 +4785,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>398227</v>
+        <v>398369</v>
       </c>
       <c r="R42" t="n">
-        <v>6950881</v>
+        <v>6950956</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4847,10 +4847,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128412950</v>
+        <v>128411735</v>
       </c>
       <c r="B43" t="n">
-        <v>57673</v>
+        <v>75171</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4858,39 +4858,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>398483</v>
+        <v>398227</v>
       </c>
       <c r="R43" t="n">
-        <v>6951117</v>
+        <v>6950881</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4949,45 +4944,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128416366</v>
+        <v>128414073</v>
       </c>
       <c r="B44" t="n">
-        <v>78395</v>
+        <v>57685</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>398419</v>
+        <v>398546</v>
       </c>
       <c r="R44" t="n">
-        <v>6950678</v>
+        <v>6951235</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5046,10 +5046,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128414073</v>
+        <v>128412950</v>
       </c>
       <c r="B45" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5086,10 +5086,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>398546</v>
+        <v>398483</v>
       </c>
       <c r="R45" t="n">
-        <v>6951235</v>
+        <v>6951117</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5151,7 +5151,7 @@
         <v>128415930</v>
       </c>
       <c r="B46" t="n">
-        <v>79621</v>
+        <v>79673</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5245,32 +5245,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128412638</v>
+        <v>128407293</v>
       </c>
       <c r="B47" t="n">
-        <v>57777</v>
+        <v>79702</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5280,13 +5280,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>398437</v>
+        <v>398263</v>
       </c>
       <c r="R47" t="n">
-        <v>6951052</v>
+        <v>6950596</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5342,10 +5342,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128407293</v>
+        <v>128415932</v>
       </c>
       <c r="B48" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>398263</v>
+        <v>398387</v>
       </c>
       <c r="R48" t="n">
-        <v>6950596</v>
+        <v>6950766</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5439,10 +5439,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128410408</v>
+        <v>128412677</v>
       </c>
       <c r="B49" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5450,34 +5450,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>398063</v>
+        <v>398462</v>
       </c>
       <c r="R49" t="n">
-        <v>6950893</v>
+        <v>6951039</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5507,9 +5512,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5524,22 +5539,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128412677</v>
+        <v>128415972</v>
       </c>
       <c r="B50" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5576,10 +5591,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>398462</v>
+        <v>398396</v>
       </c>
       <c r="R50" t="n">
-        <v>6951039</v>
+        <v>6950719</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5609,19 +5624,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5636,22 +5641,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128415972</v>
+        <v>128406327</v>
       </c>
       <c r="B51" t="n">
-        <v>57673</v>
+        <v>91470</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5659,39 +5664,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>398396</v>
+        <v>398333</v>
       </c>
       <c r="R51" t="n">
-        <v>6950719</v>
+        <v>6950603</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5750,10 +5750,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128406327</v>
+        <v>128411964</v>
       </c>
       <c r="B52" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5785,10 +5785,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>398333</v>
+        <v>398278</v>
       </c>
       <c r="R52" t="n">
-        <v>6950603</v>
+        <v>6950881</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5847,10 +5847,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128411964</v>
+        <v>128410408</v>
       </c>
       <c r="B53" t="n">
-        <v>91378</v>
+        <v>79083</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5858,21 +5858,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5882,10 +5882,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>398278</v>
+        <v>398063</v>
       </c>
       <c r="R53" t="n">
-        <v>6950881</v>
+        <v>6950893</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5944,10 +5944,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128415932</v>
+        <v>128408097</v>
       </c>
       <c r="B54" t="n">
-        <v>79650</v>
+        <v>57845</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5955,37 +5955,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>398387</v>
+        <v>398159</v>
       </c>
       <c r="R54" t="n">
-        <v>6950766</v>
+        <v>6950801</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6012,9 +6017,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6029,65 +6044,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128408097</v>
+        <v>128412638</v>
       </c>
       <c r="B55" t="n">
-        <v>57833</v>
+        <v>57789</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>398159</v>
+        <v>398437</v>
       </c>
       <c r="R55" t="n">
-        <v>6950801</v>
+        <v>6951052</v>
       </c>
       <c r="S55" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6114,19 +6124,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6141,12 +6141,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6156,7 +6156,7 @@
         <v>128408521</v>
       </c>
       <c r="B56" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6250,27 +6250,27 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128405859</v>
+        <v>128413955</v>
       </c>
       <c r="B57" t="n">
-        <v>57673</v>
+        <v>57526</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6281,7 +6281,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>398362</v>
+        <v>398517</v>
       </c>
       <c r="R57" t="n">
-        <v>6950549</v>
+        <v>6951283</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6323,19 +6323,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6350,22 +6340,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128413307</v>
+        <v>128405859</v>
       </c>
       <c r="B58" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6402,10 +6392,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>398457</v>
+        <v>398362</v>
       </c>
       <c r="R58" t="n">
-        <v>6951226</v>
+        <v>6950549</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6437,7 +6427,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6447,7 +6437,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6474,27 +6464,27 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128408773</v>
+        <v>128413307</v>
       </c>
       <c r="B59" t="n">
-        <v>58043</v>
+        <v>57685</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6505,7 +6495,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6514,13 +6504,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>398012</v>
+        <v>398457</v>
       </c>
       <c r="R59" t="n">
-        <v>6950659</v>
+        <v>6951226</v>
       </c>
       <c r="S59" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6549,7 +6539,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6559,7 +6549,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6586,10 +6576,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128413955</v>
+        <v>128408773</v>
       </c>
       <c r="B60" t="n">
-        <v>57514</v>
+        <v>58055</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6597,16 +6587,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102621</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6617,7 +6607,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6626,10 +6616,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>398517</v>
+        <v>398012</v>
       </c>
       <c r="R60" t="n">
-        <v>6951283</v>
+        <v>6950659</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -6659,9 +6649,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6676,12 +6676,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6691,7 +6691,7 @@
         <v>128409775</v>
       </c>
       <c r="B61" t="n">
-        <v>79621</v>
+        <v>79673</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6785,10 +6785,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128415706</v>
+        <v>128409691</v>
       </c>
       <c r="B62" t="n">
-        <v>57673</v>
+        <v>90485</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6796,39 +6796,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>398411</v>
+        <v>398057</v>
       </c>
       <c r="R62" t="n">
-        <v>6950796</v>
+        <v>6950739</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6858,9 +6853,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6875,22 +6880,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128416501</v>
+        <v>128406318</v>
       </c>
       <c r="B63" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6898,39 +6903,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>398382</v>
+        <v>398333</v>
       </c>
       <c r="R63" t="n">
-        <v>6950639</v>
+        <v>6950603</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6960,19 +6960,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6987,22 +6977,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128409691</v>
+        <v>128416501</v>
       </c>
       <c r="B64" t="n">
-        <v>90393</v>
+        <v>57685</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7010,34 +7000,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>398057</v>
+        <v>398382</v>
       </c>
       <c r="R64" t="n">
-        <v>6950739</v>
+        <v>6950639</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7069,7 +7064,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7079,7 +7074,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7106,10 +7101,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128406318</v>
+        <v>128407307</v>
       </c>
       <c r="B65" t="n">
-        <v>79032</v>
+        <v>78841</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7117,21 +7112,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7141,10 +7136,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>398333</v>
+        <v>398263</v>
       </c>
       <c r="R65" t="n">
-        <v>6950603</v>
+        <v>6950596</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7206,7 +7201,7 @@
         <v>128415836</v>
       </c>
       <c r="B66" t="n">
-        <v>78010</v>
+        <v>78055</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7313,7 +7308,7 @@
         <v>128406026</v>
       </c>
       <c r="B67" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7407,10 +7402,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128407307</v>
+        <v>128415706</v>
       </c>
       <c r="B68" t="n">
-        <v>78791</v>
+        <v>57685</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7418,34 +7413,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>398263</v>
+        <v>398411</v>
       </c>
       <c r="R68" t="n">
-        <v>6950596</v>
+        <v>6950796</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7507,7 +7507,7 @@
         <v>128411612</v>
       </c>
       <c r="B69" t="n">
-        <v>79111</v>
+        <v>79162</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7601,10 +7601,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128411308</v>
+        <v>128411931</v>
       </c>
       <c r="B70" t="n">
-        <v>75156</v>
+        <v>91470</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7612,21 +7612,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7636,10 +7636,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>398162</v>
+        <v>398276</v>
       </c>
       <c r="R70" t="n">
-        <v>6950923</v>
+        <v>6950842</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7698,10 +7698,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128411524</v>
+        <v>128411308</v>
       </c>
       <c r="B71" t="n">
-        <v>57673</v>
+        <v>75171</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7709,39 +7709,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>398203</v>
+        <v>398162</v>
       </c>
       <c r="R71" t="n">
-        <v>6950901</v>
+        <v>6950923</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7771,19 +7766,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7798,22 +7783,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128411931</v>
+        <v>128411524</v>
       </c>
       <c r="B72" t="n">
-        <v>91378</v>
+        <v>57685</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7821,34 +7806,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>398276</v>
+        <v>398203</v>
       </c>
       <c r="R72" t="n">
-        <v>6950842</v>
+        <v>6950901</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7878,9 +7868,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7895,12 +7895,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -7910,7 +7910,7 @@
         <v>128411180</v>
       </c>
       <c r="B73" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8019,45 +8019,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128405468</v>
+        <v>128416207</v>
       </c>
       <c r="B74" t="n">
-        <v>82873</v>
+        <v>75169</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>6486</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>398405</v>
+        <v>398414</v>
       </c>
       <c r="R74" t="n">
-        <v>6950503</v>
+        <v>6950702</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8116,45 +8116,50 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128416207</v>
+        <v>128412048</v>
       </c>
       <c r="B75" t="n">
-        <v>75154</v>
+        <v>57685</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>398414</v>
+        <v>398329</v>
       </c>
       <c r="R75" t="n">
-        <v>6950702</v>
+        <v>6950952</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8184,9 +8189,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8201,22 +8216,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128412048</v>
+        <v>128406114</v>
       </c>
       <c r="B76" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8253,10 +8268,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>398329</v>
+        <v>398351</v>
       </c>
       <c r="R76" t="n">
-        <v>6950952</v>
+        <v>6950591</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8288,7 +8303,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8298,7 +8313,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8325,27 +8340,27 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128406114</v>
+        <v>128412622</v>
       </c>
       <c r="B77" t="n">
-        <v>57673</v>
+        <v>58055</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8354,24 +8369,19 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>398351</v>
+        <v>398437</v>
       </c>
       <c r="R77" t="n">
-        <v>6950591</v>
+        <v>6951052</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8398,19 +8408,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8425,60 +8425,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128412622</v>
+        <v>128405468</v>
       </c>
       <c r="B78" t="n">
-        <v>58043</v>
+        <v>82942</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>398437</v>
+        <v>398405</v>
       </c>
       <c r="R78" t="n">
-        <v>6951052</v>
+        <v>6950503</v>
       </c>
       <c r="S78" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>128412825</v>
       </c>
       <c r="B79" t="n">
-        <v>79621</v>
+        <v>79673</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>128411329</v>
       </c>
       <c r="B80" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>128405900</v>
       </c>
       <c r="B81" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>128407528</v>
       </c>
       <c r="B82" t="n">
-        <v>78699</v>
+        <v>78749</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>128411270</v>
       </c>
       <c r="B83" t="n">
-        <v>78438</v>
+        <v>78486</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9024,49 +9024,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128404962</v>
+        <v>128416210</v>
       </c>
       <c r="B84" t="n">
-        <v>57838</v>
+        <v>91470</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>266237</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>398392</v>
+        <v>398414</v>
       </c>
       <c r="R84" t="n">
-        <v>6950406</v>
+        <v>6950702</v>
       </c>
       <c r="S84" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9093,19 +9092,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9120,12 +9109,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9135,7 +9124,7 @@
         <v>128411972</v>
       </c>
       <c r="B85" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9237,7 +9226,7 @@
         <v>128407963</v>
       </c>
       <c r="B86" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9341,48 +9330,49 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128416210</v>
+        <v>128404962</v>
       </c>
       <c r="B87" t="n">
-        <v>91378</v>
+        <v>57850</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5432</v>
+        <v>266237</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>398414</v>
+        <v>398392</v>
       </c>
       <c r="R87" t="n">
-        <v>6950702</v>
+        <v>6950406</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9409,9 +9399,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9426,62 +9426,57 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128407736</v>
+        <v>128410048</v>
       </c>
       <c r="B88" t="n">
-        <v>57673</v>
+        <v>78443</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>398169</v>
+        <v>397967</v>
       </c>
       <c r="R88" t="n">
-        <v>6950711</v>
+        <v>6950876</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9511,19 +9506,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9538,44 +9523,44 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128410048</v>
+        <v>128415905</v>
       </c>
       <c r="B89" t="n">
-        <v>78395</v>
+        <v>78486</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>498</v>
+        <v>6437</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9585,10 +9570,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>397967</v>
+        <v>398403</v>
       </c>
       <c r="R89" t="n">
-        <v>6950876</v>
+        <v>6950826</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9618,9 +9603,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9635,22 +9630,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128415905</v>
+        <v>128407736</v>
       </c>
       <c r="B90" t="n">
-        <v>78438</v>
+        <v>57685</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9658,34 +9653,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>398403</v>
+        <v>398169</v>
       </c>
       <c r="R90" t="n">
-        <v>6950826</v>
+        <v>6950711</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9757,7 +9757,7 @@
         <v>128405637</v>
       </c>
       <c r="B91" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>128413415</v>
       </c>
       <c r="B92" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>128410197</v>
       </c>
       <c r="B93" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>128411474</v>
       </c>
       <c r="B94" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>128413088</v>
       </c>
       <c r="B95" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>128411728</v>
       </c>
       <c r="B96" t="n">
-        <v>78395</v>
+        <v>78443</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>128410472</v>
       </c>
       <c r="B97" t="n">
-        <v>75156</v>
+        <v>75171</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>128407311</v>
       </c>
       <c r="B98" t="n">
-        <v>78438</v>
+        <v>78486</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>128413083</v>
       </c>
       <c r="B99" t="n">
-        <v>75156</v>
+        <v>75171</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10647,10 +10647,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128415580</v>
+        <v>128413214</v>
       </c>
       <c r="B100" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -10687,10 +10687,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>398442</v>
+        <v>398467</v>
       </c>
       <c r="R100" t="n">
-        <v>6950833</v>
+        <v>6951207</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10749,10 +10749,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128413214</v>
+        <v>128415580</v>
       </c>
       <c r="B101" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
       <c r="I101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -10789,10 +10789,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>398467</v>
+        <v>398442</v>
       </c>
       <c r="R101" t="n">
-        <v>6951207</v>
+        <v>6950833</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10854,7 +10854,7 @@
         <v>128413296</v>
       </c>
       <c r="B102" t="n">
-        <v>79621</v>
+        <v>79673</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>128407903</v>
       </c>
       <c r="B103" t="n">
-        <v>81027</v>
+        <v>81088</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>128411857</v>
       </c>
       <c r="B104" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>128406215</v>
       </c>
       <c r="B105" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>128405961</v>
       </c>
       <c r="B106" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>128408249</v>
       </c>
       <c r="B107" t="n">
-        <v>78395</v>
+        <v>78443</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>128408651</v>
       </c>
       <c r="B108" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>128405590</v>
       </c>
       <c r="B109" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>128416572</v>
       </c>
       <c r="B110" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>128414034</v>
       </c>
       <c r="B111" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>128413146</v>
       </c>
       <c r="B112" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>128413351</v>
       </c>
       <c r="B113" t="n">
-        <v>79621</v>
+        <v>79673</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 32341-2025 artfynd.xlsx
+++ b/artfynd/A 32341-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128413409</v>
+        <v>128407744</v>
       </c>
       <c r="B2" t="n">
-        <v>79673</v>
+        <v>79702</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398477</v>
+        <v>398173</v>
       </c>
       <c r="R2" t="n">
-        <v>6951277</v>
+        <v>6950715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128407744</v>
+        <v>128412069</v>
       </c>
       <c r="B3" t="n">
-        <v>79702</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398173</v>
+        <v>398298</v>
       </c>
       <c r="R3" t="n">
-        <v>6950715</v>
+        <v>6950883</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128412069</v>
+        <v>128413409</v>
       </c>
       <c r="B4" t="n">
-        <v>57685</v>
+        <v>79673</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +885,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398298</v>
+        <v>398477</v>
       </c>
       <c r="R4" t="n">
-        <v>6950883</v>
+        <v>6951277</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1466,32 +1466,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128407381</v>
+        <v>128412642</v>
       </c>
       <c r="B10" t="n">
-        <v>82942</v>
+        <v>57526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>102621</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>398271</v>
+        <v>398437</v>
       </c>
       <c r="R10" t="n">
-        <v>6950584</v>
+        <v>6951052</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1534,19 +1534,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1561,44 +1551,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128412642</v>
+        <v>128407381</v>
       </c>
       <c r="B11" t="n">
-        <v>57526</v>
+        <v>82942</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102621</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,13 +1598,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>398437</v>
+        <v>398271</v>
       </c>
       <c r="R11" t="n">
-        <v>6951052</v>
+        <v>6950584</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1641,9 +1631,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1658,12 +1658,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2429,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128415804</v>
+        <v>128415681</v>
       </c>
       <c r="B19" t="n">
-        <v>78486</v>
+        <v>79673</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2440,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128410565</v>
+        <v>128415613</v>
       </c>
       <c r="B20" t="n">
-        <v>75171</v>
+        <v>78749</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>398088</v>
+        <v>398437</v>
       </c>
       <c r="R20" t="n">
-        <v>6950909</v>
+        <v>6950808</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128415613</v>
+        <v>128415804</v>
       </c>
       <c r="B22" t="n">
-        <v>78749</v>
+        <v>78486</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2746,21 +2746,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>398437</v>
+        <v>398394</v>
       </c>
       <c r="R22" t="n">
-        <v>6950808</v>
+        <v>6950811</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2803,9 +2803,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2820,22 +2830,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128415681</v>
+        <v>128410565</v>
       </c>
       <c r="B23" t="n">
-        <v>79673</v>
+        <v>75171</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2843,21 +2853,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>398394</v>
+        <v>398088</v>
       </c>
       <c r="R23" t="n">
-        <v>6950811</v>
+        <v>6950909</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2900,19 +2910,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2927,22 +2927,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128405816</v>
+        <v>128410050</v>
       </c>
       <c r="B24" t="n">
-        <v>57685</v>
+        <v>82942</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,39 +2950,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>398390</v>
+        <v>397967</v>
       </c>
       <c r="R24" t="n">
-        <v>6950541</v>
+        <v>6950876</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3012,19 +3007,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3039,22 +3024,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128410205</v>
+        <v>128411229</v>
       </c>
       <c r="B25" t="n">
-        <v>75171</v>
+        <v>82942</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3062,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>397980</v>
+        <v>398118</v>
       </c>
       <c r="R25" t="n">
-        <v>6950909</v>
+        <v>6950921</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128411297</v>
+        <v>128416541</v>
       </c>
       <c r="B26" t="n">
-        <v>75171</v>
+        <v>82942</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3159,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3183,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>398143</v>
+        <v>398411</v>
       </c>
       <c r="R26" t="n">
-        <v>6950944</v>
+        <v>6950623</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128413330</v>
+        <v>128410205</v>
       </c>
       <c r="B27" t="n">
-        <v>78486</v>
+        <v>75171</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3256,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3280,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>398486</v>
+        <v>397980</v>
       </c>
       <c r="R27" t="n">
-        <v>6951242</v>
+        <v>6950909</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128410050</v>
+        <v>128411297</v>
       </c>
       <c r="B28" t="n">
-        <v>82942</v>
+        <v>75171</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3353,21 +3338,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3362,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>397967</v>
+        <v>398143</v>
       </c>
       <c r="R28" t="n">
-        <v>6950876</v>
+        <v>6950944</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3424,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128411229</v>
+        <v>128413330</v>
       </c>
       <c r="B29" t="n">
-        <v>82942</v>
+        <v>78486</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3450,21 +3435,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3474,10 +3459,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>398118</v>
+        <v>398486</v>
       </c>
       <c r="R29" t="n">
-        <v>6950921</v>
+        <v>6951242</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,10 +3521,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128416541</v>
+        <v>128405816</v>
       </c>
       <c r="B30" t="n">
-        <v>82942</v>
+        <v>57685</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3547,34 +3532,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>398411</v>
+        <v>398390</v>
       </c>
       <c r="R30" t="n">
-        <v>6950623</v>
+        <v>6950541</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3604,9 +3594,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3621,22 +3621,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128411736</v>
+        <v>128408399</v>
       </c>
       <c r="B31" t="n">
-        <v>91470</v>
+        <v>82942</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3644,21 +3644,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>398234</v>
+        <v>398076</v>
       </c>
       <c r="R31" t="n">
-        <v>6950852</v>
+        <v>6950793</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3701,19 +3701,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3728,12 +3718,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3934,10 +3924,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128408399</v>
+        <v>128411736</v>
       </c>
       <c r="B34" t="n">
-        <v>82942</v>
+        <v>91470</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3945,21 +3935,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3969,10 +3959,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>398076</v>
+        <v>398234</v>
       </c>
       <c r="R34" t="n">
-        <v>6950793</v>
+        <v>6950852</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4002,9 +3992,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4019,12 +4019,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4556,45 +4556,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128405841</v>
+        <v>128414073</v>
       </c>
       <c r="B40" t="n">
-        <v>92149</v>
+        <v>57685</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>398374</v>
+        <v>398546</v>
       </c>
       <c r="R40" t="n">
-        <v>6950548</v>
+        <v>6951235</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,10 +4658,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128405669</v>
+        <v>128412950</v>
       </c>
       <c r="B41" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4664,34 +4669,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>398398</v>
+        <v>398483</v>
       </c>
       <c r="R41" t="n">
-        <v>6950569</v>
+        <v>6951117</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4750,10 +4760,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128412193</v>
+        <v>128405841</v>
       </c>
       <c r="B42" t="n">
-        <v>80223</v>
+        <v>92149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4761,21 +4771,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>3298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4785,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>398369</v>
+        <v>398374</v>
       </c>
       <c r="R42" t="n">
-        <v>6950956</v>
+        <v>6950548</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4847,32 +4857,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128411735</v>
+        <v>128412193</v>
       </c>
       <c r="B43" t="n">
-        <v>75171</v>
+        <v>80223</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4882,10 +4892,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>398227</v>
+        <v>398369</v>
       </c>
       <c r="R43" t="n">
-        <v>6950881</v>
+        <v>6950956</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4944,10 +4954,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128414073</v>
+        <v>128411735</v>
       </c>
       <c r="B44" t="n">
-        <v>57685</v>
+        <v>75171</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4955,39 +4965,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>398546</v>
+        <v>398227</v>
       </c>
       <c r="R44" t="n">
-        <v>6951235</v>
+        <v>6950881</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5046,10 +5051,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128412950</v>
+        <v>128405669</v>
       </c>
       <c r="B45" t="n">
-        <v>57685</v>
+        <v>91470</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5057,39 +5062,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>398483</v>
+        <v>398398</v>
       </c>
       <c r="R45" t="n">
-        <v>6951117</v>
+        <v>6950569</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5245,10 +5245,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128407293</v>
+        <v>128408097</v>
       </c>
       <c r="B47" t="n">
-        <v>79702</v>
+        <v>57845</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5256,37 +5256,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>398263</v>
+        <v>398159</v>
       </c>
       <c r="R47" t="n">
-        <v>6950596</v>
+        <v>6950801</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5313,9 +5318,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5330,44 +5345,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128415932</v>
+        <v>128412638</v>
       </c>
       <c r="B48" t="n">
-        <v>79702</v>
+        <v>57789</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5377,13 +5392,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>398387</v>
+        <v>398437</v>
       </c>
       <c r="R48" t="n">
-        <v>6950766</v>
+        <v>6951052</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5439,10 +5454,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128412677</v>
+        <v>128407293</v>
       </c>
       <c r="B49" t="n">
-        <v>57685</v>
+        <v>79702</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5450,39 +5465,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>398462</v>
+        <v>398263</v>
       </c>
       <c r="R49" t="n">
-        <v>6951039</v>
+        <v>6950596</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5512,19 +5522,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5539,22 +5539,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128415972</v>
+        <v>128410408</v>
       </c>
       <c r="B50" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5562,39 +5562,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>398396</v>
+        <v>398063</v>
       </c>
       <c r="R50" t="n">
-        <v>6950719</v>
+        <v>6950893</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5653,10 +5648,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128406327</v>
+        <v>128415932</v>
       </c>
       <c r="B51" t="n">
-        <v>91470</v>
+        <v>79702</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5664,21 +5659,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5688,10 +5683,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>398333</v>
+        <v>398387</v>
       </c>
       <c r="R51" t="n">
-        <v>6950603</v>
+        <v>6950766</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5750,7 +5745,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128411964</v>
+        <v>128406327</v>
       </c>
       <c r="B52" t="n">
         <v>91470</v>
@@ -5785,10 +5780,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>398278</v>
+        <v>398333</v>
       </c>
       <c r="R52" t="n">
-        <v>6950881</v>
+        <v>6950603</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5847,10 +5842,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128410408</v>
+        <v>128411964</v>
       </c>
       <c r="B53" t="n">
-        <v>79083</v>
+        <v>91470</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5858,21 +5853,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5882,10 +5877,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>398063</v>
+        <v>398278</v>
       </c>
       <c r="R53" t="n">
-        <v>6950893</v>
+        <v>6950881</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5944,10 +5939,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128408097</v>
+        <v>128412677</v>
       </c>
       <c r="B54" t="n">
-        <v>57845</v>
+        <v>57685</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5955,27 +5950,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5984,13 +5979,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>398159</v>
+        <v>398462</v>
       </c>
       <c r="R54" t="n">
-        <v>6950801</v>
+        <v>6951039</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6019,7 +6014,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6029,7 +6024,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6056,27 +6051,27 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128412638</v>
+        <v>128415972</v>
       </c>
       <c r="B55" t="n">
-        <v>57789</v>
+        <v>57685</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6085,19 +6080,24 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>398437</v>
+        <v>398396</v>
       </c>
       <c r="R55" t="n">
-        <v>6951052</v>
+        <v>6950719</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6250,10 +6250,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128413955</v>
+        <v>128408773</v>
       </c>
       <c r="B57" t="n">
-        <v>57526</v>
+        <v>58055</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6261,16 +6261,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>102621</v>
+        <v>103015</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6281,7 +6281,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6290,10 +6290,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>398517</v>
+        <v>398012</v>
       </c>
       <c r="R57" t="n">
-        <v>6951283</v>
+        <v>6950659</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6323,9 +6323,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6340,12 +6350,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6576,10 +6586,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128408773</v>
+        <v>128413955</v>
       </c>
       <c r="B60" t="n">
-        <v>58055</v>
+        <v>57526</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6587,16 +6597,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>102621</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6607,7 +6617,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6616,10 +6626,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>398012</v>
+        <v>398517</v>
       </c>
       <c r="R60" t="n">
-        <v>6950659</v>
+        <v>6951283</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -6649,19 +6659,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6676,12 +6676,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6892,10 +6892,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128406318</v>
+        <v>128407307</v>
       </c>
       <c r="B63" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6903,21 +6903,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>398333</v>
+        <v>398263</v>
       </c>
       <c r="R63" t="n">
-        <v>6950603</v>
+        <v>6950596</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6989,10 +6989,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128416501</v>
+        <v>128406318</v>
       </c>
       <c r="B64" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7000,39 +7000,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>398382</v>
+        <v>398333</v>
       </c>
       <c r="R64" t="n">
-        <v>6950639</v>
+        <v>6950603</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7062,19 +7057,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7089,22 +7074,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128407307</v>
+        <v>128415836</v>
       </c>
       <c r="B65" t="n">
-        <v>78841</v>
+        <v>78055</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7112,21 +7097,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7136,10 +7121,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>398263</v>
+        <v>398394</v>
       </c>
       <c r="R65" t="n">
-        <v>6950596</v>
+        <v>6950811</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7169,9 +7154,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7186,22 +7181,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128415836</v>
+        <v>128406026</v>
       </c>
       <c r="B66" t="n">
-        <v>78055</v>
+        <v>79702</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7209,21 +7204,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7233,10 +7228,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>398394</v>
+        <v>398364</v>
       </c>
       <c r="R66" t="n">
-        <v>6950811</v>
+        <v>6950589</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7266,19 +7261,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7293,22 +7278,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128406026</v>
+        <v>128415706</v>
       </c>
       <c r="B67" t="n">
-        <v>79702</v>
+        <v>57685</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7316,34 +7301,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>398364</v>
+        <v>398411</v>
       </c>
       <c r="R67" t="n">
-        <v>6950589</v>
+        <v>6950796</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7402,7 +7392,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128415706</v>
+        <v>128416501</v>
       </c>
       <c r="B68" t="n">
         <v>57685</v>
@@ -7433,7 +7423,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7442,10 +7432,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>398411</v>
+        <v>398382</v>
       </c>
       <c r="R68" t="n">
-        <v>6950796</v>
+        <v>6950639</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7475,9 +7465,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7492,12 +7492,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7601,10 +7601,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128411931</v>
+        <v>128411308</v>
       </c>
       <c r="B70" t="n">
-        <v>91470</v>
+        <v>75171</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7612,21 +7612,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7636,10 +7636,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>398276</v>
+        <v>398162</v>
       </c>
       <c r="R70" t="n">
-        <v>6950842</v>
+        <v>6950923</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7698,10 +7698,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128411308</v>
+        <v>128411931</v>
       </c>
       <c r="B71" t="n">
-        <v>75171</v>
+        <v>91470</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7709,21 +7709,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7733,10 +7733,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>398162</v>
+        <v>398276</v>
       </c>
       <c r="R71" t="n">
-        <v>6950923</v>
+        <v>6950842</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8116,27 +8116,27 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128412048</v>
+        <v>128412622</v>
       </c>
       <c r="B75" t="n">
-        <v>57685</v>
+        <v>58055</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8145,24 +8145,19 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>398329</v>
+        <v>398437</v>
       </c>
       <c r="R75" t="n">
-        <v>6950952</v>
+        <v>6951052</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8189,19 +8184,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8216,22 +8201,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128406114</v>
+        <v>128405468</v>
       </c>
       <c r="B76" t="n">
-        <v>57685</v>
+        <v>82942</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8239,39 +8224,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>398351</v>
+        <v>398405</v>
       </c>
       <c r="R76" t="n">
-        <v>6950591</v>
+        <v>6950503</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8301,19 +8281,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8328,39 +8298,39 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128412622</v>
+        <v>128412048</v>
       </c>
       <c r="B77" t="n">
-        <v>58055</v>
+        <v>57685</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8369,19 +8339,24 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>398437</v>
+        <v>398329</v>
       </c>
       <c r="R77" t="n">
-        <v>6951052</v>
+        <v>6950952</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8408,9 +8383,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8425,22 +8410,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128405468</v>
+        <v>128406114</v>
       </c>
       <c r="B78" t="n">
-        <v>82942</v>
+        <v>57685</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8448,34 +8433,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>398405</v>
+        <v>398351</v>
       </c>
       <c r="R78" t="n">
-        <v>6950503</v>
+        <v>6950591</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8505,9 +8495,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8522,12 +8522,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9121,53 +9121,49 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128411972</v>
+        <v>128404962</v>
       </c>
       <c r="B85" t="n">
-        <v>57685</v>
+        <v>57850</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>266237</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>398278</v>
+        <v>398392</v>
       </c>
       <c r="R85" t="n">
-        <v>6950881</v>
+        <v>6950406</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9194,9 +9190,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9211,19 +9217,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128407963</v>
+        <v>128411972</v>
       </c>
       <c r="B86" t="n">
         <v>57685</v>
@@ -9252,16 +9258,21 @@
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>398154</v>
+        <v>398278</v>
       </c>
       <c r="R86" t="n">
-        <v>6950756</v>
+        <v>6950881</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9291,19 +9302,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9318,61 +9319,60 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128404962</v>
+        <v>128407963</v>
       </c>
       <c r="B87" t="n">
-        <v>57850</v>
+        <v>57685</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>266237</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>398392</v>
+        <v>398154</v>
       </c>
       <c r="R87" t="n">
-        <v>6950406</v>
+        <v>6950756</v>
       </c>
       <c r="S87" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9754,10 +9754,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128405637</v>
+        <v>128413415</v>
       </c>
       <c r="B91" t="n">
-        <v>91470</v>
+        <v>79702</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9765,34 +9765,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>398426</v>
+        <v>398477</v>
       </c>
       <c r="R91" t="n">
-        <v>6950561</v>
+        <v>6951277</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9851,10 +9851,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128413415</v>
+        <v>128410197</v>
       </c>
       <c r="B92" t="n">
-        <v>79702</v>
+        <v>57685</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9862,34 +9862,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>398477</v>
+        <v>397996</v>
       </c>
       <c r="R92" t="n">
-        <v>6951277</v>
+        <v>6950884</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9919,9 +9924,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9936,19 +9951,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128410197</v>
+        <v>128411474</v>
       </c>
       <c r="B93" t="n">
         <v>57685</v>
@@ -9979,7 +9994,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -9988,10 +10003,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>397996</v>
+        <v>398202</v>
       </c>
       <c r="R93" t="n">
-        <v>6950884</v>
+        <v>6950905</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10021,19 +10036,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10048,22 +10053,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128411474</v>
+        <v>128405637</v>
       </c>
       <c r="B94" t="n">
-        <v>57685</v>
+        <v>91470</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10071,39 +10076,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>398202</v>
+        <v>398426</v>
       </c>
       <c r="R94" t="n">
-        <v>6950905</v>
+        <v>6950561</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10162,32 +10162,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128413088</v>
+        <v>128411728</v>
       </c>
       <c r="B95" t="n">
-        <v>82942</v>
+        <v>78443</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1312</v>
+        <v>498</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10197,10 +10197,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>398494</v>
+        <v>398227</v>
       </c>
       <c r="R95" t="n">
-        <v>6951141</v>
+        <v>6950881</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10259,32 +10259,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128411728</v>
+        <v>128413088</v>
       </c>
       <c r="B96" t="n">
-        <v>78443</v>
+        <v>82942</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>498</v>
+        <v>1312</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>398227</v>
+        <v>398494</v>
       </c>
       <c r="R96" t="n">
-        <v>6950881</v>
+        <v>6951141</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11608,10 +11608,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128405590</v>
+        <v>128416572</v>
       </c>
       <c r="B109" t="n">
-        <v>57685</v>
+        <v>91470</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11619,39 +11619,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>398420</v>
+        <v>398382</v>
       </c>
       <c r="R109" t="n">
-        <v>6950543</v>
+        <v>6950639</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11683,7 +11678,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11693,7 +11688,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11720,10 +11715,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128416572</v>
+        <v>128405590</v>
       </c>
       <c r="B110" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11731,34 +11726,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>398382</v>
+        <v>398420</v>
       </c>
       <c r="R110" t="n">
-        <v>6950639</v>
+        <v>6950543</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11790,7 +11790,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 32341-2025 artfynd.xlsx
+++ b/artfynd/A 32341-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128407744</v>
+        <v>128412069</v>
       </c>
       <c r="B2" t="n">
-        <v>79702</v>
+        <v>57685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398173</v>
+        <v>398298</v>
       </c>
       <c r="R2" t="n">
-        <v>6950715</v>
+        <v>6950883</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128412069</v>
+        <v>128407744</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>79702</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398298</v>
+        <v>398173</v>
       </c>
       <c r="R3" t="n">
-        <v>6950883</v>
+        <v>6950715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1369,32 +1369,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128409340</v>
+        <v>128407381</v>
       </c>
       <c r="B9" t="n">
-        <v>80217</v>
+        <v>82942</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>397997</v>
+        <v>398271</v>
       </c>
       <c r="R9" t="n">
-        <v>6950677</v>
+        <v>6950584</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1437,9 +1437,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1454,22 +1464,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128412642</v>
+        <v>128409340</v>
       </c>
       <c r="B10" t="n">
-        <v>57526</v>
+        <v>80217</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102621</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,13 +1511,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>398437</v>
+        <v>397997</v>
       </c>
       <c r="R10" t="n">
-        <v>6951052</v>
+        <v>6950677</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1563,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128407381</v>
+        <v>128407432</v>
       </c>
       <c r="B11" t="n">
-        <v>82942</v>
+        <v>57685</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,34 +1584,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>398271</v>
+        <v>398269</v>
       </c>
       <c r="R11" t="n">
-        <v>6950584</v>
+        <v>6950563</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1670,7 +1685,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128407432</v>
+        <v>128415979</v>
       </c>
       <c r="B12" t="n">
         <v>57685</v>
@@ -1710,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>398269</v>
+        <v>398372</v>
       </c>
       <c r="R12" t="n">
-        <v>6950563</v>
+        <v>6950738</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,7 +1760,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,27 +1797,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128415979</v>
+        <v>128412642</v>
       </c>
       <c r="B13" t="n">
-        <v>57685</v>
+        <v>57526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1811,24 +1826,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>398372</v>
+        <v>398437</v>
       </c>
       <c r="R13" t="n">
-        <v>6950738</v>
+        <v>6951052</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1855,19 +1865,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1882,12 +1882,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128410050</v>
+        <v>128405816</v>
       </c>
       <c r="B24" t="n">
-        <v>82942</v>
+        <v>57685</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,34 +2950,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>397967</v>
+        <v>398390</v>
       </c>
       <c r="R24" t="n">
-        <v>6950876</v>
+        <v>6950541</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3007,9 +3012,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3024,19 +3039,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128411229</v>
+        <v>128410050</v>
       </c>
       <c r="B25" t="n">
         <v>82942</v>
@@ -3071,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>398118</v>
+        <v>397967</v>
       </c>
       <c r="R25" t="n">
-        <v>6950921</v>
+        <v>6950876</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,7 +3148,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128416541</v>
+        <v>128411229</v>
       </c>
       <c r="B26" t="n">
         <v>82942</v>
@@ -3168,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>398411</v>
+        <v>398118</v>
       </c>
       <c r="R26" t="n">
-        <v>6950623</v>
+        <v>6950921</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128410205</v>
+        <v>128416541</v>
       </c>
       <c r="B27" t="n">
-        <v>75171</v>
+        <v>82942</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,21 +3256,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>397980</v>
+        <v>398411</v>
       </c>
       <c r="R27" t="n">
-        <v>6950909</v>
+        <v>6950623</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,7 +3342,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128411297</v>
+        <v>128410205</v>
       </c>
       <c r="B28" t="n">
         <v>75171</v>
@@ -3362,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>398143</v>
+        <v>397980</v>
       </c>
       <c r="R28" t="n">
-        <v>6950944</v>
+        <v>6950909</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3424,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128413330</v>
+        <v>128411297</v>
       </c>
       <c r="B29" t="n">
-        <v>78486</v>
+        <v>75171</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3435,21 +3450,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3459,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>398486</v>
+        <v>398143</v>
       </c>
       <c r="R29" t="n">
-        <v>6951242</v>
+        <v>6950944</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3521,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128405816</v>
+        <v>128413330</v>
       </c>
       <c r="B30" t="n">
-        <v>57685</v>
+        <v>78486</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3532,39 +3547,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>398390</v>
+        <v>398486</v>
       </c>
       <c r="R30" t="n">
-        <v>6950541</v>
+        <v>6951242</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3594,19 +3604,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3621,22 +3621,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128408399</v>
+        <v>128405964</v>
       </c>
       <c r="B31" t="n">
-        <v>82942</v>
+        <v>57685</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3644,34 +3644,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>398076</v>
+        <v>398364</v>
       </c>
       <c r="R31" t="n">
-        <v>6950793</v>
+        <v>6950589</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3730,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128410403</v>
+        <v>128412757</v>
       </c>
       <c r="B32" t="n">
-        <v>75171</v>
+        <v>57685</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3741,34 +3746,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>398063</v>
+        <v>398460</v>
       </c>
       <c r="R32" t="n">
-        <v>6950893</v>
+        <v>6951061</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3798,9 +3808,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3815,60 +3835,65 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128411429</v>
+        <v>128413866</v>
       </c>
       <c r="B33" t="n">
-        <v>75171</v>
+        <v>58055</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>398176</v>
+        <v>398505</v>
       </c>
       <c r="R33" t="n">
-        <v>6950885</v>
+        <v>6951279</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3895,9 +3920,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3912,22 +3947,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128411736</v>
+        <v>128408399</v>
       </c>
       <c r="B34" t="n">
-        <v>91470</v>
+        <v>82942</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3935,21 +3970,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3959,10 +3994,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>398234</v>
+        <v>398076</v>
       </c>
       <c r="R34" t="n">
-        <v>6950852</v>
+        <v>6950793</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3992,19 +4027,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4019,22 +4044,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128405964</v>
+        <v>128410403</v>
       </c>
       <c r="B35" t="n">
-        <v>57685</v>
+        <v>75171</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4042,39 +4067,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398364</v>
+        <v>398063</v>
       </c>
       <c r="R35" t="n">
-        <v>6950589</v>
+        <v>6950893</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4133,10 +4153,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128412757</v>
+        <v>128411429</v>
       </c>
       <c r="B36" t="n">
-        <v>57685</v>
+        <v>75171</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4144,39 +4164,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398460</v>
+        <v>398176</v>
       </c>
       <c r="R36" t="n">
-        <v>6951061</v>
+        <v>6950885</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4206,19 +4221,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4233,22 +4238,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128415952</v>
+        <v>128411736</v>
       </c>
       <c r="B37" t="n">
-        <v>57685</v>
+        <v>91470</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4256,39 +4261,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>398385</v>
+        <v>398234</v>
       </c>
       <c r="R37" t="n">
-        <v>6950755</v>
+        <v>6950852</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4318,9 +4318,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4335,39 +4345,39 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128413866</v>
+        <v>128415952</v>
       </c>
       <c r="B38" t="n">
-        <v>58055</v>
+        <v>57685</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4378,7 +4388,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4387,13 +4397,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>398505</v>
+        <v>398385</v>
       </c>
       <c r="R38" t="n">
-        <v>6951279</v>
+        <v>6950755</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4420,19 +4430,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4447,12 +4447,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4556,50 +4556,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128414073</v>
+        <v>128405841</v>
       </c>
       <c r="B40" t="n">
-        <v>57685</v>
+        <v>92149</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>398546</v>
+        <v>398374</v>
       </c>
       <c r="R40" t="n">
-        <v>6951235</v>
+        <v>6950548</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4658,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128412950</v>
+        <v>128415930</v>
       </c>
       <c r="B41" t="n">
-        <v>57685</v>
+        <v>79673</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4669,39 +4664,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>398483</v>
+        <v>398387</v>
       </c>
       <c r="R41" t="n">
-        <v>6951117</v>
+        <v>6950766</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4760,10 +4750,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128405841</v>
+        <v>128412193</v>
       </c>
       <c r="B42" t="n">
-        <v>92149</v>
+        <v>80223</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4771,21 +4761,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3298</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4785,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>398374</v>
+        <v>398369</v>
       </c>
       <c r="R42" t="n">
-        <v>6950548</v>
+        <v>6950956</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4857,32 +4847,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128412193</v>
+        <v>128411735</v>
       </c>
       <c r="B43" t="n">
-        <v>80223</v>
+        <v>75171</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4892,10 +4882,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>398369</v>
+        <v>398227</v>
       </c>
       <c r="R43" t="n">
-        <v>6950956</v>
+        <v>6950881</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4954,10 +4944,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128411735</v>
+        <v>128405669</v>
       </c>
       <c r="B44" t="n">
-        <v>75171</v>
+        <v>91470</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4965,21 +4955,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4989,10 +4979,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>398227</v>
+        <v>398398</v>
       </c>
       <c r="R44" t="n">
-        <v>6950881</v>
+        <v>6950569</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5051,10 +5041,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128405669</v>
+        <v>128414073</v>
       </c>
       <c r="B45" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5062,34 +5052,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>398398</v>
+        <v>398546</v>
       </c>
       <c r="R45" t="n">
-        <v>6950569</v>
+        <v>6951235</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5148,10 +5143,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128415930</v>
+        <v>128412950</v>
       </c>
       <c r="B46" t="n">
-        <v>79673</v>
+        <v>57685</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5159,34 +5154,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>398387</v>
+        <v>398483</v>
       </c>
       <c r="R46" t="n">
-        <v>6950766</v>
+        <v>6951117</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -8019,45 +8019,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128416207</v>
+        <v>128405468</v>
       </c>
       <c r="B74" t="n">
-        <v>75169</v>
+        <v>82942</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6486</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>398414</v>
+        <v>398405</v>
       </c>
       <c r="R74" t="n">
-        <v>6950702</v>
+        <v>6950503</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8116,27 +8116,27 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128412622</v>
+        <v>128412048</v>
       </c>
       <c r="B75" t="n">
-        <v>58055</v>
+        <v>57685</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8145,19 +8145,24 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>398437</v>
+        <v>398329</v>
       </c>
       <c r="R75" t="n">
-        <v>6951052</v>
+        <v>6950952</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8184,9 +8189,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8201,22 +8216,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128405468</v>
+        <v>128406114</v>
       </c>
       <c r="B76" t="n">
-        <v>82942</v>
+        <v>57685</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8224,34 +8239,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>398405</v>
+        <v>398351</v>
       </c>
       <c r="R76" t="n">
-        <v>6950503</v>
+        <v>6950591</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8281,9 +8301,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8298,39 +8328,39 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128412048</v>
+        <v>128412622</v>
       </c>
       <c r="B77" t="n">
-        <v>57685</v>
+        <v>58055</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8339,24 +8369,19 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>398329</v>
+        <v>398437</v>
       </c>
       <c r="R77" t="n">
-        <v>6950952</v>
+        <v>6951052</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8383,19 +8408,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8410,22 +8425,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128406114</v>
+        <v>128412825</v>
       </c>
       <c r="B78" t="n">
-        <v>57685</v>
+        <v>79673</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8433,39 +8448,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>398351</v>
+        <v>398474</v>
       </c>
       <c r="R78" t="n">
-        <v>6950591</v>
+        <v>6951085</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8495,19 +8505,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8522,44 +8522,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128412825</v>
+        <v>128416207</v>
       </c>
       <c r="B79" t="n">
-        <v>79673</v>
+        <v>75169</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>6486</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>398474</v>
+        <v>398414</v>
       </c>
       <c r="R79" t="n">
-        <v>6951085</v>
+        <v>6950702</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8830,10 +8830,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128407528</v>
+        <v>128411270</v>
       </c>
       <c r="B82" t="n">
-        <v>78749</v>
+        <v>78486</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8841,21 +8841,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>398225</v>
+        <v>398139</v>
       </c>
       <c r="R82" t="n">
-        <v>6950599</v>
+        <v>6950929</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8927,10 +8927,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128411270</v>
+        <v>128407528</v>
       </c>
       <c r="B83" t="n">
-        <v>78486</v>
+        <v>78749</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8938,21 +8938,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>398139</v>
+        <v>398225</v>
       </c>
       <c r="R83" t="n">
-        <v>6950929</v>
+        <v>6950599</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9024,10 +9024,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128416210</v>
+        <v>128411972</v>
       </c>
       <c r="B84" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9035,34 +9035,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>398414</v>
+        <v>398278</v>
       </c>
       <c r="R84" t="n">
-        <v>6950702</v>
+        <v>6950881</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9121,49 +9126,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128404962</v>
+        <v>128407963</v>
       </c>
       <c r="B85" t="n">
-        <v>57850</v>
+        <v>57685</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>266237</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>398392</v>
+        <v>398154</v>
       </c>
       <c r="R85" t="n">
-        <v>6950406</v>
+        <v>6950756</v>
       </c>
       <c r="S85" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9229,10 +9233,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128411972</v>
+        <v>128416210</v>
       </c>
       <c r="B86" t="n">
-        <v>57685</v>
+        <v>91470</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9240,39 +9244,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>398278</v>
+        <v>398414</v>
       </c>
       <c r="R86" t="n">
-        <v>6950881</v>
+        <v>6950702</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9331,48 +9330,49 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128407963</v>
+        <v>128404962</v>
       </c>
       <c r="B87" t="n">
-        <v>57685</v>
+        <v>57850</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>266237</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>398154</v>
+        <v>398392</v>
       </c>
       <c r="R87" t="n">
-        <v>6950756</v>
+        <v>6950406</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10550,10 +10550,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128413083</v>
+        <v>128413296</v>
       </c>
       <c r="B99" t="n">
-        <v>75171</v>
+        <v>79673</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10561,21 +10561,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10585,10 +10585,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>398494</v>
+        <v>398463</v>
       </c>
       <c r="R99" t="n">
-        <v>6951141</v>
+        <v>6951234</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10647,10 +10647,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128413214</v>
+        <v>128407903</v>
       </c>
       <c r="B100" t="n">
-        <v>57685</v>
+        <v>81088</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10658,39 +10658,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>229436</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Halmgul örnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ochrolechia alboflavescens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wulfen) Zahlbr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>398467</v>
+        <v>398154</v>
       </c>
       <c r="R100" t="n">
-        <v>6951207</v>
+        <v>6950756</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10720,9 +10715,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10737,22 +10742,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128415580</v>
+        <v>128413083</v>
       </c>
       <c r="B101" t="n">
-        <v>57685</v>
+        <v>75171</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10760,39 +10765,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>398442</v>
+        <v>398494</v>
       </c>
       <c r="R101" t="n">
-        <v>6950833</v>
+        <v>6951141</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10851,10 +10851,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128413296</v>
+        <v>128413214</v>
       </c>
       <c r="B102" t="n">
-        <v>79673</v>
+        <v>57685</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10862,34 +10862,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>398463</v>
+        <v>398467</v>
       </c>
       <c r="R102" t="n">
-        <v>6951234</v>
+        <v>6951207</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10948,10 +10953,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128407903</v>
+        <v>128415580</v>
       </c>
       <c r="B103" t="n">
-        <v>81088</v>
+        <v>57685</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10959,34 +10964,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229436</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Halmgul örnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ochrolechia alboflavescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Wulfen) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>398154</v>
+        <v>398442</v>
       </c>
       <c r="R103" t="n">
-        <v>6950756</v>
+        <v>6950833</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11016,19 +11026,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11043,12 +11043,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>

--- a/artfynd/A 32341-2025 artfynd.xlsx
+++ b/artfynd/A 32341-2025 artfynd.xlsx
@@ -6785,10 +6785,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128409691</v>
+        <v>128407307</v>
       </c>
       <c r="B62" t="n">
-        <v>90485</v>
+        <v>78841</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6796,21 +6796,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6820,10 +6820,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>398057</v>
+        <v>398263</v>
       </c>
       <c r="R62" t="n">
-        <v>6950739</v>
+        <v>6950596</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6853,19 +6853,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6880,22 +6870,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128407307</v>
+        <v>128415706</v>
       </c>
       <c r="B63" t="n">
-        <v>78841</v>
+        <v>57685</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6903,34 +6893,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>398263</v>
+        <v>398411</v>
       </c>
       <c r="R63" t="n">
-        <v>6950596</v>
+        <v>6950796</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6989,10 +6984,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128406318</v>
+        <v>128416501</v>
       </c>
       <c r="B64" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7000,34 +6995,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>398333</v>
+        <v>398382</v>
       </c>
       <c r="R64" t="n">
-        <v>6950603</v>
+        <v>6950639</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7057,9 +7057,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7074,22 +7084,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128415836</v>
+        <v>128409691</v>
       </c>
       <c r="B65" t="n">
-        <v>78055</v>
+        <v>90485</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7097,21 +7107,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6487</v>
+        <v>1962</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7121,10 +7131,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>398394</v>
+        <v>398057</v>
       </c>
       <c r="R65" t="n">
-        <v>6950811</v>
+        <v>6950739</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7156,7 +7166,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7166,7 +7176,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7193,10 +7203,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128406026</v>
+        <v>128406318</v>
       </c>
       <c r="B66" t="n">
-        <v>79702</v>
+        <v>79083</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7204,21 +7214,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7228,10 +7238,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>398364</v>
+        <v>398333</v>
       </c>
       <c r="R66" t="n">
-        <v>6950589</v>
+        <v>6950603</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7290,10 +7300,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128415706</v>
+        <v>128415836</v>
       </c>
       <c r="B67" t="n">
-        <v>57685</v>
+        <v>78055</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7301,39 +7311,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>398411</v>
+        <v>398394</v>
       </c>
       <c r="R67" t="n">
-        <v>6950796</v>
+        <v>6950811</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7363,9 +7368,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7380,22 +7395,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128416501</v>
+        <v>128406026</v>
       </c>
       <c r="B68" t="n">
-        <v>57685</v>
+        <v>79702</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7403,39 +7418,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>398382</v>
+        <v>398364</v>
       </c>
       <c r="R68" t="n">
-        <v>6950639</v>
+        <v>6950589</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7465,19 +7475,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7492,12 +7492,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8019,45 +8019,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128405468</v>
+        <v>128416207</v>
       </c>
       <c r="B74" t="n">
-        <v>82942</v>
+        <v>75169</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>6486</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>398405</v>
+        <v>398414</v>
       </c>
       <c r="R74" t="n">
-        <v>6950503</v>
+        <v>6950702</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8116,27 +8116,27 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128412048</v>
+        <v>128412622</v>
       </c>
       <c r="B75" t="n">
-        <v>57685</v>
+        <v>58055</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8145,24 +8145,19 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>398329</v>
+        <v>398437</v>
       </c>
       <c r="R75" t="n">
-        <v>6950952</v>
+        <v>6951052</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8189,19 +8184,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8216,22 +8201,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128406114</v>
+        <v>128405468</v>
       </c>
       <c r="B76" t="n">
-        <v>57685</v>
+        <v>82942</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8239,39 +8224,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>398351</v>
+        <v>398405</v>
       </c>
       <c r="R76" t="n">
-        <v>6950591</v>
+        <v>6950503</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8301,19 +8281,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8328,39 +8298,39 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128412622</v>
+        <v>128412048</v>
       </c>
       <c r="B77" t="n">
-        <v>58055</v>
+        <v>57685</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8369,19 +8339,24 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>398437</v>
+        <v>398329</v>
       </c>
       <c r="R77" t="n">
-        <v>6951052</v>
+        <v>6950952</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8408,9 +8383,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8425,22 +8410,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128412825</v>
+        <v>128406114</v>
       </c>
       <c r="B78" t="n">
-        <v>79673</v>
+        <v>57685</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8448,34 +8433,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>398474</v>
+        <v>398351</v>
       </c>
       <c r="R78" t="n">
-        <v>6951085</v>
+        <v>6950591</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8505,9 +8495,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8522,44 +8522,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128416207</v>
+        <v>128412825</v>
       </c>
       <c r="B79" t="n">
-        <v>75169</v>
+        <v>79673</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6486</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>398414</v>
+        <v>398474</v>
       </c>
       <c r="R79" t="n">
-        <v>6950702</v>
+        <v>6951085</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -11058,7 +11058,7 @@
         <v>128411857</v>
       </c>
       <c r="B104" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>128406215</v>
       </c>
       <c r="B105" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>128405961</v>
       </c>
       <c r="B106" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>128408249</v>
       </c>
       <c r="B107" t="n">
-        <v>78443</v>
+        <v>78447</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>128408651</v>
       </c>
       <c r="B108" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>128416572</v>
       </c>
       <c r="B109" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>128405590</v>
       </c>
       <c r="B110" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>128414034</v>
       </c>
       <c r="B111" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>128413146</v>
       </c>
       <c r="B112" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>128413351</v>
       </c>
       <c r="B113" t="n">
-        <v>79673</v>
+        <v>79677</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 32341-2025 artfynd.xlsx
+++ b/artfynd/A 32341-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128412069</v>
       </c>
       <c r="B2" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128407744</v>
+        <v>128413409</v>
       </c>
       <c r="B3" t="n">
-        <v>79702</v>
+        <v>79677</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398173</v>
+        <v>398477</v>
       </c>
       <c r="R3" t="n">
-        <v>6950715</v>
+        <v>6951277</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128413409</v>
+        <v>128407744</v>
       </c>
       <c r="B4" t="n">
-        <v>79673</v>
+        <v>79706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398477</v>
+        <v>398173</v>
       </c>
       <c r="R4" t="n">
-        <v>6951277</v>
+        <v>6950715</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
         <v>128412732</v>
       </c>
       <c r="B5" t="n">
-        <v>79178</v>
+        <v>79182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128415689</v>
       </c>
       <c r="B6" t="n">
-        <v>78486</v>
+        <v>78490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>128412850</v>
       </c>
       <c r="B7" t="n">
-        <v>78486</v>
+        <v>78490</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>128411332</v>
       </c>
       <c r="B8" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,32 +1369,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128407381</v>
+        <v>128409340</v>
       </c>
       <c r="B9" t="n">
-        <v>82942</v>
+        <v>80221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>398271</v>
+        <v>397997</v>
       </c>
       <c r="R9" t="n">
-        <v>6950584</v>
+        <v>6950677</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1437,19 +1437,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1464,44 +1454,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128409340</v>
+        <v>128407381</v>
       </c>
       <c r="B10" t="n">
-        <v>80217</v>
+        <v>82946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>397997</v>
+        <v>398271</v>
       </c>
       <c r="R10" t="n">
-        <v>6950677</v>
+        <v>6950584</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,9 +1534,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1561,12 +1561,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1576,7 +1576,7 @@
         <v>128407432</v>
       </c>
       <c r="B11" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128415979</v>
       </c>
       <c r="B12" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>128412642</v>
       </c>
       <c r="B13" t="n">
-        <v>57526</v>
+        <v>57530</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1894,10 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128407947</v>
+        <v>128415142</v>
       </c>
       <c r="B14" t="n">
-        <v>82942</v>
+        <v>57689</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1905,34 +1905,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>398154</v>
+        <v>398352</v>
       </c>
       <c r="R14" t="n">
-        <v>6950756</v>
+        <v>6950954</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,7 +1969,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1974,7 +1979,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128411782</v>
+        <v>128410559</v>
       </c>
       <c r="B15" t="n">
-        <v>75171</v>
+        <v>57689</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2012,34 +2017,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>398234</v>
+        <v>398097</v>
       </c>
       <c r="R15" t="n">
-        <v>6950852</v>
+        <v>6950870</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128410038</v>
+        <v>128407947</v>
       </c>
       <c r="B16" t="n">
-        <v>75171</v>
+        <v>82946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>397967</v>
+        <v>398154</v>
       </c>
       <c r="R16" t="n">
-        <v>6950876</v>
+        <v>6950756</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2176,9 +2186,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2193,22 +2213,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128415142</v>
+        <v>128411782</v>
       </c>
       <c r="B17" t="n">
-        <v>57685</v>
+        <v>75175</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,39 +2236,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>398352</v>
+        <v>398234</v>
       </c>
       <c r="R17" t="n">
-        <v>6950954</v>
+        <v>6950852</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128410559</v>
+        <v>128410038</v>
       </c>
       <c r="B18" t="n">
-        <v>57685</v>
+        <v>75175</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,39 +2343,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>398097</v>
+        <v>397967</v>
       </c>
       <c r="R18" t="n">
-        <v>6950870</v>
+        <v>6950876</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2390,19 +2400,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2417,22 +2417,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128415681</v>
+        <v>128415613</v>
       </c>
       <c r="B19" t="n">
-        <v>79673</v>
+        <v>78753</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2440,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>398394</v>
+        <v>398437</v>
       </c>
       <c r="R19" t="n">
-        <v>6950811</v>
+        <v>6950808</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2497,19 +2497,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2524,22 +2514,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128415613</v>
+        <v>128415681</v>
       </c>
       <c r="B20" t="n">
-        <v>78749</v>
+        <v>79677</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>398437</v>
+        <v>398394</v>
       </c>
       <c r="R20" t="n">
-        <v>6950808</v>
+        <v>6950811</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2604,9 +2594,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2621,22 +2621,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128408059</v>
+        <v>128415804</v>
       </c>
       <c r="B21" t="n">
-        <v>57685</v>
+        <v>78490</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,39 +2644,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>398146</v>
+        <v>398394</v>
       </c>
       <c r="R21" t="n">
-        <v>6950784</v>
+        <v>6950811</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2706,9 +2701,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2723,22 +2728,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128415804</v>
+        <v>128410565</v>
       </c>
       <c r="B22" t="n">
-        <v>78486</v>
+        <v>75175</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2746,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>398394</v>
+        <v>398088</v>
       </c>
       <c r="R22" t="n">
-        <v>6950811</v>
+        <v>6950909</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2803,19 +2808,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2830,22 +2825,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128410565</v>
+        <v>128408059</v>
       </c>
       <c r="B23" t="n">
-        <v>75171</v>
+        <v>57689</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,34 +2848,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>398088</v>
+        <v>398146</v>
       </c>
       <c r="R23" t="n">
-        <v>6950909</v>
+        <v>6950784</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128405816</v>
+        <v>128410050</v>
       </c>
       <c r="B24" t="n">
-        <v>57685</v>
+        <v>82946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,39 +2950,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>398390</v>
+        <v>397967</v>
       </c>
       <c r="R24" t="n">
-        <v>6950541</v>
+        <v>6950876</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3012,19 +3007,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3039,22 +3024,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128410050</v>
+        <v>128411229</v>
       </c>
       <c r="B25" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3086,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>397967</v>
+        <v>398118</v>
       </c>
       <c r="R25" t="n">
-        <v>6950876</v>
+        <v>6950921</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128411229</v>
+        <v>128416541</v>
       </c>
       <c r="B26" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3183,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>398118</v>
+        <v>398411</v>
       </c>
       <c r="R26" t="n">
-        <v>6950921</v>
+        <v>6950623</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128416541</v>
+        <v>128410205</v>
       </c>
       <c r="B27" t="n">
-        <v>82942</v>
+        <v>75175</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3256,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3280,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>398411</v>
+        <v>397980</v>
       </c>
       <c r="R27" t="n">
-        <v>6950623</v>
+        <v>6950909</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128410205</v>
+        <v>128411297</v>
       </c>
       <c r="B28" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3377,10 +3362,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>397980</v>
+        <v>398143</v>
       </c>
       <c r="R28" t="n">
-        <v>6950909</v>
+        <v>6950944</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3424,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128411297</v>
+        <v>128413330</v>
       </c>
       <c r="B29" t="n">
-        <v>75171</v>
+        <v>78490</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3450,21 +3435,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3474,10 +3459,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>398143</v>
+        <v>398486</v>
       </c>
       <c r="R29" t="n">
-        <v>6950944</v>
+        <v>6951242</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,10 +3521,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128413330</v>
+        <v>128405816</v>
       </c>
       <c r="B30" t="n">
-        <v>78486</v>
+        <v>57689</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3547,34 +3532,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>398486</v>
+        <v>398390</v>
       </c>
       <c r="R30" t="n">
-        <v>6951242</v>
+        <v>6950541</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3604,9 +3594,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3621,22 +3621,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128405964</v>
+        <v>128408399</v>
       </c>
       <c r="B31" t="n">
-        <v>57685</v>
+        <v>82946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3644,39 +3644,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>398364</v>
+        <v>398076</v>
       </c>
       <c r="R31" t="n">
-        <v>6950589</v>
+        <v>6950793</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3730,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128412757</v>
+        <v>128405964</v>
       </c>
       <c r="B32" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3766,7 +3761,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3775,10 +3770,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>398460</v>
+        <v>398364</v>
       </c>
       <c r="R32" t="n">
-        <v>6951061</v>
+        <v>6950589</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3808,19 +3803,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3835,39 +3820,39 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128413866</v>
+        <v>128412757</v>
       </c>
       <c r="B33" t="n">
-        <v>58055</v>
+        <v>57689</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3878,7 +3863,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3887,13 +3872,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>398505</v>
+        <v>398460</v>
       </c>
       <c r="R33" t="n">
-        <v>6951279</v>
+        <v>6951061</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3959,10 +3944,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128408399</v>
+        <v>128415952</v>
       </c>
       <c r="B34" t="n">
-        <v>82942</v>
+        <v>57689</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3970,34 +3955,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>398076</v>
+        <v>398385</v>
       </c>
       <c r="R34" t="n">
-        <v>6950793</v>
+        <v>6950755</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4056,10 +4046,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128410403</v>
+        <v>128411736</v>
       </c>
       <c r="B35" t="n">
-        <v>75171</v>
+        <v>91482</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4067,21 +4057,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4091,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398063</v>
+        <v>398234</v>
       </c>
       <c r="R35" t="n">
-        <v>6950893</v>
+        <v>6950852</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4124,9 +4114,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4141,22 +4141,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128411429</v>
+        <v>128410403</v>
       </c>
       <c r="B36" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398176</v>
+        <v>398063</v>
       </c>
       <c r="R36" t="n">
-        <v>6950885</v>
+        <v>6950893</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4250,10 +4250,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128411736</v>
+        <v>128411429</v>
       </c>
       <c r="B37" t="n">
-        <v>91470</v>
+        <v>75175</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4261,21 +4261,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>398234</v>
+        <v>398176</v>
       </c>
       <c r="R37" t="n">
-        <v>6950852</v>
+        <v>6950885</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4318,19 +4318,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4345,39 +4335,39 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128415952</v>
+        <v>128413866</v>
       </c>
       <c r="B38" t="n">
-        <v>57685</v>
+        <v>58059</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4388,7 +4378,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4397,13 +4387,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>398385</v>
+        <v>398505</v>
       </c>
       <c r="R38" t="n">
-        <v>6950755</v>
+        <v>6951279</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4430,9 +4420,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4447,12 +4447,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4462,7 +4462,7 @@
         <v>128416366</v>
       </c>
       <c r="B39" t="n">
-        <v>78443</v>
+        <v>78447</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4556,32 +4556,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128405841</v>
+        <v>128405669</v>
       </c>
       <c r="B40" t="n">
-        <v>92149</v>
+        <v>91482</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>398374</v>
+        <v>398398</v>
       </c>
       <c r="R40" t="n">
-        <v>6950548</v>
+        <v>6950569</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4656,7 +4656,7 @@
         <v>128415930</v>
       </c>
       <c r="B41" t="n">
-        <v>79673</v>
+        <v>79677</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>128412193</v>
       </c>
       <c r="B42" t="n">
-        <v>80223</v>
+        <v>80227</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>128411735</v>
       </c>
       <c r="B43" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4944,10 +4944,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128405669</v>
+        <v>128414073</v>
       </c>
       <c r="B44" t="n">
-        <v>91470</v>
+        <v>57689</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4955,34 +4955,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>398398</v>
+        <v>398546</v>
       </c>
       <c r="R44" t="n">
-        <v>6950569</v>
+        <v>6951235</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5041,10 +5046,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128414073</v>
+        <v>128412950</v>
       </c>
       <c r="B45" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5081,10 +5086,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>398546</v>
+        <v>398483</v>
       </c>
       <c r="R45" t="n">
-        <v>6951235</v>
+        <v>6951117</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5143,50 +5148,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128412950</v>
+        <v>128405841</v>
       </c>
       <c r="B46" t="n">
-        <v>57685</v>
+        <v>92161</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>398483</v>
+        <v>398374</v>
       </c>
       <c r="R46" t="n">
-        <v>6951117</v>
+        <v>6950548</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5245,10 +5245,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128408097</v>
+        <v>128407293</v>
       </c>
       <c r="B47" t="n">
-        <v>57845</v>
+        <v>79706</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5256,42 +5256,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>398159</v>
+        <v>398263</v>
       </c>
       <c r="R47" t="n">
-        <v>6950801</v>
+        <v>6950596</v>
       </c>
       <c r="S47" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5318,19 +5313,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5345,44 +5330,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128412638</v>
+        <v>128415932</v>
       </c>
       <c r="B48" t="n">
-        <v>57789</v>
+        <v>79706</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5392,13 +5377,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>398437</v>
+        <v>398387</v>
       </c>
       <c r="R48" t="n">
-        <v>6951052</v>
+        <v>6950766</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5454,10 +5439,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128407293</v>
+        <v>128411964</v>
       </c>
       <c r="B49" t="n">
-        <v>79702</v>
+        <v>91482</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5465,21 +5450,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5489,10 +5474,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>398263</v>
+        <v>398278</v>
       </c>
       <c r="R49" t="n">
-        <v>6950596</v>
+        <v>6950881</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5551,10 +5536,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128410408</v>
+        <v>128406327</v>
       </c>
       <c r="B50" t="n">
-        <v>79083</v>
+        <v>91482</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5562,21 +5547,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5586,10 +5571,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>398063</v>
+        <v>398333</v>
       </c>
       <c r="R50" t="n">
-        <v>6950893</v>
+        <v>6950603</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5648,10 +5633,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128415932</v>
+        <v>128410408</v>
       </c>
       <c r="B51" t="n">
-        <v>79702</v>
+        <v>79087</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5659,21 +5644,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5683,10 +5668,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>398387</v>
+        <v>398063</v>
       </c>
       <c r="R51" t="n">
-        <v>6950766</v>
+        <v>6950893</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5745,10 +5730,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128406327</v>
+        <v>128412677</v>
       </c>
       <c r="B52" t="n">
-        <v>91470</v>
+        <v>57689</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5756,34 +5741,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>398333</v>
+        <v>398462</v>
       </c>
       <c r="R52" t="n">
-        <v>6950603</v>
+        <v>6951039</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5813,9 +5803,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5830,22 +5830,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128411964</v>
+        <v>128415972</v>
       </c>
       <c r="B53" t="n">
-        <v>91470</v>
+        <v>57689</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5853,34 +5853,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>398278</v>
+        <v>398396</v>
       </c>
       <c r="R53" t="n">
-        <v>6950881</v>
+        <v>6950719</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5939,27 +5944,27 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128412677</v>
+        <v>128412638</v>
       </c>
       <c r="B54" t="n">
-        <v>57685</v>
+        <v>57793</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5968,24 +5973,19 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>398462</v>
+        <v>398437</v>
       </c>
       <c r="R54" t="n">
-        <v>6951039</v>
+        <v>6951052</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6012,19 +6012,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6039,22 +6029,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128415972</v>
+        <v>128408097</v>
       </c>
       <c r="B55" t="n">
-        <v>57685</v>
+        <v>57849</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6062,27 +6052,27 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6091,13 +6081,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>398396</v>
+        <v>398159</v>
       </c>
       <c r="R55" t="n">
-        <v>6950719</v>
+        <v>6950801</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6124,9 +6114,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6141,60 +6141,65 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128408521</v>
+        <v>128413955</v>
       </c>
       <c r="B56" t="n">
-        <v>79702</v>
+        <v>57530</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>102621</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>398019</v>
+        <v>398517</v>
       </c>
       <c r="R56" t="n">
-        <v>6950740</v>
+        <v>6951283</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6250,53 +6255,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128408773</v>
+        <v>128408521</v>
       </c>
       <c r="B57" t="n">
-        <v>58055</v>
+        <v>79706</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>398012</v>
+        <v>398019</v>
       </c>
       <c r="R57" t="n">
-        <v>6950659</v>
+        <v>6950740</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6323,19 +6323,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6350,12 +6340,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6365,7 +6355,7 @@
         <v>128405859</v>
       </c>
       <c r="B58" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6477,7 +6467,7 @@
         <v>128413307</v>
       </c>
       <c r="B59" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6586,10 +6576,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128413955</v>
+        <v>128408773</v>
       </c>
       <c r="B60" t="n">
-        <v>57526</v>
+        <v>58059</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6597,16 +6587,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102621</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6617,7 +6607,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6626,10 +6616,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>398517</v>
+        <v>398012</v>
       </c>
       <c r="R60" t="n">
-        <v>6951283</v>
+        <v>6950659</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -6659,9 +6649,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6676,12 +6676,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6691,7 +6691,7 @@
         <v>128409775</v>
       </c>
       <c r="B61" t="n">
-        <v>79673</v>
+        <v>79677</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6785,10 +6785,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128407307</v>
+        <v>128406318</v>
       </c>
       <c r="B62" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6796,21 +6796,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6820,10 +6820,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>398263</v>
+        <v>398333</v>
       </c>
       <c r="R62" t="n">
-        <v>6950596</v>
+        <v>6950603</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6882,10 +6882,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128415706</v>
+        <v>128415836</v>
       </c>
       <c r="B63" t="n">
-        <v>57685</v>
+        <v>78059</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6893,39 +6893,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>398411</v>
+        <v>398394</v>
       </c>
       <c r="R63" t="n">
-        <v>6950796</v>
+        <v>6950811</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6955,9 +6950,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6972,22 +6977,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128416501</v>
+        <v>128406026</v>
       </c>
       <c r="B64" t="n">
-        <v>57685</v>
+        <v>79706</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6995,39 +7000,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>398382</v>
+        <v>398364</v>
       </c>
       <c r="R64" t="n">
-        <v>6950639</v>
+        <v>6950589</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7057,19 +7057,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7084,22 +7074,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128409691</v>
+        <v>128415706</v>
       </c>
       <c r="B65" t="n">
-        <v>90485</v>
+        <v>57689</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7107,34 +7097,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>398057</v>
+        <v>398411</v>
       </c>
       <c r="R65" t="n">
-        <v>6950739</v>
+        <v>6950796</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7164,19 +7159,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7191,22 +7176,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128406318</v>
+        <v>128416501</v>
       </c>
       <c r="B66" t="n">
-        <v>79083</v>
+        <v>57689</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7214,34 +7199,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>398333</v>
+        <v>398382</v>
       </c>
       <c r="R66" t="n">
-        <v>6950603</v>
+        <v>6950639</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7271,9 +7261,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7288,22 +7288,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128415836</v>
+        <v>128407307</v>
       </c>
       <c r="B67" t="n">
-        <v>78055</v>
+        <v>78845</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7311,21 +7311,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7335,10 +7335,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>398394</v>
+        <v>398263</v>
       </c>
       <c r="R67" t="n">
-        <v>6950811</v>
+        <v>6950596</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7368,19 +7368,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7395,22 +7385,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128406026</v>
+        <v>128409691</v>
       </c>
       <c r="B68" t="n">
-        <v>79702</v>
+        <v>90497</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7418,21 +7408,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7442,10 +7432,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>398364</v>
+        <v>398057</v>
       </c>
       <c r="R68" t="n">
-        <v>6950589</v>
+        <v>6950739</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7475,9 +7465,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7492,22 +7492,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128411612</v>
+        <v>128411308</v>
       </c>
       <c r="B69" t="n">
-        <v>79162</v>
+        <v>75175</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7515,21 +7515,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7539,10 +7539,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>398200</v>
+        <v>398162</v>
       </c>
       <c r="R69" t="n">
-        <v>6950918</v>
+        <v>6950923</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7601,10 +7601,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128411308</v>
+        <v>128411524</v>
       </c>
       <c r="B70" t="n">
-        <v>75171</v>
+        <v>57689</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7612,34 +7612,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>398162</v>
+        <v>398203</v>
       </c>
       <c r="R70" t="n">
-        <v>6950923</v>
+        <v>6950901</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7669,9 +7674,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7686,22 +7701,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128411931</v>
+        <v>128411180</v>
       </c>
       <c r="B71" t="n">
-        <v>91470</v>
+        <v>57689</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7709,34 +7724,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>398276</v>
+        <v>398102</v>
       </c>
       <c r="R71" t="n">
-        <v>6950842</v>
+        <v>6950907</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7766,9 +7786,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7783,22 +7813,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128411524</v>
+        <v>128411612</v>
       </c>
       <c r="B72" t="n">
-        <v>57685</v>
+        <v>79166</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7806,39 +7836,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>398203</v>
+        <v>398200</v>
       </c>
       <c r="R72" t="n">
-        <v>6950901</v>
+        <v>6950918</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7868,19 +7893,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7895,22 +7910,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128411180</v>
+        <v>128411931</v>
       </c>
       <c r="B73" t="n">
-        <v>57685</v>
+        <v>91482</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7918,39 +7933,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>398102</v>
+        <v>398276</v>
       </c>
       <c r="R73" t="n">
-        <v>6950907</v>
+        <v>6950842</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7980,19 +7990,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8007,12 +8007,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8022,7 +8022,7 @@
         <v>128416207</v>
       </c>
       <c r="B74" t="n">
-        <v>75169</v>
+        <v>75173</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8116,32 +8116,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128412622</v>
+        <v>128412825</v>
       </c>
       <c r="B75" t="n">
-        <v>58055</v>
+        <v>79677</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>398437</v>
+        <v>398474</v>
       </c>
       <c r="R75" t="n">
-        <v>6951052</v>
+        <v>6951085</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>128405468</v>
       </c>
       <c r="B76" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>128412048</v>
       </c>
       <c r="B77" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
         <v>128406114</v>
       </c>
       <c r="B78" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8534,32 +8534,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128412825</v>
+        <v>128412622</v>
       </c>
       <c r="B79" t="n">
-        <v>79673</v>
+        <v>58059</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8569,13 +8569,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>398474</v>
+        <v>398437</v>
       </c>
       <c r="R79" t="n">
-        <v>6951085</v>
+        <v>6951052</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>128411329</v>
       </c>
       <c r="B80" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>128405900</v>
       </c>
       <c r="B81" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8830,10 +8830,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128411270</v>
+        <v>128407528</v>
       </c>
       <c r="B82" t="n">
-        <v>78486</v>
+        <v>78753</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8841,21 +8841,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>398139</v>
+        <v>398225</v>
       </c>
       <c r="R82" t="n">
-        <v>6950929</v>
+        <v>6950599</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8927,10 +8927,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128407528</v>
+        <v>128411270</v>
       </c>
       <c r="B83" t="n">
-        <v>78749</v>
+        <v>78490</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8938,21 +8938,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>398225</v>
+        <v>398139</v>
       </c>
       <c r="R83" t="n">
-        <v>6950599</v>
+        <v>6950929</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9024,53 +9024,49 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128411972</v>
+        <v>128404962</v>
       </c>
       <c r="B84" t="n">
-        <v>57685</v>
+        <v>57854</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>266237</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>398278</v>
+        <v>398392</v>
       </c>
       <c r="R84" t="n">
-        <v>6950881</v>
+        <v>6950406</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9097,9 +9093,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9114,22 +9120,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128407963</v>
+        <v>128416210</v>
       </c>
       <c r="B85" t="n">
-        <v>57685</v>
+        <v>91482</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9137,21 +9143,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9161,10 +9167,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>398154</v>
+        <v>398414</v>
       </c>
       <c r="R85" t="n">
-        <v>6950756</v>
+        <v>6950702</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9194,19 +9200,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9221,22 +9217,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128416210</v>
+        <v>128411972</v>
       </c>
       <c r="B86" t="n">
-        <v>91470</v>
+        <v>57689</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9244,34 +9240,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>398414</v>
+        <v>398278</v>
       </c>
       <c r="R86" t="n">
-        <v>6950702</v>
+        <v>6950881</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9330,49 +9331,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128404962</v>
+        <v>128407963</v>
       </c>
       <c r="B87" t="n">
-        <v>57850</v>
+        <v>57689</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>266237</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>398392</v>
+        <v>398154</v>
       </c>
       <c r="R87" t="n">
-        <v>6950406</v>
+        <v>6950756</v>
       </c>
       <c r="S87" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>128410048</v>
       </c>
       <c r="B88" t="n">
-        <v>78443</v>
+        <v>78447</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>128415905</v>
       </c>
       <c r="B89" t="n">
-        <v>78486</v>
+        <v>78490</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>128407736</v>
       </c>
       <c r="B90" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9754,10 +9754,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128413415</v>
+        <v>128405637</v>
       </c>
       <c r="B91" t="n">
-        <v>79702</v>
+        <v>91482</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9765,34 +9765,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>398477</v>
+        <v>398426</v>
       </c>
       <c r="R91" t="n">
-        <v>6951277</v>
+        <v>6950561</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9851,10 +9851,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128410197</v>
+        <v>128413415</v>
       </c>
       <c r="B92" t="n">
-        <v>57685</v>
+        <v>79706</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9862,39 +9862,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>397996</v>
+        <v>398477</v>
       </c>
       <c r="R92" t="n">
-        <v>6950884</v>
+        <v>6951277</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9924,19 +9919,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9951,22 +9936,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128411474</v>
+        <v>128410197</v>
       </c>
       <c r="B93" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9994,7 +9979,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10003,10 +9988,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>398202</v>
+        <v>397996</v>
       </c>
       <c r="R93" t="n">
-        <v>6950905</v>
+        <v>6950884</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10036,9 +10021,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10053,22 +10048,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128405637</v>
+        <v>128411474</v>
       </c>
       <c r="B94" t="n">
-        <v>91470</v>
+        <v>57689</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10076,34 +10071,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>398426</v>
+        <v>398202</v>
       </c>
       <c r="R94" t="n">
-        <v>6950561</v>
+        <v>6950905</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10162,32 +10162,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128411728</v>
+        <v>128413088</v>
       </c>
       <c r="B95" t="n">
-        <v>78443</v>
+        <v>82946</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>498</v>
+        <v>1312</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10197,10 +10197,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>398227</v>
+        <v>398494</v>
       </c>
       <c r="R95" t="n">
-        <v>6950881</v>
+        <v>6951141</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10259,32 +10259,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128413088</v>
+        <v>128411728</v>
       </c>
       <c r="B96" t="n">
-        <v>82942</v>
+        <v>78447</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1312</v>
+        <v>498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>398494</v>
+        <v>398227</v>
       </c>
       <c r="R96" t="n">
-        <v>6951141</v>
+        <v>6950881</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10359,7 +10359,7 @@
         <v>128410472</v>
       </c>
       <c r="B97" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>128407311</v>
       </c>
       <c r="B98" t="n">
-        <v>78486</v>
+        <v>78490</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10550,10 +10550,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128413296</v>
+        <v>128413214</v>
       </c>
       <c r="B99" t="n">
-        <v>79673</v>
+        <v>57689</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10561,34 +10561,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>398463</v>
+        <v>398467</v>
       </c>
       <c r="R99" t="n">
-        <v>6951234</v>
+        <v>6951207</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10647,10 +10652,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128407903</v>
+        <v>128415580</v>
       </c>
       <c r="B100" t="n">
-        <v>81088</v>
+        <v>57689</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10658,34 +10663,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229436</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Halmgul örnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ochrolechia alboflavescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Wulfen) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>398154</v>
+        <v>398442</v>
       </c>
       <c r="R100" t="n">
-        <v>6950756</v>
+        <v>6950833</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10715,19 +10725,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10742,22 +10742,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128413083</v>
+        <v>128413296</v>
       </c>
       <c r="B101" t="n">
-        <v>75171</v>
+        <v>79677</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10765,21 +10765,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10789,10 +10789,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>398494</v>
+        <v>398463</v>
       </c>
       <c r="R101" t="n">
-        <v>6951141</v>
+        <v>6951234</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10851,10 +10851,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128413214</v>
+        <v>128407903</v>
       </c>
       <c r="B102" t="n">
-        <v>57685</v>
+        <v>81092</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10862,39 +10862,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>229436</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Halmgul örnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ochrolechia alboflavescens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wulfen) Zahlbr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>398467</v>
+        <v>398154</v>
       </c>
       <c r="R102" t="n">
-        <v>6951207</v>
+        <v>6950756</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10924,9 +10919,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10941,22 +10946,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128415580</v>
+        <v>128413083</v>
       </c>
       <c r="B103" t="n">
-        <v>57685</v>
+        <v>75175</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10964,39 +10969,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>398442</v>
+        <v>398494</v>
       </c>
       <c r="R103" t="n">
-        <v>6950833</v>
+        <v>6951141</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11504,7 +11504,7 @@
         <v>128408651</v>
       </c>
       <c r="B108" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>128416572</v>
       </c>
       <c r="B109" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>

--- a/artfynd/A 32341-2025 artfynd.xlsx
+++ b/artfynd/A 32341-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128412069</v>
+        <v>128407744</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
+        <v>79706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398298</v>
+        <v>398173</v>
       </c>
       <c r="R2" t="n">
-        <v>6950883</v>
+        <v>6950715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128413409</v>
+        <v>128412069</v>
       </c>
       <c r="B3" t="n">
-        <v>79677</v>
+        <v>57689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398477</v>
+        <v>398298</v>
       </c>
       <c r="R3" t="n">
-        <v>6951277</v>
+        <v>6950883</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128407744</v>
+        <v>128413409</v>
       </c>
       <c r="B4" t="n">
-        <v>79706</v>
+        <v>79677</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398173</v>
+        <v>398477</v>
       </c>
       <c r="R4" t="n">
-        <v>6950715</v>
+        <v>6951277</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1369,45 +1369,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128409340</v>
+        <v>128407432</v>
       </c>
       <c r="B9" t="n">
-        <v>80221</v>
+        <v>57689</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>397997</v>
+        <v>398269</v>
       </c>
       <c r="R9" t="n">
-        <v>6950677</v>
+        <v>6950563</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1437,9 +1442,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1454,22 +1469,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128407381</v>
+        <v>128415979</v>
       </c>
       <c r="B10" t="n">
-        <v>82946</v>
+        <v>57689</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,34 +1492,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>398271</v>
+        <v>398372</v>
       </c>
       <c r="R10" t="n">
-        <v>6950584</v>
+        <v>6950738</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1536,7 +1556,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1546,7 +1566,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,27 +1593,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128407432</v>
+        <v>128412642</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>57530</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1602,24 +1622,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>398269</v>
+        <v>398437</v>
       </c>
       <c r="R11" t="n">
-        <v>6950563</v>
+        <v>6951052</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1646,19 +1661,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1673,22 +1678,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128415979</v>
+        <v>128407381</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>82946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,39 +1701,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>398372</v>
+        <v>398271</v>
       </c>
       <c r="R12" t="n">
-        <v>6950738</v>
+        <v>6950584</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128412642</v>
+        <v>128409340</v>
       </c>
       <c r="B13" t="n">
-        <v>57530</v>
+        <v>80221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1808,21 +1808,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102621</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1832,13 +1832,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>398437</v>
+        <v>397997</v>
       </c>
       <c r="R13" t="n">
-        <v>6951052</v>
+        <v>6950677</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2526,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128415681</v>
+        <v>128415804</v>
       </c>
       <c r="B20" t="n">
-        <v>79677</v>
+        <v>78490</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2537,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128415804</v>
+        <v>128410565</v>
       </c>
       <c r="B21" t="n">
-        <v>78490</v>
+        <v>75175</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,21 +2644,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>398394</v>
+        <v>398088</v>
       </c>
       <c r="R21" t="n">
-        <v>6950811</v>
+        <v>6950909</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2701,19 +2701,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2728,22 +2718,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128410565</v>
+        <v>128408059</v>
       </c>
       <c r="B22" t="n">
-        <v>75175</v>
+        <v>57689</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2751,34 +2741,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>398088</v>
+        <v>398146</v>
       </c>
       <c r="R22" t="n">
-        <v>6950909</v>
+        <v>6950784</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128408059</v>
+        <v>128415681</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>79677</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2848,39 +2843,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>398146</v>
+        <v>398394</v>
       </c>
       <c r="R23" t="n">
-        <v>6950784</v>
+        <v>6950811</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2910,9 +2900,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2927,12 +2927,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -8019,45 +8019,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128416207</v>
+        <v>128405468</v>
       </c>
       <c r="B74" t="n">
-        <v>75173</v>
+        <v>82946</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6486</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>398414</v>
+        <v>398405</v>
       </c>
       <c r="R74" t="n">
-        <v>6950702</v>
+        <v>6950503</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8116,10 +8116,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128412825</v>
+        <v>128412048</v>
       </c>
       <c r="B75" t="n">
-        <v>79677</v>
+        <v>57689</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8127,34 +8127,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>398474</v>
+        <v>398329</v>
       </c>
       <c r="R75" t="n">
-        <v>6951085</v>
+        <v>6950952</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8184,9 +8189,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8201,22 +8216,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128405468</v>
+        <v>128406114</v>
       </c>
       <c r="B76" t="n">
-        <v>82946</v>
+        <v>57689</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8224,34 +8239,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>398405</v>
+        <v>398351</v>
       </c>
       <c r="R76" t="n">
-        <v>6950503</v>
+        <v>6950591</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8281,9 +8301,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8298,62 +8328,57 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128412048</v>
+        <v>128416207</v>
       </c>
       <c r="B77" t="n">
-        <v>57689</v>
+        <v>75173</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>398329</v>
+        <v>398414</v>
       </c>
       <c r="R77" t="n">
-        <v>6950952</v>
+        <v>6950702</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8383,19 +8408,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8410,22 +8425,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128406114</v>
+        <v>128412825</v>
       </c>
       <c r="B78" t="n">
-        <v>57689</v>
+        <v>79677</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8433,39 +8448,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>398351</v>
+        <v>398474</v>
       </c>
       <c r="R78" t="n">
-        <v>6950591</v>
+        <v>6951085</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8495,19 +8505,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8522,12 +8522,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9024,49 +9024,53 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128404962</v>
+        <v>128411972</v>
       </c>
       <c r="B84" t="n">
-        <v>57854</v>
+        <v>57689</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>266237</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>398392</v>
+        <v>398278</v>
       </c>
       <c r="R84" t="n">
-        <v>6950406</v>
+        <v>6950881</v>
       </c>
       <c r="S84" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9093,19 +9097,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9120,22 +9114,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128416210</v>
+        <v>128407963</v>
       </c>
       <c r="B85" t="n">
-        <v>91482</v>
+        <v>57689</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9143,21 +9137,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9167,10 +9161,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>398414</v>
+        <v>398154</v>
       </c>
       <c r="R85" t="n">
-        <v>6950702</v>
+        <v>6950756</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9200,9 +9194,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9217,65 +9221,61 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128411972</v>
+        <v>128404962</v>
       </c>
       <c r="B86" t="n">
-        <v>57689</v>
+        <v>57854</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>266237</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>398278</v>
+        <v>398392</v>
       </c>
       <c r="R86" t="n">
-        <v>6950881</v>
+        <v>6950406</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9302,9 +9302,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9319,22 +9329,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128407963</v>
+        <v>128416210</v>
       </c>
       <c r="B87" t="n">
-        <v>57689</v>
+        <v>91482</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9342,21 +9352,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9366,10 +9376,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>398154</v>
+        <v>398414</v>
       </c>
       <c r="R87" t="n">
-        <v>6950756</v>
+        <v>6950702</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9399,19 +9409,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9426,12 +9426,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10754,10 +10754,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128413296</v>
+        <v>128413083</v>
       </c>
       <c r="B101" t="n">
-        <v>79677</v>
+        <v>75175</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10765,21 +10765,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10789,10 +10789,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>398463</v>
+        <v>398494</v>
       </c>
       <c r="R101" t="n">
-        <v>6951234</v>
+        <v>6951141</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10851,10 +10851,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128407903</v>
+        <v>128413296</v>
       </c>
       <c r="B102" t="n">
-        <v>81092</v>
+        <v>79677</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10862,21 +10862,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229436</v>
+        <v>229821</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Halmgul örnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ochrolechia alboflavescens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Wulfen) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10886,10 +10886,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>398154</v>
+        <v>398463</v>
       </c>
       <c r="R102" t="n">
-        <v>6950756</v>
+        <v>6951234</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10919,19 +10919,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10946,22 +10936,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128413083</v>
+        <v>128407903</v>
       </c>
       <c r="B103" t="n">
-        <v>75175</v>
+        <v>81092</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10969,21 +10959,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6440</v>
+        <v>229436</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Halmgul örnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ochrolechia alboflavescens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Wulfen) Zahlbr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10993,10 +10983,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>398494</v>
+        <v>398154</v>
       </c>
       <c r="R103" t="n">
-        <v>6951141</v>
+        <v>6950756</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11026,9 +11016,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11043,12 +11043,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>

--- a/artfynd/A 32341-2025 artfynd.xlsx
+++ b/artfynd/A 32341-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128407744</v>
+        <v>128412069</v>
       </c>
       <c r="B2" t="n">
-        <v>79706</v>
+        <v>57689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398173</v>
+        <v>398298</v>
       </c>
       <c r="R2" t="n">
-        <v>6950715</v>
+        <v>6950883</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128412069</v>
+        <v>128407744</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398298</v>
+        <v>398173</v>
       </c>
       <c r="R3" t="n">
-        <v>6950883</v>
+        <v>6950715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
         <v>128413409</v>
       </c>
       <c r="B4" t="n">
-        <v>79677</v>
+        <v>79679</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128412732</v>
       </c>
       <c r="B5" t="n">
-        <v>79182</v>
+        <v>79184</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128415689</v>
       </c>
       <c r="B6" t="n">
-        <v>78490</v>
+        <v>78492</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>128412850</v>
       </c>
       <c r="B7" t="n">
-        <v>78490</v>
+        <v>78492</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>128411332</v>
       </c>
       <c r="B8" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,10 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128407432</v>
+        <v>128407381</v>
       </c>
       <c r="B9" t="n">
-        <v>57689</v>
+        <v>82948</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1380,39 +1380,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>398269</v>
+        <v>398271</v>
       </c>
       <c r="R9" t="n">
-        <v>6950563</v>
+        <v>6950584</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,50 +1476,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128415979</v>
+        <v>128409340</v>
       </c>
       <c r="B10" t="n">
-        <v>57689</v>
+        <v>80223</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>398372</v>
+        <v>397997</v>
       </c>
       <c r="R10" t="n">
-        <v>6950738</v>
+        <v>6950677</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1554,19 +1544,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1581,39 +1561,39 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128412642</v>
+        <v>128407432</v>
       </c>
       <c r="B11" t="n">
-        <v>57530</v>
+        <v>57689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1622,19 +1602,24 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>398437</v>
+        <v>398269</v>
       </c>
       <c r="R11" t="n">
-        <v>6951052</v>
+        <v>6950563</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1661,9 +1646,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1678,22 +1673,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128407381</v>
+        <v>128415979</v>
       </c>
       <c r="B12" t="n">
-        <v>82946</v>
+        <v>57689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1701,34 +1696,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>398271</v>
+        <v>398372</v>
       </c>
       <c r="R12" t="n">
-        <v>6950584</v>
+        <v>6950738</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128409340</v>
+        <v>128412642</v>
       </c>
       <c r="B13" t="n">
-        <v>80221</v>
+        <v>57530</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1808,21 +1808,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>102621</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1832,13 +1832,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>397997</v>
+        <v>398437</v>
       </c>
       <c r="R13" t="n">
-        <v>6950677</v>
+        <v>6951052</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1894,10 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128415142</v>
+        <v>128407947</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>82948</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1905,39 +1905,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>398352</v>
+        <v>398154</v>
       </c>
       <c r="R14" t="n">
-        <v>6950954</v>
+        <v>6950756</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,7 +1964,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1979,7 +1974,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2006,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128410559</v>
+        <v>128411782</v>
       </c>
       <c r="B15" t="n">
-        <v>57689</v>
+        <v>75177</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,39 +2012,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>398097</v>
+        <v>398234</v>
       </c>
       <c r="R15" t="n">
-        <v>6950870</v>
+        <v>6950852</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128407947</v>
+        <v>128410038</v>
       </c>
       <c r="B16" t="n">
-        <v>82946</v>
+        <v>75177</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>398154</v>
+        <v>397967</v>
       </c>
       <c r="R16" t="n">
-        <v>6950756</v>
+        <v>6950876</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,19 +2176,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2213,22 +2193,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128411782</v>
+        <v>128415142</v>
       </c>
       <c r="B17" t="n">
-        <v>75175</v>
+        <v>57689</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,34 +2216,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>398234</v>
+        <v>398352</v>
       </c>
       <c r="R17" t="n">
-        <v>6950852</v>
+        <v>6950954</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128410038</v>
+        <v>128410559</v>
       </c>
       <c r="B18" t="n">
-        <v>75175</v>
+        <v>57689</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,34 +2328,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>397967</v>
+        <v>398097</v>
       </c>
       <c r="R18" t="n">
-        <v>6950876</v>
+        <v>6950870</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,9 +2390,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2417,12 +2417,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2432,7 +2432,7 @@
         <v>128415613</v>
       </c>
       <c r="B19" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>128415804</v>
       </c>
       <c r="B20" t="n">
-        <v>78490</v>
+        <v>78492</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>128410565</v>
       </c>
       <c r="B21" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>128415681</v>
       </c>
       <c r="B23" t="n">
-        <v>79677</v>
+        <v>79679</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128410050</v>
+        <v>128411229</v>
       </c>
       <c r="B24" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>397967</v>
+        <v>398118</v>
       </c>
       <c r="R24" t="n">
-        <v>6950876</v>
+        <v>6950921</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128411229</v>
+        <v>128416541</v>
       </c>
       <c r="B25" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>398118</v>
+        <v>398411</v>
       </c>
       <c r="R25" t="n">
-        <v>6950921</v>
+        <v>6950623</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128416541</v>
+        <v>128410050</v>
       </c>
       <c r="B26" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>398411</v>
+        <v>397967</v>
       </c>
       <c r="R26" t="n">
-        <v>6950623</v>
+        <v>6950876</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3233,7 +3233,7 @@
         <v>128410205</v>
       </c>
       <c r="B27" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>128411297</v>
       </c>
       <c r="B28" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>128413330</v>
       </c>
       <c r="B29" t="n">
-        <v>78490</v>
+        <v>78492</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128408399</v>
+        <v>128411736</v>
       </c>
       <c r="B31" t="n">
-        <v>82946</v>
+        <v>91484</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3644,21 +3644,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>398076</v>
+        <v>398234</v>
       </c>
       <c r="R31" t="n">
-        <v>6950793</v>
+        <v>6950852</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3701,9 +3701,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3718,22 +3728,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128405964</v>
+        <v>128410403</v>
       </c>
       <c r="B32" t="n">
-        <v>57689</v>
+        <v>75177</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3741,39 +3751,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>398364</v>
+        <v>398063</v>
       </c>
       <c r="R32" t="n">
-        <v>6950589</v>
+        <v>6950893</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3832,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128412757</v>
+        <v>128411429</v>
       </c>
       <c r="B33" t="n">
-        <v>57689</v>
+        <v>75177</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3843,39 +3848,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>398460</v>
+        <v>398176</v>
       </c>
       <c r="R33" t="n">
-        <v>6951061</v>
+        <v>6950885</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3905,19 +3905,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3932,19 +3922,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128415952</v>
+        <v>128405964</v>
       </c>
       <c r="B34" t="n">
         <v>57689</v>
@@ -3984,10 +3974,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>398385</v>
+        <v>398364</v>
       </c>
       <c r="R34" t="n">
-        <v>6950755</v>
+        <v>6950589</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4046,10 +4036,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128411736</v>
+        <v>128412757</v>
       </c>
       <c r="B35" t="n">
-        <v>91482</v>
+        <v>57689</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4057,34 +4047,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398234</v>
+        <v>398460</v>
       </c>
       <c r="R35" t="n">
-        <v>6950852</v>
+        <v>6951061</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4153,10 +4148,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128410403</v>
+        <v>128415952</v>
       </c>
       <c r="B36" t="n">
-        <v>75175</v>
+        <v>57689</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4164,34 +4159,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398063</v>
+        <v>398385</v>
       </c>
       <c r="R36" t="n">
-        <v>6950893</v>
+        <v>6950755</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4250,48 +4250,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128411429</v>
+        <v>128413866</v>
       </c>
       <c r="B37" t="n">
-        <v>75175</v>
+        <v>58059</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>398176</v>
+        <v>398505</v>
       </c>
       <c r="R37" t="n">
-        <v>6950885</v>
+        <v>6951279</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4318,9 +4323,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4335,65 +4350,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128413866</v>
+        <v>128408399</v>
       </c>
       <c r="B38" t="n">
-        <v>58059</v>
+        <v>82948</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>398505</v>
+        <v>398076</v>
       </c>
       <c r="R38" t="n">
-        <v>6951279</v>
+        <v>6950793</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4420,19 +4430,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4447,44 +4447,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128416366</v>
+        <v>128405669</v>
       </c>
       <c r="B39" t="n">
-        <v>78447</v>
+        <v>91484</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>398419</v>
+        <v>398398</v>
       </c>
       <c r="R39" t="n">
-        <v>6950678</v>
+        <v>6950569</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4556,32 +4556,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128405669</v>
+        <v>128416366</v>
       </c>
       <c r="B40" t="n">
-        <v>91482</v>
+        <v>78449</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>398398</v>
+        <v>398419</v>
       </c>
       <c r="R40" t="n">
-        <v>6950569</v>
+        <v>6950678</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,32 +4653,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128415930</v>
+        <v>128405841</v>
       </c>
       <c r="B41" t="n">
-        <v>79677</v>
+        <v>92163</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>3298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>398387</v>
+        <v>398374</v>
       </c>
       <c r="R41" t="n">
-        <v>6950766</v>
+        <v>6950548</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4753,7 +4753,7 @@
         <v>128412193</v>
       </c>
       <c r="B42" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>128411735</v>
       </c>
       <c r="B43" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5148,32 +5148,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128405841</v>
+        <v>128415930</v>
       </c>
       <c r="B46" t="n">
-        <v>92161</v>
+        <v>79679</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5183,10 +5183,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>398374</v>
+        <v>398387</v>
       </c>
       <c r="R46" t="n">
-        <v>6950548</v>
+        <v>6950766</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5248,7 +5248,7 @@
         <v>128407293</v>
       </c>
       <c r="B47" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5342,10 +5342,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128415932</v>
+        <v>128410408</v>
       </c>
       <c r="B48" t="n">
-        <v>79706</v>
+        <v>79089</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5353,21 +5353,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>398387</v>
+        <v>398063</v>
       </c>
       <c r="R48" t="n">
-        <v>6950766</v>
+        <v>6950893</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5439,10 +5439,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128411964</v>
+        <v>128415932</v>
       </c>
       <c r="B49" t="n">
-        <v>91482</v>
+        <v>79708</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5450,21 +5450,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>398278</v>
+        <v>398387</v>
       </c>
       <c r="R49" t="n">
-        <v>6950881</v>
+        <v>6950766</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5536,10 +5536,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128406327</v>
+        <v>128412677</v>
       </c>
       <c r="B50" t="n">
-        <v>91482</v>
+        <v>57689</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5547,34 +5547,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>398333</v>
+        <v>398462</v>
       </c>
       <c r="R50" t="n">
-        <v>6950603</v>
+        <v>6951039</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5604,9 +5609,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5621,22 +5636,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128410408</v>
+        <v>128415972</v>
       </c>
       <c r="B51" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5644,34 +5659,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>398063</v>
+        <v>398396</v>
       </c>
       <c r="R51" t="n">
-        <v>6950893</v>
+        <v>6950719</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5730,10 +5750,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128412677</v>
+        <v>128406327</v>
       </c>
       <c r="B52" t="n">
-        <v>57689</v>
+        <v>91484</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5741,39 +5761,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>398462</v>
+        <v>398333</v>
       </c>
       <c r="R52" t="n">
-        <v>6951039</v>
+        <v>6950603</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5803,19 +5818,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5830,22 +5835,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128415972</v>
+        <v>128411964</v>
       </c>
       <c r="B53" t="n">
-        <v>57689</v>
+        <v>91484</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5853,39 +5858,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>398396</v>
+        <v>398278</v>
       </c>
       <c r="R53" t="n">
-        <v>6950719</v>
+        <v>6950881</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5944,48 +5944,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128412638</v>
+        <v>128408097</v>
       </c>
       <c r="B54" t="n">
-        <v>57793</v>
+        <v>57849</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>398437</v>
+        <v>398159</v>
       </c>
       <c r="R54" t="n">
-        <v>6951052</v>
+        <v>6950801</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6012,9 +6017,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6029,65 +6044,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128408097</v>
+        <v>128412638</v>
       </c>
       <c r="B55" t="n">
-        <v>57849</v>
+        <v>57793</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>398159</v>
+        <v>398437</v>
       </c>
       <c r="R55" t="n">
-        <v>6950801</v>
+        <v>6951052</v>
       </c>
       <c r="S55" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6114,19 +6124,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6141,22 +6141,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128413955</v>
+        <v>128408773</v>
       </c>
       <c r="B56" t="n">
-        <v>57530</v>
+        <v>58059</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6164,16 +6164,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>102621</v>
+        <v>103015</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6184,7 +6184,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>398517</v>
+        <v>398012</v>
       </c>
       <c r="R56" t="n">
-        <v>6951283</v>
+        <v>6950659</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6226,9 +6226,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6243,22 +6253,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128408521</v>
+        <v>128409775</v>
       </c>
       <c r="B57" t="n">
-        <v>79706</v>
+        <v>79679</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6266,21 +6276,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6290,10 +6300,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>398019</v>
+        <v>398008</v>
       </c>
       <c r="R57" t="n">
-        <v>6950740</v>
+        <v>6950745</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6352,7 +6362,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128405859</v>
+        <v>128413307</v>
       </c>
       <c r="B58" t="n">
         <v>57689</v>
@@ -6392,10 +6402,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>398362</v>
+        <v>398457</v>
       </c>
       <c r="R58" t="n">
-        <v>6950549</v>
+        <v>6951226</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6427,7 +6437,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6437,7 +6447,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6464,27 +6474,27 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128413307</v>
+        <v>128413955</v>
       </c>
       <c r="B59" t="n">
-        <v>57689</v>
+        <v>57530</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6495,7 +6505,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6504,13 +6514,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>398457</v>
+        <v>398517</v>
       </c>
       <c r="R59" t="n">
-        <v>6951226</v>
+        <v>6951283</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6537,19 +6547,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6564,65 +6564,60 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128408773</v>
+        <v>128408521</v>
       </c>
       <c r="B60" t="n">
-        <v>58059</v>
+        <v>79708</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>398012</v>
+        <v>398019</v>
       </c>
       <c r="R60" t="n">
-        <v>6950659</v>
+        <v>6950740</v>
       </c>
       <c r="S60" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6649,19 +6644,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6676,22 +6661,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128409775</v>
+        <v>128405859</v>
       </c>
       <c r="B61" t="n">
-        <v>79677</v>
+        <v>57689</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6699,34 +6684,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>398008</v>
+        <v>398362</v>
       </c>
       <c r="R61" t="n">
-        <v>6950745</v>
+        <v>6950549</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6756,9 +6746,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6773,12 +6773,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6788,7 +6788,7 @@
         <v>128406318</v>
       </c>
       <c r="B62" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6882,10 +6882,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128415836</v>
+        <v>128409691</v>
       </c>
       <c r="B63" t="n">
-        <v>78059</v>
+        <v>90499</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6893,21 +6893,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6487</v>
+        <v>1962</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6917,10 +6917,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>398394</v>
+        <v>398057</v>
       </c>
       <c r="R63" t="n">
-        <v>6950811</v>
+        <v>6950739</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6989,10 +6989,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128406026</v>
+        <v>128415836</v>
       </c>
       <c r="B64" t="n">
-        <v>79706</v>
+        <v>78061</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7000,21 +7000,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7024,10 +7024,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>398364</v>
+        <v>398394</v>
       </c>
       <c r="R64" t="n">
-        <v>6950589</v>
+        <v>6950811</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7057,9 +7057,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7074,22 +7084,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128415706</v>
+        <v>128406026</v>
       </c>
       <c r="B65" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7097,39 +7107,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>398411</v>
+        <v>398364</v>
       </c>
       <c r="R65" t="n">
-        <v>6950796</v>
+        <v>6950589</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7188,7 +7193,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128416501</v>
+        <v>128415706</v>
       </c>
       <c r="B66" t="n">
         <v>57689</v>
@@ -7219,7 +7224,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7228,10 +7233,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>398382</v>
+        <v>398411</v>
       </c>
       <c r="R66" t="n">
-        <v>6950639</v>
+        <v>6950796</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7261,19 +7266,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7288,22 +7283,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128407307</v>
+        <v>128416501</v>
       </c>
       <c r="B67" t="n">
-        <v>78845</v>
+        <v>57689</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7311,34 +7306,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>398263</v>
+        <v>398382</v>
       </c>
       <c r="R67" t="n">
-        <v>6950596</v>
+        <v>6950639</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7368,9 +7368,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7385,22 +7395,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128409691</v>
+        <v>128407307</v>
       </c>
       <c r="B68" t="n">
-        <v>90497</v>
+        <v>78847</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7408,21 +7418,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7432,10 +7442,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>398057</v>
+        <v>398263</v>
       </c>
       <c r="R68" t="n">
-        <v>6950739</v>
+        <v>6950596</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7465,19 +7475,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7492,22 +7492,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128411308</v>
+        <v>128411180</v>
       </c>
       <c r="B69" t="n">
-        <v>75175</v>
+        <v>57689</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7515,34 +7515,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>398162</v>
+        <v>398102</v>
       </c>
       <c r="R69" t="n">
-        <v>6950923</v>
+        <v>6950907</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7572,9 +7577,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7589,22 +7604,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128411524</v>
+        <v>128411308</v>
       </c>
       <c r="B70" t="n">
-        <v>57689</v>
+        <v>75177</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7612,39 +7627,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>398203</v>
+        <v>398162</v>
       </c>
       <c r="R70" t="n">
-        <v>6950901</v>
+        <v>6950923</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7674,19 +7684,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7701,19 +7701,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128411180</v>
+        <v>128411524</v>
       </c>
       <c r="B71" t="n">
         <v>57689</v>
@@ -7753,10 +7753,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>398102</v>
+        <v>398203</v>
       </c>
       <c r="R71" t="n">
-        <v>6950907</v>
+        <v>6950901</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7825,10 +7825,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128411612</v>
+        <v>128411931</v>
       </c>
       <c r="B72" t="n">
-        <v>79166</v>
+        <v>91484</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7836,21 +7836,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7860,10 +7860,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>398200</v>
+        <v>398276</v>
       </c>
       <c r="R72" t="n">
-        <v>6950918</v>
+        <v>6950842</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7922,10 +7922,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128411931</v>
+        <v>128411612</v>
       </c>
       <c r="B73" t="n">
-        <v>91482</v>
+        <v>79168</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7933,21 +7933,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7957,10 +7957,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>398276</v>
+        <v>398200</v>
       </c>
       <c r="R73" t="n">
-        <v>6950842</v>
+        <v>6950918</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8019,48 +8019,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128405468</v>
+        <v>128412622</v>
       </c>
       <c r="B74" t="n">
-        <v>82946</v>
+        <v>58059</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>398405</v>
+        <v>398437</v>
       </c>
       <c r="R74" t="n">
-        <v>6950503</v>
+        <v>6951052</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8116,10 +8116,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128412048</v>
+        <v>128412825</v>
       </c>
       <c r="B75" t="n">
-        <v>57689</v>
+        <v>79679</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8127,39 +8127,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>398329</v>
+        <v>398474</v>
       </c>
       <c r="R75" t="n">
-        <v>6950952</v>
+        <v>6951085</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8189,19 +8184,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8216,22 +8201,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128406114</v>
+        <v>128405468</v>
       </c>
       <c r="B76" t="n">
-        <v>57689</v>
+        <v>82948</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8239,39 +8224,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>398351</v>
+        <v>398405</v>
       </c>
       <c r="R76" t="n">
-        <v>6950591</v>
+        <v>6950503</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8301,19 +8281,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8328,12 +8298,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8343,7 +8313,7 @@
         <v>128416207</v>
       </c>
       <c r="B77" t="n">
-        <v>75173</v>
+        <v>75175</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8437,10 +8407,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128412825</v>
+        <v>128412048</v>
       </c>
       <c r="B78" t="n">
-        <v>79677</v>
+        <v>57689</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8448,34 +8418,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>398474</v>
+        <v>398329</v>
       </c>
       <c r="R78" t="n">
-        <v>6951085</v>
+        <v>6950952</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8505,9 +8480,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8522,39 +8507,39 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128412622</v>
+        <v>128406114</v>
       </c>
       <c r="B79" t="n">
-        <v>58059</v>
+        <v>57689</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -8563,19 +8548,24 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>398437</v>
+        <v>398351</v>
       </c>
       <c r="R79" t="n">
-        <v>6951052</v>
+        <v>6950591</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8602,9 +8592,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8619,12 +8619,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8634,7 +8634,7 @@
         <v>128411329</v>
       </c>
       <c r="B80" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>128407528</v>
       </c>
       <c r="B82" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>128411270</v>
       </c>
       <c r="B83" t="n">
-        <v>78490</v>
+        <v>78492</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9024,10 +9024,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128411972</v>
+        <v>128416210</v>
       </c>
       <c r="B84" t="n">
-        <v>57689</v>
+        <v>91484</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9035,39 +9035,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>398278</v>
+        <v>398414</v>
       </c>
       <c r="R84" t="n">
-        <v>6950881</v>
+        <v>6950702</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9126,7 +9121,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128407963</v>
+        <v>128411972</v>
       </c>
       <c r="B85" t="n">
         <v>57689</v>
@@ -9155,16 +9150,21 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>398154</v>
+        <v>398278</v>
       </c>
       <c r="R85" t="n">
-        <v>6950756</v>
+        <v>6950881</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9194,19 +9194,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9221,61 +9211,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128404962</v>
+        <v>128407963</v>
       </c>
       <c r="B86" t="n">
-        <v>57854</v>
+        <v>57689</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>266237</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>398392</v>
+        <v>398154</v>
       </c>
       <c r="R86" t="n">
-        <v>6950406</v>
+        <v>6950756</v>
       </c>
       <c r="S86" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9341,48 +9330,49 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128416210</v>
+        <v>128404962</v>
       </c>
       <c r="B87" t="n">
-        <v>91482</v>
+        <v>57854</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5432</v>
+        <v>266237</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>398414</v>
+        <v>398392</v>
       </c>
       <c r="R87" t="n">
-        <v>6950702</v>
+        <v>6950406</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9409,9 +9399,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9426,12 +9426,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9441,7 +9441,7 @@
         <v>128410048</v>
       </c>
       <c r="B88" t="n">
-        <v>78447</v>
+        <v>78449</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>128415905</v>
       </c>
       <c r="B89" t="n">
-        <v>78490</v>
+        <v>78492</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>128405637</v>
       </c>
       <c r="B91" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>128413415</v>
       </c>
       <c r="B92" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>128413088</v>
       </c>
       <c r="B95" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>128411728</v>
       </c>
       <c r="B96" t="n">
-        <v>78447</v>
+        <v>78449</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>128410472</v>
       </c>
       <c r="B97" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>128407311</v>
       </c>
       <c r="B98" t="n">
-        <v>78490</v>
+        <v>78492</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10550,10 +10550,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128413214</v>
+        <v>128413083</v>
       </c>
       <c r="B99" t="n">
-        <v>57689</v>
+        <v>75177</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10561,39 +10561,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>398467</v>
+        <v>398494</v>
       </c>
       <c r="R99" t="n">
-        <v>6951207</v>
+        <v>6951141</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10652,7 +10647,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128415580</v>
+        <v>128413214</v>
       </c>
       <c r="B100" t="n">
         <v>57689</v>
@@ -10683,7 +10678,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -10692,10 +10687,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>398442</v>
+        <v>398467</v>
       </c>
       <c r="R100" t="n">
-        <v>6950833</v>
+        <v>6951207</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10754,10 +10749,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128413083</v>
+        <v>128415580</v>
       </c>
       <c r="B101" t="n">
-        <v>75175</v>
+        <v>57689</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10765,34 +10760,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>398494</v>
+        <v>398442</v>
       </c>
       <c r="R101" t="n">
-        <v>6951141</v>
+        <v>6950833</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10854,7 +10854,7 @@
         <v>128413296</v>
       </c>
       <c r="B102" t="n">
-        <v>79677</v>
+        <v>79679</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>128407903</v>
       </c>
       <c r="B103" t="n">
-        <v>81092</v>
+        <v>81094</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>128406215</v>
       </c>
       <c r="B105" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>128408249</v>
       </c>
       <c r="B107" t="n">
-        <v>78447</v>
+        <v>78449</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>128408651</v>
       </c>
       <c r="B108" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>128416572</v>
       </c>
       <c r="B109" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>128413351</v>
       </c>
       <c r="B113" t="n">
-        <v>79677</v>
+        <v>79679</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 32341-2025 artfynd.xlsx
+++ b/artfynd/A 32341-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128412069</v>
+        <v>128407744</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398298</v>
+        <v>398173</v>
       </c>
       <c r="R2" t="n">
-        <v>6950883</v>
+        <v>6950715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128407744</v>
+        <v>128413409</v>
       </c>
       <c r="B3" t="n">
-        <v>79708</v>
+        <v>79679</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398173</v>
+        <v>398477</v>
       </c>
       <c r="R3" t="n">
-        <v>6950715</v>
+        <v>6951277</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128413409</v>
+        <v>128412069</v>
       </c>
       <c r="B4" t="n">
-        <v>79679</v>
+        <v>57689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398477</v>
+        <v>398298</v>
       </c>
       <c r="R4" t="n">
-        <v>6951277</v>
+        <v>6950883</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1369,32 +1369,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128407381</v>
+        <v>128412642</v>
       </c>
       <c r="B9" t="n">
-        <v>82948</v>
+        <v>57530</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>102621</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,13 +1404,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>398271</v>
+        <v>398437</v>
       </c>
       <c r="R9" t="n">
-        <v>6950584</v>
+        <v>6951052</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1437,19 +1437,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1464,12 +1454,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1797,32 +1787,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128412642</v>
+        <v>128407381</v>
       </c>
       <c r="B13" t="n">
-        <v>57530</v>
+        <v>82948</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102621</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1832,13 +1822,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>398437</v>
+        <v>398271</v>
       </c>
       <c r="R13" t="n">
-        <v>6951052</v>
+        <v>6950584</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1865,9 +1855,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1882,12 +1882,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128416541</v>
+        <v>128405816</v>
       </c>
       <c r="B25" t="n">
-        <v>82948</v>
+        <v>57689</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3047,34 +3047,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>398411</v>
+        <v>398390</v>
       </c>
       <c r="R25" t="n">
-        <v>6950623</v>
+        <v>6950541</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3104,9 +3109,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3121,12 +3136,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3230,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128410205</v>
+        <v>128416541</v>
       </c>
       <c r="B27" t="n">
-        <v>75177</v>
+        <v>82948</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,21 +3256,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>397980</v>
+        <v>398411</v>
       </c>
       <c r="R27" t="n">
-        <v>6950909</v>
+        <v>6950623</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,7 +3342,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128411297</v>
+        <v>128410205</v>
       </c>
       <c r="B28" t="n">
         <v>75177</v>
@@ -3362,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>398143</v>
+        <v>397980</v>
       </c>
       <c r="R28" t="n">
-        <v>6950944</v>
+        <v>6950909</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3424,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128413330</v>
+        <v>128411297</v>
       </c>
       <c r="B29" t="n">
-        <v>78492</v>
+        <v>75177</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3435,21 +3450,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3459,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>398486</v>
+        <v>398143</v>
       </c>
       <c r="R29" t="n">
-        <v>6951242</v>
+        <v>6950944</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3521,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128405816</v>
+        <v>128413330</v>
       </c>
       <c r="B30" t="n">
-        <v>57689</v>
+        <v>78492</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3532,39 +3547,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>398390</v>
+        <v>398486</v>
       </c>
       <c r="R30" t="n">
-        <v>6950541</v>
+        <v>6951242</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3594,19 +3604,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3621,12 +3621,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4250,53 +4250,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128413866</v>
+        <v>128408399</v>
       </c>
       <c r="B37" t="n">
-        <v>58059</v>
+        <v>82948</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>398505</v>
+        <v>398076</v>
       </c>
       <c r="R37" t="n">
-        <v>6951279</v>
+        <v>6950793</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4323,19 +4318,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4350,60 +4335,65 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128408399</v>
+        <v>128413866</v>
       </c>
       <c r="B38" t="n">
-        <v>82948</v>
+        <v>58059</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>398076</v>
+        <v>398505</v>
       </c>
       <c r="R38" t="n">
-        <v>6950793</v>
+        <v>6951279</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4430,9 +4420,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4447,12 +4447,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4556,45 +4556,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128416366</v>
+        <v>128414073</v>
       </c>
       <c r="B40" t="n">
-        <v>78449</v>
+        <v>57689</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>398419</v>
+        <v>398546</v>
       </c>
       <c r="R40" t="n">
-        <v>6950678</v>
+        <v>6951235</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,45 +4658,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128405841</v>
+        <v>128412950</v>
       </c>
       <c r="B41" t="n">
-        <v>92163</v>
+        <v>57689</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>398374</v>
+        <v>398483</v>
       </c>
       <c r="R41" t="n">
-        <v>6950548</v>
+        <v>6951117</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4750,10 +4760,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128412193</v>
+        <v>128405841</v>
       </c>
       <c r="B42" t="n">
-        <v>80229</v>
+        <v>92163</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4761,21 +4771,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>3298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4785,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>398369</v>
+        <v>398374</v>
       </c>
       <c r="R42" t="n">
-        <v>6950956</v>
+        <v>6950548</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4847,32 +4857,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128411735</v>
+        <v>128416366</v>
       </c>
       <c r="B43" t="n">
-        <v>75177</v>
+        <v>78449</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4882,10 +4892,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>398227</v>
+        <v>398419</v>
       </c>
       <c r="R43" t="n">
-        <v>6950881</v>
+        <v>6950678</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4944,50 +4954,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128414073</v>
+        <v>128412193</v>
       </c>
       <c r="B44" t="n">
-        <v>57689</v>
+        <v>80229</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>398546</v>
+        <v>398369</v>
       </c>
       <c r="R44" t="n">
-        <v>6951235</v>
+        <v>6950956</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5046,10 +5051,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128412950</v>
+        <v>128411735</v>
       </c>
       <c r="B45" t="n">
-        <v>57689</v>
+        <v>75177</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5057,39 +5062,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>398483</v>
+        <v>398227</v>
       </c>
       <c r="R45" t="n">
-        <v>6951117</v>
+        <v>6950881</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5245,10 +5245,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128407293</v>
+        <v>128408097</v>
       </c>
       <c r="B47" t="n">
-        <v>79708</v>
+        <v>57849</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5256,37 +5256,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>398263</v>
+        <v>398159</v>
       </c>
       <c r="R47" t="n">
-        <v>6950596</v>
+        <v>6950801</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5313,9 +5318,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5330,22 +5345,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128410408</v>
+        <v>128411964</v>
       </c>
       <c r="B48" t="n">
-        <v>79089</v>
+        <v>91484</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5353,21 +5368,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5377,10 +5392,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>398063</v>
+        <v>398278</v>
       </c>
       <c r="R48" t="n">
-        <v>6950893</v>
+        <v>6950881</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5439,10 +5454,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128415932</v>
+        <v>128406327</v>
       </c>
       <c r="B49" t="n">
-        <v>79708</v>
+        <v>91484</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5450,21 +5465,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5474,10 +5489,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>398387</v>
+        <v>398333</v>
       </c>
       <c r="R49" t="n">
-        <v>6950766</v>
+        <v>6950603</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5536,10 +5551,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128412677</v>
+        <v>128410408</v>
       </c>
       <c r="B50" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5547,39 +5562,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>398462</v>
+        <v>398063</v>
       </c>
       <c r="R50" t="n">
-        <v>6951039</v>
+        <v>6950893</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5609,19 +5619,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5636,22 +5636,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128415972</v>
+        <v>128407293</v>
       </c>
       <c r="B51" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5659,39 +5659,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>398396</v>
+        <v>398263</v>
       </c>
       <c r="R51" t="n">
-        <v>6950719</v>
+        <v>6950596</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5750,10 +5745,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128406327</v>
+        <v>128415932</v>
       </c>
       <c r="B52" t="n">
-        <v>91484</v>
+        <v>79708</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5761,21 +5756,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5785,10 +5780,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>398333</v>
+        <v>398387</v>
       </c>
       <c r="R52" t="n">
-        <v>6950603</v>
+        <v>6950766</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5847,10 +5842,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128411964</v>
+        <v>128412677</v>
       </c>
       <c r="B53" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5858,34 +5853,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>398278</v>
+        <v>398462</v>
       </c>
       <c r="R53" t="n">
-        <v>6950881</v>
+        <v>6951039</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5915,9 +5915,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5932,22 +5942,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128408097</v>
+        <v>128415972</v>
       </c>
       <c r="B54" t="n">
-        <v>57849</v>
+        <v>57689</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5955,27 +5965,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5984,13 +5994,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>398159</v>
+        <v>398396</v>
       </c>
       <c r="R54" t="n">
-        <v>6950801</v>
+        <v>6950719</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6017,19 +6027,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6044,12 +6044,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6153,53 +6153,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128408773</v>
+        <v>128408521</v>
       </c>
       <c r="B56" t="n">
-        <v>58059</v>
+        <v>79708</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>398012</v>
+        <v>398019</v>
       </c>
       <c r="R56" t="n">
-        <v>6950659</v>
+        <v>6950740</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6226,19 +6221,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6253,22 +6238,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128409775</v>
+        <v>128405859</v>
       </c>
       <c r="B57" t="n">
-        <v>79679</v>
+        <v>57689</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6276,34 +6261,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>398008</v>
+        <v>398362</v>
       </c>
       <c r="R57" t="n">
-        <v>6950745</v>
+        <v>6950549</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6333,9 +6323,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6350,12 +6350,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6576,48 +6576,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128408521</v>
+        <v>128408773</v>
       </c>
       <c r="B60" t="n">
-        <v>79708</v>
+        <v>58059</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>398019</v>
+        <v>398012</v>
       </c>
       <c r="R60" t="n">
-        <v>6950740</v>
+        <v>6950659</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6644,9 +6649,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6661,22 +6676,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128405859</v>
+        <v>128409775</v>
       </c>
       <c r="B61" t="n">
-        <v>57689</v>
+        <v>79679</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6684,39 +6699,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>398362</v>
+        <v>398008</v>
       </c>
       <c r="R61" t="n">
-        <v>6950549</v>
+        <v>6950745</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6746,19 +6756,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6773,22 +6773,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128406318</v>
+        <v>128409691</v>
       </c>
       <c r="B62" t="n">
-        <v>79089</v>
+        <v>90499</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6796,21 +6796,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6820,10 +6820,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>398333</v>
+        <v>398057</v>
       </c>
       <c r="R62" t="n">
-        <v>6950603</v>
+        <v>6950739</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6853,9 +6853,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6870,22 +6880,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128409691</v>
+        <v>128415836</v>
       </c>
       <c r="B63" t="n">
-        <v>90499</v>
+        <v>78061</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6893,21 +6903,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6917,10 +6927,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>398057</v>
+        <v>398394</v>
       </c>
       <c r="R63" t="n">
-        <v>6950739</v>
+        <v>6950811</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6952,7 +6962,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -6962,7 +6972,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6989,10 +6999,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128415836</v>
+        <v>128406026</v>
       </c>
       <c r="B64" t="n">
-        <v>78061</v>
+        <v>79708</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7000,21 +7010,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7024,10 +7034,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>398394</v>
+        <v>398364</v>
       </c>
       <c r="R64" t="n">
-        <v>6950811</v>
+        <v>6950589</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7057,19 +7067,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7084,22 +7084,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128406026</v>
+        <v>128415706</v>
       </c>
       <c r="B65" t="n">
-        <v>79708</v>
+        <v>57689</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7107,34 +7107,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>398364</v>
+        <v>398411</v>
       </c>
       <c r="R65" t="n">
-        <v>6950589</v>
+        <v>6950796</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7193,7 +7198,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128415706</v>
+        <v>128416501</v>
       </c>
       <c r="B66" t="n">
         <v>57689</v>
@@ -7224,7 +7229,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7233,10 +7238,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>398411</v>
+        <v>398382</v>
       </c>
       <c r="R66" t="n">
-        <v>6950796</v>
+        <v>6950639</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7266,9 +7271,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7283,22 +7298,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128416501</v>
+        <v>128406318</v>
       </c>
       <c r="B67" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7306,39 +7321,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>398382</v>
+        <v>398333</v>
       </c>
       <c r="R67" t="n">
-        <v>6950639</v>
+        <v>6950603</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7368,19 +7378,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7395,12 +7395,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7504,10 +7504,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128411180</v>
+        <v>128411612</v>
       </c>
       <c r="B69" t="n">
-        <v>57689</v>
+        <v>79168</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7515,39 +7515,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>398102</v>
+        <v>398200</v>
       </c>
       <c r="R69" t="n">
-        <v>6950907</v>
+        <v>6950918</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7577,19 +7572,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7604,22 +7589,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128411308</v>
+        <v>128411931</v>
       </c>
       <c r="B70" t="n">
-        <v>75177</v>
+        <v>91484</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7627,21 +7612,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7651,10 +7636,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>398162</v>
+        <v>398276</v>
       </c>
       <c r="R70" t="n">
-        <v>6950923</v>
+        <v>6950842</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7713,10 +7698,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128411524</v>
+        <v>128411308</v>
       </c>
       <c r="B71" t="n">
-        <v>57689</v>
+        <v>75177</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7724,39 +7709,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>398203</v>
+        <v>398162</v>
       </c>
       <c r="R71" t="n">
-        <v>6950901</v>
+        <v>6950923</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7786,19 +7766,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7813,22 +7783,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128411931</v>
+        <v>128411524</v>
       </c>
       <c r="B72" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7836,34 +7806,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>398276</v>
+        <v>398203</v>
       </c>
       <c r="R72" t="n">
-        <v>6950842</v>
+        <v>6950901</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7893,9 +7868,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7910,22 +7895,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128411612</v>
+        <v>128411180</v>
       </c>
       <c r="B73" t="n">
-        <v>79168</v>
+        <v>57689</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7933,34 +7918,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>398200</v>
+        <v>398102</v>
       </c>
       <c r="R73" t="n">
-        <v>6950918</v>
+        <v>6950907</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7990,9 +7980,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8007,44 +8007,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128412622</v>
+        <v>128412825</v>
       </c>
       <c r="B74" t="n">
-        <v>58059</v>
+        <v>79679</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8054,13 +8054,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>398437</v>
+        <v>398474</v>
       </c>
       <c r="R74" t="n">
-        <v>6951052</v>
+        <v>6951085</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8116,10 +8116,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128412825</v>
+        <v>128405468</v>
       </c>
       <c r="B75" t="n">
-        <v>79679</v>
+        <v>82948</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8127,34 +8127,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>398474</v>
+        <v>398405</v>
       </c>
       <c r="R75" t="n">
-        <v>6951085</v>
+        <v>6950503</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8213,45 +8213,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128405468</v>
+        <v>128416207</v>
       </c>
       <c r="B76" t="n">
-        <v>82948</v>
+        <v>75175</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1312</v>
+        <v>6486</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>398405</v>
+        <v>398414</v>
       </c>
       <c r="R76" t="n">
-        <v>6950503</v>
+        <v>6950702</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8310,45 +8310,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128416207</v>
+        <v>128412048</v>
       </c>
       <c r="B77" t="n">
-        <v>75175</v>
+        <v>57689</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>398414</v>
+        <v>398329</v>
       </c>
       <c r="R77" t="n">
-        <v>6950702</v>
+        <v>6950952</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8378,9 +8383,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8395,19 +8410,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128412048</v>
+        <v>128406114</v>
       </c>
       <c r="B78" t="n">
         <v>57689</v>
@@ -8447,10 +8462,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>398329</v>
+        <v>398351</v>
       </c>
       <c r="R78" t="n">
-        <v>6950952</v>
+        <v>6950591</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8482,7 +8497,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8492,7 +8507,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8519,27 +8534,27 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128406114</v>
+        <v>128412622</v>
       </c>
       <c r="B79" t="n">
-        <v>57689</v>
+        <v>58059</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -8548,24 +8563,19 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>398351</v>
+        <v>398437</v>
       </c>
       <c r="R79" t="n">
-        <v>6950591</v>
+        <v>6951052</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8592,19 +8602,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8619,22 +8619,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128411329</v>
+        <v>128405900</v>
       </c>
       <c r="B80" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8642,34 +8642,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>398173</v>
+        <v>398362</v>
       </c>
       <c r="R80" t="n">
-        <v>6950901</v>
+        <v>6950568</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8728,10 +8733,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128405900</v>
+        <v>128411329</v>
       </c>
       <c r="B81" t="n">
-        <v>57689</v>
+        <v>91484</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8739,39 +8744,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>398362</v>
+        <v>398173</v>
       </c>
       <c r="R81" t="n">
-        <v>6950568</v>
+        <v>6950901</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9438,32 +9438,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128410048</v>
+        <v>128415905</v>
       </c>
       <c r="B88" t="n">
-        <v>78449</v>
+        <v>78492</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>498</v>
+        <v>6437</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9473,10 +9473,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>397967</v>
+        <v>398403</v>
       </c>
       <c r="R88" t="n">
-        <v>6950876</v>
+        <v>6950826</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9506,9 +9506,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9523,22 +9533,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128415905</v>
+        <v>128407736</v>
       </c>
       <c r="B89" t="n">
-        <v>78492</v>
+        <v>57689</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9546,34 +9556,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>398403</v>
+        <v>398169</v>
       </c>
       <c r="R89" t="n">
-        <v>6950826</v>
+        <v>6950711</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9605,7 +9620,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9615,7 +9630,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9642,50 +9657,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128407736</v>
+        <v>128410048</v>
       </c>
       <c r="B90" t="n">
-        <v>57689</v>
+        <v>78449</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>398169</v>
+        <v>397967</v>
       </c>
       <c r="R90" t="n">
-        <v>6950711</v>
+        <v>6950876</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9715,19 +9725,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9742,12 +9742,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -9851,10 +9851,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128413415</v>
+        <v>128410197</v>
       </c>
       <c r="B92" t="n">
-        <v>79708</v>
+        <v>57689</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9862,34 +9862,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>398477</v>
+        <v>397996</v>
       </c>
       <c r="R92" t="n">
-        <v>6951277</v>
+        <v>6950884</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9919,9 +9924,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9936,19 +9951,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128410197</v>
+        <v>128411474</v>
       </c>
       <c r="B93" t="n">
         <v>57689</v>
@@ -9979,7 +9994,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -9988,10 +10003,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>397996</v>
+        <v>398202</v>
       </c>
       <c r="R93" t="n">
-        <v>6950884</v>
+        <v>6950905</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10021,19 +10036,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10048,22 +10053,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128411474</v>
+        <v>128413415</v>
       </c>
       <c r="B94" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10071,39 +10076,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>398202</v>
+        <v>398477</v>
       </c>
       <c r="R94" t="n">
-        <v>6950905</v>
+        <v>6951277</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10162,10 +10162,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128413088</v>
+        <v>128410472</v>
       </c>
       <c r="B95" t="n">
-        <v>82948</v>
+        <v>75177</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10173,21 +10173,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10197,10 +10197,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>398494</v>
+        <v>398075</v>
       </c>
       <c r="R95" t="n">
-        <v>6951141</v>
+        <v>6950912</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10259,32 +10259,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128411728</v>
+        <v>128407311</v>
       </c>
       <c r="B96" t="n">
-        <v>78449</v>
+        <v>78492</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>498</v>
+        <v>6437</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>398227</v>
+        <v>398263</v>
       </c>
       <c r="R96" t="n">
-        <v>6950881</v>
+        <v>6950596</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10356,10 +10356,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128410472</v>
+        <v>128413088</v>
       </c>
       <c r="B97" t="n">
-        <v>75177</v>
+        <v>82948</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10367,21 +10367,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10391,10 +10391,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>398075</v>
+        <v>398494</v>
       </c>
       <c r="R97" t="n">
-        <v>6950912</v>
+        <v>6951141</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10453,32 +10453,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128407311</v>
+        <v>128411728</v>
       </c>
       <c r="B98" t="n">
-        <v>78492</v>
+        <v>78449</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6437</v>
+        <v>498</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10488,10 +10488,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>398263</v>
+        <v>398227</v>
       </c>
       <c r="R98" t="n">
-        <v>6950596</v>
+        <v>6950881</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10550,10 +10550,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128413083</v>
+        <v>128413214</v>
       </c>
       <c r="B99" t="n">
-        <v>75177</v>
+        <v>57689</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10561,34 +10561,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>398494</v>
+        <v>398467</v>
       </c>
       <c r="R99" t="n">
-        <v>6951141</v>
+        <v>6951207</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10647,7 +10652,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128413214</v>
+        <v>128415580</v>
       </c>
       <c r="B100" t="n">
         <v>57689</v>
@@ -10678,7 +10683,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -10687,10 +10692,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>398467</v>
+        <v>398442</v>
       </c>
       <c r="R100" t="n">
-        <v>6951207</v>
+        <v>6950833</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10749,10 +10754,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128415580</v>
+        <v>128413296</v>
       </c>
       <c r="B101" t="n">
-        <v>57689</v>
+        <v>79679</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10760,39 +10765,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>398442</v>
+        <v>398463</v>
       </c>
       <c r="R101" t="n">
-        <v>6950833</v>
+        <v>6951234</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10851,10 +10851,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128413296</v>
+        <v>128407903</v>
       </c>
       <c r="B102" t="n">
-        <v>79679</v>
+        <v>81094</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10862,21 +10862,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229821</v>
+        <v>229436</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Halmgul örnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Ochrolechia alboflavescens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Wulfen) Zahlbr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10886,10 +10886,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>398463</v>
+        <v>398154</v>
       </c>
       <c r="R102" t="n">
-        <v>6951234</v>
+        <v>6950756</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10919,9 +10919,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10936,22 +10946,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128407903</v>
+        <v>128413083</v>
       </c>
       <c r="B103" t="n">
-        <v>81094</v>
+        <v>75177</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10959,21 +10969,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229436</v>
+        <v>6440</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Halmgul örnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ochrolechia alboflavescens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Wulfen) Zahlbr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10983,10 +10993,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>398154</v>
+        <v>398494</v>
       </c>
       <c r="R103" t="n">
-        <v>6950756</v>
+        <v>6951141</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11016,19 +11026,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11043,12 +11043,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>

--- a/artfynd/A 32341-2025 artfynd.xlsx
+++ b/artfynd/A 32341-2025 artfynd.xlsx
@@ -1369,10 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128412642</v>
+        <v>128409340</v>
       </c>
       <c r="B9" t="n">
-        <v>57530</v>
+        <v>80223</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1380,21 +1380,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102621</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,13 +1404,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>398437</v>
+        <v>397997</v>
       </c>
       <c r="R9" t="n">
-        <v>6951052</v>
+        <v>6950677</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1466,45 +1466,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128409340</v>
+        <v>128407432</v>
       </c>
       <c r="B10" t="n">
-        <v>80223</v>
+        <v>57689</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>397997</v>
+        <v>398269</v>
       </c>
       <c r="R10" t="n">
-        <v>6950677</v>
+        <v>6950563</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1534,9 +1539,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1551,19 +1566,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128407432</v>
+        <v>128415979</v>
       </c>
       <c r="B11" t="n">
         <v>57689</v>
@@ -1603,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>398269</v>
+        <v>398372</v>
       </c>
       <c r="R11" t="n">
-        <v>6950563</v>
+        <v>6950738</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1638,7 +1653,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1648,7 +1663,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1675,10 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128415979</v>
+        <v>128407381</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>82948</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1686,39 +1701,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>398372</v>
+        <v>398271</v>
       </c>
       <c r="R12" t="n">
-        <v>6950738</v>
+        <v>6950584</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,7 +1760,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1760,7 +1770,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,32 +1797,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128407381</v>
+        <v>128412642</v>
       </c>
       <c r="B13" t="n">
-        <v>82948</v>
+        <v>57530</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>102621</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1822,13 +1832,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>398271</v>
+        <v>398437</v>
       </c>
       <c r="R13" t="n">
-        <v>6950584</v>
+        <v>6951052</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1855,19 +1865,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1882,12 +1882,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128415804</v>
+        <v>128408059</v>
       </c>
       <c r="B20" t="n">
-        <v>78492</v>
+        <v>57689</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2537,34 +2537,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>398394</v>
+        <v>398146</v>
       </c>
       <c r="R20" t="n">
-        <v>6950811</v>
+        <v>6950784</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2594,19 +2599,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2621,22 +2616,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128410565</v>
+        <v>128415804</v>
       </c>
       <c r="B21" t="n">
-        <v>75177</v>
+        <v>78492</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,21 +2639,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>398088</v>
+        <v>398394</v>
       </c>
       <c r="R21" t="n">
-        <v>6950909</v>
+        <v>6950811</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2701,9 +2696,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2718,22 +2723,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128408059</v>
+        <v>128410565</v>
       </c>
       <c r="B22" t="n">
-        <v>57689</v>
+        <v>75177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2741,39 +2746,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>398146</v>
+        <v>398088</v>
       </c>
       <c r="R22" t="n">
-        <v>6950784</v>
+        <v>6950909</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -4459,32 +4459,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128405669</v>
+        <v>128405841</v>
       </c>
       <c r="B39" t="n">
-        <v>91484</v>
+        <v>92163</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>398398</v>
+        <v>398374</v>
       </c>
       <c r="R39" t="n">
-        <v>6950569</v>
+        <v>6950548</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4556,50 +4556,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128414073</v>
+        <v>128416366</v>
       </c>
       <c r="B40" t="n">
-        <v>57689</v>
+        <v>78449</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>398546</v>
+        <v>398419</v>
       </c>
       <c r="R40" t="n">
-        <v>6951235</v>
+        <v>6950678</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4658,50 +4653,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128412950</v>
+        <v>128412193</v>
       </c>
       <c r="B41" t="n">
-        <v>57689</v>
+        <v>80229</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>398483</v>
+        <v>398369</v>
       </c>
       <c r="R41" t="n">
-        <v>6951117</v>
+        <v>6950956</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4760,32 +4750,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128405841</v>
+        <v>128411735</v>
       </c>
       <c r="B42" t="n">
-        <v>92163</v>
+        <v>75177</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4785,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>398374</v>
+        <v>398227</v>
       </c>
       <c r="R42" t="n">
-        <v>6950548</v>
+        <v>6950881</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4857,32 +4847,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128416366</v>
+        <v>128415930</v>
       </c>
       <c r="B43" t="n">
-        <v>78449</v>
+        <v>79679</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>498</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4892,10 +4882,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>398419</v>
+        <v>398387</v>
       </c>
       <c r="R43" t="n">
-        <v>6950678</v>
+        <v>6950766</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4954,32 +4944,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128412193</v>
+        <v>128405669</v>
       </c>
       <c r="B44" t="n">
-        <v>80229</v>
+        <v>91484</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4989,10 +4979,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>398369</v>
+        <v>398398</v>
       </c>
       <c r="R44" t="n">
-        <v>6950956</v>
+        <v>6950569</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5051,10 +5041,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128411735</v>
+        <v>128414073</v>
       </c>
       <c r="B45" t="n">
-        <v>75177</v>
+        <v>57689</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5062,34 +5052,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>398227</v>
+        <v>398546</v>
       </c>
       <c r="R45" t="n">
-        <v>6950881</v>
+        <v>6951235</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5148,10 +5143,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128415930</v>
+        <v>128412950</v>
       </c>
       <c r="B46" t="n">
-        <v>79679</v>
+        <v>57689</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5159,34 +5154,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>398387</v>
+        <v>398483</v>
       </c>
       <c r="R46" t="n">
-        <v>6950766</v>
+        <v>6951117</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5245,53 +5245,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128408097</v>
+        <v>128412638</v>
       </c>
       <c r="B47" t="n">
-        <v>57849</v>
+        <v>57793</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>398159</v>
+        <v>398437</v>
       </c>
       <c r="R47" t="n">
-        <v>6950801</v>
+        <v>6951052</v>
       </c>
       <c r="S47" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5318,19 +5313,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5345,12 +5330,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6056,48 +6041,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128412638</v>
+        <v>128408097</v>
       </c>
       <c r="B55" t="n">
-        <v>57793</v>
+        <v>57849</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>398437</v>
+        <v>398159</v>
       </c>
       <c r="R55" t="n">
-        <v>6951052</v>
+        <v>6950801</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6124,9 +6114,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6141,12 +6141,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7504,10 +7504,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128411612</v>
+        <v>128411931</v>
       </c>
       <c r="B69" t="n">
-        <v>79168</v>
+        <v>91484</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7515,21 +7515,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7539,10 +7539,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>398200</v>
+        <v>398276</v>
       </c>
       <c r="R69" t="n">
-        <v>6950918</v>
+        <v>6950842</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7601,10 +7601,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128411931</v>
+        <v>128411308</v>
       </c>
       <c r="B70" t="n">
-        <v>91484</v>
+        <v>75177</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7612,21 +7612,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7636,10 +7636,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>398276</v>
+        <v>398162</v>
       </c>
       <c r="R70" t="n">
-        <v>6950842</v>
+        <v>6950923</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7698,10 +7698,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128411308</v>
+        <v>128411524</v>
       </c>
       <c r="B71" t="n">
-        <v>75177</v>
+        <v>57689</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7709,34 +7709,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>398162</v>
+        <v>398203</v>
       </c>
       <c r="R71" t="n">
-        <v>6950923</v>
+        <v>6950901</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7766,9 +7771,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7783,19 +7798,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128411524</v>
+        <v>128411180</v>
       </c>
       <c r="B72" t="n">
         <v>57689</v>
@@ -7835,10 +7850,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>398203</v>
+        <v>398102</v>
       </c>
       <c r="R72" t="n">
-        <v>6950901</v>
+        <v>6950907</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7907,10 +7922,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128411180</v>
+        <v>128411612</v>
       </c>
       <c r="B73" t="n">
-        <v>57689</v>
+        <v>79168</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7918,39 +7933,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>398102</v>
+        <v>398200</v>
       </c>
       <c r="R73" t="n">
-        <v>6950907</v>
+        <v>6950918</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7980,19 +7990,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8007,12 +8007,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8631,10 +8631,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128405900</v>
+        <v>128411329</v>
       </c>
       <c r="B80" t="n">
-        <v>57689</v>
+        <v>91484</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8642,39 +8642,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>398362</v>
+        <v>398173</v>
       </c>
       <c r="R80" t="n">
-        <v>6950568</v>
+        <v>6950901</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8733,10 +8728,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128411329</v>
+        <v>128405900</v>
       </c>
       <c r="B81" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8744,34 +8739,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>398173</v>
+        <v>398362</v>
       </c>
       <c r="R81" t="n">
-        <v>6950901</v>
+        <v>6950568</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9024,10 +9024,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128416210</v>
+        <v>128411972</v>
       </c>
       <c r="B84" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9035,34 +9035,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>398414</v>
+        <v>398278</v>
       </c>
       <c r="R84" t="n">
-        <v>6950702</v>
+        <v>6950881</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9121,7 +9126,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128411972</v>
+        <v>128407963</v>
       </c>
       <c r="B85" t="n">
         <v>57689</v>
@@ -9150,21 +9155,16 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>398278</v>
+        <v>398154</v>
       </c>
       <c r="R85" t="n">
-        <v>6950881</v>
+        <v>6950756</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9194,9 +9194,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9211,60 +9221,61 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128407963</v>
+        <v>128404962</v>
       </c>
       <c r="B86" t="n">
-        <v>57689</v>
+        <v>57854</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>266237</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>398154</v>
+        <v>398392</v>
       </c>
       <c r="R86" t="n">
-        <v>6950756</v>
+        <v>6950406</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9330,49 +9341,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128404962</v>
+        <v>128416210</v>
       </c>
       <c r="B87" t="n">
-        <v>57854</v>
+        <v>91484</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>266237</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>398392</v>
+        <v>398414</v>
       </c>
       <c r="R87" t="n">
-        <v>6950406</v>
+        <v>6950702</v>
       </c>
       <c r="S87" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9399,19 +9409,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9426,12 +9426,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10162,10 +10162,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128410472</v>
+        <v>128413088</v>
       </c>
       <c r="B95" t="n">
-        <v>75177</v>
+        <v>82948</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10173,21 +10173,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10197,10 +10197,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>398075</v>
+        <v>398494</v>
       </c>
       <c r="R95" t="n">
-        <v>6950912</v>
+        <v>6951141</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10259,32 +10259,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128407311</v>
+        <v>128411728</v>
       </c>
       <c r="B96" t="n">
-        <v>78492</v>
+        <v>78449</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6437</v>
+        <v>498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>398263</v>
+        <v>398227</v>
       </c>
       <c r="R96" t="n">
-        <v>6950596</v>
+        <v>6950881</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10356,10 +10356,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128413088</v>
+        <v>128410472</v>
       </c>
       <c r="B97" t="n">
-        <v>82948</v>
+        <v>75177</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10367,21 +10367,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10391,10 +10391,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>398494</v>
+        <v>398075</v>
       </c>
       <c r="R97" t="n">
-        <v>6951141</v>
+        <v>6950912</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10453,32 +10453,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128411728</v>
+        <v>128407311</v>
       </c>
       <c r="B98" t="n">
-        <v>78449</v>
+        <v>78492</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>498</v>
+        <v>6437</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10488,10 +10488,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>398227</v>
+        <v>398263</v>
       </c>
       <c r="R98" t="n">
-        <v>6950881</v>
+        <v>6950596</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10550,10 +10550,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128413214</v>
+        <v>128413296</v>
       </c>
       <c r="B99" t="n">
-        <v>57689</v>
+        <v>79679</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10561,39 +10561,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>398467</v>
+        <v>398463</v>
       </c>
       <c r="R99" t="n">
-        <v>6951207</v>
+        <v>6951234</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10652,10 +10647,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128415580</v>
+        <v>128407903</v>
       </c>
       <c r="B100" t="n">
-        <v>57689</v>
+        <v>81094</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10663,39 +10658,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>229436</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Halmgul örnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ochrolechia alboflavescens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wulfen) Zahlbr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>398442</v>
+        <v>398154</v>
       </c>
       <c r="R100" t="n">
-        <v>6950833</v>
+        <v>6950756</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10725,9 +10715,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10742,22 +10742,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128413296</v>
+        <v>128413083</v>
       </c>
       <c r="B101" t="n">
-        <v>79679</v>
+        <v>75177</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10765,21 +10765,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10789,10 +10789,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>398463</v>
+        <v>398494</v>
       </c>
       <c r="R101" t="n">
-        <v>6951234</v>
+        <v>6951141</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10851,10 +10851,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128407903</v>
+        <v>128413214</v>
       </c>
       <c r="B102" t="n">
-        <v>81094</v>
+        <v>57689</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10862,34 +10862,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229436</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Halmgul örnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ochrolechia alboflavescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Wulfen) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>398154</v>
+        <v>398467</v>
       </c>
       <c r="R102" t="n">
-        <v>6950756</v>
+        <v>6951207</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10919,19 +10924,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10946,22 +10941,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128413083</v>
+        <v>128415580</v>
       </c>
       <c r="B103" t="n">
-        <v>75177</v>
+        <v>57689</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10969,34 +10964,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>398494</v>
+        <v>398442</v>
       </c>
       <c r="R103" t="n">
-        <v>6951141</v>
+        <v>6950833</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>

--- a/artfynd/A 32341-2025 artfynd.xlsx
+++ b/artfynd/A 32341-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128413409</v>
+        <v>128412069</v>
       </c>
       <c r="B3" t="n">
-        <v>79679</v>
+        <v>57689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398477</v>
+        <v>398298</v>
       </c>
       <c r="R3" t="n">
-        <v>6951277</v>
+        <v>6950883</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128412069</v>
+        <v>128413409</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>79679</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +885,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398298</v>
+        <v>398477</v>
       </c>
       <c r="R4" t="n">
-        <v>6950883</v>
+        <v>6951277</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128412850</v>
+        <v>128411332</v>
       </c>
       <c r="B7" t="n">
-        <v>78492</v>
+        <v>75177</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>398474</v>
+        <v>398187</v>
       </c>
       <c r="R7" t="n">
-        <v>6951085</v>
+        <v>6950935</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1233,9 +1233,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1250,22 +1260,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128411332</v>
+        <v>128412850</v>
       </c>
       <c r="B8" t="n">
-        <v>75177</v>
+        <v>78492</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>398187</v>
+        <v>398474</v>
       </c>
       <c r="R8" t="n">
-        <v>6950935</v>
+        <v>6951085</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1330,19 +1340,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1357,44 +1357,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128409340</v>
+        <v>128407381</v>
       </c>
       <c r="B9" t="n">
-        <v>80223</v>
+        <v>82948</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>397997</v>
+        <v>398271</v>
       </c>
       <c r="R9" t="n">
-        <v>6950677</v>
+        <v>6950584</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1437,9 +1437,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1454,62 +1464,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128407432</v>
+        <v>128409340</v>
       </c>
       <c r="B10" t="n">
-        <v>57689</v>
+        <v>80223</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>398269</v>
+        <v>397997</v>
       </c>
       <c r="R10" t="n">
-        <v>6950563</v>
+        <v>6950677</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1539,19 +1544,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1566,19 +1561,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128415979</v>
+        <v>128407432</v>
       </c>
       <c r="B11" t="n">
         <v>57689</v>
@@ -1618,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>398372</v>
+        <v>398269</v>
       </c>
       <c r="R11" t="n">
-        <v>6950738</v>
+        <v>6950563</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,7 +1648,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1663,7 +1658,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1690,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128407381</v>
+        <v>128415979</v>
       </c>
       <c r="B12" t="n">
-        <v>82948</v>
+        <v>57689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1701,34 +1696,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>398271</v>
+        <v>398372</v>
       </c>
       <c r="R12" t="n">
-        <v>6950584</v>
+        <v>6950738</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128411782</v>
+        <v>128410038</v>
       </c>
       <c r="B15" t="n">
         <v>75177</v>
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>398234</v>
+        <v>397967</v>
       </c>
       <c r="R15" t="n">
-        <v>6950852</v>
+        <v>6950876</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2069,19 +2069,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2096,19 +2086,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128410038</v>
+        <v>128411782</v>
       </c>
       <c r="B16" t="n">
         <v>75177</v>
@@ -2143,10 +2133,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>397967</v>
+        <v>398234</v>
       </c>
       <c r="R16" t="n">
-        <v>6950876</v>
+        <v>6950852</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2176,9 +2166,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2193,12 +2193,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2429,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128415613</v>
+        <v>128410565</v>
       </c>
       <c r="B19" t="n">
-        <v>78755</v>
+        <v>75177</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2440,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>398437</v>
+        <v>398088</v>
       </c>
       <c r="R19" t="n">
-        <v>6950808</v>
+        <v>6950909</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128408059</v>
+        <v>128415804</v>
       </c>
       <c r="B20" t="n">
-        <v>57689</v>
+        <v>78492</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2537,39 +2537,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>398146</v>
+        <v>398394</v>
       </c>
       <c r="R20" t="n">
-        <v>6950784</v>
+        <v>6950811</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2599,9 +2594,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2616,22 +2621,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128415804</v>
+        <v>128415613</v>
       </c>
       <c r="B21" t="n">
-        <v>78492</v>
+        <v>78755</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2639,21 +2644,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>398394</v>
+        <v>398437</v>
       </c>
       <c r="R21" t="n">
-        <v>6950811</v>
+        <v>6950808</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2696,19 +2701,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2723,22 +2718,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128410565</v>
+        <v>128408059</v>
       </c>
       <c r="B22" t="n">
-        <v>75177</v>
+        <v>57689</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2746,34 +2741,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>398088</v>
+        <v>398146</v>
       </c>
       <c r="R22" t="n">
-        <v>6950909</v>
+        <v>6950784</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128411229</v>
+        <v>128405816</v>
       </c>
       <c r="B24" t="n">
-        <v>82948</v>
+        <v>57689</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,34 +2950,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>398118</v>
+        <v>398390</v>
       </c>
       <c r="R24" t="n">
-        <v>6950921</v>
+        <v>6950541</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3007,9 +3012,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3024,22 +3039,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128405816</v>
+        <v>128416541</v>
       </c>
       <c r="B25" t="n">
-        <v>57689</v>
+        <v>82948</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3047,39 +3062,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>398390</v>
+        <v>398411</v>
       </c>
       <c r="R25" t="n">
-        <v>6950541</v>
+        <v>6950623</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3109,19 +3119,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3136,12 +3136,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3245,7 +3245,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128416541</v>
+        <v>128411229</v>
       </c>
       <c r="B27" t="n">
         <v>82948</v>
@@ -3280,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>398411</v>
+        <v>398118</v>
       </c>
       <c r="R27" t="n">
-        <v>6950623</v>
+        <v>6950921</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128410205</v>
+        <v>128411297</v>
       </c>
       <c r="B28" t="n">
         <v>75177</v>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>397980</v>
+        <v>398143</v>
       </c>
       <c r="R28" t="n">
-        <v>6950909</v>
+        <v>6950944</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128411297</v>
+        <v>128410205</v>
       </c>
       <c r="B29" t="n">
         <v>75177</v>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>398143</v>
+        <v>397980</v>
       </c>
       <c r="R29" t="n">
-        <v>6950944</v>
+        <v>6950909</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128411736</v>
+        <v>128411429</v>
       </c>
       <c r="B31" t="n">
-        <v>91484</v>
+        <v>75177</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3644,21 +3644,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>398234</v>
+        <v>398176</v>
       </c>
       <c r="R31" t="n">
-        <v>6950852</v>
+        <v>6950885</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3701,19 +3701,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3728,12 +3718,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3837,10 +3827,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128411429</v>
+        <v>128408399</v>
       </c>
       <c r="B33" t="n">
-        <v>75177</v>
+        <v>82948</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3848,21 +3838,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3872,10 +3862,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>398176</v>
+        <v>398076</v>
       </c>
       <c r="R33" t="n">
-        <v>6950885</v>
+        <v>6950793</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3934,10 +3924,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128405964</v>
+        <v>128411736</v>
       </c>
       <c r="B34" t="n">
-        <v>57689</v>
+        <v>91485</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3945,39 +3935,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>398364</v>
+        <v>398234</v>
       </c>
       <c r="R34" t="n">
-        <v>6950589</v>
+        <v>6950852</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4007,9 +3992,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4024,19 +4019,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128412757</v>
+        <v>128405964</v>
       </c>
       <c r="B35" t="n">
         <v>57689</v>
@@ -4067,7 +4062,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4076,10 +4071,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398460</v>
+        <v>398364</v>
       </c>
       <c r="R35" t="n">
-        <v>6951061</v>
+        <v>6950589</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4109,19 +4104,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4136,19 +4121,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128415952</v>
+        <v>128412757</v>
       </c>
       <c r="B36" t="n">
         <v>57689</v>
@@ -4179,7 +4164,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4188,10 +4173,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398385</v>
+        <v>398460</v>
       </c>
       <c r="R36" t="n">
-        <v>6950755</v>
+        <v>6951061</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4221,9 +4206,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4238,22 +4233,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128408399</v>
+        <v>128415952</v>
       </c>
       <c r="B37" t="n">
-        <v>82948</v>
+        <v>57689</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4261,34 +4256,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>398076</v>
+        <v>398385</v>
       </c>
       <c r="R37" t="n">
-        <v>6950793</v>
+        <v>6950755</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4459,32 +4459,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128405841</v>
+        <v>128416366</v>
       </c>
       <c r="B39" t="n">
-        <v>92163</v>
+        <v>78449</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3298</v>
+        <v>498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>398374</v>
+        <v>398419</v>
       </c>
       <c r="R39" t="n">
-        <v>6950548</v>
+        <v>6950678</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4556,32 +4556,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128416366</v>
+        <v>128405841</v>
       </c>
       <c r="B40" t="n">
-        <v>78449</v>
+        <v>92164</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>498</v>
+        <v>3298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>398419</v>
+        <v>398374</v>
       </c>
       <c r="R40" t="n">
-        <v>6950678</v>
+        <v>6950548</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4847,10 +4847,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128415930</v>
+        <v>128405669</v>
       </c>
       <c r="B43" t="n">
-        <v>79679</v>
+        <v>91485</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4858,21 +4858,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4882,10 +4882,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>398387</v>
+        <v>398398</v>
       </c>
       <c r="R43" t="n">
-        <v>6950766</v>
+        <v>6950569</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4944,10 +4944,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128405669</v>
+        <v>128414073</v>
       </c>
       <c r="B44" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4955,34 +4955,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>398398</v>
+        <v>398546</v>
       </c>
       <c r="R44" t="n">
-        <v>6950569</v>
+        <v>6951235</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5041,7 +5046,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128414073</v>
+        <v>128412950</v>
       </c>
       <c r="B45" t="n">
         <v>57689</v>
@@ -5081,10 +5086,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>398546</v>
+        <v>398483</v>
       </c>
       <c r="R45" t="n">
-        <v>6951235</v>
+        <v>6951117</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5143,10 +5148,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128412950</v>
+        <v>128415930</v>
       </c>
       <c r="B46" t="n">
-        <v>57689</v>
+        <v>79679</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5154,39 +5159,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>398483</v>
+        <v>398387</v>
       </c>
       <c r="R46" t="n">
-        <v>6951117</v>
+        <v>6950766</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5245,32 +5245,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128412638</v>
+        <v>128415932</v>
       </c>
       <c r="B47" t="n">
-        <v>57793</v>
+        <v>79708</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5280,13 +5280,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>398437</v>
+        <v>398387</v>
       </c>
       <c r="R47" t="n">
-        <v>6951052</v>
+        <v>6950766</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5342,10 +5342,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128411964</v>
+        <v>128407293</v>
       </c>
       <c r="B48" t="n">
-        <v>91484</v>
+        <v>79708</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5353,21 +5353,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>398278</v>
+        <v>398263</v>
       </c>
       <c r="R48" t="n">
-        <v>6950881</v>
+        <v>6950596</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5439,10 +5439,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128406327</v>
+        <v>128410408</v>
       </c>
       <c r="B49" t="n">
-        <v>91484</v>
+        <v>79089</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5450,21 +5450,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>398333</v>
+        <v>398063</v>
       </c>
       <c r="R49" t="n">
-        <v>6950603</v>
+        <v>6950893</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5536,10 +5536,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128410408</v>
+        <v>128406327</v>
       </c>
       <c r="B50" t="n">
-        <v>79089</v>
+        <v>91485</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5547,21 +5547,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5571,10 +5571,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>398063</v>
+        <v>398333</v>
       </c>
       <c r="R50" t="n">
-        <v>6950893</v>
+        <v>6950603</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5633,10 +5633,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128407293</v>
+        <v>128411964</v>
       </c>
       <c r="B51" t="n">
-        <v>79708</v>
+        <v>91485</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5644,21 +5644,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5668,10 +5668,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>398263</v>
+        <v>398278</v>
       </c>
       <c r="R51" t="n">
-        <v>6950596</v>
+        <v>6950881</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5730,10 +5730,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128415932</v>
+        <v>128412677</v>
       </c>
       <c r="B52" t="n">
-        <v>79708</v>
+        <v>57689</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5741,34 +5741,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>398387</v>
+        <v>398462</v>
       </c>
       <c r="R52" t="n">
-        <v>6950766</v>
+        <v>6951039</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5798,9 +5803,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5815,19 +5830,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128412677</v>
+        <v>128415972</v>
       </c>
       <c r="B53" t="n">
         <v>57689</v>
@@ -5867,10 +5882,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>398462</v>
+        <v>398396</v>
       </c>
       <c r="R53" t="n">
-        <v>6951039</v>
+        <v>6950719</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5900,19 +5915,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5927,22 +5932,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128415972</v>
+        <v>128408097</v>
       </c>
       <c r="B54" t="n">
-        <v>57689</v>
+        <v>57849</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5950,27 +5955,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5979,13 +5984,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>398396</v>
+        <v>398159</v>
       </c>
       <c r="R54" t="n">
-        <v>6950719</v>
+        <v>6950801</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6012,9 +6017,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6029,65 +6044,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128408097</v>
+        <v>128412638</v>
       </c>
       <c r="B55" t="n">
-        <v>57849</v>
+        <v>57793</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>398159</v>
+        <v>398437</v>
       </c>
       <c r="R55" t="n">
-        <v>6950801</v>
+        <v>6951052</v>
       </c>
       <c r="S55" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6114,19 +6124,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6141,60 +6141,65 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128408521</v>
+        <v>128413955</v>
       </c>
       <c r="B56" t="n">
-        <v>79708</v>
+        <v>57530</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>102621</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>398019</v>
+        <v>398517</v>
       </c>
       <c r="R56" t="n">
-        <v>6950740</v>
+        <v>6951283</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6250,10 +6255,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128405859</v>
+        <v>128408521</v>
       </c>
       <c r="B57" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6261,39 +6266,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>398362</v>
+        <v>398019</v>
       </c>
       <c r="R57" t="n">
-        <v>6950549</v>
+        <v>6950740</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6323,19 +6323,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6350,39 +6340,39 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128413307</v>
+        <v>128408773</v>
       </c>
       <c r="B58" t="n">
-        <v>57689</v>
+        <v>58059</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6393,7 +6383,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6402,13 +6392,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>398457</v>
+        <v>398012</v>
       </c>
       <c r="R58" t="n">
-        <v>6951226</v>
+        <v>6950659</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6437,7 +6427,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6447,7 +6437,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6474,53 +6464,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128413955</v>
+        <v>128409775</v>
       </c>
       <c r="B59" t="n">
-        <v>57530</v>
+        <v>79679</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102621</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>398517</v>
+        <v>398008</v>
       </c>
       <c r="R59" t="n">
-        <v>6951283</v>
+        <v>6950745</v>
       </c>
       <c r="S59" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6576,27 +6561,27 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128408773</v>
+        <v>128405859</v>
       </c>
       <c r="B60" t="n">
-        <v>58059</v>
+        <v>57689</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6607,7 +6592,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6616,13 +6601,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>398012</v>
+        <v>398362</v>
       </c>
       <c r="R60" t="n">
-        <v>6950659</v>
+        <v>6950549</v>
       </c>
       <c r="S60" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6688,10 +6673,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128409775</v>
+        <v>128413307</v>
       </c>
       <c r="B61" t="n">
-        <v>79679</v>
+        <v>57689</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6699,34 +6684,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>398008</v>
+        <v>398457</v>
       </c>
       <c r="R61" t="n">
-        <v>6950745</v>
+        <v>6951226</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6756,9 +6746,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6773,12 +6773,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6892,10 +6892,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128415836</v>
+        <v>128406026</v>
       </c>
       <c r="B63" t="n">
-        <v>78061</v>
+        <v>79708</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6903,21 +6903,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>398394</v>
+        <v>398364</v>
       </c>
       <c r="R63" t="n">
-        <v>6950811</v>
+        <v>6950589</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6960,19 +6960,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6987,22 +6977,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128406026</v>
+        <v>128415836</v>
       </c>
       <c r="B64" t="n">
-        <v>79708</v>
+        <v>78061</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7010,21 +7000,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7034,10 +7024,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>398364</v>
+        <v>398394</v>
       </c>
       <c r="R64" t="n">
-        <v>6950589</v>
+        <v>6950811</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7067,9 +7057,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7084,22 +7084,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128415706</v>
+        <v>128406318</v>
       </c>
       <c r="B65" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7107,39 +7107,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>398411</v>
+        <v>398333</v>
       </c>
       <c r="R65" t="n">
-        <v>6950796</v>
+        <v>6950603</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7198,7 +7193,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128416501</v>
+        <v>128415706</v>
       </c>
       <c r="B66" t="n">
         <v>57689</v>
@@ -7229,7 +7224,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7238,10 +7233,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>398382</v>
+        <v>398411</v>
       </c>
       <c r="R66" t="n">
-        <v>6950639</v>
+        <v>6950796</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7271,19 +7266,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7298,22 +7283,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128406318</v>
+        <v>128416501</v>
       </c>
       <c r="B67" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7321,34 +7306,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>398333</v>
+        <v>398382</v>
       </c>
       <c r="R67" t="n">
-        <v>6950603</v>
+        <v>6950639</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7378,9 +7368,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7395,12 +7395,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7504,10 +7504,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128411931</v>
+        <v>128411308</v>
       </c>
       <c r="B69" t="n">
-        <v>91484</v>
+        <v>75177</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7515,21 +7515,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7539,10 +7539,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>398276</v>
+        <v>398162</v>
       </c>
       <c r="R69" t="n">
-        <v>6950842</v>
+        <v>6950923</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7601,10 +7601,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128411308</v>
+        <v>128411931</v>
       </c>
       <c r="B70" t="n">
-        <v>75177</v>
+        <v>91485</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7612,21 +7612,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7636,10 +7636,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>398162</v>
+        <v>398276</v>
       </c>
       <c r="R70" t="n">
-        <v>6950923</v>
+        <v>6950842</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7698,10 +7698,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128411524</v>
+        <v>128411612</v>
       </c>
       <c r="B71" t="n">
-        <v>57689</v>
+        <v>79168</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7709,39 +7709,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>398203</v>
+        <v>398200</v>
       </c>
       <c r="R71" t="n">
-        <v>6950901</v>
+        <v>6950918</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7771,19 +7766,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7798,19 +7783,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128411180</v>
+        <v>128411524</v>
       </c>
       <c r="B72" t="n">
         <v>57689</v>
@@ -7850,10 +7835,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>398102</v>
+        <v>398203</v>
       </c>
       <c r="R72" t="n">
-        <v>6950907</v>
+        <v>6950901</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7922,10 +7907,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128411612</v>
+        <v>128411180</v>
       </c>
       <c r="B73" t="n">
-        <v>79168</v>
+        <v>57689</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7933,34 +7918,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>398200</v>
+        <v>398102</v>
       </c>
       <c r="R73" t="n">
-        <v>6950918</v>
+        <v>6950907</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7990,9 +7980,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8007,22 +8007,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128412825</v>
+        <v>128405468</v>
       </c>
       <c r="B74" t="n">
-        <v>79679</v>
+        <v>82948</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8030,34 +8030,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>398474</v>
+        <v>398405</v>
       </c>
       <c r="R74" t="n">
-        <v>6951085</v>
+        <v>6950503</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8116,45 +8116,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128405468</v>
+        <v>128416207</v>
       </c>
       <c r="B75" t="n">
-        <v>82948</v>
+        <v>75175</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1312</v>
+        <v>6486</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>398405</v>
+        <v>398414</v>
       </c>
       <c r="R75" t="n">
-        <v>6950503</v>
+        <v>6950702</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8213,45 +8213,50 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128416207</v>
+        <v>128412048</v>
       </c>
       <c r="B76" t="n">
-        <v>75175</v>
+        <v>57689</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>398414</v>
+        <v>398329</v>
       </c>
       <c r="R76" t="n">
-        <v>6950702</v>
+        <v>6950952</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8281,9 +8286,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8298,19 +8313,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128412048</v>
+        <v>128406114</v>
       </c>
       <c r="B77" t="n">
         <v>57689</v>
@@ -8350,10 +8365,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>398329</v>
+        <v>398351</v>
       </c>
       <c r="R77" t="n">
-        <v>6950952</v>
+        <v>6950591</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8385,7 +8400,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8395,7 +8410,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8422,27 +8437,27 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128406114</v>
+        <v>128412622</v>
       </c>
       <c r="B78" t="n">
-        <v>57689</v>
+        <v>58059</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -8451,24 +8466,19 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>398351</v>
+        <v>398437</v>
       </c>
       <c r="R78" t="n">
-        <v>6950591</v>
+        <v>6951052</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8495,19 +8505,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8522,44 +8522,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128412622</v>
+        <v>128412825</v>
       </c>
       <c r="B79" t="n">
-        <v>58059</v>
+        <v>79679</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8569,13 +8569,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>398437</v>
+        <v>398474</v>
       </c>
       <c r="R79" t="n">
-        <v>6951052</v>
+        <v>6951085</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8631,10 +8631,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128411329</v>
+        <v>128405900</v>
       </c>
       <c r="B80" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8642,34 +8642,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>398173</v>
+        <v>398362</v>
       </c>
       <c r="R80" t="n">
-        <v>6950901</v>
+        <v>6950568</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8728,10 +8733,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128405900</v>
+        <v>128411329</v>
       </c>
       <c r="B81" t="n">
-        <v>57689</v>
+        <v>91485</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8739,39 +8744,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>398362</v>
+        <v>398173</v>
       </c>
       <c r="R81" t="n">
-        <v>6950568</v>
+        <v>6950901</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9024,53 +9024,49 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128411972</v>
+        <v>128404962</v>
       </c>
       <c r="B84" t="n">
-        <v>57689</v>
+        <v>57854</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>266237</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>398278</v>
+        <v>398392</v>
       </c>
       <c r="R84" t="n">
-        <v>6950881</v>
+        <v>6950406</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9097,9 +9093,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9114,19 +9120,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128407963</v>
+        <v>128411972</v>
       </c>
       <c r="B85" t="n">
         <v>57689</v>
@@ -9155,16 +9161,21 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>398154</v>
+        <v>398278</v>
       </c>
       <c r="R85" t="n">
-        <v>6950756</v>
+        <v>6950881</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9194,19 +9205,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9221,61 +9222,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128404962</v>
+        <v>128407963</v>
       </c>
       <c r="B86" t="n">
-        <v>57854</v>
+        <v>57689</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>266237</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>398392</v>
+        <v>398154</v>
       </c>
       <c r="R86" t="n">
-        <v>6950406</v>
+        <v>6950756</v>
       </c>
       <c r="S86" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>128416210</v>
       </c>
       <c r="B87" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9438,32 +9438,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128415905</v>
+        <v>128410048</v>
       </c>
       <c r="B88" t="n">
-        <v>78492</v>
+        <v>78449</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6437</v>
+        <v>498</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9473,10 +9473,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>398403</v>
+        <v>397967</v>
       </c>
       <c r="R88" t="n">
-        <v>6950826</v>
+        <v>6950876</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9506,19 +9506,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9533,12 +9523,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9657,32 +9647,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128410048</v>
+        <v>128415905</v>
       </c>
       <c r="B90" t="n">
-        <v>78449</v>
+        <v>78492</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>498</v>
+        <v>6437</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9692,10 +9682,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>397967</v>
+        <v>398403</v>
       </c>
       <c r="R90" t="n">
-        <v>6950876</v>
+        <v>6950826</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9725,9 +9715,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9742,12 +9742,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -9757,7 +9757,7 @@
         <v>128405637</v>
       </c>
       <c r="B91" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10259,32 +10259,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128411728</v>
+        <v>128407311</v>
       </c>
       <c r="B96" t="n">
-        <v>78449</v>
+        <v>78492</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>498</v>
+        <v>6437</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>398227</v>
+        <v>398263</v>
       </c>
       <c r="R96" t="n">
-        <v>6950881</v>
+        <v>6950596</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10453,32 +10453,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128407311</v>
+        <v>128411728</v>
       </c>
       <c r="B98" t="n">
-        <v>78492</v>
+        <v>78449</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6437</v>
+        <v>498</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10488,10 +10488,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>398263</v>
+        <v>398227</v>
       </c>
       <c r="R98" t="n">
-        <v>6950596</v>
+        <v>6950881</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10550,10 +10550,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128413296</v>
+        <v>128413083</v>
       </c>
       <c r="B99" t="n">
-        <v>79679</v>
+        <v>75177</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10561,21 +10561,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10585,10 +10585,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>398463</v>
+        <v>398494</v>
       </c>
       <c r="R99" t="n">
-        <v>6951234</v>
+        <v>6951141</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10647,10 +10647,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128407903</v>
+        <v>128413214</v>
       </c>
       <c r="B100" t="n">
-        <v>81094</v>
+        <v>57689</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10658,34 +10658,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229436</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Halmgul örnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ochrolechia alboflavescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Wulfen) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>398154</v>
+        <v>398467</v>
       </c>
       <c r="R100" t="n">
-        <v>6950756</v>
+        <v>6951207</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10715,19 +10720,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10742,22 +10737,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128413083</v>
+        <v>128415580</v>
       </c>
       <c r="B101" t="n">
-        <v>75177</v>
+        <v>57689</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10765,34 +10760,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>398494</v>
+        <v>398442</v>
       </c>
       <c r="R101" t="n">
-        <v>6951141</v>
+        <v>6950833</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10851,10 +10851,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128413214</v>
+        <v>128407903</v>
       </c>
       <c r="B102" t="n">
-        <v>57689</v>
+        <v>81094</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10862,39 +10862,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>229436</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Halmgul örnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ochrolechia alboflavescens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wulfen) Zahlbr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>398467</v>
+        <v>398154</v>
       </c>
       <c r="R102" t="n">
-        <v>6951207</v>
+        <v>6950756</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10924,9 +10919,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10941,22 +10946,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128415580</v>
+        <v>128413296</v>
       </c>
       <c r="B103" t="n">
-        <v>57689</v>
+        <v>79679</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10964,39 +10969,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>398442</v>
+        <v>398463</v>
       </c>
       <c r="R103" t="n">
-        <v>6950833</v>
+        <v>6951234</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11504,7 +11504,7 @@
         <v>128408651</v>
       </c>
       <c r="B108" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>128416572</v>
       </c>
       <c r="B109" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>

--- a/artfynd/A 32341-2025 artfynd.xlsx
+++ b/artfynd/A 32341-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128407744</v>
+        <v>128413409</v>
       </c>
       <c r="B2" t="n">
-        <v>79708</v>
+        <v>79679</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398173</v>
+        <v>398477</v>
       </c>
       <c r="R2" t="n">
-        <v>6950715</v>
+        <v>6951277</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128412069</v>
+        <v>128407744</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398298</v>
+        <v>398173</v>
       </c>
       <c r="R3" t="n">
-        <v>6950883</v>
+        <v>6950715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128413409</v>
+        <v>128412069</v>
       </c>
       <c r="B4" t="n">
-        <v>79679</v>
+        <v>57689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398477</v>
+        <v>398298</v>
       </c>
       <c r="R4" t="n">
-        <v>6951277</v>
+        <v>6950883</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128410038</v>
+        <v>128410559</v>
       </c>
       <c r="B15" t="n">
-        <v>75177</v>
+        <v>57689</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2012,34 +2012,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>397967</v>
+        <v>398097</v>
       </c>
       <c r="R15" t="n">
-        <v>6950876</v>
+        <v>6950870</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2069,9 +2074,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2086,19 +2101,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128411782</v>
+        <v>128410038</v>
       </c>
       <c r="B16" t="n">
         <v>75177</v>
@@ -2133,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>398234</v>
+        <v>397967</v>
       </c>
       <c r="R16" t="n">
-        <v>6950852</v>
+        <v>6950876</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2166,19 +2181,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2193,22 +2198,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128415142</v>
+        <v>128411782</v>
       </c>
       <c r="B17" t="n">
-        <v>57689</v>
+        <v>75177</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,39 +2221,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>398352</v>
+        <v>398234</v>
       </c>
       <c r="R17" t="n">
-        <v>6950954</v>
+        <v>6950852</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128410559</v>
+        <v>128415142</v>
       </c>
       <c r="B18" t="n">
         <v>57689</v>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>398097</v>
+        <v>398352</v>
       </c>
       <c r="R18" t="n">
-        <v>6950870</v>
+        <v>6950954</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128410565</v>
+        <v>128415681</v>
       </c>
       <c r="B19" t="n">
-        <v>75177</v>
+        <v>79679</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2440,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>398088</v>
+        <v>398394</v>
       </c>
       <c r="R19" t="n">
-        <v>6950909</v>
+        <v>6950811</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2497,9 +2497,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2514,22 +2524,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128415804</v>
+        <v>128415613</v>
       </c>
       <c r="B20" t="n">
-        <v>78492</v>
+        <v>78755</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2537,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>398394</v>
+        <v>398437</v>
       </c>
       <c r="R20" t="n">
-        <v>6950811</v>
+        <v>6950808</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2594,19 +2604,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2621,22 +2621,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128415613</v>
+        <v>128408059</v>
       </c>
       <c r="B21" t="n">
-        <v>78755</v>
+        <v>57689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,34 +2644,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>398437</v>
+        <v>398146</v>
       </c>
       <c r="R21" t="n">
-        <v>6950808</v>
+        <v>6950784</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128408059</v>
+        <v>128410565</v>
       </c>
       <c r="B22" t="n">
-        <v>57689</v>
+        <v>75177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2741,39 +2746,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>398146</v>
+        <v>398088</v>
       </c>
       <c r="R22" t="n">
-        <v>6950784</v>
+        <v>6950909</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128415681</v>
+        <v>128415804</v>
       </c>
       <c r="B23" t="n">
-        <v>79679</v>
+        <v>78492</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2843,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128405816</v>
+        <v>128416541</v>
       </c>
       <c r="B24" t="n">
-        <v>57689</v>
+        <v>82948</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,39 +2950,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>398390</v>
+        <v>398411</v>
       </c>
       <c r="R24" t="n">
-        <v>6950541</v>
+        <v>6950623</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3012,19 +3007,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3039,19 +3024,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128416541</v>
+        <v>128410050</v>
       </c>
       <c r="B25" t="n">
         <v>82948</v>
@@ -3086,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>398411</v>
+        <v>397967</v>
       </c>
       <c r="R25" t="n">
-        <v>6950623</v>
+        <v>6950876</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,7 +3133,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128410050</v>
+        <v>128411229</v>
       </c>
       <c r="B26" t="n">
         <v>82948</v>
@@ -3183,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>397967</v>
+        <v>398118</v>
       </c>
       <c r="R26" t="n">
-        <v>6950876</v>
+        <v>6950921</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128411229</v>
+        <v>128411297</v>
       </c>
       <c r="B27" t="n">
-        <v>82948</v>
+        <v>75177</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3256,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3280,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>398118</v>
+        <v>398143</v>
       </c>
       <c r="R27" t="n">
-        <v>6950921</v>
+        <v>6950944</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,7 +3327,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128411297</v>
+        <v>128410205</v>
       </c>
       <c r="B28" t="n">
         <v>75177</v>
@@ -3377,10 +3362,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>398143</v>
+        <v>397980</v>
       </c>
       <c r="R28" t="n">
-        <v>6950944</v>
+        <v>6950909</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3424,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128410205</v>
+        <v>128413330</v>
       </c>
       <c r="B29" t="n">
-        <v>75177</v>
+        <v>78492</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3450,21 +3435,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3474,10 +3459,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>397980</v>
+        <v>398486</v>
       </c>
       <c r="R29" t="n">
-        <v>6950909</v>
+        <v>6951242</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,10 +3521,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128413330</v>
+        <v>128405816</v>
       </c>
       <c r="B30" t="n">
-        <v>78492</v>
+        <v>57689</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3547,34 +3532,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>398486</v>
+        <v>398390</v>
       </c>
       <c r="R30" t="n">
-        <v>6951242</v>
+        <v>6950541</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3604,9 +3594,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3621,12 +3621,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -5245,32 +5245,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128415932</v>
+        <v>128412638</v>
       </c>
       <c r="B47" t="n">
-        <v>79708</v>
+        <v>57793</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5280,13 +5280,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>398387</v>
+        <v>398437</v>
       </c>
       <c r="R47" t="n">
-        <v>6950766</v>
+        <v>6951052</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5342,10 +5342,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128407293</v>
+        <v>128408097</v>
       </c>
       <c r="B48" t="n">
-        <v>79708</v>
+        <v>57849</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5353,37 +5353,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>398263</v>
+        <v>398159</v>
       </c>
       <c r="R48" t="n">
-        <v>6950596</v>
+        <v>6950801</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5410,9 +5415,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5427,22 +5442,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128410408</v>
+        <v>128415932</v>
       </c>
       <c r="B49" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5450,21 +5465,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5474,10 +5489,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>398063</v>
+        <v>398387</v>
       </c>
       <c r="R49" t="n">
-        <v>6950893</v>
+        <v>6950766</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5536,10 +5551,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128406327</v>
+        <v>128407293</v>
       </c>
       <c r="B50" t="n">
-        <v>91485</v>
+        <v>79708</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5547,21 +5562,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5571,10 +5586,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>398333</v>
+        <v>398263</v>
       </c>
       <c r="R50" t="n">
-        <v>6950603</v>
+        <v>6950596</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5633,10 +5648,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128411964</v>
+        <v>128410408</v>
       </c>
       <c r="B51" t="n">
-        <v>91485</v>
+        <v>79089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5644,21 +5659,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5668,10 +5683,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>398278</v>
+        <v>398063</v>
       </c>
       <c r="R51" t="n">
-        <v>6950881</v>
+        <v>6950893</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5730,10 +5745,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128412677</v>
+        <v>128406327</v>
       </c>
       <c r="B52" t="n">
-        <v>57689</v>
+        <v>91485</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5741,39 +5756,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>398462</v>
+        <v>398333</v>
       </c>
       <c r="R52" t="n">
-        <v>6951039</v>
+        <v>6950603</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5803,19 +5813,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5830,22 +5830,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128415972</v>
+        <v>128411964</v>
       </c>
       <c r="B53" t="n">
-        <v>57689</v>
+        <v>91485</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5853,39 +5853,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>398396</v>
+        <v>398278</v>
       </c>
       <c r="R53" t="n">
-        <v>6950719</v>
+        <v>6950881</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5944,10 +5939,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128408097</v>
+        <v>128412677</v>
       </c>
       <c r="B54" t="n">
-        <v>57849</v>
+        <v>57689</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5955,27 +5950,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5984,13 +5979,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>398159</v>
+        <v>398462</v>
       </c>
       <c r="R54" t="n">
-        <v>6950801</v>
+        <v>6951039</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6019,7 +6014,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6029,7 +6024,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6056,27 +6051,27 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128412638</v>
+        <v>128415972</v>
       </c>
       <c r="B55" t="n">
-        <v>57793</v>
+        <v>57689</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6085,19 +6080,24 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>398437</v>
+        <v>398396</v>
       </c>
       <c r="R55" t="n">
-        <v>6951052</v>
+        <v>6950719</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -9132,10 +9132,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128411972</v>
+        <v>128416210</v>
       </c>
       <c r="B85" t="n">
-        <v>57689</v>
+        <v>91485</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9143,39 +9143,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>398278</v>
+        <v>398414</v>
       </c>
       <c r="R85" t="n">
-        <v>6950881</v>
+        <v>6950702</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9234,7 +9229,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128407963</v>
+        <v>128411972</v>
       </c>
       <c r="B86" t="n">
         <v>57689</v>
@@ -9263,16 +9258,21 @@
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>398154</v>
+        <v>398278</v>
       </c>
       <c r="R86" t="n">
-        <v>6950756</v>
+        <v>6950881</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9302,19 +9302,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9329,22 +9319,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128416210</v>
+        <v>128407963</v>
       </c>
       <c r="B87" t="n">
-        <v>91485</v>
+        <v>57689</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9352,21 +9342,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9376,10 +9366,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>398414</v>
+        <v>398154</v>
       </c>
       <c r="R87" t="n">
-        <v>6950702</v>
+        <v>6950756</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9409,9 +9399,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9426,57 +9426,62 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128410048</v>
+        <v>128407736</v>
       </c>
       <c r="B88" t="n">
-        <v>78449</v>
+        <v>57689</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>397967</v>
+        <v>398169</v>
       </c>
       <c r="R88" t="n">
-        <v>6950876</v>
+        <v>6950711</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9506,9 +9511,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9523,22 +9538,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128407736</v>
+        <v>128415905</v>
       </c>
       <c r="B89" t="n">
-        <v>57689</v>
+        <v>78492</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9546,39 +9561,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>398169</v>
+        <v>398403</v>
       </c>
       <c r="R89" t="n">
-        <v>6950711</v>
+        <v>6950826</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9610,7 +9620,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9620,7 +9630,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9647,32 +9657,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128415905</v>
+        <v>128410048</v>
       </c>
       <c r="B90" t="n">
-        <v>78492</v>
+        <v>78449</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6437</v>
+        <v>498</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9682,10 +9692,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>398403</v>
+        <v>397967</v>
       </c>
       <c r="R90" t="n">
-        <v>6950826</v>
+        <v>6950876</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9715,19 +9725,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9742,12 +9742,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -10550,10 +10550,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128413083</v>
+        <v>128413214</v>
       </c>
       <c r="B99" t="n">
-        <v>75177</v>
+        <v>57689</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10561,34 +10561,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>398494</v>
+        <v>398467</v>
       </c>
       <c r="R99" t="n">
-        <v>6951141</v>
+        <v>6951207</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10647,7 +10652,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128413214</v>
+        <v>128415580</v>
       </c>
       <c r="B100" t="n">
         <v>57689</v>
@@ -10678,7 +10683,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -10687,10 +10692,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>398467</v>
+        <v>398442</v>
       </c>
       <c r="R100" t="n">
-        <v>6951207</v>
+        <v>6950833</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10749,10 +10754,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128415580</v>
+        <v>128413083</v>
       </c>
       <c r="B101" t="n">
-        <v>57689</v>
+        <v>75177</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10760,39 +10765,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>398442</v>
+        <v>398494</v>
       </c>
       <c r="R101" t="n">
-        <v>6950833</v>
+        <v>6951141</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10851,10 +10851,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128407903</v>
+        <v>128413296</v>
       </c>
       <c r="B102" t="n">
-        <v>81094</v>
+        <v>79679</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10862,21 +10862,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229436</v>
+        <v>229821</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Halmgul örnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ochrolechia alboflavescens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Wulfen) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10886,10 +10886,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>398154</v>
+        <v>398463</v>
       </c>
       <c r="R102" t="n">
-        <v>6950756</v>
+        <v>6951234</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10919,19 +10919,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10946,22 +10936,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128413296</v>
+        <v>128407903</v>
       </c>
       <c r="B103" t="n">
-        <v>79679</v>
+        <v>81094</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10969,21 +10959,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>229436</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Halmgul örnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Ochrolechia alboflavescens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Wulfen) Zahlbr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10993,10 +10983,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>398463</v>
+        <v>398154</v>
       </c>
       <c r="R103" t="n">
-        <v>6951234</v>
+        <v>6950756</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11026,9 +11016,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11043,12 +11043,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -11058,7 +11058,7 @@
         <v>128411857</v>
       </c>
       <c r="B104" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>128406215</v>
       </c>
       <c r="B105" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>128405961</v>
       </c>
       <c r="B106" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>128408249</v>
       </c>
       <c r="B107" t="n">
-        <v>78449</v>
+        <v>78476</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>128408651</v>
       </c>
       <c r="B108" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>128416572</v>
       </c>
       <c r="B109" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>128405590</v>
       </c>
       <c r="B110" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>128414034</v>
       </c>
       <c r="B111" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>128413146</v>
       </c>
       <c r="B112" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>128413351</v>
       </c>
       <c r="B113" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 32341-2025 artfynd.xlsx
+++ b/artfynd/A 32341-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128413409</v>
+        <v>128407744</v>
       </c>
       <c r="B2" t="n">
-        <v>79679</v>
+        <v>79735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398477</v>
+        <v>398173</v>
       </c>
       <c r="R2" t="n">
-        <v>6951277</v>
+        <v>6950715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128407744</v>
+        <v>128413409</v>
       </c>
       <c r="B3" t="n">
-        <v>79708</v>
+        <v>79706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398173</v>
+        <v>398477</v>
       </c>
       <c r="R3" t="n">
-        <v>6950715</v>
+        <v>6951277</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>128412069</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128412732</v>
       </c>
       <c r="B5" t="n">
-        <v>79184</v>
+        <v>79211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128415689</v>
       </c>
       <c r="B6" t="n">
-        <v>78492</v>
+        <v>78519</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128411332</v>
+        <v>128412850</v>
       </c>
       <c r="B7" t="n">
-        <v>75177</v>
+        <v>78519</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>398187</v>
+        <v>398474</v>
       </c>
       <c r="R7" t="n">
-        <v>6950935</v>
+        <v>6951085</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1233,19 +1233,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1260,22 +1250,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128412850</v>
+        <v>128411332</v>
       </c>
       <c r="B8" t="n">
-        <v>78492</v>
+        <v>75204</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>398474</v>
+        <v>398187</v>
       </c>
       <c r="R8" t="n">
-        <v>6951085</v>
+        <v>6950935</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1340,9 +1330,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1357,12 +1357,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1372,7 +1372,7 @@
         <v>128407381</v>
       </c>
       <c r="B9" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>128409340</v>
       </c>
       <c r="B10" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>128407432</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128415979</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>128412642</v>
       </c>
       <c r="B13" t="n">
-        <v>57530</v>
+        <v>57557</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1894,10 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128407947</v>
+        <v>128415142</v>
       </c>
       <c r="B14" t="n">
-        <v>82948</v>
+        <v>57716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1905,34 +1905,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>398154</v>
+        <v>398352</v>
       </c>
       <c r="R14" t="n">
-        <v>6950756</v>
+        <v>6950954</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,7 +1969,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1974,7 +1979,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2004,7 +2009,7 @@
         <v>128410559</v>
       </c>
       <c r="B15" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2113,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128410038</v>
+        <v>128407947</v>
       </c>
       <c r="B16" t="n">
-        <v>75177</v>
+        <v>82975</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2124,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>397967</v>
+        <v>398154</v>
       </c>
       <c r="R16" t="n">
-        <v>6950876</v>
+        <v>6950756</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2181,9 +2186,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2198,12 +2213,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2213,7 +2228,7 @@
         <v>128411782</v>
       </c>
       <c r="B17" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2317,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128415142</v>
+        <v>128410038</v>
       </c>
       <c r="B18" t="n">
-        <v>57689</v>
+        <v>75204</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,39 +2343,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>398352</v>
+        <v>397967</v>
       </c>
       <c r="R18" t="n">
-        <v>6950954</v>
+        <v>6950876</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2390,19 +2400,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2417,22 +2417,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128415681</v>
+        <v>128415804</v>
       </c>
       <c r="B19" t="n">
-        <v>79679</v>
+        <v>78519</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2440,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128415613</v>
+        <v>128410565</v>
       </c>
       <c r="B20" t="n">
-        <v>78755</v>
+        <v>75204</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>398437</v>
+        <v>398088</v>
       </c>
       <c r="R20" t="n">
-        <v>6950808</v>
+        <v>6950909</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2636,7 +2636,7 @@
         <v>128408059</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128410565</v>
+        <v>128415681</v>
       </c>
       <c r="B22" t="n">
-        <v>75177</v>
+        <v>79706</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2746,21 +2746,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>398088</v>
+        <v>398394</v>
       </c>
       <c r="R22" t="n">
-        <v>6950909</v>
+        <v>6950811</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2803,9 +2803,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2820,22 +2830,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128415804</v>
+        <v>128415613</v>
       </c>
       <c r="B23" t="n">
-        <v>78492</v>
+        <v>78782</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2843,21 +2853,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>398394</v>
+        <v>398437</v>
       </c>
       <c r="R23" t="n">
-        <v>6950811</v>
+        <v>6950808</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2900,19 +2910,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2927,22 +2927,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128416541</v>
+        <v>128410050</v>
       </c>
       <c r="B24" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>398411</v>
+        <v>397967</v>
       </c>
       <c r="R24" t="n">
-        <v>6950623</v>
+        <v>6950876</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128410050</v>
+        <v>128411229</v>
       </c>
       <c r="B25" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>397967</v>
+        <v>398118</v>
       </c>
       <c r="R25" t="n">
-        <v>6950876</v>
+        <v>6950921</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128411229</v>
+        <v>128416541</v>
       </c>
       <c r="B26" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>398118</v>
+        <v>398411</v>
       </c>
       <c r="R26" t="n">
-        <v>6950921</v>
+        <v>6950623</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128411297</v>
+        <v>128410205</v>
       </c>
       <c r="B27" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>398143</v>
+        <v>397980</v>
       </c>
       <c r="R27" t="n">
-        <v>6950944</v>
+        <v>6950909</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128410205</v>
+        <v>128411297</v>
       </c>
       <c r="B28" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>397980</v>
+        <v>398143</v>
       </c>
       <c r="R28" t="n">
-        <v>6950909</v>
+        <v>6950944</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3427,7 +3427,7 @@
         <v>128413330</v>
       </c>
       <c r="B29" t="n">
-        <v>78492</v>
+        <v>78519</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>128405816</v>
       </c>
       <c r="B30" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3633,48 +3633,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128411429</v>
+        <v>128413866</v>
       </c>
       <c r="B31" t="n">
-        <v>75177</v>
+        <v>58086</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>398176</v>
+        <v>398505</v>
       </c>
       <c r="R31" t="n">
-        <v>6950885</v>
+        <v>6951279</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3701,9 +3706,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3718,22 +3733,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128410403</v>
+        <v>128408399</v>
       </c>
       <c r="B32" t="n">
-        <v>75177</v>
+        <v>82975</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3741,21 +3756,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3765,10 +3780,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>398063</v>
+        <v>398076</v>
       </c>
       <c r="R32" t="n">
-        <v>6950893</v>
+        <v>6950793</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3827,10 +3842,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128408399</v>
+        <v>128411736</v>
       </c>
       <c r="B33" t="n">
-        <v>82948</v>
+        <v>91512</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3838,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3862,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>398076</v>
+        <v>398234</v>
       </c>
       <c r="R33" t="n">
-        <v>6950793</v>
+        <v>6950852</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3895,9 +3910,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3912,22 +3937,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128411736</v>
+        <v>128410403</v>
       </c>
       <c r="B34" t="n">
-        <v>91485</v>
+        <v>75204</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3935,21 +3960,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3959,10 +3984,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>398234</v>
+        <v>398063</v>
       </c>
       <c r="R34" t="n">
-        <v>6950852</v>
+        <v>6950893</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3992,19 +4017,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4019,22 +4034,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128405964</v>
+        <v>128411429</v>
       </c>
       <c r="B35" t="n">
-        <v>57689</v>
+        <v>75204</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4042,39 +4057,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398364</v>
+        <v>398176</v>
       </c>
       <c r="R35" t="n">
-        <v>6950589</v>
+        <v>6950885</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4133,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128412757</v>
+        <v>128405964</v>
       </c>
       <c r="B36" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4164,7 +4174,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4173,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398460</v>
+        <v>398364</v>
       </c>
       <c r="R36" t="n">
-        <v>6951061</v>
+        <v>6950589</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4206,19 +4216,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4233,22 +4233,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128415952</v>
+        <v>128412757</v>
       </c>
       <c r="B37" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>398385</v>
+        <v>398460</v>
       </c>
       <c r="R37" t="n">
-        <v>6950755</v>
+        <v>6951061</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4318,9 +4318,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4335,39 +4345,39 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128413866</v>
+        <v>128415952</v>
       </c>
       <c r="B38" t="n">
-        <v>58059</v>
+        <v>57716</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4378,7 +4388,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4387,13 +4397,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>398505</v>
+        <v>398385</v>
       </c>
       <c r="R38" t="n">
-        <v>6951279</v>
+        <v>6950755</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4420,19 +4430,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4447,44 +4447,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128416366</v>
+        <v>128405841</v>
       </c>
       <c r="B39" t="n">
-        <v>78449</v>
+        <v>92191</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>498</v>
+        <v>3298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>398419</v>
+        <v>398374</v>
       </c>
       <c r="R39" t="n">
-        <v>6950678</v>
+        <v>6950548</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4556,32 +4556,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128405841</v>
+        <v>128405669</v>
       </c>
       <c r="B40" t="n">
-        <v>92164</v>
+        <v>91512</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>398374</v>
+        <v>398398</v>
       </c>
       <c r="R40" t="n">
-        <v>6950548</v>
+        <v>6950569</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4656,7 +4656,7 @@
         <v>128412193</v>
       </c>
       <c r="B41" t="n">
-        <v>80229</v>
+        <v>80256</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4750,32 +4750,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128411735</v>
+        <v>128416366</v>
       </c>
       <c r="B42" t="n">
-        <v>75177</v>
+        <v>78476</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4785,10 +4785,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>398227</v>
+        <v>398419</v>
       </c>
       <c r="R42" t="n">
-        <v>6950881</v>
+        <v>6950678</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4847,10 +4847,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128405669</v>
+        <v>128411735</v>
       </c>
       <c r="B43" t="n">
-        <v>91485</v>
+        <v>75204</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4858,21 +4858,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4882,10 +4882,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>398398</v>
+        <v>398227</v>
       </c>
       <c r="R43" t="n">
-        <v>6950569</v>
+        <v>6950881</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4947,7 +4947,7 @@
         <v>128414073</v>
       </c>
       <c r="B44" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>128412950</v>
       </c>
       <c r="B45" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>128415930</v>
       </c>
       <c r="B46" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5245,32 +5245,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128412638</v>
+        <v>128407293</v>
       </c>
       <c r="B47" t="n">
-        <v>57793</v>
+        <v>79735</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5280,13 +5280,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>398437</v>
+        <v>398263</v>
       </c>
       <c r="R47" t="n">
-        <v>6951052</v>
+        <v>6950596</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5342,10 +5342,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128408097</v>
+        <v>128410408</v>
       </c>
       <c r="B48" t="n">
-        <v>57849</v>
+        <v>79116</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5353,42 +5353,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>398159</v>
+        <v>398063</v>
       </c>
       <c r="R48" t="n">
-        <v>6950801</v>
+        <v>6950893</v>
       </c>
       <c r="S48" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5415,19 +5410,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5442,12 +5427,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5457,7 +5442,7 @@
         <v>128415932</v>
       </c>
       <c r="B49" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5551,10 +5536,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128407293</v>
+        <v>128412677</v>
       </c>
       <c r="B50" t="n">
-        <v>79708</v>
+        <v>57716</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5562,34 +5547,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>398263</v>
+        <v>398462</v>
       </c>
       <c r="R50" t="n">
-        <v>6950596</v>
+        <v>6951039</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5619,9 +5609,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5636,22 +5636,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128410408</v>
+        <v>128415972</v>
       </c>
       <c r="B51" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5659,34 +5659,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>398063</v>
+        <v>398396</v>
       </c>
       <c r="R51" t="n">
-        <v>6950893</v>
+        <v>6950719</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5745,10 +5750,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128406327</v>
+        <v>128408097</v>
       </c>
       <c r="B52" t="n">
-        <v>91485</v>
+        <v>57876</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5756,37 +5761,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>398333</v>
+        <v>398159</v>
       </c>
       <c r="R52" t="n">
-        <v>6950603</v>
+        <v>6950801</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5813,9 +5823,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5830,12 +5850,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5845,7 +5865,7 @@
         <v>128411964</v>
       </c>
       <c r="B53" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5939,10 +5959,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128412677</v>
+        <v>128406327</v>
       </c>
       <c r="B54" t="n">
-        <v>57689</v>
+        <v>91512</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5950,39 +5970,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>398462</v>
+        <v>398333</v>
       </c>
       <c r="R54" t="n">
-        <v>6951039</v>
+        <v>6950603</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6012,19 +6027,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6039,39 +6044,39 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128415972</v>
+        <v>128412638</v>
       </c>
       <c r="B55" t="n">
-        <v>57689</v>
+        <v>57820</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6080,24 +6085,19 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>398396</v>
+        <v>398437</v>
       </c>
       <c r="R55" t="n">
-        <v>6950719</v>
+        <v>6951052</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6153,27 +6153,27 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128413955</v>
+        <v>128405859</v>
       </c>
       <c r="B56" t="n">
-        <v>57530</v>
+        <v>57716</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6184,7 +6184,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6193,13 +6193,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>398517</v>
+        <v>398362</v>
       </c>
       <c r="R56" t="n">
-        <v>6951283</v>
+        <v>6950549</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6226,9 +6226,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6243,22 +6253,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128408521</v>
+        <v>128413307</v>
       </c>
       <c r="B57" t="n">
-        <v>79708</v>
+        <v>57716</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6266,34 +6276,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>398019</v>
+        <v>398457</v>
       </c>
       <c r="R57" t="n">
-        <v>6950740</v>
+        <v>6951226</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6323,9 +6338,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6340,12 +6365,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6355,7 +6380,7 @@
         <v>128408773</v>
       </c>
       <c r="B58" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6467,7 +6492,7 @@
         <v>128409775</v>
       </c>
       <c r="B59" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6561,10 +6586,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128405859</v>
+        <v>128408521</v>
       </c>
       <c r="B60" t="n">
-        <v>57689</v>
+        <v>79735</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6572,39 +6597,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>398362</v>
+        <v>398019</v>
       </c>
       <c r="R60" t="n">
-        <v>6950549</v>
+        <v>6950740</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6634,19 +6654,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6661,39 +6671,39 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128413307</v>
+        <v>128413955</v>
       </c>
       <c r="B61" t="n">
-        <v>57689</v>
+        <v>57557</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6704,7 +6714,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6713,13 +6723,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>398457</v>
+        <v>398517</v>
       </c>
       <c r="R61" t="n">
-        <v>6951226</v>
+        <v>6951283</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6746,19 +6756,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6773,22 +6773,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128409691</v>
+        <v>128415706</v>
       </c>
       <c r="B62" t="n">
-        <v>90499</v>
+        <v>57716</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6796,34 +6796,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>398057</v>
+        <v>398411</v>
       </c>
       <c r="R62" t="n">
-        <v>6950739</v>
+        <v>6950796</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6853,19 +6858,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6880,22 +6875,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128406026</v>
+        <v>128416501</v>
       </c>
       <c r="B63" t="n">
-        <v>79708</v>
+        <v>57716</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6903,34 +6898,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>398364</v>
+        <v>398382</v>
       </c>
       <c r="R63" t="n">
-        <v>6950589</v>
+        <v>6950639</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6960,9 +6960,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6977,22 +6987,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128415836</v>
+        <v>128409691</v>
       </c>
       <c r="B64" t="n">
-        <v>78061</v>
+        <v>90526</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7000,21 +7010,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6487</v>
+        <v>1962</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7024,10 +7034,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>398394</v>
+        <v>398057</v>
       </c>
       <c r="R64" t="n">
-        <v>6950811</v>
+        <v>6950739</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7059,7 +7069,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7069,7 +7079,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7096,10 +7106,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128406318</v>
+        <v>128415836</v>
       </c>
       <c r="B65" t="n">
-        <v>79089</v>
+        <v>78088</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7107,21 +7117,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7131,10 +7141,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>398333</v>
+        <v>398394</v>
       </c>
       <c r="R65" t="n">
-        <v>6950603</v>
+        <v>6950811</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7164,9 +7174,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7181,22 +7201,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128415706</v>
+        <v>128406318</v>
       </c>
       <c r="B66" t="n">
-        <v>57689</v>
+        <v>79116</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7204,39 +7224,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>398411</v>
+        <v>398333</v>
       </c>
       <c r="R66" t="n">
-        <v>6950796</v>
+        <v>6950603</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7295,10 +7310,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128416501</v>
+        <v>128406026</v>
       </c>
       <c r="B67" t="n">
-        <v>57689</v>
+        <v>79735</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7306,39 +7321,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>398382</v>
+        <v>398364</v>
       </c>
       <c r="R67" t="n">
-        <v>6950639</v>
+        <v>6950589</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7368,19 +7378,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7395,12 +7395,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7410,7 +7410,7 @@
         <v>128407307</v>
       </c>
       <c r="B68" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7504,10 +7504,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128411308</v>
+        <v>128411931</v>
       </c>
       <c r="B69" t="n">
-        <v>75177</v>
+        <v>91512</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7515,21 +7515,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7539,10 +7539,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>398162</v>
+        <v>398276</v>
       </c>
       <c r="R69" t="n">
-        <v>6950923</v>
+        <v>6950842</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7601,10 +7601,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128411931</v>
+        <v>128411180</v>
       </c>
       <c r="B70" t="n">
-        <v>91485</v>
+        <v>57716</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7612,34 +7612,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>398276</v>
+        <v>398102</v>
       </c>
       <c r="R70" t="n">
-        <v>6950842</v>
+        <v>6950907</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7669,9 +7674,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7686,12 +7701,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7701,7 +7716,7 @@
         <v>128411612</v>
       </c>
       <c r="B71" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7795,10 +7810,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128411524</v>
+        <v>128411308</v>
       </c>
       <c r="B72" t="n">
-        <v>57689</v>
+        <v>75204</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7806,39 +7821,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>398203</v>
+        <v>398162</v>
       </c>
       <c r="R72" t="n">
-        <v>6950901</v>
+        <v>6950923</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7868,19 +7878,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7895,22 +7895,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128411180</v>
+        <v>128411524</v>
       </c>
       <c r="B73" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7947,10 +7947,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>398102</v>
+        <v>398203</v>
       </c>
       <c r="R73" t="n">
-        <v>6950907</v>
+        <v>6950901</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8019,48 +8019,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128405468</v>
+        <v>128412622</v>
       </c>
       <c r="B74" t="n">
-        <v>82948</v>
+        <v>58086</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>398405</v>
+        <v>398437</v>
       </c>
       <c r="R74" t="n">
-        <v>6950503</v>
+        <v>6951052</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8116,45 +8116,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128416207</v>
+        <v>128405468</v>
       </c>
       <c r="B75" t="n">
-        <v>75175</v>
+        <v>82975</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6486</v>
+        <v>1312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>398414</v>
+        <v>398405</v>
       </c>
       <c r="R75" t="n">
-        <v>6950702</v>
+        <v>6950503</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8213,50 +8213,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128412048</v>
+        <v>128416207</v>
       </c>
       <c r="B76" t="n">
-        <v>57689</v>
+        <v>75202</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>398329</v>
+        <v>398414</v>
       </c>
       <c r="R76" t="n">
-        <v>6950952</v>
+        <v>6950702</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8286,19 +8281,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8313,22 +8298,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128406114</v>
+        <v>128412048</v>
       </c>
       <c r="B77" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8365,10 +8350,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>398351</v>
+        <v>398329</v>
       </c>
       <c r="R77" t="n">
-        <v>6950591</v>
+        <v>6950952</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8400,7 +8385,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8410,7 +8395,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8437,27 +8422,27 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128412622</v>
+        <v>128406114</v>
       </c>
       <c r="B78" t="n">
-        <v>58059</v>
+        <v>57716</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -8466,19 +8451,24 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>398437</v>
+        <v>398351</v>
       </c>
       <c r="R78" t="n">
-        <v>6951052</v>
+        <v>6950591</v>
       </c>
       <c r="S78" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8505,9 +8495,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8522,12 +8522,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8537,7 +8537,7 @@
         <v>128412825</v>
       </c>
       <c r="B79" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8631,10 +8631,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128405900</v>
+        <v>128411329</v>
       </c>
       <c r="B80" t="n">
-        <v>57689</v>
+        <v>91512</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8642,39 +8642,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>398362</v>
+        <v>398173</v>
       </c>
       <c r="R80" t="n">
-        <v>6950568</v>
+        <v>6950901</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8733,10 +8728,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128411329</v>
+        <v>128405900</v>
       </c>
       <c r="B81" t="n">
-        <v>91485</v>
+        <v>57716</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8744,34 +8739,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>398173</v>
+        <v>398362</v>
       </c>
       <c r="R81" t="n">
-        <v>6950901</v>
+        <v>6950568</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8833,7 +8833,7 @@
         <v>128407528</v>
       </c>
       <c r="B82" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>128411270</v>
       </c>
       <c r="B83" t="n">
-        <v>78492</v>
+        <v>78519</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9024,49 +9024,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128404962</v>
+        <v>128416210</v>
       </c>
       <c r="B84" t="n">
-        <v>57854</v>
+        <v>91512</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>266237</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>398392</v>
+        <v>398414</v>
       </c>
       <c r="R84" t="n">
-        <v>6950406</v>
+        <v>6950702</v>
       </c>
       <c r="S84" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9093,19 +9092,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9120,22 +9109,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128416210</v>
+        <v>128411972</v>
       </c>
       <c r="B85" t="n">
-        <v>91485</v>
+        <v>57716</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9143,34 +9132,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>398414</v>
+        <v>398278</v>
       </c>
       <c r="R85" t="n">
-        <v>6950702</v>
+        <v>6950881</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9229,10 +9223,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128411972</v>
+        <v>128407963</v>
       </c>
       <c r="B86" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9258,21 +9252,16 @@
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>398278</v>
+        <v>398154</v>
       </c>
       <c r="R86" t="n">
-        <v>6950881</v>
+        <v>6950756</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9302,9 +9291,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9319,60 +9318,61 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128407963</v>
+        <v>128404962</v>
       </c>
       <c r="B87" t="n">
-        <v>57689</v>
+        <v>57881</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>266237</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>398154</v>
+        <v>398392</v>
       </c>
       <c r="R87" t="n">
-        <v>6950756</v>
+        <v>6950406</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9438,50 +9438,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128407736</v>
+        <v>128410048</v>
       </c>
       <c r="B88" t="n">
-        <v>57689</v>
+        <v>78476</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>398169</v>
+        <v>397967</v>
       </c>
       <c r="R88" t="n">
-        <v>6950711</v>
+        <v>6950876</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9511,19 +9506,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9538,12 +9523,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9553,7 +9538,7 @@
         <v>128415905</v>
       </c>
       <c r="B89" t="n">
-        <v>78492</v>
+        <v>78519</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9657,45 +9642,50 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128410048</v>
+        <v>128407736</v>
       </c>
       <c r="B90" t="n">
-        <v>78449</v>
+        <v>57716</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>397967</v>
+        <v>398169</v>
       </c>
       <c r="R90" t="n">
-        <v>6950876</v>
+        <v>6950711</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9725,9 +9715,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9742,22 +9742,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128405637</v>
+        <v>128410197</v>
       </c>
       <c r="B91" t="n">
-        <v>91485</v>
+        <v>57716</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9765,34 +9765,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>398426</v>
+        <v>397996</v>
       </c>
       <c r="R91" t="n">
-        <v>6950561</v>
+        <v>6950884</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9822,9 +9827,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9839,22 +9854,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128410197</v>
+        <v>128411474</v>
       </c>
       <c r="B92" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9882,7 +9897,7 @@
       <c r="I92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -9891,10 +9906,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>397996</v>
+        <v>398202</v>
       </c>
       <c r="R92" t="n">
-        <v>6950884</v>
+        <v>6950905</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9924,19 +9939,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9951,22 +9956,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128411474</v>
+        <v>128405637</v>
       </c>
       <c r="B93" t="n">
-        <v>57689</v>
+        <v>91512</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9974,39 +9979,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>398202</v>
+        <v>398426</v>
       </c>
       <c r="R93" t="n">
-        <v>6950905</v>
+        <v>6950561</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10068,7 +10068,7 @@
         <v>128413415</v>
       </c>
       <c r="B94" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>128413088</v>
       </c>
       <c r="B95" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10259,32 +10259,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128407311</v>
+        <v>128411728</v>
       </c>
       <c r="B96" t="n">
-        <v>78492</v>
+        <v>78476</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6437</v>
+        <v>498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>398263</v>
+        <v>398227</v>
       </c>
       <c r="R96" t="n">
-        <v>6950596</v>
+        <v>6950881</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10359,7 +10359,7 @@
         <v>128410472</v>
       </c>
       <c r="B97" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10453,32 +10453,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128411728</v>
+        <v>128407311</v>
       </c>
       <c r="B98" t="n">
-        <v>78449</v>
+        <v>78519</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>498</v>
+        <v>6437</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10488,10 +10488,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>398227</v>
+        <v>398263</v>
       </c>
       <c r="R98" t="n">
-        <v>6950881</v>
+        <v>6950596</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10550,10 +10550,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128413214</v>
+        <v>128413083</v>
       </c>
       <c r="B99" t="n">
-        <v>57689</v>
+        <v>75204</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10561,39 +10561,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>398467</v>
+        <v>398494</v>
       </c>
       <c r="R99" t="n">
-        <v>6951207</v>
+        <v>6951141</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10652,10 +10647,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128415580</v>
+        <v>128413214</v>
       </c>
       <c r="B100" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10683,7 +10678,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -10692,10 +10687,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>398442</v>
+        <v>398467</v>
       </c>
       <c r="R100" t="n">
-        <v>6950833</v>
+        <v>6951207</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10754,10 +10749,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128413083</v>
+        <v>128415580</v>
       </c>
       <c r="B101" t="n">
-        <v>75177</v>
+        <v>57716</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10765,34 +10760,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>398494</v>
+        <v>398442</v>
       </c>
       <c r="R101" t="n">
-        <v>6951141</v>
+        <v>6950833</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10854,7 +10854,7 @@
         <v>128413296</v>
       </c>
       <c r="B102" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>128407903</v>
       </c>
       <c r="B103" t="n">
-        <v>81094</v>
+        <v>81121</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>

--- a/artfynd/A 32341-2025 artfynd.xlsx
+++ b/artfynd/A 32341-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128407744</v>
+        <v>128413409</v>
       </c>
       <c r="B2" t="n">
-        <v>79735</v>
+        <v>79706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398173</v>
+        <v>398477</v>
       </c>
       <c r="R2" t="n">
-        <v>6950715</v>
+        <v>6951277</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128413409</v>
+        <v>128407744</v>
       </c>
       <c r="B3" t="n">
-        <v>79706</v>
+        <v>79735</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398477</v>
+        <v>398173</v>
       </c>
       <c r="R3" t="n">
-        <v>6951277</v>
+        <v>6950715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128412732</v>
+        <v>128415689</v>
       </c>
       <c r="B5" t="n">
-        <v>79211</v>
+        <v>78519</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>967</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>398474</v>
+        <v>398409</v>
       </c>
       <c r="R5" t="n">
-        <v>6951085</v>
+        <v>6950805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,7 +1068,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128415689</v>
+        <v>128412850</v>
       </c>
       <c r="B6" t="n">
         <v>78519</v>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>398409</v>
+        <v>398474</v>
       </c>
       <c r="R6" t="n">
-        <v>6950805</v>
+        <v>6951085</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128412850</v>
+        <v>128411332</v>
       </c>
       <c r="B7" t="n">
-        <v>78519</v>
+        <v>75204</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>398474</v>
+        <v>398187</v>
       </c>
       <c r="R7" t="n">
-        <v>6951085</v>
+        <v>6950935</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1233,9 +1233,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1250,22 +1260,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128411332</v>
+        <v>128412732</v>
       </c>
       <c r="B8" t="n">
-        <v>75204</v>
+        <v>79211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>967</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>398187</v>
+        <v>398474</v>
       </c>
       <c r="R8" t="n">
-        <v>6950935</v>
+        <v>6951085</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1330,19 +1340,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1357,44 +1357,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128407381</v>
+        <v>128412642</v>
       </c>
       <c r="B9" t="n">
-        <v>82975</v>
+        <v>57557</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>102621</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,13 +1404,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>398271</v>
+        <v>398437</v>
       </c>
       <c r="R9" t="n">
-        <v>6950584</v>
+        <v>6951052</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1437,19 +1437,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1464,44 +1454,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128409340</v>
+        <v>128407381</v>
       </c>
       <c r="B10" t="n">
-        <v>80250</v>
+        <v>82975</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>397997</v>
+        <v>398271</v>
       </c>
       <c r="R10" t="n">
-        <v>6950677</v>
+        <v>6950584</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,9 +1534,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1561,62 +1561,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128407432</v>
+        <v>128409340</v>
       </c>
       <c r="B11" t="n">
-        <v>57716</v>
+        <v>80250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>398269</v>
+        <v>397997</v>
       </c>
       <c r="R11" t="n">
-        <v>6950563</v>
+        <v>6950677</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,19 +1641,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1673,19 +1658,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128415979</v>
+        <v>128407432</v>
       </c>
       <c r="B12" t="n">
         <v>57716</v>
@@ -1725,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>398372</v>
+        <v>398269</v>
       </c>
       <c r="R12" t="n">
-        <v>6950738</v>
+        <v>6950563</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,7 +1745,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1770,7 +1755,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,27 +1782,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128412642</v>
+        <v>128415979</v>
       </c>
       <c r="B13" t="n">
-        <v>57557</v>
+        <v>57716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1826,19 +1811,24 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>398437</v>
+        <v>398372</v>
       </c>
       <c r="R13" t="n">
-        <v>6951052</v>
+        <v>6950738</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1865,9 +1855,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1882,12 +1882,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128415681</v>
+        <v>128415613</v>
       </c>
       <c r="B22" t="n">
-        <v>79706</v>
+        <v>78782</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2746,21 +2746,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>398394</v>
+        <v>398437</v>
       </c>
       <c r="R22" t="n">
-        <v>6950811</v>
+        <v>6950808</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2803,19 +2803,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2830,22 +2820,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128415613</v>
+        <v>128415681</v>
       </c>
       <c r="B23" t="n">
-        <v>78782</v>
+        <v>79706</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>398437</v>
+        <v>398394</v>
       </c>
       <c r="R23" t="n">
-        <v>6950808</v>
+        <v>6950811</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2910,9 +2900,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2927,22 +2927,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128410050</v>
+        <v>128410205</v>
       </c>
       <c r="B24" t="n">
-        <v>82975</v>
+        <v>75204</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,21 +2950,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>397967</v>
+        <v>397980</v>
       </c>
       <c r="R24" t="n">
-        <v>6950876</v>
+        <v>6950909</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128411229</v>
+        <v>128411297</v>
       </c>
       <c r="B25" t="n">
-        <v>82975</v>
+        <v>75204</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>398118</v>
+        <v>398143</v>
       </c>
       <c r="R25" t="n">
-        <v>6950921</v>
+        <v>6950944</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128416541</v>
+        <v>128413330</v>
       </c>
       <c r="B26" t="n">
-        <v>82975</v>
+        <v>78519</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>6437</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>398411</v>
+        <v>398486</v>
       </c>
       <c r="R26" t="n">
-        <v>6950623</v>
+        <v>6951242</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128410205</v>
+        <v>128410050</v>
       </c>
       <c r="B27" t="n">
-        <v>75204</v>
+        <v>82975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>397980</v>
+        <v>397967</v>
       </c>
       <c r="R27" t="n">
-        <v>6950909</v>
+        <v>6950876</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128411297</v>
+        <v>128411229</v>
       </c>
       <c r="B28" t="n">
-        <v>75204</v>
+        <v>82975</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3338,21 +3338,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>398143</v>
+        <v>398118</v>
       </c>
       <c r="R28" t="n">
-        <v>6950944</v>
+        <v>6950921</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3424,10 +3424,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128413330</v>
+        <v>128416541</v>
       </c>
       <c r="B29" t="n">
-        <v>78519</v>
+        <v>82975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3435,21 +3435,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3459,10 +3459,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>398486</v>
+        <v>398411</v>
       </c>
       <c r="R29" t="n">
-        <v>6951242</v>
+        <v>6950623</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3633,53 +3633,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128413866</v>
+        <v>128408399</v>
       </c>
       <c r="B31" t="n">
-        <v>58086</v>
+        <v>82975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>398505</v>
+        <v>398076</v>
       </c>
       <c r="R31" t="n">
-        <v>6951279</v>
+        <v>6950793</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3706,19 +3701,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3733,22 +3718,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128408399</v>
+        <v>128410403</v>
       </c>
       <c r="B32" t="n">
-        <v>82975</v>
+        <v>75204</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3756,21 +3741,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3780,10 +3765,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>398076</v>
+        <v>398063</v>
       </c>
       <c r="R32" t="n">
-        <v>6950793</v>
+        <v>6950893</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3842,10 +3827,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128411736</v>
+        <v>128411429</v>
       </c>
       <c r="B33" t="n">
-        <v>91512</v>
+        <v>75204</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,21 +3838,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3862,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>398234</v>
+        <v>398176</v>
       </c>
       <c r="R33" t="n">
-        <v>6950852</v>
+        <v>6950885</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3910,19 +3895,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3937,22 +3912,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128410403</v>
+        <v>128405964</v>
       </c>
       <c r="B34" t="n">
-        <v>75204</v>
+        <v>57716</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3960,34 +3935,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>398063</v>
+        <v>398364</v>
       </c>
       <c r="R34" t="n">
-        <v>6950893</v>
+        <v>6950589</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4046,10 +4026,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128411429</v>
+        <v>128412757</v>
       </c>
       <c r="B35" t="n">
-        <v>75204</v>
+        <v>57716</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4057,34 +4037,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398176</v>
+        <v>398460</v>
       </c>
       <c r="R35" t="n">
-        <v>6950885</v>
+        <v>6951061</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4114,9 +4099,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4131,19 +4126,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128405964</v>
+        <v>128415952</v>
       </c>
       <c r="B36" t="n">
         <v>57716</v>
@@ -4183,10 +4178,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398364</v>
+        <v>398385</v>
       </c>
       <c r="R36" t="n">
-        <v>6950589</v>
+        <v>6950755</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,10 +4240,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128412757</v>
+        <v>128411736</v>
       </c>
       <c r="B37" t="n">
-        <v>57716</v>
+        <v>91512</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4256,39 +4251,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>398460</v>
+        <v>398234</v>
       </c>
       <c r="R37" t="n">
-        <v>6951061</v>
+        <v>6950852</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4357,27 +4347,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128415952</v>
+        <v>128413866</v>
       </c>
       <c r="B38" t="n">
-        <v>57716</v>
+        <v>58086</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4388,7 +4378,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4397,13 +4387,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>398385</v>
+        <v>398505</v>
       </c>
       <c r="R38" t="n">
-        <v>6950755</v>
+        <v>6951279</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4430,9 +4420,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4447,44 +4447,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128405841</v>
+        <v>128416366</v>
       </c>
       <c r="B39" t="n">
-        <v>92191</v>
+        <v>78476</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3298</v>
+        <v>498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>398374</v>
+        <v>398419</v>
       </c>
       <c r="R39" t="n">
-        <v>6950548</v>
+        <v>6950678</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128412193</v>
+        <v>128405841</v>
       </c>
       <c r="B41" t="n">
-        <v>80256</v>
+        <v>92191</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4664,21 +4664,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6463</v>
+        <v>3298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>398369</v>
+        <v>398374</v>
       </c>
       <c r="R41" t="n">
-        <v>6950956</v>
+        <v>6950548</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4750,32 +4750,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128416366</v>
+        <v>128412193</v>
       </c>
       <c r="B42" t="n">
-        <v>78476</v>
+        <v>80256</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>498</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4785,10 +4785,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>398419</v>
+        <v>398369</v>
       </c>
       <c r="R42" t="n">
-        <v>6950678</v>
+        <v>6950956</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5750,10 +5750,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128408097</v>
+        <v>128406327</v>
       </c>
       <c r="B52" t="n">
-        <v>57876</v>
+        <v>91512</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5761,42 +5761,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>398159</v>
+        <v>398333</v>
       </c>
       <c r="R52" t="n">
-        <v>6950801</v>
+        <v>6950603</v>
       </c>
       <c r="S52" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5823,19 +5818,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5850,12 +5835,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5959,10 +5944,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128406327</v>
+        <v>128408097</v>
       </c>
       <c r="B54" t="n">
-        <v>91512</v>
+        <v>57876</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5970,37 +5955,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>398333</v>
+        <v>398159</v>
       </c>
       <c r="R54" t="n">
-        <v>6950603</v>
+        <v>6950801</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6027,9 +6017,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6044,12 +6044,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6153,27 +6153,27 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128405859</v>
+        <v>128408773</v>
       </c>
       <c r="B56" t="n">
-        <v>57716</v>
+        <v>58086</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6184,7 +6184,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6193,13 +6193,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>398362</v>
+        <v>398012</v>
       </c>
       <c r="R56" t="n">
-        <v>6950549</v>
+        <v>6950659</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6265,10 +6265,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128413307</v>
+        <v>128409775</v>
       </c>
       <c r="B57" t="n">
-        <v>57716</v>
+        <v>79706</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6276,39 +6276,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>398457</v>
+        <v>398008</v>
       </c>
       <c r="R57" t="n">
-        <v>6951226</v>
+        <v>6950745</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6338,19 +6333,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6365,65 +6350,60 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128408773</v>
+        <v>128408521</v>
       </c>
       <c r="B58" t="n">
-        <v>58086</v>
+        <v>79735</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>398012</v>
+        <v>398019</v>
       </c>
       <c r="R58" t="n">
-        <v>6950659</v>
+        <v>6950740</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6450,19 +6430,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6477,22 +6447,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128409775</v>
+        <v>128405859</v>
       </c>
       <c r="B59" t="n">
-        <v>79706</v>
+        <v>57716</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6500,34 +6470,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>398008</v>
+        <v>398362</v>
       </c>
       <c r="R59" t="n">
-        <v>6950745</v>
+        <v>6950549</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6557,9 +6532,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6574,22 +6559,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128408521</v>
+        <v>128413307</v>
       </c>
       <c r="B60" t="n">
-        <v>79735</v>
+        <v>57716</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6597,34 +6582,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>398019</v>
+        <v>398457</v>
       </c>
       <c r="R60" t="n">
-        <v>6950740</v>
+        <v>6951226</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6654,9 +6644,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6671,12 +6671,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6785,10 +6785,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128415706</v>
+        <v>128415836</v>
       </c>
       <c r="B62" t="n">
-        <v>57716</v>
+        <v>78088</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6796,39 +6796,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>398411</v>
+        <v>398394</v>
       </c>
       <c r="R62" t="n">
-        <v>6950796</v>
+        <v>6950811</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6858,9 +6853,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6875,22 +6880,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128416501</v>
+        <v>128406026</v>
       </c>
       <c r="B63" t="n">
-        <v>57716</v>
+        <v>79735</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6898,39 +6903,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>398382</v>
+        <v>398364</v>
       </c>
       <c r="R63" t="n">
-        <v>6950639</v>
+        <v>6950589</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6960,19 +6960,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6987,12 +6977,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7106,10 +7096,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128415836</v>
+        <v>128415706</v>
       </c>
       <c r="B65" t="n">
-        <v>78088</v>
+        <v>57716</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7117,34 +7107,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>398394</v>
+        <v>398411</v>
       </c>
       <c r="R65" t="n">
-        <v>6950811</v>
+        <v>6950796</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7174,19 +7169,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7201,22 +7186,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128406318</v>
+        <v>128416501</v>
       </c>
       <c r="B66" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7224,34 +7209,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>398333</v>
+        <v>398382</v>
       </c>
       <c r="R66" t="n">
-        <v>6950603</v>
+        <v>6950639</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7281,9 +7271,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7298,22 +7298,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128406026</v>
+        <v>128406318</v>
       </c>
       <c r="B67" t="n">
-        <v>79735</v>
+        <v>79116</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7321,21 +7321,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>398364</v>
+        <v>398333</v>
       </c>
       <c r="R67" t="n">
-        <v>6950589</v>
+        <v>6950603</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7504,10 +7504,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128411931</v>
+        <v>128411612</v>
       </c>
       <c r="B69" t="n">
-        <v>91512</v>
+        <v>79195</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7515,21 +7515,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7539,10 +7539,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>398276</v>
+        <v>398200</v>
       </c>
       <c r="R69" t="n">
-        <v>6950842</v>
+        <v>6950918</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7601,10 +7601,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128411180</v>
+        <v>128411931</v>
       </c>
       <c r="B70" t="n">
-        <v>57716</v>
+        <v>91512</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7612,39 +7612,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>398102</v>
+        <v>398276</v>
       </c>
       <c r="R70" t="n">
-        <v>6950907</v>
+        <v>6950842</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7674,19 +7669,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7701,22 +7686,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128411612</v>
+        <v>128411308</v>
       </c>
       <c r="B71" t="n">
-        <v>79195</v>
+        <v>75204</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7724,21 +7709,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7748,10 +7733,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>398200</v>
+        <v>398162</v>
       </c>
       <c r="R71" t="n">
-        <v>6950918</v>
+        <v>6950923</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7810,10 +7795,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128411308</v>
+        <v>128411524</v>
       </c>
       <c r="B72" t="n">
-        <v>75204</v>
+        <v>57716</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7821,34 +7806,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>398162</v>
+        <v>398203</v>
       </c>
       <c r="R72" t="n">
-        <v>6950923</v>
+        <v>6950901</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7878,9 +7868,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7895,19 +7895,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128411524</v>
+        <v>128411180</v>
       </c>
       <c r="B73" t="n">
         <v>57716</v>
@@ -7947,10 +7947,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>398203</v>
+        <v>398102</v>
       </c>
       <c r="R73" t="n">
-        <v>6950901</v>
+        <v>6950907</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8019,27 +8019,27 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128412622</v>
+        <v>128412048</v>
       </c>
       <c r="B74" t="n">
-        <v>58086</v>
+        <v>57716</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8048,19 +8048,24 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>398437</v>
+        <v>398329</v>
       </c>
       <c r="R74" t="n">
-        <v>6951052</v>
+        <v>6950952</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8087,9 +8092,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8104,22 +8119,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128405468</v>
+        <v>128406114</v>
       </c>
       <c r="B75" t="n">
-        <v>82975</v>
+        <v>57716</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8127,34 +8142,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>398405</v>
+        <v>398351</v>
       </c>
       <c r="R75" t="n">
-        <v>6950503</v>
+        <v>6950591</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8184,9 +8204,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8201,44 +8231,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128416207</v>
+        <v>128412622</v>
       </c>
       <c r="B76" t="n">
-        <v>75202</v>
+        <v>58086</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6486</v>
+        <v>103015</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8248,13 +8278,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>398414</v>
+        <v>398437</v>
       </c>
       <c r="R76" t="n">
-        <v>6950702</v>
+        <v>6951052</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8310,10 +8340,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128412048</v>
+        <v>128412825</v>
       </c>
       <c r="B77" t="n">
-        <v>57716</v>
+        <v>79706</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8321,39 +8351,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>398329</v>
+        <v>398474</v>
       </c>
       <c r="R77" t="n">
-        <v>6950952</v>
+        <v>6951085</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8383,19 +8408,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8410,22 +8425,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128406114</v>
+        <v>128405468</v>
       </c>
       <c r="B78" t="n">
-        <v>57716</v>
+        <v>82975</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8433,39 +8448,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>398351</v>
+        <v>398405</v>
       </c>
       <c r="R78" t="n">
-        <v>6950591</v>
+        <v>6950503</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8495,19 +8505,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8522,44 +8522,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128412825</v>
+        <v>128416207</v>
       </c>
       <c r="B79" t="n">
-        <v>79706</v>
+        <v>75202</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>6486</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>398474</v>
+        <v>398414</v>
       </c>
       <c r="R79" t="n">
-        <v>6951085</v>
+        <v>6950702</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8631,10 +8631,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128411329</v>
+        <v>128405900</v>
       </c>
       <c r="B80" t="n">
-        <v>91512</v>
+        <v>57716</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8642,34 +8642,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>398173</v>
+        <v>398362</v>
       </c>
       <c r="R80" t="n">
-        <v>6950901</v>
+        <v>6950568</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8728,10 +8733,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128405900</v>
+        <v>128411329</v>
       </c>
       <c r="B81" t="n">
-        <v>57716</v>
+        <v>91512</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8739,39 +8744,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>398362</v>
+        <v>398173</v>
       </c>
       <c r="R81" t="n">
-        <v>6950568</v>
+        <v>6950901</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8830,10 +8830,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128407528</v>
+        <v>128411270</v>
       </c>
       <c r="B82" t="n">
-        <v>78782</v>
+        <v>78519</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8841,21 +8841,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>398225</v>
+        <v>398139</v>
       </c>
       <c r="R82" t="n">
-        <v>6950599</v>
+        <v>6950929</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8927,10 +8927,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128411270</v>
+        <v>128407528</v>
       </c>
       <c r="B83" t="n">
-        <v>78519</v>
+        <v>78782</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8938,21 +8938,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>398139</v>
+        <v>398225</v>
       </c>
       <c r="R83" t="n">
-        <v>6950929</v>
+        <v>6950599</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9024,10 +9024,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128416210</v>
+        <v>128411972</v>
       </c>
       <c r="B84" t="n">
-        <v>91512</v>
+        <v>57716</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9035,34 +9035,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>398414</v>
+        <v>398278</v>
       </c>
       <c r="R84" t="n">
-        <v>6950702</v>
+        <v>6950881</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9121,7 +9126,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128411972</v>
+        <v>128407963</v>
       </c>
       <c r="B85" t="n">
         <v>57716</v>
@@ -9150,21 +9155,16 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>398278</v>
+        <v>398154</v>
       </c>
       <c r="R85" t="n">
-        <v>6950881</v>
+        <v>6950756</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9194,9 +9194,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9211,60 +9221,61 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128407963</v>
+        <v>128404962</v>
       </c>
       <c r="B86" t="n">
-        <v>57716</v>
+        <v>57881</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>266237</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>398154</v>
+        <v>398392</v>
       </c>
       <c r="R86" t="n">
-        <v>6950756</v>
+        <v>6950406</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9330,49 +9341,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128404962</v>
+        <v>128416210</v>
       </c>
       <c r="B87" t="n">
-        <v>57881</v>
+        <v>91512</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>266237</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>398392</v>
+        <v>398414</v>
       </c>
       <c r="R87" t="n">
-        <v>6950406</v>
+        <v>6950702</v>
       </c>
       <c r="S87" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9399,19 +9409,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9426,12 +9426,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9754,10 +9754,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128410197</v>
+        <v>128413415</v>
       </c>
       <c r="B91" t="n">
-        <v>57716</v>
+        <v>79735</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9765,39 +9765,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>397996</v>
+        <v>398477</v>
       </c>
       <c r="R91" t="n">
-        <v>6950884</v>
+        <v>6951277</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9827,19 +9822,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9854,19 +9839,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128411474</v>
+        <v>128410197</v>
       </c>
       <c r="B92" t="n">
         <v>57716</v>
@@ -9897,7 +9882,7 @@
       <c r="I92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -9906,10 +9891,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>398202</v>
+        <v>397996</v>
       </c>
       <c r="R92" t="n">
-        <v>6950905</v>
+        <v>6950884</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9939,9 +9924,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9956,22 +9951,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128405637</v>
+        <v>128411474</v>
       </c>
       <c r="B93" t="n">
-        <v>91512</v>
+        <v>57716</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9979,34 +9974,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>398426</v>
+        <v>398202</v>
       </c>
       <c r="R93" t="n">
-        <v>6950561</v>
+        <v>6950905</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10065,10 +10065,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128413415</v>
+        <v>128405637</v>
       </c>
       <c r="B94" t="n">
-        <v>79735</v>
+        <v>91512</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10076,34 +10076,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>398477</v>
+        <v>398426</v>
       </c>
       <c r="R94" t="n">
-        <v>6951277</v>
+        <v>6950561</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11178,7 +11178,7 @@
         <v>128406215</v>
       </c>
       <c r="B105" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>128408249</v>
       </c>
       <c r="B107" t="n">
-        <v>78476</v>
+        <v>78480</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>128408651</v>
       </c>
       <c r="B108" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>128416572</v>
       </c>
       <c r="B109" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>128413351</v>
       </c>
       <c r="B113" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 32341-2025 artfynd.xlsx
+++ b/artfynd/A 32341-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128413409</v>
+        <v>128407744</v>
       </c>
       <c r="B2" t="n">
-        <v>79706</v>
+        <v>79739</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398477</v>
+        <v>398173</v>
       </c>
       <c r="R2" t="n">
-        <v>6951277</v>
+        <v>6950715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128407744</v>
+        <v>128412069</v>
       </c>
       <c r="B3" t="n">
-        <v>79735</v>
+        <v>57716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398173</v>
+        <v>398298</v>
       </c>
       <c r="R3" t="n">
-        <v>6950715</v>
+        <v>6950883</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128412069</v>
+        <v>128413409</v>
       </c>
       <c r="B4" t="n">
-        <v>57716</v>
+        <v>79710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +885,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398298</v>
+        <v>398477</v>
       </c>
       <c r="R4" t="n">
-        <v>6950883</v>
+        <v>6951277</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
         <v>128415689</v>
       </c>
       <c r="B5" t="n">
-        <v>78519</v>
+        <v>78523</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128412850</v>
       </c>
       <c r="B6" t="n">
-        <v>78519</v>
+        <v>78523</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>128411332</v>
       </c>
       <c r="B7" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>128412732</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
+        <v>79215</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,32 +1369,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128412642</v>
+        <v>128407381</v>
       </c>
       <c r="B9" t="n">
-        <v>57557</v>
+        <v>82979</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102621</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,13 +1404,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>398437</v>
+        <v>398271</v>
       </c>
       <c r="R9" t="n">
-        <v>6951052</v>
+        <v>6950584</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1437,9 +1437,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1454,44 +1464,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128407381</v>
+        <v>128409340</v>
       </c>
       <c r="B10" t="n">
-        <v>82975</v>
+        <v>80254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>398271</v>
+        <v>397997</v>
       </c>
       <c r="R10" t="n">
-        <v>6950584</v>
+        <v>6950677</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1534,19 +1544,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1561,22 +1561,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128409340</v>
+        <v>128412642</v>
       </c>
       <c r="B11" t="n">
-        <v>80250</v>
+        <v>57557</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1584,21 +1584,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>102621</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,13 +1608,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>397997</v>
+        <v>398437</v>
       </c>
       <c r="R11" t="n">
-        <v>6950677</v>
+        <v>6951052</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128415142</v>
+        <v>128410559</v>
       </c>
       <c r="B14" t="n">
         <v>57716</v>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>398352</v>
+        <v>398097</v>
       </c>
       <c r="R14" t="n">
-        <v>6950954</v>
+        <v>6950870</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128410559</v>
+        <v>128411782</v>
       </c>
       <c r="B15" t="n">
-        <v>57716</v>
+        <v>75205</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,39 +2017,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>398097</v>
+        <v>398234</v>
       </c>
       <c r="R15" t="n">
-        <v>6950870</v>
+        <v>6950852</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128407947</v>
+        <v>128410038</v>
       </c>
       <c r="B16" t="n">
-        <v>82975</v>
+        <v>75205</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>398154</v>
+        <v>397967</v>
       </c>
       <c r="R16" t="n">
-        <v>6950756</v>
+        <v>6950876</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,19 +2181,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2213,22 +2198,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128411782</v>
+        <v>128407947</v>
       </c>
       <c r="B17" t="n">
-        <v>75204</v>
+        <v>82979</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>398234</v>
+        <v>398154</v>
       </c>
       <c r="R17" t="n">
-        <v>6950852</v>
+        <v>6950756</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2295,7 +2280,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2305,7 +2290,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2332,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128410038</v>
+        <v>128415142</v>
       </c>
       <c r="B18" t="n">
-        <v>75204</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,34 +2328,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>397967</v>
+        <v>398352</v>
       </c>
       <c r="R18" t="n">
-        <v>6950876</v>
+        <v>6950954</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,9 +2390,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2417,22 +2417,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128415804</v>
+        <v>128415613</v>
       </c>
       <c r="B19" t="n">
-        <v>78519</v>
+        <v>78786</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2440,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>398394</v>
+        <v>398437</v>
       </c>
       <c r="R19" t="n">
-        <v>6950811</v>
+        <v>6950808</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2497,19 +2497,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2524,22 +2514,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128410565</v>
+        <v>128415804</v>
       </c>
       <c r="B20" t="n">
-        <v>75204</v>
+        <v>78523</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>398088</v>
+        <v>398394</v>
       </c>
       <c r="R20" t="n">
-        <v>6950909</v>
+        <v>6950811</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2604,9 +2594,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2621,22 +2621,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128408059</v>
+        <v>128410565</v>
       </c>
       <c r="B21" t="n">
-        <v>57716</v>
+        <v>75205</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,39 +2644,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>398146</v>
+        <v>398088</v>
       </c>
       <c r="R21" t="n">
-        <v>6950784</v>
+        <v>6950909</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128415613</v>
+        <v>128415681</v>
       </c>
       <c r="B22" t="n">
-        <v>78782</v>
+        <v>79710</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2746,21 +2741,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>398437</v>
+        <v>398394</v>
       </c>
       <c r="R22" t="n">
-        <v>6950808</v>
+        <v>6950811</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2803,9 +2798,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2820,22 +2825,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128415681</v>
+        <v>128408059</v>
       </c>
       <c r="B23" t="n">
-        <v>79706</v>
+        <v>57716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2843,34 +2848,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>398394</v>
+        <v>398146</v>
       </c>
       <c r="R23" t="n">
-        <v>6950811</v>
+        <v>6950784</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2900,19 +2910,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2927,22 +2927,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128410205</v>
+        <v>128405816</v>
       </c>
       <c r="B24" t="n">
-        <v>75204</v>
+        <v>57716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,34 +2950,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>397980</v>
+        <v>398390</v>
       </c>
       <c r="R24" t="n">
-        <v>6950909</v>
+        <v>6950541</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3007,9 +3012,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3024,22 +3039,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128411297</v>
+        <v>128410205</v>
       </c>
       <c r="B25" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3071,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>398143</v>
+        <v>397980</v>
       </c>
       <c r="R25" t="n">
-        <v>6950944</v>
+        <v>6950909</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128413330</v>
+        <v>128411297</v>
       </c>
       <c r="B26" t="n">
-        <v>78519</v>
+        <v>75205</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,21 +3159,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>398486</v>
+        <v>398143</v>
       </c>
       <c r="R26" t="n">
-        <v>6951242</v>
+        <v>6950944</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128410050</v>
+        <v>128413330</v>
       </c>
       <c r="B27" t="n">
-        <v>82975</v>
+        <v>78523</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,21 +3256,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6437</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>397967</v>
+        <v>398486</v>
       </c>
       <c r="R27" t="n">
-        <v>6950876</v>
+        <v>6951242</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3342,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128411229</v>
+        <v>128410050</v>
       </c>
       <c r="B28" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3362,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>398118</v>
+        <v>397967</v>
       </c>
       <c r="R28" t="n">
-        <v>6950921</v>
+        <v>6950876</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3424,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128416541</v>
+        <v>128411229</v>
       </c>
       <c r="B29" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3459,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>398411</v>
+        <v>398118</v>
       </c>
       <c r="R29" t="n">
-        <v>6950623</v>
+        <v>6950921</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3521,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128405816</v>
+        <v>128416541</v>
       </c>
       <c r="B30" t="n">
-        <v>57716</v>
+        <v>82979</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3532,39 +3547,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>398390</v>
+        <v>398411</v>
       </c>
       <c r="R30" t="n">
-        <v>6950541</v>
+        <v>6950623</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3594,19 +3604,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3621,22 +3621,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128408399</v>
+        <v>128405964</v>
       </c>
       <c r="B31" t="n">
-        <v>82975</v>
+        <v>57716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3644,34 +3644,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>398076</v>
+        <v>398364</v>
       </c>
       <c r="R31" t="n">
-        <v>6950793</v>
+        <v>6950589</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3730,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128410403</v>
+        <v>128412757</v>
       </c>
       <c r="B32" t="n">
-        <v>75204</v>
+        <v>57716</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3741,34 +3746,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>398063</v>
+        <v>398460</v>
       </c>
       <c r="R32" t="n">
-        <v>6950893</v>
+        <v>6951061</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3798,9 +3808,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3815,22 +3835,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128411429</v>
+        <v>128415952</v>
       </c>
       <c r="B33" t="n">
-        <v>75204</v>
+        <v>57716</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3838,34 +3858,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>398176</v>
+        <v>398385</v>
       </c>
       <c r="R33" t="n">
-        <v>6950885</v>
+        <v>6950755</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3924,27 +3949,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128405964</v>
+        <v>128413866</v>
       </c>
       <c r="B34" t="n">
-        <v>57716</v>
+        <v>58086</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3955,7 +3980,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3964,13 +3989,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>398364</v>
+        <v>398505</v>
       </c>
       <c r="R34" t="n">
-        <v>6950589</v>
+        <v>6951279</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3997,9 +4022,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4014,22 +4049,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128412757</v>
+        <v>128408399</v>
       </c>
       <c r="B35" t="n">
-        <v>57716</v>
+        <v>82979</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4037,39 +4072,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398460</v>
+        <v>398076</v>
       </c>
       <c r="R35" t="n">
-        <v>6951061</v>
+        <v>6950793</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4099,19 +4129,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4126,22 +4146,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128415952</v>
+        <v>128411736</v>
       </c>
       <c r="B36" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4149,39 +4169,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398385</v>
+        <v>398234</v>
       </c>
       <c r="R36" t="n">
-        <v>6950755</v>
+        <v>6950852</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4211,9 +4226,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4228,22 +4253,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128411736</v>
+        <v>128410403</v>
       </c>
       <c r="B37" t="n">
-        <v>91512</v>
+        <v>75205</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4251,21 +4276,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4275,10 +4300,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>398234</v>
+        <v>398063</v>
       </c>
       <c r="R37" t="n">
-        <v>6950852</v>
+        <v>6950893</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4308,19 +4333,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4335,65 +4350,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128413866</v>
+        <v>128411429</v>
       </c>
       <c r="B38" t="n">
-        <v>58086</v>
+        <v>75205</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>398505</v>
+        <v>398176</v>
       </c>
       <c r="R38" t="n">
-        <v>6951279</v>
+        <v>6950885</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4420,19 +4430,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4447,12 +4447,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4462,7 +4462,7 @@
         <v>128416366</v>
       </c>
       <c r="B39" t="n">
-        <v>78476</v>
+        <v>78480</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4556,32 +4556,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128405669</v>
+        <v>128405841</v>
       </c>
       <c r="B40" t="n">
-        <v>91512</v>
+        <v>92201</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>398398</v>
+        <v>398374</v>
       </c>
       <c r="R40" t="n">
-        <v>6950569</v>
+        <v>6950548</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,32 +4653,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128405841</v>
+        <v>128411735</v>
       </c>
       <c r="B41" t="n">
-        <v>92191</v>
+        <v>75205</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>398374</v>
+        <v>398227</v>
       </c>
       <c r="R41" t="n">
-        <v>6950548</v>
+        <v>6950881</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4753,7 +4753,7 @@
         <v>128412193</v>
       </c>
       <c r="B42" t="n">
-        <v>80256</v>
+        <v>80260</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4847,10 +4847,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128411735</v>
+        <v>128415930</v>
       </c>
       <c r="B43" t="n">
-        <v>75204</v>
+        <v>79710</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4858,21 +4858,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4882,10 +4882,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>398227</v>
+        <v>398387</v>
       </c>
       <c r="R43" t="n">
-        <v>6950881</v>
+        <v>6950766</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4944,10 +4944,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128414073</v>
+        <v>128405669</v>
       </c>
       <c r="B44" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4955,39 +4955,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>398546</v>
+        <v>398398</v>
       </c>
       <c r="R44" t="n">
-        <v>6951235</v>
+        <v>6950569</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5046,7 +5041,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128412950</v>
+        <v>128414073</v>
       </c>
       <c r="B45" t="n">
         <v>57716</v>
@@ -5086,10 +5081,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>398483</v>
+        <v>398546</v>
       </c>
       <c r="R45" t="n">
-        <v>6951117</v>
+        <v>6951235</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5148,10 +5143,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128415930</v>
+        <v>128412950</v>
       </c>
       <c r="B46" t="n">
-        <v>79706</v>
+        <v>57716</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5159,34 +5154,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>398387</v>
+        <v>398483</v>
       </c>
       <c r="R46" t="n">
-        <v>6950766</v>
+        <v>6951117</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5245,10 +5245,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128407293</v>
+        <v>128410408</v>
       </c>
       <c r="B47" t="n">
-        <v>79735</v>
+        <v>79120</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5256,21 +5256,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>398263</v>
+        <v>398063</v>
       </c>
       <c r="R47" t="n">
-        <v>6950596</v>
+        <v>6950893</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5342,32 +5342,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128410408</v>
+        <v>128412638</v>
       </c>
       <c r="B48" t="n">
-        <v>79116</v>
+        <v>57820</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5377,13 +5377,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>398063</v>
+        <v>398437</v>
       </c>
       <c r="R48" t="n">
-        <v>6950893</v>
+        <v>6951052</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5439,10 +5439,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128415932</v>
+        <v>128406327</v>
       </c>
       <c r="B49" t="n">
-        <v>79735</v>
+        <v>91522</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5450,21 +5450,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>398387</v>
+        <v>398333</v>
       </c>
       <c r="R49" t="n">
-        <v>6950766</v>
+        <v>6950603</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5536,10 +5536,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128412677</v>
+        <v>128411964</v>
       </c>
       <c r="B50" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5547,39 +5547,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>398462</v>
+        <v>398278</v>
       </c>
       <c r="R50" t="n">
-        <v>6951039</v>
+        <v>6950881</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5609,19 +5604,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5636,22 +5621,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128415972</v>
+        <v>128407293</v>
       </c>
       <c r="B51" t="n">
-        <v>57716</v>
+        <v>79739</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5659,39 +5644,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>398396</v>
+        <v>398263</v>
       </c>
       <c r="R51" t="n">
-        <v>6950719</v>
+        <v>6950596</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5750,10 +5730,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128406327</v>
+        <v>128415932</v>
       </c>
       <c r="B52" t="n">
-        <v>91512</v>
+        <v>79739</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5761,21 +5741,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5785,10 +5765,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>398333</v>
+        <v>398387</v>
       </c>
       <c r="R52" t="n">
-        <v>6950603</v>
+        <v>6950766</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5847,10 +5827,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128411964</v>
+        <v>128412677</v>
       </c>
       <c r="B53" t="n">
-        <v>91512</v>
+        <v>57716</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5858,34 +5838,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>398278</v>
+        <v>398462</v>
       </c>
       <c r="R53" t="n">
-        <v>6950881</v>
+        <v>6951039</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5915,9 +5900,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5932,22 +5927,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128408097</v>
+        <v>128415972</v>
       </c>
       <c r="B54" t="n">
-        <v>57876</v>
+        <v>57716</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5955,27 +5950,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5984,13 +5979,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>398159</v>
+        <v>398396</v>
       </c>
       <c r="R54" t="n">
-        <v>6950801</v>
+        <v>6950719</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6017,19 +6012,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6044,60 +6029,65 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128412638</v>
+        <v>128408097</v>
       </c>
       <c r="B55" t="n">
-        <v>57820</v>
+        <v>57876</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>398437</v>
+        <v>398159</v>
       </c>
       <c r="R55" t="n">
-        <v>6951052</v>
+        <v>6950801</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6124,9 +6114,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6141,65 +6141,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128408773</v>
+        <v>128408521</v>
       </c>
       <c r="B56" t="n">
-        <v>58086</v>
+        <v>79739</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>398012</v>
+        <v>398019</v>
       </c>
       <c r="R56" t="n">
-        <v>6950659</v>
+        <v>6950740</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6226,19 +6221,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6253,60 +6238,65 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128409775</v>
+        <v>128408773</v>
       </c>
       <c r="B57" t="n">
-        <v>79706</v>
+        <v>58086</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>398008</v>
+        <v>398012</v>
       </c>
       <c r="R57" t="n">
-        <v>6950745</v>
+        <v>6950659</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6333,9 +6323,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6350,22 +6350,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128408521</v>
+        <v>128409775</v>
       </c>
       <c r="B58" t="n">
-        <v>79735</v>
+        <v>79710</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6373,21 +6373,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6397,10 +6397,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>398019</v>
+        <v>398008</v>
       </c>
       <c r="R58" t="n">
-        <v>6950740</v>
+        <v>6950745</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6459,7 +6459,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128405859</v>
+        <v>128413307</v>
       </c>
       <c r="B59" t="n">
         <v>57716</v>
@@ -6499,10 +6499,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>398362</v>
+        <v>398457</v>
       </c>
       <c r="R59" t="n">
-        <v>6950549</v>
+        <v>6951226</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6571,7 +6571,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128413307</v>
+        <v>128405859</v>
       </c>
       <c r="B60" t="n">
         <v>57716</v>
@@ -6611,10 +6611,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>398457</v>
+        <v>398362</v>
       </c>
       <c r="R60" t="n">
-        <v>6951226</v>
+        <v>6950549</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6785,10 +6785,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128415836</v>
+        <v>128406318</v>
       </c>
       <c r="B62" t="n">
-        <v>78088</v>
+        <v>79120</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6796,21 +6796,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6820,10 +6820,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>398394</v>
+        <v>398333</v>
       </c>
       <c r="R62" t="n">
-        <v>6950811</v>
+        <v>6950603</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6853,19 +6853,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6880,22 +6870,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128406026</v>
+        <v>128409691</v>
       </c>
       <c r="B63" t="n">
-        <v>79735</v>
+        <v>90536</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6903,21 +6893,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6927,10 +6917,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>398364</v>
+        <v>398057</v>
       </c>
       <c r="R63" t="n">
-        <v>6950589</v>
+        <v>6950739</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6960,9 +6950,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6977,22 +6977,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128409691</v>
+        <v>128415836</v>
       </c>
       <c r="B64" t="n">
-        <v>90526</v>
+        <v>78092</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7000,21 +7000,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7024,10 +7024,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>398057</v>
+        <v>398394</v>
       </c>
       <c r="R64" t="n">
-        <v>6950739</v>
+        <v>6950811</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7096,10 +7096,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128415706</v>
+        <v>128406026</v>
       </c>
       <c r="B65" t="n">
-        <v>57716</v>
+        <v>79739</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7107,39 +7107,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>398411</v>
+        <v>398364</v>
       </c>
       <c r="R65" t="n">
-        <v>6950796</v>
+        <v>6950589</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7198,10 +7193,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128416501</v>
+        <v>128407307</v>
       </c>
       <c r="B66" t="n">
-        <v>57716</v>
+        <v>78878</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7209,39 +7204,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>398382</v>
+        <v>398263</v>
       </c>
       <c r="R66" t="n">
-        <v>6950639</v>
+        <v>6950596</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7271,19 +7261,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7298,22 +7278,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128406318</v>
+        <v>128415706</v>
       </c>
       <c r="B67" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7321,34 +7301,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>398333</v>
+        <v>398411</v>
       </c>
       <c r="R67" t="n">
-        <v>6950603</v>
+        <v>6950796</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7407,10 +7392,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128407307</v>
+        <v>128416501</v>
       </c>
       <c r="B68" t="n">
-        <v>78874</v>
+        <v>57716</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7418,34 +7403,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>398263</v>
+        <v>398382</v>
       </c>
       <c r="R68" t="n">
-        <v>6950596</v>
+        <v>6950639</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7475,9 +7465,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7492,22 +7492,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128411612</v>
+        <v>128411524</v>
       </c>
       <c r="B69" t="n">
-        <v>79195</v>
+        <v>57716</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7515,34 +7515,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>398200</v>
+        <v>398203</v>
       </c>
       <c r="R69" t="n">
-        <v>6950918</v>
+        <v>6950901</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7572,9 +7577,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7589,22 +7604,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128411931</v>
+        <v>128411180</v>
       </c>
       <c r="B70" t="n">
-        <v>91512</v>
+        <v>57716</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7612,34 +7627,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>398276</v>
+        <v>398102</v>
       </c>
       <c r="R70" t="n">
-        <v>6950842</v>
+        <v>6950907</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7669,9 +7689,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7686,12 +7716,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7701,7 +7731,7 @@
         <v>128411308</v>
       </c>
       <c r="B71" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7795,10 +7825,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128411524</v>
+        <v>128411612</v>
       </c>
       <c r="B72" t="n">
-        <v>57716</v>
+        <v>79199</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7806,39 +7836,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>398203</v>
+        <v>398200</v>
       </c>
       <c r="R72" t="n">
-        <v>6950901</v>
+        <v>6950918</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7868,19 +7893,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7895,22 +7910,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128411180</v>
+        <v>128411931</v>
       </c>
       <c r="B73" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7918,39 +7933,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>398102</v>
+        <v>398276</v>
       </c>
       <c r="R73" t="n">
-        <v>6950907</v>
+        <v>6950842</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7980,19 +7990,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8007,22 +8007,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128412048</v>
+        <v>128405468</v>
       </c>
       <c r="B74" t="n">
-        <v>57716</v>
+        <v>82979</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8030,39 +8030,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>398329</v>
+        <v>398405</v>
       </c>
       <c r="R74" t="n">
-        <v>6950952</v>
+        <v>6950503</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8092,19 +8087,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8119,62 +8104,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128406114</v>
+        <v>128416207</v>
       </c>
       <c r="B75" t="n">
-        <v>57716</v>
+        <v>75203</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>398351</v>
+        <v>398414</v>
       </c>
       <c r="R75" t="n">
-        <v>6950591</v>
+        <v>6950702</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8204,19 +8184,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8231,12 +8201,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8340,10 +8310,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128412825</v>
+        <v>128406114</v>
       </c>
       <c r="B77" t="n">
-        <v>79706</v>
+        <v>57716</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8351,34 +8321,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>398474</v>
+        <v>398351</v>
       </c>
       <c r="R77" t="n">
-        <v>6951085</v>
+        <v>6950591</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8408,9 +8383,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8425,22 +8410,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128405468</v>
+        <v>128412048</v>
       </c>
       <c r="B78" t="n">
-        <v>82975</v>
+        <v>57716</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8448,34 +8433,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>398405</v>
+        <v>398329</v>
       </c>
       <c r="R78" t="n">
-        <v>6950503</v>
+        <v>6950952</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8505,9 +8495,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8522,44 +8522,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128416207</v>
+        <v>128412825</v>
       </c>
       <c r="B79" t="n">
-        <v>75202</v>
+        <v>79710</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6486</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>398414</v>
+        <v>398474</v>
       </c>
       <c r="R79" t="n">
-        <v>6950702</v>
+        <v>6951085</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8631,10 +8631,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128405900</v>
+        <v>128411329</v>
       </c>
       <c r="B80" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8642,39 +8642,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>398362</v>
+        <v>398173</v>
       </c>
       <c r="R80" t="n">
-        <v>6950568</v>
+        <v>6950901</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8733,10 +8728,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128411329</v>
+        <v>128405900</v>
       </c>
       <c r="B81" t="n">
-        <v>91512</v>
+        <v>57716</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8744,34 +8739,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>398173</v>
+        <v>398362</v>
       </c>
       <c r="R81" t="n">
-        <v>6950901</v>
+        <v>6950568</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8833,7 +8833,7 @@
         <v>128411270</v>
       </c>
       <c r="B82" t="n">
-        <v>78519</v>
+        <v>78523</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>128407528</v>
       </c>
       <c r="B83" t="n">
-        <v>78782</v>
+        <v>78786</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9024,10 +9024,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128411972</v>
+        <v>128416210</v>
       </c>
       <c r="B84" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9035,39 +9035,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>398278</v>
+        <v>398414</v>
       </c>
       <c r="R84" t="n">
-        <v>6950881</v>
+        <v>6950702</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9126,7 +9121,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128407963</v>
+        <v>128411972</v>
       </c>
       <c r="B85" t="n">
         <v>57716</v>
@@ -9155,16 +9150,21 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>398154</v>
+        <v>398278</v>
       </c>
       <c r="R85" t="n">
-        <v>6950756</v>
+        <v>6950881</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9194,19 +9194,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9221,61 +9211,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128404962</v>
+        <v>128407963</v>
       </c>
       <c r="B86" t="n">
-        <v>57881</v>
+        <v>57716</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>266237</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>398392</v>
+        <v>398154</v>
       </c>
       <c r="R86" t="n">
-        <v>6950406</v>
+        <v>6950756</v>
       </c>
       <c r="S86" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9341,48 +9330,49 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128416210</v>
+        <v>128404962</v>
       </c>
       <c r="B87" t="n">
-        <v>91512</v>
+        <v>57881</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5432</v>
+        <v>266237</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>398414</v>
+        <v>398392</v>
       </c>
       <c r="R87" t="n">
-        <v>6950702</v>
+        <v>6950406</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9409,9 +9399,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9426,12 +9426,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9441,7 +9441,7 @@
         <v>128410048</v>
       </c>
       <c r="B88" t="n">
-        <v>78476</v>
+        <v>78480</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9535,10 +9535,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128415905</v>
+        <v>128407736</v>
       </c>
       <c r="B89" t="n">
-        <v>78519</v>
+        <v>57716</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9546,34 +9546,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>398403</v>
+        <v>398169</v>
       </c>
       <c r="R89" t="n">
-        <v>6950826</v>
+        <v>6950711</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9605,7 +9610,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9615,7 +9620,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9642,10 +9647,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128407736</v>
+        <v>128415905</v>
       </c>
       <c r="B90" t="n">
-        <v>57716</v>
+        <v>78523</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9653,39 +9658,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>398169</v>
+        <v>398403</v>
       </c>
       <c r="R90" t="n">
-        <v>6950711</v>
+        <v>6950826</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9754,10 +9754,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128413415</v>
+        <v>128410197</v>
       </c>
       <c r="B91" t="n">
-        <v>79735</v>
+        <v>57716</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9765,34 +9765,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>398477</v>
+        <v>397996</v>
       </c>
       <c r="R91" t="n">
-        <v>6951277</v>
+        <v>6950884</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9822,9 +9827,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9839,22 +9854,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128410197</v>
+        <v>128413415</v>
       </c>
       <c r="B92" t="n">
-        <v>57716</v>
+        <v>79739</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9862,39 +9877,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>397996</v>
+        <v>398477</v>
       </c>
       <c r="R92" t="n">
-        <v>6950884</v>
+        <v>6951277</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9924,19 +9934,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9951,22 +9951,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128411474</v>
+        <v>128405637</v>
       </c>
       <c r="B93" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9974,39 +9974,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>398202</v>
+        <v>398426</v>
       </c>
       <c r="R93" t="n">
-        <v>6950905</v>
+        <v>6950561</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10065,10 +10060,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128405637</v>
+        <v>128411474</v>
       </c>
       <c r="B94" t="n">
-        <v>91512</v>
+        <v>57716</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10076,34 +10071,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>398426</v>
+        <v>398202</v>
       </c>
       <c r="R94" t="n">
-        <v>6950561</v>
+        <v>6950905</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10162,32 +10162,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128413088</v>
+        <v>128411728</v>
       </c>
       <c r="B95" t="n">
-        <v>82975</v>
+        <v>78480</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1312</v>
+        <v>498</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10197,10 +10197,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>398494</v>
+        <v>398227</v>
       </c>
       <c r="R95" t="n">
-        <v>6951141</v>
+        <v>6950881</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10259,32 +10259,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128411728</v>
+        <v>128410472</v>
       </c>
       <c r="B96" t="n">
-        <v>78476</v>
+        <v>75205</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>398227</v>
+        <v>398075</v>
       </c>
       <c r="R96" t="n">
-        <v>6950881</v>
+        <v>6950912</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10356,10 +10356,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128410472</v>
+        <v>128407311</v>
       </c>
       <c r="B97" t="n">
-        <v>75204</v>
+        <v>78523</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10367,21 +10367,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10391,10 +10391,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>398075</v>
+        <v>398263</v>
       </c>
       <c r="R97" t="n">
-        <v>6950912</v>
+        <v>6950596</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10453,10 +10453,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128407311</v>
+        <v>128413088</v>
       </c>
       <c r="B98" t="n">
-        <v>78519</v>
+        <v>82979</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10464,21 +10464,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10488,10 +10488,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>398263</v>
+        <v>398494</v>
       </c>
       <c r="R98" t="n">
-        <v>6950596</v>
+        <v>6951141</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10550,10 +10550,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128413083</v>
+        <v>128413214</v>
       </c>
       <c r="B99" t="n">
-        <v>75204</v>
+        <v>57716</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10561,34 +10561,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>398494</v>
+        <v>398467</v>
       </c>
       <c r="R99" t="n">
-        <v>6951141</v>
+        <v>6951207</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10647,7 +10652,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128413214</v>
+        <v>128415580</v>
       </c>
       <c r="B100" t="n">
         <v>57716</v>
@@ -10678,7 +10683,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -10687,10 +10692,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>398467</v>
+        <v>398442</v>
       </c>
       <c r="R100" t="n">
-        <v>6951207</v>
+        <v>6950833</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10749,10 +10754,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128415580</v>
+        <v>128413083</v>
       </c>
       <c r="B101" t="n">
-        <v>57716</v>
+        <v>75205</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10760,39 +10765,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>398442</v>
+        <v>398494</v>
       </c>
       <c r="R101" t="n">
-        <v>6950833</v>
+        <v>6951141</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10854,7 +10854,7 @@
         <v>128413296</v>
       </c>
       <c r="B102" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>128407903</v>
       </c>
       <c r="B103" t="n">
-        <v>81121</v>
+        <v>81125</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>128408651</v>
       </c>
       <c r="B108" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>128416572</v>
       </c>
       <c r="B109" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>

--- a/artfynd/A 32341-2025 artfynd.xlsx
+++ b/artfynd/A 32341-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128407744</v>
+        <v>128413409</v>
       </c>
       <c r="B2" t="n">
-        <v>79739</v>
+        <v>79710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398173</v>
+        <v>398477</v>
       </c>
       <c r="R2" t="n">
-        <v>6950715</v>
+        <v>6951277</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128412069</v>
+        <v>128407744</v>
       </c>
       <c r="B3" t="n">
-        <v>57716</v>
+        <v>79739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398298</v>
+        <v>398173</v>
       </c>
       <c r="R3" t="n">
-        <v>6950883</v>
+        <v>6950715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128413409</v>
+        <v>128412069</v>
       </c>
       <c r="B4" t="n">
-        <v>79710</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398477</v>
+        <v>398298</v>
       </c>
       <c r="R4" t="n">
-        <v>6951277</v>
+        <v>6950883</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128415689</v>
+        <v>128412732</v>
       </c>
       <c r="B5" t="n">
-        <v>78523</v>
+        <v>79215</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>967</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>398409</v>
+        <v>398474</v>
       </c>
       <c r="R5" t="n">
-        <v>6950805</v>
+        <v>6951085</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,7 +1068,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128412850</v>
+        <v>128415689</v>
       </c>
       <c r="B6" t="n">
         <v>78523</v>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>398474</v>
+        <v>398409</v>
       </c>
       <c r="R6" t="n">
-        <v>6951085</v>
+        <v>6950805</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128411332</v>
+        <v>128412850</v>
       </c>
       <c r="B7" t="n">
-        <v>75205</v>
+        <v>78523</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>398187</v>
+        <v>398474</v>
       </c>
       <c r="R7" t="n">
-        <v>6950935</v>
+        <v>6951085</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1233,19 +1233,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1260,22 +1250,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128412732</v>
+        <v>128411332</v>
       </c>
       <c r="B8" t="n">
-        <v>79215</v>
+        <v>75205</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>967</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>398474</v>
+        <v>398187</v>
       </c>
       <c r="R8" t="n">
-        <v>6951085</v>
+        <v>6950935</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1340,9 +1330,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1357,12 +1357,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1573,27 +1573,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128412642</v>
+        <v>128407432</v>
       </c>
       <c r="B11" t="n">
-        <v>57557</v>
+        <v>57716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1602,19 +1602,24 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>398437</v>
+        <v>398269</v>
       </c>
       <c r="R11" t="n">
-        <v>6951052</v>
+        <v>6950563</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1641,9 +1646,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1658,19 +1673,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128407432</v>
+        <v>128415979</v>
       </c>
       <c r="B12" t="n">
         <v>57716</v>
@@ -1710,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>398269</v>
+        <v>398372</v>
       </c>
       <c r="R12" t="n">
-        <v>6950563</v>
+        <v>6950738</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,7 +1760,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,27 +1797,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128415979</v>
+        <v>128412642</v>
       </c>
       <c r="B13" t="n">
-        <v>57716</v>
+        <v>57557</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1811,24 +1826,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>398372</v>
+        <v>398437</v>
       </c>
       <c r="R13" t="n">
-        <v>6950738</v>
+        <v>6951052</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1855,19 +1865,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1882,22 +1882,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128410559</v>
+        <v>128407947</v>
       </c>
       <c r="B14" t="n">
-        <v>57716</v>
+        <v>82979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1905,39 +1905,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>398097</v>
+        <v>398154</v>
       </c>
       <c r="R14" t="n">
-        <v>6950870</v>
+        <v>6950756</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,7 +1964,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1979,7 +1974,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2210,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128407947</v>
+        <v>128415142</v>
       </c>
       <c r="B17" t="n">
-        <v>82979</v>
+        <v>57716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2221,34 +2216,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>398154</v>
+        <v>398352</v>
       </c>
       <c r="R17" t="n">
-        <v>6950756</v>
+        <v>6950954</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2317,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128415142</v>
+        <v>128410559</v>
       </c>
       <c r="B18" t="n">
         <v>57716</v>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>398352</v>
+        <v>398097</v>
       </c>
       <c r="R18" t="n">
-        <v>6950954</v>
+        <v>6950870</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128415613</v>
+        <v>128415681</v>
       </c>
       <c r="B19" t="n">
-        <v>78786</v>
+        <v>79710</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2440,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>398437</v>
+        <v>398394</v>
       </c>
       <c r="R19" t="n">
-        <v>6950808</v>
+        <v>6950811</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2497,9 +2497,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2514,22 +2524,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128415804</v>
+        <v>128415613</v>
       </c>
       <c r="B20" t="n">
-        <v>78523</v>
+        <v>78786</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2537,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>398394</v>
+        <v>398437</v>
       </c>
       <c r="R20" t="n">
-        <v>6950811</v>
+        <v>6950808</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2594,19 +2604,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2621,22 +2621,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128410565</v>
+        <v>128415804</v>
       </c>
       <c r="B21" t="n">
-        <v>75205</v>
+        <v>78523</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,21 +2644,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>398088</v>
+        <v>398394</v>
       </c>
       <c r="R21" t="n">
-        <v>6950909</v>
+        <v>6950811</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2701,9 +2701,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2718,22 +2728,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128415681</v>
+        <v>128410565</v>
       </c>
       <c r="B22" t="n">
-        <v>79710</v>
+        <v>75205</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2741,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>398394</v>
+        <v>398088</v>
       </c>
       <c r="R22" t="n">
-        <v>6950811</v>
+        <v>6950909</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2798,19 +2808,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2825,12 +2825,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3051,10 +3051,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128410205</v>
+        <v>128410050</v>
       </c>
       <c r="B25" t="n">
-        <v>75205</v>
+        <v>82979</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3062,21 +3062,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>397980</v>
+        <v>397967</v>
       </c>
       <c r="R25" t="n">
-        <v>6950909</v>
+        <v>6950876</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128411297</v>
+        <v>128411229</v>
       </c>
       <c r="B26" t="n">
-        <v>75205</v>
+        <v>82979</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3159,21 +3159,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>398143</v>
+        <v>398118</v>
       </c>
       <c r="R26" t="n">
-        <v>6950944</v>
+        <v>6950921</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128413330</v>
+        <v>128416541</v>
       </c>
       <c r="B27" t="n">
-        <v>78523</v>
+        <v>82979</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3256,21 +3256,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3280,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>398486</v>
+        <v>398411</v>
       </c>
       <c r="R27" t="n">
-        <v>6951242</v>
+        <v>6950623</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,10 +3342,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128410050</v>
+        <v>128410205</v>
       </c>
       <c r="B28" t="n">
-        <v>82979</v>
+        <v>75205</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3353,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>397967</v>
+        <v>397980</v>
       </c>
       <c r="R28" t="n">
-        <v>6950876</v>
+        <v>6950909</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128411229</v>
+        <v>128411297</v>
       </c>
       <c r="B29" t="n">
-        <v>82979</v>
+        <v>75205</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3450,21 +3450,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>398118</v>
+        <v>398143</v>
       </c>
       <c r="R29" t="n">
-        <v>6950921</v>
+        <v>6950944</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128416541</v>
+        <v>128413330</v>
       </c>
       <c r="B30" t="n">
-        <v>82979</v>
+        <v>78523</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3547,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>398411</v>
+        <v>398486</v>
       </c>
       <c r="R30" t="n">
-        <v>6950623</v>
+        <v>6951242</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128405964</v>
+        <v>128411736</v>
       </c>
       <c r="B31" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3644,39 +3644,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>398364</v>
+        <v>398234</v>
       </c>
       <c r="R31" t="n">
-        <v>6950589</v>
+        <v>6950852</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3706,9 +3701,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3723,19 +3728,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128412757</v>
+        <v>128405964</v>
       </c>
       <c r="B32" t="n">
         <v>57716</v>
@@ -3766,7 +3771,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3775,10 +3780,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>398460</v>
+        <v>398364</v>
       </c>
       <c r="R32" t="n">
-        <v>6951061</v>
+        <v>6950589</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3808,19 +3813,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3835,19 +3830,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128415952</v>
+        <v>128412757</v>
       </c>
       <c r="B33" t="n">
         <v>57716</v>
@@ -3878,7 +3873,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3887,10 +3882,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>398385</v>
+        <v>398460</v>
       </c>
       <c r="R33" t="n">
-        <v>6950755</v>
+        <v>6951061</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3920,9 +3915,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3937,39 +3942,39 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128413866</v>
+        <v>128415952</v>
       </c>
       <c r="B34" t="n">
-        <v>58086</v>
+        <v>57716</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3980,7 +3985,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3989,13 +3994,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>398505</v>
+        <v>398385</v>
       </c>
       <c r="R34" t="n">
-        <v>6951279</v>
+        <v>6950755</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4022,19 +4027,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4049,12 +4044,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4158,10 +4153,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128411736</v>
+        <v>128410403</v>
       </c>
       <c r="B36" t="n">
-        <v>91522</v>
+        <v>75205</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4169,21 +4164,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4193,10 +4188,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398234</v>
+        <v>398063</v>
       </c>
       <c r="R36" t="n">
-        <v>6950852</v>
+        <v>6950893</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4226,19 +4221,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4253,19 +4238,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128410403</v>
+        <v>128411429</v>
       </c>
       <c r="B37" t="n">
         <v>75205</v>
@@ -4300,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>398063</v>
+        <v>398176</v>
       </c>
       <c r="R37" t="n">
-        <v>6950893</v>
+        <v>6950885</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4362,48 +4347,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128411429</v>
+        <v>128413866</v>
       </c>
       <c r="B38" t="n">
-        <v>75205</v>
+        <v>58086</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>398176</v>
+        <v>398505</v>
       </c>
       <c r="R38" t="n">
-        <v>6950885</v>
+        <v>6951279</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4430,9 +4420,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4447,12 +4447,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4556,10 +4556,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128405841</v>
+        <v>128412193</v>
       </c>
       <c r="B40" t="n">
-        <v>92201</v>
+        <v>80260</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4567,21 +4567,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3298</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>398374</v>
+        <v>398369</v>
       </c>
       <c r="R40" t="n">
-        <v>6950548</v>
+        <v>6950956</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4750,32 +4750,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128412193</v>
+        <v>128405669</v>
       </c>
       <c r="B42" t="n">
-        <v>80260</v>
+        <v>91522</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4785,10 +4785,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>398369</v>
+        <v>398398</v>
       </c>
       <c r="R42" t="n">
-        <v>6950956</v>
+        <v>6950569</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4847,32 +4847,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128415930</v>
+        <v>128405841</v>
       </c>
       <c r="B43" t="n">
-        <v>79710</v>
+        <v>92201</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>3298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4882,10 +4882,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>398387</v>
+        <v>398374</v>
       </c>
       <c r="R43" t="n">
-        <v>6950766</v>
+        <v>6950548</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4944,10 +4944,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128405669</v>
+        <v>128414073</v>
       </c>
       <c r="B44" t="n">
-        <v>91522</v>
+        <v>57716</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4955,34 +4955,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>398398</v>
+        <v>398546</v>
       </c>
       <c r="R44" t="n">
-        <v>6950569</v>
+        <v>6951235</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5041,7 +5046,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128414073</v>
+        <v>128412950</v>
       </c>
       <c r="B45" t="n">
         <v>57716</v>
@@ -5081,10 +5086,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>398546</v>
+        <v>398483</v>
       </c>
       <c r="R45" t="n">
-        <v>6951235</v>
+        <v>6951117</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5143,10 +5148,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128412950</v>
+        <v>128415930</v>
       </c>
       <c r="B46" t="n">
-        <v>57716</v>
+        <v>79710</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5154,39 +5159,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>398483</v>
+        <v>398387</v>
       </c>
       <c r="R46" t="n">
-        <v>6951117</v>
+        <v>6950766</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5245,10 +5245,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128410408</v>
+        <v>128407293</v>
       </c>
       <c r="B47" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5256,21 +5256,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>398063</v>
+        <v>398263</v>
       </c>
       <c r="R47" t="n">
-        <v>6950893</v>
+        <v>6950596</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5342,32 +5342,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128412638</v>
+        <v>128410408</v>
       </c>
       <c r="B48" t="n">
-        <v>57820</v>
+        <v>79120</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5377,13 +5377,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>398437</v>
+        <v>398063</v>
       </c>
       <c r="R48" t="n">
-        <v>6951052</v>
+        <v>6950893</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5439,10 +5439,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128406327</v>
+        <v>128415932</v>
       </c>
       <c r="B49" t="n">
-        <v>91522</v>
+        <v>79739</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5450,21 +5450,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>398333</v>
+        <v>398387</v>
       </c>
       <c r="R49" t="n">
-        <v>6950603</v>
+        <v>6950766</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5536,10 +5536,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128411964</v>
+        <v>128408097</v>
       </c>
       <c r="B50" t="n">
-        <v>91522</v>
+        <v>57876</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5547,37 +5547,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>398278</v>
+        <v>398159</v>
       </c>
       <c r="R50" t="n">
-        <v>6950881</v>
+        <v>6950801</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5604,9 +5609,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5621,22 +5636,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128407293</v>
+        <v>128406327</v>
       </c>
       <c r="B51" t="n">
-        <v>79739</v>
+        <v>91522</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5644,21 +5659,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5668,10 +5683,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>398263</v>
+        <v>398333</v>
       </c>
       <c r="R51" t="n">
-        <v>6950596</v>
+        <v>6950603</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5730,10 +5745,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128415932</v>
+        <v>128411964</v>
       </c>
       <c r="B52" t="n">
-        <v>79739</v>
+        <v>91522</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5741,21 +5756,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5765,10 +5780,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>398387</v>
+        <v>398278</v>
       </c>
       <c r="R52" t="n">
-        <v>6950766</v>
+        <v>6950881</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6041,53 +6056,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128408097</v>
+        <v>128412638</v>
       </c>
       <c r="B55" t="n">
-        <v>57876</v>
+        <v>57820</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>398159</v>
+        <v>398437</v>
       </c>
       <c r="R55" t="n">
-        <v>6950801</v>
+        <v>6951052</v>
       </c>
       <c r="S55" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6114,19 +6124,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6141,12 +6141,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6250,27 +6250,27 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128408773</v>
+        <v>128405859</v>
       </c>
       <c r="B57" t="n">
-        <v>58086</v>
+        <v>57716</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6281,7 +6281,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>398012</v>
+        <v>398362</v>
       </c>
       <c r="R57" t="n">
-        <v>6950659</v>
+        <v>6950549</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6362,10 +6362,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128409775</v>
+        <v>128413307</v>
       </c>
       <c r="B58" t="n">
-        <v>79710</v>
+        <v>57716</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6373,34 +6373,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>398008</v>
+        <v>398457</v>
       </c>
       <c r="R58" t="n">
-        <v>6950745</v>
+        <v>6951226</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6430,9 +6435,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6447,39 +6462,39 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128413307</v>
+        <v>128408773</v>
       </c>
       <c r="B59" t="n">
-        <v>57716</v>
+        <v>58086</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6490,7 +6505,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6499,13 +6514,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>398457</v>
+        <v>398012</v>
       </c>
       <c r="R59" t="n">
-        <v>6951226</v>
+        <v>6950659</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6534,7 +6549,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6544,7 +6559,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6571,10 +6586,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128405859</v>
+        <v>128409775</v>
       </c>
       <c r="B60" t="n">
-        <v>57716</v>
+        <v>79710</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6582,39 +6597,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>398362</v>
+        <v>398008</v>
       </c>
       <c r="R60" t="n">
-        <v>6950549</v>
+        <v>6950745</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6644,19 +6654,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6671,12 +6671,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6785,10 +6785,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128406318</v>
+        <v>128407307</v>
       </c>
       <c r="B62" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6796,21 +6796,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6820,10 +6820,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>398333</v>
+        <v>398263</v>
       </c>
       <c r="R62" t="n">
-        <v>6950603</v>
+        <v>6950596</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6882,10 +6882,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128409691</v>
+        <v>128406318</v>
       </c>
       <c r="B63" t="n">
-        <v>90536</v>
+        <v>79120</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6893,21 +6893,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6917,10 +6917,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>398057</v>
+        <v>398333</v>
       </c>
       <c r="R63" t="n">
-        <v>6950739</v>
+        <v>6950603</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6950,19 +6950,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6977,12 +6967,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7193,10 +7183,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128407307</v>
+        <v>128415706</v>
       </c>
       <c r="B66" t="n">
-        <v>78878</v>
+        <v>57716</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7204,34 +7194,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>398263</v>
+        <v>398411</v>
       </c>
       <c r="R66" t="n">
-        <v>6950596</v>
+        <v>6950796</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7290,7 +7285,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128415706</v>
+        <v>128416501</v>
       </c>
       <c r="B67" t="n">
         <v>57716</v>
@@ -7321,7 +7316,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7330,10 +7325,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>398411</v>
+        <v>398382</v>
       </c>
       <c r="R67" t="n">
-        <v>6950796</v>
+        <v>6950639</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7363,9 +7358,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7380,22 +7385,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128416501</v>
+        <v>128409691</v>
       </c>
       <c r="B68" t="n">
-        <v>57716</v>
+        <v>90536</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7403,39 +7408,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>398382</v>
+        <v>398057</v>
       </c>
       <c r="R68" t="n">
-        <v>6950639</v>
+        <v>6950739</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7504,10 +7504,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128411524</v>
+        <v>128411612</v>
       </c>
       <c r="B69" t="n">
-        <v>57716</v>
+        <v>79199</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7515,39 +7515,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>398203</v>
+        <v>398200</v>
       </c>
       <c r="R69" t="n">
-        <v>6950901</v>
+        <v>6950918</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7577,19 +7572,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7604,22 +7589,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128411180</v>
+        <v>128411308</v>
       </c>
       <c r="B70" t="n">
-        <v>57716</v>
+        <v>75205</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7627,39 +7612,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>398102</v>
+        <v>398162</v>
       </c>
       <c r="R70" t="n">
-        <v>6950907</v>
+        <v>6950923</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7689,19 +7669,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7716,22 +7686,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128411308</v>
+        <v>128411524</v>
       </c>
       <c r="B71" t="n">
-        <v>75205</v>
+        <v>57716</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7739,34 +7709,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>398162</v>
+        <v>398203</v>
       </c>
       <c r="R71" t="n">
-        <v>6950923</v>
+        <v>6950901</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7796,9 +7771,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7813,22 +7798,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128411612</v>
+        <v>128411180</v>
       </c>
       <c r="B72" t="n">
-        <v>79199</v>
+        <v>57716</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7836,34 +7821,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>398200</v>
+        <v>398102</v>
       </c>
       <c r="R72" t="n">
-        <v>6950918</v>
+        <v>6950907</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7893,9 +7883,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7910,12 +7910,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8019,10 +8019,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128405468</v>
+        <v>128412825</v>
       </c>
       <c r="B74" t="n">
-        <v>82979</v>
+        <v>79710</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8030,34 +8030,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>398405</v>
+        <v>398474</v>
       </c>
       <c r="R74" t="n">
-        <v>6950503</v>
+        <v>6951085</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8116,45 +8116,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128416207</v>
+        <v>128405468</v>
       </c>
       <c r="B75" t="n">
-        <v>75203</v>
+        <v>82979</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6486</v>
+        <v>1312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>398414</v>
+        <v>398405</v>
       </c>
       <c r="R75" t="n">
-        <v>6950702</v>
+        <v>6950503</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8213,32 +8213,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128412622</v>
+        <v>128416207</v>
       </c>
       <c r="B76" t="n">
-        <v>58086</v>
+        <v>75203</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103015</v>
+        <v>6486</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8248,13 +8248,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>398437</v>
+        <v>398414</v>
       </c>
       <c r="R76" t="n">
-        <v>6951052</v>
+        <v>6950702</v>
       </c>
       <c r="S76" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128406114</v>
+        <v>128412048</v>
       </c>
       <c r="B77" t="n">
         <v>57716</v>
@@ -8350,10 +8350,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>398351</v>
+        <v>398329</v>
       </c>
       <c r="R77" t="n">
-        <v>6950591</v>
+        <v>6950952</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8385,7 +8385,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8422,7 +8422,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128412048</v>
+        <v>128406114</v>
       </c>
       <c r="B78" t="n">
         <v>57716</v>
@@ -8462,10 +8462,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>398329</v>
+        <v>398351</v>
       </c>
       <c r="R78" t="n">
-        <v>6950952</v>
+        <v>6950591</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8497,7 +8497,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8534,32 +8534,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128412825</v>
+        <v>128412622</v>
       </c>
       <c r="B79" t="n">
-        <v>79710</v>
+        <v>58086</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8569,13 +8569,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>398474</v>
+        <v>398437</v>
       </c>
       <c r="R79" t="n">
-        <v>6951085</v>
+        <v>6951052</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8631,10 +8631,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128411329</v>
+        <v>128405900</v>
       </c>
       <c r="B80" t="n">
-        <v>91522</v>
+        <v>57716</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8642,34 +8642,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>398173</v>
+        <v>398362</v>
       </c>
       <c r="R80" t="n">
-        <v>6950901</v>
+        <v>6950568</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8728,10 +8733,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128405900</v>
+        <v>128411329</v>
       </c>
       <c r="B81" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8739,39 +8744,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>398362</v>
+        <v>398173</v>
       </c>
       <c r="R81" t="n">
-        <v>6950568</v>
+        <v>6950901</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8830,10 +8830,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128411270</v>
+        <v>128407528</v>
       </c>
       <c r="B82" t="n">
-        <v>78523</v>
+        <v>78786</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8841,21 +8841,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>398139</v>
+        <v>398225</v>
       </c>
       <c r="R82" t="n">
-        <v>6950929</v>
+        <v>6950599</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8927,10 +8927,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128407528</v>
+        <v>128411270</v>
       </c>
       <c r="B83" t="n">
-        <v>78786</v>
+        <v>78523</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8938,21 +8938,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>398225</v>
+        <v>398139</v>
       </c>
       <c r="R83" t="n">
-        <v>6950599</v>
+        <v>6950929</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9438,32 +9438,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128410048</v>
+        <v>128415905</v>
       </c>
       <c r="B88" t="n">
-        <v>78480</v>
+        <v>78523</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>498</v>
+        <v>6437</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9473,10 +9473,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>397967</v>
+        <v>398403</v>
       </c>
       <c r="R88" t="n">
-        <v>6950876</v>
+        <v>6950826</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9506,9 +9506,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9523,12 +9533,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9647,32 +9657,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128415905</v>
+        <v>128410048</v>
       </c>
       <c r="B90" t="n">
-        <v>78523</v>
+        <v>78480</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6437</v>
+        <v>498</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9682,10 +9692,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>398403</v>
+        <v>397967</v>
       </c>
       <c r="R90" t="n">
-        <v>6950826</v>
+        <v>6950876</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9715,19 +9725,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9742,12 +9742,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -9866,10 +9866,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128413415</v>
+        <v>128411474</v>
       </c>
       <c r="B92" t="n">
-        <v>79739</v>
+        <v>57716</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9877,34 +9877,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>398477</v>
+        <v>398202</v>
       </c>
       <c r="R92" t="n">
-        <v>6951277</v>
+        <v>6950905</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10060,10 +10065,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128411474</v>
+        <v>128413415</v>
       </c>
       <c r="B94" t="n">
-        <v>57716</v>
+        <v>79739</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10071,39 +10076,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>398202</v>
+        <v>398477</v>
       </c>
       <c r="R94" t="n">
-        <v>6950905</v>
+        <v>6951277</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10162,32 +10162,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128411728</v>
+        <v>128407311</v>
       </c>
       <c r="B95" t="n">
-        <v>78480</v>
+        <v>78523</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>498</v>
+        <v>6437</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10197,10 +10197,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>398227</v>
+        <v>398263</v>
       </c>
       <c r="R95" t="n">
-        <v>6950881</v>
+        <v>6950596</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10259,10 +10259,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128410472</v>
+        <v>128413088</v>
       </c>
       <c r="B96" t="n">
-        <v>75205</v>
+        <v>82979</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10270,21 +10270,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>398075</v>
+        <v>398494</v>
       </c>
       <c r="R96" t="n">
-        <v>6950912</v>
+        <v>6951141</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10356,32 +10356,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128407311</v>
+        <v>128411728</v>
       </c>
       <c r="B97" t="n">
-        <v>78523</v>
+        <v>78480</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6437</v>
+        <v>498</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10391,10 +10391,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>398263</v>
+        <v>398227</v>
       </c>
       <c r="R97" t="n">
-        <v>6950596</v>
+        <v>6950881</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10453,10 +10453,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128413088</v>
+        <v>128410472</v>
       </c>
       <c r="B98" t="n">
-        <v>82979</v>
+        <v>75205</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10464,21 +10464,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10488,10 +10488,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>398494</v>
+        <v>398075</v>
       </c>
       <c r="R98" t="n">
-        <v>6951141</v>
+        <v>6950912</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10550,10 +10550,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128413214</v>
+        <v>128413083</v>
       </c>
       <c r="B99" t="n">
-        <v>57716</v>
+        <v>75205</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10561,39 +10561,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>398467</v>
+        <v>398494</v>
       </c>
       <c r="R99" t="n">
-        <v>6951207</v>
+        <v>6951141</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10652,7 +10647,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128415580</v>
+        <v>128413214</v>
       </c>
       <c r="B100" t="n">
         <v>57716</v>
@@ -10683,7 +10678,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -10692,10 +10687,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>398442</v>
+        <v>398467</v>
       </c>
       <c r="R100" t="n">
-        <v>6950833</v>
+        <v>6951207</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10754,10 +10749,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128413083</v>
+        <v>128415580</v>
       </c>
       <c r="B101" t="n">
-        <v>75205</v>
+        <v>57716</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10765,34 +10760,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>398494</v>
+        <v>398442</v>
       </c>
       <c r="R101" t="n">
-        <v>6951141</v>
+        <v>6950833</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11608,10 +11608,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128416572</v>
+        <v>128405590</v>
       </c>
       <c r="B109" t="n">
-        <v>91522</v>
+        <v>57716</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11619,34 +11619,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>398382</v>
+        <v>398420</v>
       </c>
       <c r="R109" t="n">
-        <v>6950639</v>
+        <v>6950543</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11678,7 +11683,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11688,7 +11693,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11715,10 +11720,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128405590</v>
+        <v>128416572</v>
       </c>
       <c r="B110" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11726,39 +11731,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>398420</v>
+        <v>398382</v>
       </c>
       <c r="R110" t="n">
-        <v>6950543</v>
+        <v>6950639</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11790,7 +11790,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 32341-2025 artfynd.xlsx
+++ b/artfynd/A 32341-2025 artfynd.xlsx
@@ -2429,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128415681</v>
+        <v>128415613</v>
       </c>
       <c r="B19" t="n">
-        <v>79710</v>
+        <v>78786</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2440,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>398394</v>
+        <v>398437</v>
       </c>
       <c r="R19" t="n">
-        <v>6950811</v>
+        <v>6950808</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2497,19 +2497,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2524,22 +2514,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128415613</v>
+        <v>128415804</v>
       </c>
       <c r="B20" t="n">
-        <v>78786</v>
+        <v>78523</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>398437</v>
+        <v>398394</v>
       </c>
       <c r="R20" t="n">
-        <v>6950808</v>
+        <v>6950811</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2604,9 +2594,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2621,22 +2621,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128415804</v>
+        <v>128410565</v>
       </c>
       <c r="B21" t="n">
-        <v>78523</v>
+        <v>75205</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,21 +2644,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>398394</v>
+        <v>398088</v>
       </c>
       <c r="R21" t="n">
-        <v>6950811</v>
+        <v>6950909</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2701,19 +2701,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2728,22 +2718,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128410565</v>
+        <v>128408059</v>
       </c>
       <c r="B22" t="n">
-        <v>75205</v>
+        <v>57716</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2751,34 +2741,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>398088</v>
+        <v>398146</v>
       </c>
       <c r="R22" t="n">
-        <v>6950909</v>
+        <v>6950784</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128408059</v>
+        <v>128415681</v>
       </c>
       <c r="B23" t="n">
-        <v>57716</v>
+        <v>79710</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2848,39 +2843,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>398146</v>
+        <v>398394</v>
       </c>
       <c r="R23" t="n">
-        <v>6950784</v>
+        <v>6950811</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2910,9 +2900,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2927,12 +2927,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -4459,32 +4459,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128416366</v>
+        <v>128412193</v>
       </c>
       <c r="B39" t="n">
-        <v>78480</v>
+        <v>80260</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>498</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>398419</v>
+        <v>398369</v>
       </c>
       <c r="R39" t="n">
-        <v>6950678</v>
+        <v>6950956</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4556,32 +4556,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128412193</v>
+        <v>128411735</v>
       </c>
       <c r="B40" t="n">
-        <v>80260</v>
+        <v>75205</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>398369</v>
+        <v>398227</v>
       </c>
       <c r="R40" t="n">
-        <v>6950956</v>
+        <v>6950881</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128411735</v>
+        <v>128405669</v>
       </c>
       <c r="B41" t="n">
-        <v>75205</v>
+        <v>91522</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4664,21 +4664,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>398227</v>
+        <v>398398</v>
       </c>
       <c r="R41" t="n">
-        <v>6950881</v>
+        <v>6950569</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4750,10 +4750,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128405669</v>
+        <v>128414073</v>
       </c>
       <c r="B42" t="n">
-        <v>91522</v>
+        <v>57716</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4761,34 +4761,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>398398</v>
+        <v>398546</v>
       </c>
       <c r="R42" t="n">
-        <v>6950569</v>
+        <v>6951235</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4847,45 +4852,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128405841</v>
+        <v>128412950</v>
       </c>
       <c r="B43" t="n">
-        <v>92201</v>
+        <v>57716</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>398374</v>
+        <v>398483</v>
       </c>
       <c r="R43" t="n">
-        <v>6950548</v>
+        <v>6951117</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4944,50 +4954,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128414073</v>
+        <v>128405841</v>
       </c>
       <c r="B44" t="n">
-        <v>57716</v>
+        <v>92201</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>398546</v>
+        <v>398374</v>
       </c>
       <c r="R44" t="n">
-        <v>6951235</v>
+        <v>6950548</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5046,50 +5051,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128412950</v>
+        <v>128416366</v>
       </c>
       <c r="B45" t="n">
-        <v>57716</v>
+        <v>78480</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>398483</v>
+        <v>398419</v>
       </c>
       <c r="R45" t="n">
-        <v>6951117</v>
+        <v>6950678</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6153,48 +6153,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128408521</v>
+        <v>128408773</v>
       </c>
       <c r="B56" t="n">
-        <v>79739</v>
+        <v>58086</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>398019</v>
+        <v>398012</v>
       </c>
       <c r="R56" t="n">
-        <v>6950740</v>
+        <v>6950659</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6221,9 +6226,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6238,22 +6253,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128405859</v>
+        <v>128409775</v>
       </c>
       <c r="B57" t="n">
-        <v>57716</v>
+        <v>79710</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6261,39 +6276,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>398362</v>
+        <v>398008</v>
       </c>
       <c r="R57" t="n">
-        <v>6950549</v>
+        <v>6950745</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6323,19 +6333,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6350,22 +6350,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128413307</v>
+        <v>128408521</v>
       </c>
       <c r="B58" t="n">
-        <v>57716</v>
+        <v>79739</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6373,39 +6373,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>398457</v>
+        <v>398019</v>
       </c>
       <c r="R58" t="n">
-        <v>6951226</v>
+        <v>6950740</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6435,19 +6430,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6462,39 +6447,39 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128408773</v>
+        <v>128405859</v>
       </c>
       <c r="B59" t="n">
-        <v>58086</v>
+        <v>57716</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6505,7 +6490,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6514,13 +6499,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>398012</v>
+        <v>398362</v>
       </c>
       <c r="R59" t="n">
-        <v>6950659</v>
+        <v>6950549</v>
       </c>
       <c r="S59" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6586,10 +6571,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128409775</v>
+        <v>128413307</v>
       </c>
       <c r="B60" t="n">
-        <v>79710</v>
+        <v>57716</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6597,34 +6582,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>398008</v>
+        <v>398457</v>
       </c>
       <c r="R60" t="n">
-        <v>6950745</v>
+        <v>6951226</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6654,9 +6644,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6671,12 +6671,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6882,10 +6882,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128406318</v>
+        <v>128409691</v>
       </c>
       <c r="B63" t="n">
-        <v>79120</v>
+        <v>90536</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6893,21 +6893,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6917,10 +6917,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>398333</v>
+        <v>398057</v>
       </c>
       <c r="R63" t="n">
-        <v>6950603</v>
+        <v>6950739</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6950,9 +6950,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6967,22 +6977,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128415836</v>
+        <v>128406318</v>
       </c>
       <c r="B64" t="n">
-        <v>78092</v>
+        <v>79120</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6990,21 +7000,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7014,10 +7024,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>398394</v>
+        <v>398333</v>
       </c>
       <c r="R64" t="n">
-        <v>6950811</v>
+        <v>6950603</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7047,19 +7057,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7074,22 +7074,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128406026</v>
+        <v>128415836</v>
       </c>
       <c r="B65" t="n">
-        <v>79739</v>
+        <v>78092</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7097,21 +7097,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>398364</v>
+        <v>398394</v>
       </c>
       <c r="R65" t="n">
-        <v>6950589</v>
+        <v>6950811</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7154,9 +7154,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7171,22 +7181,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128415706</v>
+        <v>128406026</v>
       </c>
       <c r="B66" t="n">
-        <v>57716</v>
+        <v>79739</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7194,39 +7204,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>398411</v>
+        <v>398364</v>
       </c>
       <c r="R66" t="n">
-        <v>6950796</v>
+        <v>6950589</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7285,7 +7290,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128416501</v>
+        <v>128415706</v>
       </c>
       <c r="B67" t="n">
         <v>57716</v>
@@ -7316,7 +7321,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7325,10 +7330,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>398382</v>
+        <v>398411</v>
       </c>
       <c r="R67" t="n">
-        <v>6950639</v>
+        <v>6950796</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7358,19 +7363,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7385,22 +7380,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128409691</v>
+        <v>128416501</v>
       </c>
       <c r="B68" t="n">
-        <v>90536</v>
+        <v>57716</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7408,34 +7403,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>398057</v>
+        <v>398382</v>
       </c>
       <c r="R68" t="n">
-        <v>6950739</v>
+        <v>6950639</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8631,10 +8631,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128405900</v>
+        <v>128411329</v>
       </c>
       <c r="B80" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8642,39 +8642,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>398362</v>
+        <v>398173</v>
       </c>
       <c r="R80" t="n">
-        <v>6950568</v>
+        <v>6950901</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8733,10 +8728,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128411329</v>
+        <v>128405900</v>
       </c>
       <c r="B81" t="n">
-        <v>91522</v>
+        <v>57716</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8744,34 +8739,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>398173</v>
+        <v>398362</v>
       </c>
       <c r="R81" t="n">
-        <v>6950901</v>
+        <v>6950568</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9438,32 +9438,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128415905</v>
+        <v>128410048</v>
       </c>
       <c r="B88" t="n">
-        <v>78523</v>
+        <v>78480</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6437</v>
+        <v>498</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9473,10 +9473,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>398403</v>
+        <v>397967</v>
       </c>
       <c r="R88" t="n">
-        <v>6950826</v>
+        <v>6950876</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9506,19 +9506,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9533,22 +9523,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128407736</v>
+        <v>128415905</v>
       </c>
       <c r="B89" t="n">
-        <v>57716</v>
+        <v>78523</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9556,39 +9546,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>398169</v>
+        <v>398403</v>
       </c>
       <c r="R89" t="n">
-        <v>6950711</v>
+        <v>6950826</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9620,7 +9605,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9630,7 +9615,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9657,45 +9642,50 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128410048</v>
+        <v>128407736</v>
       </c>
       <c r="B90" t="n">
-        <v>78480</v>
+        <v>57716</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>397967</v>
+        <v>398169</v>
       </c>
       <c r="R90" t="n">
-        <v>6950876</v>
+        <v>6950711</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9725,9 +9715,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9742,12 +9742,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -9968,10 +9968,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128405637</v>
+        <v>128413415</v>
       </c>
       <c r="B93" t="n">
-        <v>91522</v>
+        <v>79739</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9979,34 +9979,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>398426</v>
+        <v>398477</v>
       </c>
       <c r="R93" t="n">
-        <v>6950561</v>
+        <v>6951277</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10065,10 +10065,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128413415</v>
+        <v>128405637</v>
       </c>
       <c r="B94" t="n">
-        <v>79739</v>
+        <v>91522</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10076,34 +10076,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>398477</v>
+        <v>398426</v>
       </c>
       <c r="R94" t="n">
-        <v>6951277</v>
+        <v>6950561</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10162,10 +10162,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128407311</v>
+        <v>128413088</v>
       </c>
       <c r="B95" t="n">
-        <v>78523</v>
+        <v>82979</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10173,21 +10173,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10197,10 +10197,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>398263</v>
+        <v>398494</v>
       </c>
       <c r="R95" t="n">
-        <v>6950596</v>
+        <v>6951141</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10259,32 +10259,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128413088</v>
+        <v>128411728</v>
       </c>
       <c r="B96" t="n">
-        <v>82979</v>
+        <v>78480</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1312</v>
+        <v>498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>398494</v>
+        <v>398227</v>
       </c>
       <c r="R96" t="n">
-        <v>6951141</v>
+        <v>6950881</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10356,32 +10356,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128411728</v>
+        <v>128410472</v>
       </c>
       <c r="B97" t="n">
-        <v>78480</v>
+        <v>75205</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10391,10 +10391,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>398227</v>
+        <v>398075</v>
       </c>
       <c r="R97" t="n">
-        <v>6950881</v>
+        <v>6950912</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10453,10 +10453,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128410472</v>
+        <v>128407311</v>
       </c>
       <c r="B98" t="n">
-        <v>75205</v>
+        <v>78523</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10464,21 +10464,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10488,10 +10488,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>398075</v>
+        <v>398263</v>
       </c>
       <c r="R98" t="n">
-        <v>6950912</v>
+        <v>6950596</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>

--- a/artfynd/A 32341-2025 artfynd.xlsx
+++ b/artfynd/A 32341-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128413409</v>
+        <v>128407744</v>
       </c>
       <c r="B2" t="n">
-        <v>79710</v>
+        <v>79739</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398477</v>
+        <v>398173</v>
       </c>
       <c r="R2" t="n">
-        <v>6951277</v>
+        <v>6950715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128407744</v>
+        <v>128412069</v>
       </c>
       <c r="B3" t="n">
-        <v>79739</v>
+        <v>57716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398173</v>
+        <v>398298</v>
       </c>
       <c r="R3" t="n">
-        <v>6950715</v>
+        <v>6950883</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128412069</v>
+        <v>128413409</v>
       </c>
       <c r="B4" t="n">
-        <v>57716</v>
+        <v>79710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +885,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398298</v>
+        <v>398477</v>
       </c>
       <c r="R4" t="n">
-        <v>6950883</v>
+        <v>6951277</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1369,32 +1369,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128407381</v>
+        <v>128412642</v>
       </c>
       <c r="B9" t="n">
-        <v>82979</v>
+        <v>57557</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>102621</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,13 +1404,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>398271</v>
+        <v>398437</v>
       </c>
       <c r="R9" t="n">
-        <v>6950584</v>
+        <v>6951052</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1437,19 +1437,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1464,57 +1454,62 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128409340</v>
+        <v>128407432</v>
       </c>
       <c r="B10" t="n">
-        <v>80254</v>
+        <v>57716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>397997</v>
+        <v>398269</v>
       </c>
       <c r="R10" t="n">
-        <v>6950677</v>
+        <v>6950563</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,9 +1539,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1561,19 +1566,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128407432</v>
+        <v>128415979</v>
       </c>
       <c r="B11" t="n">
         <v>57716</v>
@@ -1613,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>398269</v>
+        <v>398372</v>
       </c>
       <c r="R11" t="n">
-        <v>6950563</v>
+        <v>6950738</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1653,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1658,7 +1663,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,10 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128415979</v>
+        <v>128407381</v>
       </c>
       <c r="B12" t="n">
-        <v>57716</v>
+        <v>82979</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,39 +1701,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>398372</v>
+        <v>398271</v>
       </c>
       <c r="R12" t="n">
-        <v>6950738</v>
+        <v>6950584</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128412642</v>
+        <v>128409340</v>
       </c>
       <c r="B13" t="n">
-        <v>57557</v>
+        <v>80254</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1808,21 +1808,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102621</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1832,13 +1832,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>398437</v>
+        <v>397997</v>
       </c>
       <c r="R13" t="n">
-        <v>6951052</v>
+        <v>6950677</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1894,10 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128407947</v>
+        <v>128415142</v>
       </c>
       <c r="B14" t="n">
-        <v>82979</v>
+        <v>57716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1905,34 +1905,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>398154</v>
+        <v>398352</v>
       </c>
       <c r="R14" t="n">
-        <v>6950756</v>
+        <v>6950954</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,7 +1969,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1974,7 +1979,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128411782</v>
+        <v>128410559</v>
       </c>
       <c r="B15" t="n">
-        <v>75205</v>
+        <v>57716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2012,34 +2017,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>398234</v>
+        <v>398097</v>
       </c>
       <c r="R15" t="n">
-        <v>6950852</v>
+        <v>6950870</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128410038</v>
+        <v>128407947</v>
       </c>
       <c r="B16" t="n">
-        <v>75205</v>
+        <v>82979</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>397967</v>
+        <v>398154</v>
       </c>
       <c r="R16" t="n">
-        <v>6950876</v>
+        <v>6950756</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2176,9 +2186,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2193,22 +2213,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128415142</v>
+        <v>128411782</v>
       </c>
       <c r="B17" t="n">
-        <v>57716</v>
+        <v>75205</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,39 +2236,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>398352</v>
+        <v>398234</v>
       </c>
       <c r="R17" t="n">
-        <v>6950954</v>
+        <v>6950852</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128410559</v>
+        <v>128410038</v>
       </c>
       <c r="B18" t="n">
-        <v>57716</v>
+        <v>75205</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,39 +2343,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>398097</v>
+        <v>397967</v>
       </c>
       <c r="R18" t="n">
-        <v>6950870</v>
+        <v>6950876</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2390,19 +2400,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2417,22 +2417,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128415613</v>
+        <v>128415804</v>
       </c>
       <c r="B19" t="n">
-        <v>78786</v>
+        <v>78523</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2440,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>398437</v>
+        <v>398394</v>
       </c>
       <c r="R19" t="n">
-        <v>6950808</v>
+        <v>6950811</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2497,9 +2497,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2514,22 +2524,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128415804</v>
+        <v>128410565</v>
       </c>
       <c r="B20" t="n">
-        <v>78523</v>
+        <v>75205</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2537,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>398394</v>
+        <v>398088</v>
       </c>
       <c r="R20" t="n">
-        <v>6950811</v>
+        <v>6950909</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2594,19 +2604,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2621,22 +2621,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128410565</v>
+        <v>128408059</v>
       </c>
       <c r="B21" t="n">
-        <v>75205</v>
+        <v>57716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,34 +2644,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>398088</v>
+        <v>398146</v>
       </c>
       <c r="R21" t="n">
-        <v>6950909</v>
+        <v>6950784</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128408059</v>
+        <v>128415681</v>
       </c>
       <c r="B22" t="n">
-        <v>57716</v>
+        <v>79710</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2741,39 +2746,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>398146</v>
+        <v>398394</v>
       </c>
       <c r="R22" t="n">
-        <v>6950784</v>
+        <v>6950811</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2803,9 +2803,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2820,22 +2830,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128415681</v>
+        <v>128415613</v>
       </c>
       <c r="B23" t="n">
-        <v>79710</v>
+        <v>78786</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2843,21 +2853,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>398394</v>
+        <v>398437</v>
       </c>
       <c r="R23" t="n">
-        <v>6950811</v>
+        <v>6950808</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2900,19 +2910,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2927,22 +2927,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128405816</v>
+        <v>128410050</v>
       </c>
       <c r="B24" t="n">
-        <v>57716</v>
+        <v>82979</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,39 +2950,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>398390</v>
+        <v>397967</v>
       </c>
       <c r="R24" t="n">
-        <v>6950541</v>
+        <v>6950876</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3012,19 +3007,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3039,19 +3024,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128410050</v>
+        <v>128411229</v>
       </c>
       <c r="B25" t="n">
         <v>82979</v>
@@ -3086,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>397967</v>
+        <v>398118</v>
       </c>
       <c r="R25" t="n">
-        <v>6950876</v>
+        <v>6950921</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,7 +3133,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128411229</v>
+        <v>128416541</v>
       </c>
       <c r="B26" t="n">
         <v>82979</v>
@@ -3183,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>398118</v>
+        <v>398411</v>
       </c>
       <c r="R26" t="n">
-        <v>6950921</v>
+        <v>6950623</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128416541</v>
+        <v>128405816</v>
       </c>
       <c r="B27" t="n">
-        <v>82979</v>
+        <v>57716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3256,34 +3241,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>398411</v>
+        <v>398390</v>
       </c>
       <c r="R27" t="n">
-        <v>6950623</v>
+        <v>6950541</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3313,9 +3303,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3330,12 +3330,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128411736</v>
+        <v>128408399</v>
       </c>
       <c r="B31" t="n">
-        <v>91522</v>
+        <v>82979</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3644,21 +3644,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>398234</v>
+        <v>398076</v>
       </c>
       <c r="R31" t="n">
-        <v>6950852</v>
+        <v>6950793</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3701,19 +3701,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3728,12 +3718,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4056,48 +4046,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128408399</v>
+        <v>128413866</v>
       </c>
       <c r="B35" t="n">
-        <v>82979</v>
+        <v>58086</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398076</v>
+        <v>398505</v>
       </c>
       <c r="R35" t="n">
-        <v>6950793</v>
+        <v>6951279</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4124,9 +4119,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4141,22 +4146,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128410403</v>
+        <v>128411736</v>
       </c>
       <c r="B36" t="n">
-        <v>75205</v>
+        <v>91522</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4164,21 +4169,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4188,10 +4193,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398063</v>
+        <v>398234</v>
       </c>
       <c r="R36" t="n">
-        <v>6950893</v>
+        <v>6950852</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4221,9 +4226,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4238,19 +4253,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128411429</v>
+        <v>128410403</v>
       </c>
       <c r="B37" t="n">
         <v>75205</v>
@@ -4285,10 +4300,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>398176</v>
+        <v>398063</v>
       </c>
       <c r="R37" t="n">
-        <v>6950885</v>
+        <v>6950893</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,53 +4362,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128413866</v>
+        <v>128411429</v>
       </c>
       <c r="B38" t="n">
-        <v>58086</v>
+        <v>75205</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>398505</v>
+        <v>398176</v>
       </c>
       <c r="R38" t="n">
-        <v>6951279</v>
+        <v>6950885</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4420,19 +4430,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4447,44 +4447,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128412193</v>
+        <v>128415930</v>
       </c>
       <c r="B39" t="n">
-        <v>80260</v>
+        <v>79710</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>398369</v>
+        <v>398387</v>
       </c>
       <c r="R39" t="n">
-        <v>6950956</v>
+        <v>6950766</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4653,32 +4653,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128405669</v>
+        <v>128405841</v>
       </c>
       <c r="B41" t="n">
-        <v>91522</v>
+        <v>92201</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>398398</v>
+        <v>398374</v>
       </c>
       <c r="R41" t="n">
-        <v>6950569</v>
+        <v>6950548</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4750,50 +4750,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128414073</v>
+        <v>128416366</v>
       </c>
       <c r="B42" t="n">
-        <v>57716</v>
+        <v>78480</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>398546</v>
+        <v>398419</v>
       </c>
       <c r="R42" t="n">
-        <v>6951235</v>
+        <v>6950678</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4852,10 +4847,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128412950</v>
+        <v>128405669</v>
       </c>
       <c r="B43" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4863,39 +4858,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>398483</v>
+        <v>398398</v>
       </c>
       <c r="R43" t="n">
-        <v>6951117</v>
+        <v>6950569</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4954,10 +4944,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128405841</v>
+        <v>128412193</v>
       </c>
       <c r="B44" t="n">
-        <v>92201</v>
+        <v>80260</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4965,21 +4955,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3298</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4989,10 +4979,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>398374</v>
+        <v>398369</v>
       </c>
       <c r="R44" t="n">
-        <v>6950548</v>
+        <v>6950956</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5051,45 +5041,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128416366</v>
+        <v>128414073</v>
       </c>
       <c r="B45" t="n">
-        <v>78480</v>
+        <v>57716</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>398419</v>
+        <v>398546</v>
       </c>
       <c r="R45" t="n">
-        <v>6950678</v>
+        <v>6951235</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5148,10 +5143,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128415930</v>
+        <v>128412950</v>
       </c>
       <c r="B46" t="n">
-        <v>79710</v>
+        <v>57716</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5159,34 +5154,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>398387</v>
+        <v>398483</v>
       </c>
       <c r="R46" t="n">
-        <v>6950766</v>
+        <v>6951117</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5245,10 +5245,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128407293</v>
+        <v>128412677</v>
       </c>
       <c r="B47" t="n">
-        <v>79739</v>
+        <v>57716</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5256,34 +5256,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>398263</v>
+        <v>398462</v>
       </c>
       <c r="R47" t="n">
-        <v>6950596</v>
+        <v>6951039</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5313,9 +5318,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5330,22 +5345,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128410408</v>
+        <v>128415972</v>
       </c>
       <c r="B48" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5353,34 +5368,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>398063</v>
+        <v>398396</v>
       </c>
       <c r="R48" t="n">
-        <v>6950893</v>
+        <v>6950719</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5439,10 +5459,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128415932</v>
+        <v>128406327</v>
       </c>
       <c r="B49" t="n">
-        <v>79739</v>
+        <v>91522</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5450,21 +5470,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5474,10 +5494,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>398387</v>
+        <v>398333</v>
       </c>
       <c r="R49" t="n">
-        <v>6950766</v>
+        <v>6950603</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5536,10 +5556,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128408097</v>
+        <v>128411964</v>
       </c>
       <c r="B50" t="n">
-        <v>57876</v>
+        <v>91522</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5547,42 +5567,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>398159</v>
+        <v>398278</v>
       </c>
       <c r="R50" t="n">
-        <v>6950801</v>
+        <v>6950881</v>
       </c>
       <c r="S50" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5609,19 +5624,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5636,22 +5641,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128406327</v>
+        <v>128407293</v>
       </c>
       <c r="B51" t="n">
-        <v>91522</v>
+        <v>79739</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5659,21 +5664,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5683,10 +5688,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>398333</v>
+        <v>398263</v>
       </c>
       <c r="R51" t="n">
-        <v>6950603</v>
+        <v>6950596</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5745,10 +5750,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128411964</v>
+        <v>128410408</v>
       </c>
       <c r="B52" t="n">
-        <v>91522</v>
+        <v>79120</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5756,21 +5761,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5780,10 +5785,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>398278</v>
+        <v>398063</v>
       </c>
       <c r="R52" t="n">
-        <v>6950881</v>
+        <v>6950893</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5842,10 +5847,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128412677</v>
+        <v>128415932</v>
       </c>
       <c r="B53" t="n">
-        <v>57716</v>
+        <v>79739</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5853,39 +5858,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>398462</v>
+        <v>398387</v>
       </c>
       <c r="R53" t="n">
-        <v>6951039</v>
+        <v>6950766</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5915,19 +5915,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5942,22 +5932,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128415972</v>
+        <v>128408097</v>
       </c>
       <c r="B54" t="n">
-        <v>57716</v>
+        <v>57876</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5965,27 +5955,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5994,13 +5984,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>398396</v>
+        <v>398159</v>
       </c>
       <c r="R54" t="n">
-        <v>6950719</v>
+        <v>6950801</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6027,9 +6017,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6044,12 +6044,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6153,27 +6153,27 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128408773</v>
+        <v>128405859</v>
       </c>
       <c r="B56" t="n">
-        <v>58086</v>
+        <v>57716</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6184,7 +6184,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6193,13 +6193,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>398012</v>
+        <v>398362</v>
       </c>
       <c r="R56" t="n">
-        <v>6950659</v>
+        <v>6950549</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6265,10 +6265,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128409775</v>
+        <v>128413307</v>
       </c>
       <c r="B57" t="n">
-        <v>79710</v>
+        <v>57716</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6276,34 +6276,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>398008</v>
+        <v>398457</v>
       </c>
       <c r="R57" t="n">
-        <v>6950745</v>
+        <v>6951226</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6333,9 +6338,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6350,22 +6365,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128408521</v>
+        <v>128409775</v>
       </c>
       <c r="B58" t="n">
-        <v>79739</v>
+        <v>79710</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6373,21 +6388,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6397,10 +6412,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>398019</v>
+        <v>398008</v>
       </c>
       <c r="R58" t="n">
-        <v>6950740</v>
+        <v>6950745</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6459,10 +6474,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128405859</v>
+        <v>128408521</v>
       </c>
       <c r="B59" t="n">
-        <v>57716</v>
+        <v>79739</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6470,39 +6485,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>398362</v>
+        <v>398019</v>
       </c>
       <c r="R59" t="n">
-        <v>6950549</v>
+        <v>6950740</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6532,19 +6542,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6559,39 +6559,39 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128413307</v>
+        <v>128413955</v>
       </c>
       <c r="B60" t="n">
-        <v>57716</v>
+        <v>57557</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6602,7 +6602,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>398457</v>
+        <v>398517</v>
       </c>
       <c r="R60" t="n">
-        <v>6951226</v>
+        <v>6951283</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6644,19 +6644,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6671,22 +6661,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128413955</v>
+        <v>128408773</v>
       </c>
       <c r="B61" t="n">
-        <v>57557</v>
+        <v>58086</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6694,16 +6684,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102621</v>
+        <v>103015</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6714,7 +6704,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6723,10 +6713,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>398517</v>
+        <v>398012</v>
       </c>
       <c r="R61" t="n">
-        <v>6951283</v>
+        <v>6950659</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -6756,9 +6746,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6773,22 +6773,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128407307</v>
+        <v>128406318</v>
       </c>
       <c r="B62" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6796,21 +6796,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6820,10 +6820,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>398263</v>
+        <v>398333</v>
       </c>
       <c r="R62" t="n">
-        <v>6950596</v>
+        <v>6950603</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6882,10 +6882,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128409691</v>
+        <v>128406026</v>
       </c>
       <c r="B63" t="n">
-        <v>90536</v>
+        <v>79739</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6893,21 +6893,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6917,10 +6917,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>398057</v>
+        <v>398364</v>
       </c>
       <c r="R63" t="n">
-        <v>6950739</v>
+        <v>6950589</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6950,19 +6950,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6977,22 +6967,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128406318</v>
+        <v>128415836</v>
       </c>
       <c r="B64" t="n">
-        <v>79120</v>
+        <v>78092</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7000,21 +6990,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7024,10 +7014,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>398333</v>
+        <v>398394</v>
       </c>
       <c r="R64" t="n">
-        <v>6950603</v>
+        <v>6950811</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7057,9 +7047,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7074,22 +7074,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128415836</v>
+        <v>128409691</v>
       </c>
       <c r="B65" t="n">
-        <v>78092</v>
+        <v>90536</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7097,21 +7097,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6487</v>
+        <v>1962</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>398394</v>
+        <v>398057</v>
       </c>
       <c r="R65" t="n">
-        <v>6950811</v>
+        <v>6950739</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7193,10 +7193,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128406026</v>
+        <v>128415706</v>
       </c>
       <c r="B66" t="n">
-        <v>79739</v>
+        <v>57716</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7204,34 +7204,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>398364</v>
+        <v>398411</v>
       </c>
       <c r="R66" t="n">
-        <v>6950589</v>
+        <v>6950796</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7290,7 +7295,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128415706</v>
+        <v>128416501</v>
       </c>
       <c r="B67" t="n">
         <v>57716</v>
@@ -7321,7 +7326,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7330,10 +7335,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>398411</v>
+        <v>398382</v>
       </c>
       <c r="R67" t="n">
-        <v>6950796</v>
+        <v>6950639</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7363,9 +7368,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7380,22 +7395,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128416501</v>
+        <v>128407307</v>
       </c>
       <c r="B68" t="n">
-        <v>57716</v>
+        <v>78878</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7403,39 +7418,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>398382</v>
+        <v>398263</v>
       </c>
       <c r="R68" t="n">
-        <v>6950639</v>
+        <v>6950596</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7465,19 +7475,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7492,22 +7492,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128411612</v>
+        <v>128411931</v>
       </c>
       <c r="B69" t="n">
-        <v>79199</v>
+        <v>91522</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7515,21 +7515,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7539,10 +7539,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>398200</v>
+        <v>398276</v>
       </c>
       <c r="R69" t="n">
-        <v>6950918</v>
+        <v>6950842</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7601,10 +7601,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128411308</v>
+        <v>128411612</v>
       </c>
       <c r="B70" t="n">
-        <v>75205</v>
+        <v>79199</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7612,21 +7612,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7636,10 +7636,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>398162</v>
+        <v>398200</v>
       </c>
       <c r="R70" t="n">
-        <v>6950923</v>
+        <v>6950918</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7922,10 +7922,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128411931</v>
+        <v>128411308</v>
       </c>
       <c r="B73" t="n">
-        <v>91522</v>
+        <v>75205</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7933,21 +7933,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7957,10 +7957,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>398276</v>
+        <v>398162</v>
       </c>
       <c r="R73" t="n">
-        <v>6950842</v>
+        <v>6950923</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8019,32 +8019,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128412825</v>
+        <v>128412622</v>
       </c>
       <c r="B74" t="n">
-        <v>79710</v>
+        <v>58086</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8054,13 +8054,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>398474</v>
+        <v>398437</v>
       </c>
       <c r="R74" t="n">
-        <v>6951085</v>
+        <v>6951052</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8116,10 +8116,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128405468</v>
+        <v>128412825</v>
       </c>
       <c r="B75" t="n">
-        <v>82979</v>
+        <v>79710</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8127,34 +8127,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1312</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>398405</v>
+        <v>398474</v>
       </c>
       <c r="R75" t="n">
-        <v>6950503</v>
+        <v>6951085</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8213,45 +8213,50 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128416207</v>
+        <v>128412048</v>
       </c>
       <c r="B76" t="n">
-        <v>75203</v>
+        <v>57716</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>398414</v>
+        <v>398329</v>
       </c>
       <c r="R76" t="n">
-        <v>6950702</v>
+        <v>6950952</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8281,9 +8286,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8298,22 +8313,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128412048</v>
+        <v>128405468</v>
       </c>
       <c r="B77" t="n">
-        <v>57716</v>
+        <v>82979</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8321,39 +8336,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>398329</v>
+        <v>398405</v>
       </c>
       <c r="R77" t="n">
-        <v>6950952</v>
+        <v>6950503</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8383,19 +8393,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8410,62 +8410,57 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128406114</v>
+        <v>128416207</v>
       </c>
       <c r="B78" t="n">
-        <v>57716</v>
+        <v>75203</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>398351</v>
+        <v>398414</v>
       </c>
       <c r="R78" t="n">
-        <v>6950591</v>
+        <v>6950702</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8495,19 +8490,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8522,39 +8507,39 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128412622</v>
+        <v>128406114</v>
       </c>
       <c r="B79" t="n">
-        <v>58086</v>
+        <v>57716</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -8563,19 +8548,24 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>398437</v>
+        <v>398351</v>
       </c>
       <c r="R79" t="n">
-        <v>6951052</v>
+        <v>6950591</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8602,9 +8592,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8619,12 +8619,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9024,10 +9024,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128416210</v>
+        <v>128411972</v>
       </c>
       <c r="B84" t="n">
-        <v>91522</v>
+        <v>57716</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9035,34 +9035,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>398414</v>
+        <v>398278</v>
       </c>
       <c r="R84" t="n">
-        <v>6950702</v>
+        <v>6950881</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9121,7 +9126,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128411972</v>
+        <v>128407963</v>
       </c>
       <c r="B85" t="n">
         <v>57716</v>
@@ -9150,21 +9155,16 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>398278</v>
+        <v>398154</v>
       </c>
       <c r="R85" t="n">
-        <v>6950881</v>
+        <v>6950756</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9194,9 +9194,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9211,60 +9221,61 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128407963</v>
+        <v>128404962</v>
       </c>
       <c r="B86" t="n">
-        <v>57716</v>
+        <v>57881</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>266237</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>398154</v>
+        <v>398392</v>
       </c>
       <c r="R86" t="n">
-        <v>6950756</v>
+        <v>6950406</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9330,49 +9341,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128404962</v>
+        <v>128416210</v>
       </c>
       <c r="B87" t="n">
-        <v>57881</v>
+        <v>91522</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>266237</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>398392</v>
+        <v>398414</v>
       </c>
       <c r="R87" t="n">
-        <v>6950406</v>
+        <v>6950702</v>
       </c>
       <c r="S87" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9399,19 +9409,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9426,57 +9426,62 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128410048</v>
+        <v>128407736</v>
       </c>
       <c r="B88" t="n">
-        <v>78480</v>
+        <v>57716</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>397967</v>
+        <v>398169</v>
       </c>
       <c r="R88" t="n">
-        <v>6950876</v>
+        <v>6950711</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9506,9 +9511,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9523,44 +9538,44 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128415905</v>
+        <v>128410048</v>
       </c>
       <c r="B89" t="n">
-        <v>78523</v>
+        <v>78480</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6437</v>
+        <v>498</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9570,10 +9585,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>398403</v>
+        <v>397967</v>
       </c>
       <c r="R89" t="n">
-        <v>6950826</v>
+        <v>6950876</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9603,19 +9618,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9630,22 +9635,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128407736</v>
+        <v>128415905</v>
       </c>
       <c r="B90" t="n">
-        <v>57716</v>
+        <v>78523</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9653,39 +9658,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>398169</v>
+        <v>398403</v>
       </c>
       <c r="R90" t="n">
-        <v>6950711</v>
+        <v>6950826</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9754,10 +9754,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128410197</v>
+        <v>128405637</v>
       </c>
       <c r="B91" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9765,39 +9765,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>397996</v>
+        <v>398426</v>
       </c>
       <c r="R91" t="n">
-        <v>6950884</v>
+        <v>6950561</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9827,19 +9822,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9854,22 +9839,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128411474</v>
+        <v>128413415</v>
       </c>
       <c r="B92" t="n">
-        <v>57716</v>
+        <v>79739</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9877,39 +9862,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>398202</v>
+        <v>398477</v>
       </c>
       <c r="R92" t="n">
-        <v>6950905</v>
+        <v>6951277</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9968,10 +9948,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128413415</v>
+        <v>128410197</v>
       </c>
       <c r="B93" t="n">
-        <v>79739</v>
+        <v>57716</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9979,34 +9959,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>398477</v>
+        <v>397996</v>
       </c>
       <c r="R93" t="n">
-        <v>6951277</v>
+        <v>6950884</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10036,9 +10021,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10053,22 +10048,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128405637</v>
+        <v>128411474</v>
       </c>
       <c r="B94" t="n">
-        <v>91522</v>
+        <v>57716</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10076,34 +10071,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>398426</v>
+        <v>398202</v>
       </c>
       <c r="R94" t="n">
-        <v>6950561</v>
+        <v>6950905</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10259,32 +10259,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128411728</v>
+        <v>128410472</v>
       </c>
       <c r="B96" t="n">
-        <v>78480</v>
+        <v>75205</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>398227</v>
+        <v>398075</v>
       </c>
       <c r="R96" t="n">
-        <v>6950881</v>
+        <v>6950912</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10356,10 +10356,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128410472</v>
+        <v>128407311</v>
       </c>
       <c r="B97" t="n">
-        <v>75205</v>
+        <v>78523</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10367,21 +10367,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10391,10 +10391,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>398075</v>
+        <v>398263</v>
       </c>
       <c r="R97" t="n">
-        <v>6950912</v>
+        <v>6950596</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10453,32 +10453,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128407311</v>
+        <v>128411728</v>
       </c>
       <c r="B98" t="n">
-        <v>78523</v>
+        <v>78480</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6437</v>
+        <v>498</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10488,10 +10488,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>398263</v>
+        <v>398227</v>
       </c>
       <c r="R98" t="n">
-        <v>6950596</v>
+        <v>6950881</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10550,10 +10550,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128413083</v>
+        <v>128413214</v>
       </c>
       <c r="B99" t="n">
-        <v>75205</v>
+        <v>57716</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10561,34 +10561,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>398494</v>
+        <v>398467</v>
       </c>
       <c r="R99" t="n">
-        <v>6951141</v>
+        <v>6951207</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10647,7 +10652,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128413214</v>
+        <v>128415580</v>
       </c>
       <c r="B100" t="n">
         <v>57716</v>
@@ -10678,7 +10683,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -10687,10 +10692,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>398467</v>
+        <v>398442</v>
       </c>
       <c r="R100" t="n">
-        <v>6951207</v>
+        <v>6950833</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10749,10 +10754,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128415580</v>
+        <v>128413296</v>
       </c>
       <c r="B101" t="n">
-        <v>57716</v>
+        <v>79710</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10760,39 +10765,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>398442</v>
+        <v>398463</v>
       </c>
       <c r="R101" t="n">
-        <v>6950833</v>
+        <v>6951234</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10851,10 +10851,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128413296</v>
+        <v>128407903</v>
       </c>
       <c r="B102" t="n">
-        <v>79710</v>
+        <v>81125</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10862,21 +10862,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229821</v>
+        <v>229436</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Halmgul örnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Ochrolechia alboflavescens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Wulfen) Zahlbr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10886,10 +10886,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>398463</v>
+        <v>398154</v>
       </c>
       <c r="R102" t="n">
-        <v>6951234</v>
+        <v>6950756</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10919,9 +10919,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10936,22 +10946,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128407903</v>
+        <v>128413083</v>
       </c>
       <c r="B103" t="n">
-        <v>81125</v>
+        <v>75205</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10959,21 +10969,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229436</v>
+        <v>6440</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Halmgul örnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ochrolechia alboflavescens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Wulfen) Zahlbr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10983,10 +10993,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>398154</v>
+        <v>398494</v>
       </c>
       <c r="R103" t="n">
-        <v>6950756</v>
+        <v>6951141</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11016,19 +11026,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11043,12 +11043,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -11058,7 +11058,7 @@
         <v>128411857</v>
       </c>
       <c r="B104" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>128406215</v>
       </c>
       <c r="B105" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>128405961</v>
       </c>
       <c r="B106" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>128408249</v>
       </c>
       <c r="B107" t="n">
-        <v>78480</v>
+        <v>78484</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>128408651</v>
       </c>
       <c r="B108" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11608,10 +11608,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128405590</v>
+        <v>128416572</v>
       </c>
       <c r="B109" t="n">
-        <v>57716</v>
+        <v>91526</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11619,39 +11619,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>398420</v>
+        <v>398382</v>
       </c>
       <c r="R109" t="n">
-        <v>6950543</v>
+        <v>6950639</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11683,7 +11678,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11693,7 +11688,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11720,10 +11715,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128416572</v>
+        <v>128405590</v>
       </c>
       <c r="B110" t="n">
-        <v>91522</v>
+        <v>57720</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11731,34 +11726,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>398382</v>
+        <v>398420</v>
       </c>
       <c r="R110" t="n">
-        <v>6950639</v>
+        <v>6950543</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11790,7 +11790,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11830,7 +11830,7 @@
         <v>128414034</v>
       </c>
       <c r="B111" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>128413146</v>
       </c>
       <c r="B112" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>128413351</v>
       </c>
       <c r="B113" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 32341-2025 artfynd.xlsx
+++ b/artfynd/A 32341-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128407744</v>
       </c>
       <c r="B2" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128412069</v>
       </c>
       <c r="B3" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128413409</v>
       </c>
       <c r="B4" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128412732</v>
       </c>
       <c r="B5" t="n">
-        <v>79215</v>
+        <v>79219</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128415689</v>
       </c>
       <c r="B6" t="n">
-        <v>78523</v>
+        <v>78527</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>128412850</v>
       </c>
       <c r="B7" t="n">
-        <v>78523</v>
+        <v>78527</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>128411332</v>
       </c>
       <c r="B8" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,32 +1369,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128412642</v>
+        <v>128407381</v>
       </c>
       <c r="B9" t="n">
-        <v>57557</v>
+        <v>82983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102621</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,13 +1404,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>398437</v>
+        <v>398271</v>
       </c>
       <c r="R9" t="n">
-        <v>6951052</v>
+        <v>6950584</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1437,9 +1437,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1454,12 +1464,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1469,7 +1479,7 @@
         <v>128407432</v>
       </c>
       <c r="B10" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1591,7 @@
         <v>128415979</v>
       </c>
       <c r="B11" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,32 +1700,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128407381</v>
+        <v>128409340</v>
       </c>
       <c r="B12" t="n">
-        <v>82979</v>
+        <v>80258</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1725,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>398271</v>
+        <v>397997</v>
       </c>
       <c r="R12" t="n">
-        <v>6950584</v>
+        <v>6950677</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,19 +1768,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1785,22 +1785,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128409340</v>
+        <v>128412642</v>
       </c>
       <c r="B13" t="n">
-        <v>80254</v>
+        <v>57561</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1808,21 +1808,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>102621</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1832,13 +1832,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>397997</v>
+        <v>398437</v>
       </c>
       <c r="R13" t="n">
-        <v>6950677</v>
+        <v>6951052</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>128415142</v>
       </c>
       <c r="B14" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>128410559</v>
       </c>
       <c r="B15" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128407947</v>
+        <v>128411782</v>
       </c>
       <c r="B16" t="n">
-        <v>82979</v>
+        <v>75209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>398154</v>
+        <v>398234</v>
       </c>
       <c r="R16" t="n">
-        <v>6950756</v>
+        <v>6950852</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2225,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128411782</v>
+        <v>128410038</v>
       </c>
       <c r="B17" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>398234</v>
+        <v>397967</v>
       </c>
       <c r="R17" t="n">
-        <v>6950852</v>
+        <v>6950876</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2293,19 +2293,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2320,22 +2310,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128410038</v>
+        <v>128407947</v>
       </c>
       <c r="B18" t="n">
-        <v>75205</v>
+        <v>82983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>397967</v>
+        <v>398154</v>
       </c>
       <c r="R18" t="n">
-        <v>6950876</v>
+        <v>6950756</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,9 +2390,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2417,22 +2417,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128415804</v>
+        <v>128415613</v>
       </c>
       <c r="B19" t="n">
-        <v>78523</v>
+        <v>78790</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2440,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>398394</v>
+        <v>398437</v>
       </c>
       <c r="R19" t="n">
-        <v>6950811</v>
+        <v>6950808</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2497,19 +2497,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2524,22 +2514,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128410565</v>
+        <v>128408059</v>
       </c>
       <c r="B20" t="n">
-        <v>75205</v>
+        <v>57720</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,34 +2537,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>398088</v>
+        <v>398146</v>
       </c>
       <c r="R20" t="n">
-        <v>6950909</v>
+        <v>6950784</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128408059</v>
+        <v>128415804</v>
       </c>
       <c r="B21" t="n">
-        <v>57716</v>
+        <v>78527</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,39 +2639,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>398146</v>
+        <v>398394</v>
       </c>
       <c r="R21" t="n">
-        <v>6950784</v>
+        <v>6950811</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2706,9 +2696,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2723,22 +2723,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128415681</v>
+        <v>128410565</v>
       </c>
       <c r="B22" t="n">
-        <v>79710</v>
+        <v>75209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2746,21 +2746,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>398394</v>
+        <v>398088</v>
       </c>
       <c r="R22" t="n">
-        <v>6950811</v>
+        <v>6950909</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2803,19 +2803,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2830,22 +2820,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128415613</v>
+        <v>128415681</v>
       </c>
       <c r="B23" t="n">
-        <v>78786</v>
+        <v>79714</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>398437</v>
+        <v>398394</v>
       </c>
       <c r="R23" t="n">
-        <v>6950808</v>
+        <v>6950811</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2910,9 +2900,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2927,22 +2927,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128410050</v>
+        <v>128405816</v>
       </c>
       <c r="B24" t="n">
-        <v>82979</v>
+        <v>57720</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,34 +2950,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>397967</v>
+        <v>398390</v>
       </c>
       <c r="R24" t="n">
-        <v>6950876</v>
+        <v>6950541</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3007,9 +3012,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3024,22 +3039,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128411229</v>
+        <v>128410205</v>
       </c>
       <c r="B25" t="n">
-        <v>82979</v>
+        <v>75209</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3047,21 +3062,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>398118</v>
+        <v>397980</v>
       </c>
       <c r="R25" t="n">
-        <v>6950921</v>
+        <v>6950909</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128416541</v>
+        <v>128411297</v>
       </c>
       <c r="B26" t="n">
-        <v>82979</v>
+        <v>75209</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,21 +3159,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>398411</v>
+        <v>398143</v>
       </c>
       <c r="R26" t="n">
-        <v>6950623</v>
+        <v>6950944</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128405816</v>
+        <v>128413330</v>
       </c>
       <c r="B27" t="n">
-        <v>57716</v>
+        <v>78527</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,39 +3256,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>398390</v>
+        <v>398486</v>
       </c>
       <c r="R27" t="n">
-        <v>6950541</v>
+        <v>6951242</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3303,19 +3313,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3330,22 +3330,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128410205</v>
+        <v>128410050</v>
       </c>
       <c r="B28" t="n">
-        <v>75205</v>
+        <v>82983</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3353,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>397980</v>
+        <v>397967</v>
       </c>
       <c r="R28" t="n">
-        <v>6950909</v>
+        <v>6950876</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128411297</v>
+        <v>128411229</v>
       </c>
       <c r="B29" t="n">
-        <v>75205</v>
+        <v>82983</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3450,21 +3450,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>398143</v>
+        <v>398118</v>
       </c>
       <c r="R29" t="n">
-        <v>6950944</v>
+        <v>6950921</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128413330</v>
+        <v>128416541</v>
       </c>
       <c r="B30" t="n">
-        <v>78523</v>
+        <v>82983</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3547,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>398486</v>
+        <v>398411</v>
       </c>
       <c r="R30" t="n">
-        <v>6951242</v>
+        <v>6950623</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128408399</v>
+        <v>128410403</v>
       </c>
       <c r="B31" t="n">
-        <v>82979</v>
+        <v>75209</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3644,21 +3644,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>398076</v>
+        <v>398063</v>
       </c>
       <c r="R31" t="n">
-        <v>6950793</v>
+        <v>6950893</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3730,10 +3730,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128405964</v>
+        <v>128411429</v>
       </c>
       <c r="B32" t="n">
-        <v>57716</v>
+        <v>75209</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3741,39 +3741,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>398364</v>
+        <v>398176</v>
       </c>
       <c r="R32" t="n">
-        <v>6950589</v>
+        <v>6950885</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3832,27 +3827,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128412757</v>
+        <v>128413866</v>
       </c>
       <c r="B33" t="n">
-        <v>57716</v>
+        <v>58090</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3863,7 +3858,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3872,13 +3867,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>398460</v>
+        <v>398505</v>
       </c>
       <c r="R33" t="n">
-        <v>6951061</v>
+        <v>6951279</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3944,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128415952</v>
+        <v>128408399</v>
       </c>
       <c r="B34" t="n">
-        <v>57716</v>
+        <v>82983</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3955,39 +3950,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>398385</v>
+        <v>398076</v>
       </c>
       <c r="R34" t="n">
-        <v>6950755</v>
+        <v>6950793</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4046,27 +4036,27 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128413866</v>
+        <v>128405964</v>
       </c>
       <c r="B35" t="n">
-        <v>58086</v>
+        <v>57720</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4077,7 +4067,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4086,13 +4076,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398505</v>
+        <v>398364</v>
       </c>
       <c r="R35" t="n">
-        <v>6951279</v>
+        <v>6950589</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4119,19 +4109,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4146,22 +4126,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128411736</v>
+        <v>128412757</v>
       </c>
       <c r="B36" t="n">
-        <v>91522</v>
+        <v>57720</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4169,34 +4149,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398234</v>
+        <v>398460</v>
       </c>
       <c r="R36" t="n">
-        <v>6950852</v>
+        <v>6951061</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,10 +4250,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128410403</v>
+        <v>128415952</v>
       </c>
       <c r="B37" t="n">
-        <v>75205</v>
+        <v>57720</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4276,34 +4261,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>398063</v>
+        <v>398385</v>
       </c>
       <c r="R37" t="n">
-        <v>6950893</v>
+        <v>6950755</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4362,10 +4352,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128411429</v>
+        <v>128411736</v>
       </c>
       <c r="B38" t="n">
-        <v>75205</v>
+        <v>91526</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4373,21 +4363,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4397,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>398176</v>
+        <v>398234</v>
       </c>
       <c r="R38" t="n">
-        <v>6950885</v>
+        <v>6950852</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4430,9 +4420,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4447,44 +4447,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128415930</v>
+        <v>128416366</v>
       </c>
       <c r="B39" t="n">
-        <v>79710</v>
+        <v>78484</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>398387</v>
+        <v>398419</v>
       </c>
       <c r="R39" t="n">
-        <v>6950766</v>
+        <v>6950678</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4556,10 +4556,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128411735</v>
+        <v>128405669</v>
       </c>
       <c r="B40" t="n">
-        <v>75205</v>
+        <v>91526</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4567,21 +4567,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>398227</v>
+        <v>398398</v>
       </c>
       <c r="R40" t="n">
-        <v>6950881</v>
+        <v>6950569</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128405841</v>
+        <v>128412193</v>
       </c>
       <c r="B41" t="n">
-        <v>92201</v>
+        <v>80264</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4664,21 +4664,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>6463</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>398374</v>
+        <v>398369</v>
       </c>
       <c r="R41" t="n">
-        <v>6950548</v>
+        <v>6950956</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4750,32 +4750,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128416366</v>
+        <v>128411735</v>
       </c>
       <c r="B42" t="n">
-        <v>78480</v>
+        <v>75209</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4785,10 +4785,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>398419</v>
+        <v>398227</v>
       </c>
       <c r="R42" t="n">
-        <v>6950678</v>
+        <v>6950881</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4847,10 +4847,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128405669</v>
+        <v>128415930</v>
       </c>
       <c r="B43" t="n">
-        <v>91522</v>
+        <v>79714</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4858,21 +4858,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4882,10 +4882,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>398398</v>
+        <v>398387</v>
       </c>
       <c r="R43" t="n">
-        <v>6950569</v>
+        <v>6950766</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4944,45 +4944,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128412193</v>
+        <v>128414073</v>
       </c>
       <c r="B44" t="n">
-        <v>80260</v>
+        <v>57720</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>398369</v>
+        <v>398546</v>
       </c>
       <c r="R44" t="n">
-        <v>6950956</v>
+        <v>6951235</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5041,10 +5046,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128414073</v>
+        <v>128412950</v>
       </c>
       <c r="B45" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5081,10 +5086,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>398546</v>
+        <v>398483</v>
       </c>
       <c r="R45" t="n">
-        <v>6951235</v>
+        <v>6951117</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5143,50 +5148,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128412950</v>
+        <v>128405841</v>
       </c>
       <c r="B46" t="n">
-        <v>57716</v>
+        <v>92205</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>398483</v>
+        <v>398374</v>
       </c>
       <c r="R46" t="n">
-        <v>6951117</v>
+        <v>6950548</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5248,7 +5248,7 @@
         <v>128412677</v>
       </c>
       <c r="B47" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>128415972</v>
       </c>
       <c r="B48" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5459,10 +5459,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128406327</v>
+        <v>128407293</v>
       </c>
       <c r="B49" t="n">
-        <v>91522</v>
+        <v>79743</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5470,21 +5470,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5494,10 +5494,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>398333</v>
+        <v>398263</v>
       </c>
       <c r="R49" t="n">
-        <v>6950603</v>
+        <v>6950596</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5556,10 +5556,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128411964</v>
+        <v>128415932</v>
       </c>
       <c r="B50" t="n">
-        <v>91522</v>
+        <v>79743</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5567,21 +5567,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5591,10 +5591,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>398278</v>
+        <v>398387</v>
       </c>
       <c r="R50" t="n">
-        <v>6950881</v>
+        <v>6950766</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5653,32 +5653,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128407293</v>
+        <v>128412638</v>
       </c>
       <c r="B51" t="n">
-        <v>79739</v>
+        <v>57824</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>398263</v>
+        <v>398437</v>
       </c>
       <c r="R51" t="n">
-        <v>6950596</v>
+        <v>6951052</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5750,10 +5750,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128410408</v>
+        <v>128408097</v>
       </c>
       <c r="B52" t="n">
-        <v>79120</v>
+        <v>57880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5761,37 +5761,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>398063</v>
+        <v>398159</v>
       </c>
       <c r="R52" t="n">
-        <v>6950893</v>
+        <v>6950801</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5818,9 +5823,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5835,22 +5850,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128415932</v>
+        <v>128411964</v>
       </c>
       <c r="B53" t="n">
-        <v>79739</v>
+        <v>91526</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5858,21 +5873,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5882,10 +5897,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>398387</v>
+        <v>398278</v>
       </c>
       <c r="R53" t="n">
-        <v>6950766</v>
+        <v>6950881</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5944,10 +5959,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128408097</v>
+        <v>128406327</v>
       </c>
       <c r="B54" t="n">
-        <v>57876</v>
+        <v>91526</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5955,42 +5970,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>398159</v>
+        <v>398333</v>
       </c>
       <c r="R54" t="n">
-        <v>6950801</v>
+        <v>6950603</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6017,19 +6027,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6044,44 +6044,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128412638</v>
+        <v>128410408</v>
       </c>
       <c r="B55" t="n">
-        <v>57820</v>
+        <v>79124</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6091,13 +6091,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>398437</v>
+        <v>398063</v>
       </c>
       <c r="R55" t="n">
-        <v>6951052</v>
+        <v>6950893</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>128405859</v>
       </c>
       <c r="B56" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>128413307</v>
       </c>
       <c r="B57" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6377,48 +6377,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128409775</v>
+        <v>128413955</v>
       </c>
       <c r="B58" t="n">
-        <v>79710</v>
+        <v>57561</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>102621</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>398008</v>
+        <v>398517</v>
       </c>
       <c r="R58" t="n">
-        <v>6950745</v>
+        <v>6951283</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6474,10 +6479,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128408521</v>
+        <v>128409775</v>
       </c>
       <c r="B59" t="n">
-        <v>79739</v>
+        <v>79714</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6485,21 +6490,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6509,10 +6514,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>398019</v>
+        <v>398008</v>
       </c>
       <c r="R59" t="n">
-        <v>6950740</v>
+        <v>6950745</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6571,53 +6576,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128413955</v>
+        <v>128408521</v>
       </c>
       <c r="B60" t="n">
-        <v>57557</v>
+        <v>79743</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102621</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>398517</v>
+        <v>398019</v>
       </c>
       <c r="R60" t="n">
-        <v>6951283</v>
+        <v>6950740</v>
       </c>
       <c r="S60" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>128408773</v>
       </c>
       <c r="B61" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6785,10 +6785,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128406318</v>
+        <v>128415706</v>
       </c>
       <c r="B62" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6796,34 +6796,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>398333</v>
+        <v>398411</v>
       </c>
       <c r="R62" t="n">
-        <v>6950603</v>
+        <v>6950796</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6882,10 +6887,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128406026</v>
+        <v>128416501</v>
       </c>
       <c r="B63" t="n">
-        <v>79739</v>
+        <v>57720</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6893,34 +6898,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>398364</v>
+        <v>398382</v>
       </c>
       <c r="R63" t="n">
-        <v>6950589</v>
+        <v>6950639</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6950,9 +6960,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6967,22 +6987,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128415836</v>
+        <v>128406318</v>
       </c>
       <c r="B64" t="n">
-        <v>78092</v>
+        <v>79124</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6990,21 +7010,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7014,10 +7034,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>398394</v>
+        <v>398333</v>
       </c>
       <c r="R64" t="n">
-        <v>6950811</v>
+        <v>6950603</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7047,19 +7067,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7074,22 +7084,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128409691</v>
+        <v>128415836</v>
       </c>
       <c r="B65" t="n">
-        <v>90536</v>
+        <v>78096</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7097,21 +7107,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7121,10 +7131,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>398057</v>
+        <v>398394</v>
       </c>
       <c r="R65" t="n">
-        <v>6950739</v>
+        <v>6950811</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7156,7 +7166,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7166,7 +7176,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7193,10 +7203,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128415706</v>
+        <v>128406026</v>
       </c>
       <c r="B66" t="n">
-        <v>57716</v>
+        <v>79743</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7204,39 +7214,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>398411</v>
+        <v>398364</v>
       </c>
       <c r="R66" t="n">
-        <v>6950796</v>
+        <v>6950589</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7295,10 +7300,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128416501</v>
+        <v>128409691</v>
       </c>
       <c r="B67" t="n">
-        <v>57716</v>
+        <v>90540</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7306,39 +7311,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>398382</v>
+        <v>398057</v>
       </c>
       <c r="R67" t="n">
-        <v>6950639</v>
+        <v>6950739</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7410,7 +7410,7 @@
         <v>128407307</v>
       </c>
       <c r="B68" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7504,10 +7504,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128411931</v>
+        <v>128411524</v>
       </c>
       <c r="B69" t="n">
-        <v>91522</v>
+        <v>57720</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7515,34 +7515,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>398276</v>
+        <v>398203</v>
       </c>
       <c r="R69" t="n">
-        <v>6950842</v>
+        <v>6950901</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7572,9 +7577,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7589,22 +7604,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128411612</v>
+        <v>128411180</v>
       </c>
       <c r="B70" t="n">
-        <v>79199</v>
+        <v>57720</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7612,34 +7627,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>398200</v>
+        <v>398102</v>
       </c>
       <c r="R70" t="n">
-        <v>6950918</v>
+        <v>6950907</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7669,9 +7689,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7686,22 +7716,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128411524</v>
+        <v>128411308</v>
       </c>
       <c r="B71" t="n">
-        <v>57716</v>
+        <v>75209</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7709,39 +7739,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>398203</v>
+        <v>398162</v>
       </c>
       <c r="R71" t="n">
-        <v>6950901</v>
+        <v>6950923</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7771,19 +7796,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7798,22 +7813,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128411180</v>
+        <v>128411612</v>
       </c>
       <c r="B72" t="n">
-        <v>57716</v>
+        <v>79203</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7821,39 +7836,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>398102</v>
+        <v>398200</v>
       </c>
       <c r="R72" t="n">
-        <v>6950907</v>
+        <v>6950918</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7883,19 +7893,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7910,22 +7910,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128411308</v>
+        <v>128411931</v>
       </c>
       <c r="B73" t="n">
-        <v>75205</v>
+        <v>91526</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7933,21 +7933,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7957,10 +7957,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>398162</v>
+        <v>398276</v>
       </c>
       <c r="R73" t="n">
-        <v>6950923</v>
+        <v>6950842</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8019,27 +8019,27 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128412622</v>
+        <v>128412048</v>
       </c>
       <c r="B74" t="n">
-        <v>58086</v>
+        <v>57720</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8048,19 +8048,24 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>398437</v>
+        <v>398329</v>
       </c>
       <c r="R74" t="n">
-        <v>6951052</v>
+        <v>6950952</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8087,9 +8092,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8104,22 +8119,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128412825</v>
+        <v>128406114</v>
       </c>
       <c r="B75" t="n">
-        <v>79710</v>
+        <v>57720</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8127,34 +8142,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>398474</v>
+        <v>398351</v>
       </c>
       <c r="R75" t="n">
-        <v>6951085</v>
+        <v>6950591</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8184,9 +8204,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8201,62 +8231,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128412048</v>
+        <v>128416207</v>
       </c>
       <c r="B76" t="n">
-        <v>57716</v>
+        <v>75207</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>398329</v>
+        <v>398414</v>
       </c>
       <c r="R76" t="n">
-        <v>6950952</v>
+        <v>6950702</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8286,19 +8311,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8313,60 +8328,60 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128405468</v>
+        <v>128412622</v>
       </c>
       <c r="B77" t="n">
-        <v>82979</v>
+        <v>58090</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>398405</v>
+        <v>398437</v>
       </c>
       <c r="R77" t="n">
-        <v>6950503</v>
+        <v>6951052</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8422,32 +8437,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128416207</v>
+        <v>128412825</v>
       </c>
       <c r="B78" t="n">
-        <v>75203</v>
+        <v>79714</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6486</v>
+        <v>229821</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8457,10 +8472,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>398414</v>
+        <v>398474</v>
       </c>
       <c r="R78" t="n">
-        <v>6950702</v>
+        <v>6951085</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8519,10 +8534,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128406114</v>
+        <v>128405468</v>
       </c>
       <c r="B79" t="n">
-        <v>57716</v>
+        <v>82983</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8530,39 +8545,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>398351</v>
+        <v>398405</v>
       </c>
       <c r="R79" t="n">
-        <v>6950591</v>
+        <v>6950503</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8592,19 +8602,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8619,12 +8619,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8634,7 +8634,7 @@
         <v>128411329</v>
       </c>
       <c r="B80" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>128405900</v>
       </c>
       <c r="B81" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8830,10 +8830,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128407528</v>
+        <v>128411270</v>
       </c>
       <c r="B82" t="n">
-        <v>78786</v>
+        <v>78527</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8841,21 +8841,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>398225</v>
+        <v>398139</v>
       </c>
       <c r="R82" t="n">
-        <v>6950599</v>
+        <v>6950929</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8927,10 +8927,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128411270</v>
+        <v>128407528</v>
       </c>
       <c r="B83" t="n">
-        <v>78523</v>
+        <v>78790</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8938,21 +8938,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>398139</v>
+        <v>398225</v>
       </c>
       <c r="R83" t="n">
-        <v>6950929</v>
+        <v>6950599</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9024,53 +9024,49 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128411972</v>
+        <v>128404962</v>
       </c>
       <c r="B84" t="n">
-        <v>57716</v>
+        <v>57885</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>266237</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>398278</v>
+        <v>398392</v>
       </c>
       <c r="R84" t="n">
-        <v>6950881</v>
+        <v>6950406</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9097,9 +9093,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9114,22 +9120,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128407963</v>
+        <v>128411972</v>
       </c>
       <c r="B85" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9155,16 +9161,21 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>398154</v>
+        <v>398278</v>
       </c>
       <c r="R85" t="n">
-        <v>6950756</v>
+        <v>6950881</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9194,19 +9205,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9221,61 +9222,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128404962</v>
+        <v>128407963</v>
       </c>
       <c r="B86" t="n">
-        <v>57881</v>
+        <v>57720</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>266237</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>398392</v>
+        <v>398154</v>
       </c>
       <c r="R86" t="n">
-        <v>6950406</v>
+        <v>6950756</v>
       </c>
       <c r="S86" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>128416210</v>
       </c>
       <c r="B87" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9438,50 +9438,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128407736</v>
+        <v>128410048</v>
       </c>
       <c r="B88" t="n">
-        <v>57716</v>
+        <v>78484</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>398169</v>
+        <v>397967</v>
       </c>
       <c r="R88" t="n">
-        <v>6950711</v>
+        <v>6950876</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9511,19 +9506,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9538,57 +9523,62 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128410048</v>
+        <v>128407736</v>
       </c>
       <c r="B89" t="n">
-        <v>78480</v>
+        <v>57720</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>397967</v>
+        <v>398169</v>
       </c>
       <c r="R89" t="n">
-        <v>6950876</v>
+        <v>6950711</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9618,9 +9608,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9635,12 +9635,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -9650,7 +9650,7 @@
         <v>128415905</v>
       </c>
       <c r="B90" t="n">
-        <v>78523</v>
+        <v>78527</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9754,10 +9754,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128405637</v>
+        <v>128410197</v>
       </c>
       <c r="B91" t="n">
-        <v>91522</v>
+        <v>57720</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9765,34 +9765,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>398426</v>
+        <v>397996</v>
       </c>
       <c r="R91" t="n">
-        <v>6950561</v>
+        <v>6950884</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9822,9 +9827,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9839,22 +9854,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128413415</v>
+        <v>128411474</v>
       </c>
       <c r="B92" t="n">
-        <v>79739</v>
+        <v>57720</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9862,34 +9877,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>398477</v>
+        <v>398202</v>
       </c>
       <c r="R92" t="n">
-        <v>6951277</v>
+        <v>6950905</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9948,10 +9968,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128410197</v>
+        <v>128413415</v>
       </c>
       <c r="B93" t="n">
-        <v>57716</v>
+        <v>79743</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9959,39 +9979,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>397996</v>
+        <v>398477</v>
       </c>
       <c r="R93" t="n">
-        <v>6950884</v>
+        <v>6951277</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10021,19 +10036,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10048,22 +10053,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128411474</v>
+        <v>128405637</v>
       </c>
       <c r="B94" t="n">
-        <v>57716</v>
+        <v>91526</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10071,39 +10076,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>398202</v>
+        <v>398426</v>
       </c>
       <c r="R94" t="n">
-        <v>6950905</v>
+        <v>6950561</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10165,7 +10165,7 @@
         <v>128413088</v>
       </c>
       <c r="B95" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10259,32 +10259,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128410472</v>
+        <v>128411728</v>
       </c>
       <c r="B96" t="n">
-        <v>75205</v>
+        <v>78484</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6440</v>
+        <v>498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>398075</v>
+        <v>398227</v>
       </c>
       <c r="R96" t="n">
-        <v>6950912</v>
+        <v>6950881</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10356,10 +10356,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128407311</v>
+        <v>128410472</v>
       </c>
       <c r="B97" t="n">
-        <v>78523</v>
+        <v>75209</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10367,21 +10367,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10391,10 +10391,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>398263</v>
+        <v>398075</v>
       </c>
       <c r="R97" t="n">
-        <v>6950596</v>
+        <v>6950912</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10453,32 +10453,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128411728</v>
+        <v>128407311</v>
       </c>
       <c r="B98" t="n">
-        <v>78480</v>
+        <v>78527</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>498</v>
+        <v>6437</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10488,10 +10488,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>398227</v>
+        <v>398263</v>
       </c>
       <c r="R98" t="n">
-        <v>6950881</v>
+        <v>6950596</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10550,10 +10550,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128413214</v>
+        <v>128413296</v>
       </c>
       <c r="B99" t="n">
-        <v>57716</v>
+        <v>79714</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10561,39 +10561,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>398467</v>
+        <v>398463</v>
       </c>
       <c r="R99" t="n">
-        <v>6951207</v>
+        <v>6951234</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10652,10 +10647,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128415580</v>
+        <v>128407903</v>
       </c>
       <c r="B100" t="n">
-        <v>57716</v>
+        <v>81129</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10663,39 +10658,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>229436</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Halmgul örnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ochrolechia alboflavescens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wulfen) Zahlbr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>398442</v>
+        <v>398154</v>
       </c>
       <c r="R100" t="n">
-        <v>6950833</v>
+        <v>6950756</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10725,9 +10715,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10742,22 +10742,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128413296</v>
+        <v>128413214</v>
       </c>
       <c r="B101" t="n">
-        <v>79710</v>
+        <v>57720</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10765,34 +10765,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>398463</v>
+        <v>398467</v>
       </c>
       <c r="R101" t="n">
-        <v>6951234</v>
+        <v>6951207</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10851,10 +10856,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128407903</v>
+        <v>128415580</v>
       </c>
       <c r="B102" t="n">
-        <v>81125</v>
+        <v>57720</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10862,34 +10867,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229436</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Halmgul örnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ochrolechia alboflavescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Wulfen) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>398154</v>
+        <v>398442</v>
       </c>
       <c r="R102" t="n">
-        <v>6950756</v>
+        <v>6950833</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10919,19 +10929,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10946,12 +10946,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -10961,7 +10961,7 @@
         <v>128413083</v>
       </c>
       <c r="B103" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11608,10 +11608,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128416572</v>
+        <v>128405590</v>
       </c>
       <c r="B109" t="n">
-        <v>91526</v>
+        <v>57720</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11619,34 +11619,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>398382</v>
+        <v>398420</v>
       </c>
       <c r="R109" t="n">
-        <v>6950639</v>
+        <v>6950543</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11678,7 +11683,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11688,7 +11693,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11715,10 +11720,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128405590</v>
+        <v>128416572</v>
       </c>
       <c r="B110" t="n">
-        <v>57720</v>
+        <v>91526</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11726,39 +11731,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>398420</v>
+        <v>398382</v>
       </c>
       <c r="R110" t="n">
-        <v>6950543</v>
+        <v>6950639</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11790,7 +11790,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 32341-2025 artfynd.xlsx
+++ b/artfynd/A 32341-2025 artfynd.xlsx
@@ -1894,10 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128415142</v>
+        <v>128407947</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>82983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1905,39 +1905,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>398352</v>
+        <v>398154</v>
       </c>
       <c r="R14" t="n">
-        <v>6950954</v>
+        <v>6950756</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,7 +1964,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1979,7 +1974,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2006,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128410559</v>
+        <v>128415142</v>
       </c>
       <c r="B15" t="n">
         <v>57720</v>
@@ -2046,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>398097</v>
+        <v>398352</v>
       </c>
       <c r="R15" t="n">
-        <v>6950870</v>
+        <v>6950954</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128411782</v>
+        <v>128410559</v>
       </c>
       <c r="B16" t="n">
-        <v>75209</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,34 +2124,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>398234</v>
+        <v>398097</v>
       </c>
       <c r="R16" t="n">
-        <v>6950852</v>
+        <v>6950870</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128410038</v>
+        <v>128411782</v>
       </c>
       <c r="B17" t="n">
         <v>75209</v>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>397967</v>
+        <v>398234</v>
       </c>
       <c r="R17" t="n">
-        <v>6950876</v>
+        <v>6950852</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2293,9 +2293,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,22 +2320,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128407947</v>
+        <v>128410038</v>
       </c>
       <c r="B18" t="n">
-        <v>82983</v>
+        <v>75209</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>398154</v>
+        <v>397967</v>
       </c>
       <c r="R18" t="n">
-        <v>6950756</v>
+        <v>6950876</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2390,19 +2400,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2417,22 +2417,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128415613</v>
+        <v>128408059</v>
       </c>
       <c r="B19" t="n">
-        <v>78790</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2440,34 +2440,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>398437</v>
+        <v>398146</v>
       </c>
       <c r="R19" t="n">
-        <v>6950808</v>
+        <v>6950784</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128408059</v>
+        <v>128415804</v>
       </c>
       <c r="B20" t="n">
-        <v>57720</v>
+        <v>78527</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2537,39 +2542,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>398146</v>
+        <v>398394</v>
       </c>
       <c r="R20" t="n">
-        <v>6950784</v>
+        <v>6950811</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2599,9 +2599,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2616,22 +2626,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128415804</v>
+        <v>128410565</v>
       </c>
       <c r="B21" t="n">
-        <v>78527</v>
+        <v>75209</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2639,21 +2649,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>398394</v>
+        <v>398088</v>
       </c>
       <c r="R21" t="n">
-        <v>6950811</v>
+        <v>6950909</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2696,19 +2706,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2723,22 +2723,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128410565</v>
+        <v>128415681</v>
       </c>
       <c r="B22" t="n">
-        <v>75209</v>
+        <v>79714</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2746,21 +2746,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>398088</v>
+        <v>398394</v>
       </c>
       <c r="R22" t="n">
-        <v>6950909</v>
+        <v>6950811</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2803,9 +2803,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2820,22 +2830,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128415681</v>
+        <v>128415613</v>
       </c>
       <c r="B23" t="n">
-        <v>79714</v>
+        <v>78790</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2843,21 +2853,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>398394</v>
+        <v>398437</v>
       </c>
       <c r="R23" t="n">
-        <v>6950811</v>
+        <v>6950808</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2900,19 +2910,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2927,12 +2927,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -6153,10 +6153,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128405859</v>
+        <v>128408521</v>
       </c>
       <c r="B56" t="n">
-        <v>57720</v>
+        <v>79743</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6164,39 +6164,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>398362</v>
+        <v>398019</v>
       </c>
       <c r="R56" t="n">
-        <v>6950549</v>
+        <v>6950740</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6226,19 +6221,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6253,39 +6238,39 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128413307</v>
+        <v>128408773</v>
       </c>
       <c r="B57" t="n">
-        <v>57720</v>
+        <v>58090</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6296,7 +6281,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6305,13 +6290,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>398457</v>
+        <v>398012</v>
       </c>
       <c r="R57" t="n">
-        <v>6951226</v>
+        <v>6950659</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6340,7 +6325,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6350,7 +6335,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6377,27 +6362,27 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128413955</v>
+        <v>128405859</v>
       </c>
       <c r="B58" t="n">
-        <v>57561</v>
+        <v>57720</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6408,7 +6393,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6417,13 +6402,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>398517</v>
+        <v>398362</v>
       </c>
       <c r="R58" t="n">
-        <v>6951283</v>
+        <v>6950549</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6450,9 +6435,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6467,22 +6462,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128409775</v>
+        <v>128413307</v>
       </c>
       <c r="B59" t="n">
-        <v>79714</v>
+        <v>57720</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6490,34 +6485,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>398008</v>
+        <v>398457</v>
       </c>
       <c r="R59" t="n">
-        <v>6950745</v>
+        <v>6951226</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6547,9 +6547,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6564,60 +6574,65 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128408521</v>
+        <v>128413955</v>
       </c>
       <c r="B60" t="n">
-        <v>79743</v>
+        <v>57561</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>102621</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>398019</v>
+        <v>398517</v>
       </c>
       <c r="R60" t="n">
-        <v>6950740</v>
+        <v>6951283</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6673,53 +6688,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128408773</v>
+        <v>128409775</v>
       </c>
       <c r="B61" t="n">
-        <v>58090</v>
+        <v>79714</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>398012</v>
+        <v>398008</v>
       </c>
       <c r="R61" t="n">
-        <v>6950659</v>
+        <v>6950745</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6746,19 +6756,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6773,12 +6773,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -8830,10 +8830,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128411270</v>
+        <v>128407528</v>
       </c>
       <c r="B82" t="n">
-        <v>78527</v>
+        <v>78790</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8841,21 +8841,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>398139</v>
+        <v>398225</v>
       </c>
       <c r="R82" t="n">
-        <v>6950929</v>
+        <v>6950599</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8927,10 +8927,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128407528</v>
+        <v>128411270</v>
       </c>
       <c r="B83" t="n">
-        <v>78790</v>
+        <v>78527</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8938,21 +8938,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>398225</v>
+        <v>398139</v>
       </c>
       <c r="R83" t="n">
-        <v>6950599</v>
+        <v>6950929</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9024,49 +9024,53 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128404962</v>
+        <v>128411972</v>
       </c>
       <c r="B84" t="n">
-        <v>57885</v>
+        <v>57720</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>266237</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Talltita x tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>398392</v>
+        <v>398278</v>
       </c>
       <c r="R84" t="n">
-        <v>6950406</v>
+        <v>6950881</v>
       </c>
       <c r="S84" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9093,19 +9097,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9120,19 +9114,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128411972</v>
+        <v>128407963</v>
       </c>
       <c r="B85" t="n">
         <v>57720</v>
@@ -9161,21 +9155,16 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>398278</v>
+        <v>398154</v>
       </c>
       <c r="R85" t="n">
-        <v>6950881</v>
+        <v>6950756</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9205,9 +9194,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9222,22 +9221,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128407963</v>
+        <v>128416210</v>
       </c>
       <c r="B86" t="n">
-        <v>57720</v>
+        <v>91526</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9245,21 +9244,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9269,10 +9268,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>398154</v>
+        <v>398414</v>
       </c>
       <c r="R86" t="n">
-        <v>6950756</v>
+        <v>6950702</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9302,19 +9301,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9329,60 +9318,61 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128416210</v>
+        <v>128404962</v>
       </c>
       <c r="B87" t="n">
-        <v>91526</v>
+        <v>57885</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5432</v>
+        <v>266237</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>398414</v>
+        <v>398392</v>
       </c>
       <c r="R87" t="n">
-        <v>6950702</v>
+        <v>6950406</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9409,9 +9399,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9426,12 +9426,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9754,10 +9754,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128410197</v>
+        <v>128405637</v>
       </c>
       <c r="B91" t="n">
-        <v>57720</v>
+        <v>91526</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9765,39 +9765,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Brändåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>397996</v>
+        <v>398426</v>
       </c>
       <c r="R91" t="n">
-        <v>6950884</v>
+        <v>6950561</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9827,19 +9822,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9854,19 +9839,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128411474</v>
+        <v>128410197</v>
       </c>
       <c r="B92" t="n">
         <v>57720</v>
@@ -9897,7 +9882,7 @@
       <c r="I92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -9906,10 +9891,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>398202</v>
+        <v>397996</v>
       </c>
       <c r="R92" t="n">
-        <v>6950905</v>
+        <v>6950884</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9939,9 +9924,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9956,22 +9951,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128413415</v>
+        <v>128411474</v>
       </c>
       <c r="B93" t="n">
-        <v>79743</v>
+        <v>57720</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9979,34 +9974,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>398477</v>
+        <v>398202</v>
       </c>
       <c r="R93" t="n">
-        <v>6951277</v>
+        <v>6950905</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10065,10 +10065,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128405637</v>
+        <v>128413415</v>
       </c>
       <c r="B94" t="n">
-        <v>91526</v>
+        <v>79743</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10076,34 +10076,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>398426</v>
+        <v>398477</v>
       </c>
       <c r="R94" t="n">
-        <v>6950561</v>
+        <v>6951277</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11608,10 +11608,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128405590</v>
+        <v>128416572</v>
       </c>
       <c r="B109" t="n">
-        <v>57720</v>
+        <v>91526</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11619,39 +11619,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>398420</v>
+        <v>398382</v>
       </c>
       <c r="R109" t="n">
-        <v>6950543</v>
+        <v>6950639</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11683,7 +11678,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11693,7 +11688,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11720,10 +11715,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128416572</v>
+        <v>128405590</v>
       </c>
       <c r="B110" t="n">
-        <v>91526</v>
+        <v>57720</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11731,34 +11726,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>398382</v>
+        <v>398420</v>
       </c>
       <c r="R110" t="n">
-        <v>6950639</v>
+        <v>6950543</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11790,7 +11790,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 32341-2025 artfynd.xlsx
+++ b/artfynd/A 32341-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128407744</v>
+        <v>128412069</v>
       </c>
       <c r="B2" t="n">
-        <v>79743</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398173</v>
+        <v>398298</v>
       </c>
       <c r="R2" t="n">
-        <v>6950715</v>
+        <v>6950883</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128412069</v>
+        <v>128413409</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>79619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398298</v>
+        <v>398477</v>
       </c>
       <c r="R3" t="n">
-        <v>6950883</v>
+        <v>6951277</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128413409</v>
+        <v>128407744</v>
       </c>
       <c r="B4" t="n">
-        <v>79714</v>
+        <v>79648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398477</v>
+        <v>398173</v>
       </c>
       <c r="R4" t="n">
-        <v>6951277</v>
+        <v>6950715</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128412732</v>
+        <v>128415689</v>
       </c>
       <c r="B5" t="n">
-        <v>79219</v>
+        <v>78432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>967</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>398474</v>
+        <v>398409</v>
       </c>
       <c r="R5" t="n">
-        <v>6951085</v>
+        <v>6950805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128415689</v>
+        <v>128412850</v>
       </c>
       <c r="B6" t="n">
-        <v>78527</v>
+        <v>78432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>398409</v>
+        <v>398474</v>
       </c>
       <c r="R6" t="n">
-        <v>6950805</v>
+        <v>6951085</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128412850</v>
+        <v>128411332</v>
       </c>
       <c r="B7" t="n">
-        <v>78527</v>
+        <v>83005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>398474</v>
+        <v>398187</v>
       </c>
       <c r="R7" t="n">
-        <v>6951085</v>
+        <v>6950935</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1233,9 +1233,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1250,22 +1260,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128411332</v>
+        <v>128412732</v>
       </c>
       <c r="B8" t="n">
-        <v>75209</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>967</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>398187</v>
+        <v>398474</v>
       </c>
       <c r="R8" t="n">
-        <v>6950935</v>
+        <v>6951085</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1330,19 +1340,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1357,12 +1357,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1372,7 +1372,7 @@
         <v>128407381</v>
       </c>
       <c r="B9" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,50 +1476,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128407432</v>
+        <v>128409340</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>80163</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>398269</v>
+        <v>397997</v>
       </c>
       <c r="R10" t="n">
-        <v>6950563</v>
+        <v>6950677</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,19 +1544,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1576,22 +1561,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128415979</v>
+        <v>128407432</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1628,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>398372</v>
+        <v>398269</v>
       </c>
       <c r="R11" t="n">
-        <v>6950738</v>
+        <v>6950563</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,7 +1648,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1673,7 +1658,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,45 +1685,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128409340</v>
+        <v>128415979</v>
       </c>
       <c r="B12" t="n">
-        <v>80258</v>
+        <v>57723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>397997</v>
+        <v>398372</v>
       </c>
       <c r="R12" t="n">
-        <v>6950677</v>
+        <v>6950738</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,9 +1758,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1785,12 +1785,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1800,7 +1800,7 @@
         <v>128412642</v>
       </c>
       <c r="B13" t="n">
-        <v>57561</v>
+        <v>57564</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>128407947</v>
       </c>
       <c r="B14" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128415142</v>
+        <v>128410559</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>398352</v>
+        <v>398097</v>
       </c>
       <c r="R15" t="n">
-        <v>6950954</v>
+        <v>6950870</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128410559</v>
+        <v>128415142</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>398097</v>
+        <v>398352</v>
       </c>
       <c r="R16" t="n">
-        <v>6950870</v>
+        <v>6950954</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,7 +2228,7 @@
         <v>128411782</v>
       </c>
       <c r="B17" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>128410038</v>
       </c>
       <c r="B18" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>128408059</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128415804</v>
+        <v>128415681</v>
       </c>
       <c r="B20" t="n">
-        <v>78527</v>
+        <v>79619</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2542,21 +2542,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2638,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128410565</v>
+        <v>128415613</v>
       </c>
       <c r="B21" t="n">
-        <v>75209</v>
+        <v>78695</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2649,21 +2649,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>398088</v>
+        <v>398437</v>
       </c>
       <c r="R21" t="n">
-        <v>6950909</v>
+        <v>6950808</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128415681</v>
+        <v>128415804</v>
       </c>
       <c r="B22" t="n">
-        <v>79714</v>
+        <v>78432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2746,21 +2746,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2842,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128415613</v>
+        <v>128410565</v>
       </c>
       <c r="B23" t="n">
-        <v>78790</v>
+        <v>83005</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,21 +2853,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>398437</v>
+        <v>398088</v>
       </c>
       <c r="R23" t="n">
-        <v>6950808</v>
+        <v>6950909</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128405816</v>
+        <v>128410205</v>
       </c>
       <c r="B24" t="n">
-        <v>57720</v>
+        <v>83005</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,39 +2950,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>398390</v>
+        <v>397980</v>
       </c>
       <c r="R24" t="n">
-        <v>6950541</v>
+        <v>6950909</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3012,19 +3007,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3039,22 +3024,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128410205</v>
+        <v>128411297</v>
       </c>
       <c r="B25" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3086,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>397980</v>
+        <v>398143</v>
       </c>
       <c r="R25" t="n">
-        <v>6950909</v>
+        <v>6950944</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128411297</v>
+        <v>128413330</v>
       </c>
       <c r="B26" t="n">
-        <v>75209</v>
+        <v>78432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3159,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3183,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>398143</v>
+        <v>398486</v>
       </c>
       <c r="R26" t="n">
-        <v>6950944</v>
+        <v>6951242</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128413330</v>
+        <v>128410050</v>
       </c>
       <c r="B27" t="n">
-        <v>78527</v>
+        <v>82892</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3256,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3280,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>398486</v>
+        <v>397967</v>
       </c>
       <c r="R27" t="n">
-        <v>6951242</v>
+        <v>6950876</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128410050</v>
+        <v>128411229</v>
       </c>
       <c r="B28" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3377,10 +3362,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>397967</v>
+        <v>398118</v>
       </c>
       <c r="R28" t="n">
-        <v>6950876</v>
+        <v>6950921</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3424,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128411229</v>
+        <v>128416541</v>
       </c>
       <c r="B29" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3474,10 +3459,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>398118</v>
+        <v>398411</v>
       </c>
       <c r="R29" t="n">
-        <v>6950921</v>
+        <v>6950623</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,10 +3521,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128416541</v>
+        <v>128405816</v>
       </c>
       <c r="B30" t="n">
-        <v>82983</v>
+        <v>57723</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3547,34 +3532,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>398411</v>
+        <v>398390</v>
       </c>
       <c r="R30" t="n">
-        <v>6950623</v>
+        <v>6950541</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3604,9 +3594,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3621,22 +3621,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128410403</v>
+        <v>128408399</v>
       </c>
       <c r="B31" t="n">
-        <v>75209</v>
+        <v>82892</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3644,21 +3644,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>398063</v>
+        <v>398076</v>
       </c>
       <c r="R31" t="n">
-        <v>6950893</v>
+        <v>6950793</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3730,10 +3730,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128411429</v>
+        <v>128411736</v>
       </c>
       <c r="B32" t="n">
-        <v>75209</v>
+        <v>91531</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3741,21 +3741,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>398176</v>
+        <v>398234</v>
       </c>
       <c r="R32" t="n">
-        <v>6950885</v>
+        <v>6950852</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3798,9 +3798,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3815,65 +3825,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128413866</v>
+        <v>128410403</v>
       </c>
       <c r="B33" t="n">
-        <v>58090</v>
+        <v>83005</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>398505</v>
+        <v>398063</v>
       </c>
       <c r="R33" t="n">
-        <v>6951279</v>
+        <v>6950893</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3900,19 +3905,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3927,22 +3922,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128408399</v>
+        <v>128411429</v>
       </c>
       <c r="B34" t="n">
-        <v>82983</v>
+        <v>83005</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3950,21 +3945,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3974,10 +3969,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>398076</v>
+        <v>398176</v>
       </c>
       <c r="R34" t="n">
-        <v>6950793</v>
+        <v>6950885</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4036,10 +4031,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128405964</v>
+        <v>128412757</v>
       </c>
       <c r="B35" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4067,7 +4062,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4076,10 +4071,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398364</v>
+        <v>398460</v>
       </c>
       <c r="R35" t="n">
-        <v>6950589</v>
+        <v>6951061</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4109,9 +4104,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4126,22 +4131,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128412757</v>
+        <v>128405964</v>
       </c>
       <c r="B36" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4169,7 +4174,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4178,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398460</v>
+        <v>398364</v>
       </c>
       <c r="R36" t="n">
-        <v>6951061</v>
+        <v>6950589</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4211,19 +4216,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4238,12 +4233,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4253,7 +4248,7 @@
         <v>128415952</v>
       </c>
       <c r="B37" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4352,48 +4347,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128411736</v>
+        <v>128413866</v>
       </c>
       <c r="B38" t="n">
-        <v>91526</v>
+        <v>58093</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>398234</v>
+        <v>398505</v>
       </c>
       <c r="R38" t="n">
-        <v>6950852</v>
+        <v>6951279</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4459,32 +4459,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128416366</v>
+        <v>128405669</v>
       </c>
       <c r="B39" t="n">
-        <v>78484</v>
+        <v>91531</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>398419</v>
+        <v>398398</v>
       </c>
       <c r="R39" t="n">
-        <v>6950678</v>
+        <v>6950569</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4556,32 +4556,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128405669</v>
+        <v>128405841</v>
       </c>
       <c r="B40" t="n">
-        <v>91526</v>
+        <v>92210</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>398398</v>
+        <v>398374</v>
       </c>
       <c r="R40" t="n">
-        <v>6950569</v>
+        <v>6950548</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4656,7 +4656,7 @@
         <v>128412193</v>
       </c>
       <c r="B41" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>128411735</v>
       </c>
       <c r="B42" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4847,10 +4847,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128415930</v>
+        <v>128412950</v>
       </c>
       <c r="B43" t="n">
-        <v>79714</v>
+        <v>57723</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4858,34 +4858,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>398387</v>
+        <v>398483</v>
       </c>
       <c r="R43" t="n">
-        <v>6950766</v>
+        <v>6951117</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4944,10 +4949,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128414073</v>
+        <v>128415930</v>
       </c>
       <c r="B44" t="n">
-        <v>57720</v>
+        <v>79619</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4955,39 +4960,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>398546</v>
+        <v>398387</v>
       </c>
       <c r="R44" t="n">
-        <v>6951235</v>
+        <v>6950766</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5046,50 +5046,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128412950</v>
+        <v>128416366</v>
       </c>
       <c r="B45" t="n">
-        <v>57720</v>
+        <v>78389</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>398483</v>
+        <v>398419</v>
       </c>
       <c r="R45" t="n">
-        <v>6951117</v>
+        <v>6950678</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5148,45 +5143,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128405841</v>
+        <v>128414073</v>
       </c>
       <c r="B46" t="n">
-        <v>92205</v>
+        <v>57723</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>398374</v>
+        <v>398546</v>
       </c>
       <c r="R46" t="n">
-        <v>6950548</v>
+        <v>6951235</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5245,10 +5245,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128412677</v>
+        <v>128406327</v>
       </c>
       <c r="B47" t="n">
-        <v>57720</v>
+        <v>91531</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5256,39 +5256,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>398462</v>
+        <v>398333</v>
       </c>
       <c r="R47" t="n">
-        <v>6951039</v>
+        <v>6950603</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5318,19 +5313,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5345,22 +5330,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128415972</v>
+        <v>128411964</v>
       </c>
       <c r="B48" t="n">
-        <v>57720</v>
+        <v>91531</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5368,39 +5353,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>398396</v>
+        <v>398278</v>
       </c>
       <c r="R48" t="n">
-        <v>6950719</v>
+        <v>6950881</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5459,10 +5439,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128407293</v>
+        <v>128410408</v>
       </c>
       <c r="B49" t="n">
-        <v>79743</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5470,21 +5450,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5494,10 +5474,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>398263</v>
+        <v>398063</v>
       </c>
       <c r="R49" t="n">
-        <v>6950596</v>
+        <v>6950893</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5556,32 +5536,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128415932</v>
+        <v>128412638</v>
       </c>
       <c r="B50" t="n">
-        <v>79743</v>
+        <v>57827</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5591,13 +5571,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>398387</v>
+        <v>398437</v>
       </c>
       <c r="R50" t="n">
-        <v>6950766</v>
+        <v>6951052</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5653,32 +5633,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128412638</v>
+        <v>128407293</v>
       </c>
       <c r="B51" t="n">
-        <v>57824</v>
+        <v>79648</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5688,13 +5668,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>398437</v>
+        <v>398263</v>
       </c>
       <c r="R51" t="n">
-        <v>6951052</v>
+        <v>6950596</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5750,10 +5730,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128408097</v>
+        <v>128415932</v>
       </c>
       <c r="B52" t="n">
-        <v>57880</v>
+        <v>79648</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5761,42 +5741,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>398159</v>
+        <v>398387</v>
       </c>
       <c r="R52" t="n">
-        <v>6950801</v>
+        <v>6950766</v>
       </c>
       <c r="S52" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5823,19 +5798,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5850,22 +5815,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128411964</v>
+        <v>128408097</v>
       </c>
       <c r="B53" t="n">
-        <v>91526</v>
+        <v>57883</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5873,37 +5838,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>398278</v>
+        <v>398159</v>
       </c>
       <c r="R53" t="n">
-        <v>6950881</v>
+        <v>6950801</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5930,9 +5900,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5947,22 +5927,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128406327</v>
+        <v>128412677</v>
       </c>
       <c r="B54" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5970,34 +5950,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>398333</v>
+        <v>398462</v>
       </c>
       <c r="R54" t="n">
-        <v>6950603</v>
+        <v>6951039</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6027,9 +6012,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6044,22 +6039,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128410408</v>
+        <v>128415972</v>
       </c>
       <c r="B55" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6067,34 +6062,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>398063</v>
+        <v>398396</v>
       </c>
       <c r="R55" t="n">
-        <v>6950893</v>
+        <v>6950719</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6153,10 +6153,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128408521</v>
+        <v>128405859</v>
       </c>
       <c r="B56" t="n">
-        <v>79743</v>
+        <v>57723</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6164,34 +6164,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>398019</v>
+        <v>398362</v>
       </c>
       <c r="R56" t="n">
-        <v>6950740</v>
+        <v>6950549</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6221,9 +6226,19 @@
           <t>2025-09-13</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6238,22 +6253,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128408773</v>
+        <v>128413955</v>
       </c>
       <c r="B57" t="n">
-        <v>58090</v>
+        <v>57564</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6261,16 +6276,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103015</v>
+        <v>102621</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6281,7 +6296,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6290,10 +6305,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>398012</v>
+        <v>398517</v>
       </c>
       <c r="R57" t="n">
-        <v>6950659</v>
+        <v>6951283</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6323,19 +6338,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6350,22 +6355,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128405859</v>
+        <v>128408521</v>
       </c>
       <c r="B58" t="n">
-        <v>57720</v>
+        <v>79648</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6373,39 +6378,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Brändåsen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>398362</v>
+        <v>398019</v>
       </c>
       <c r="R58" t="n">
-        <v>6950549</v>
+        <v>6950740</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6435,19 +6435,9 @@
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6462,12 +6452,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenande